--- a/tracker/static/tracker/task_import_template.xlsx
+++ b/tracker/static/tracker/task_import_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frige\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frige\PycharmProjects\task-tracker\tracker\static\tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54056ADD-A5EA-43AE-9CEF-47FC48D3F607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E19664F-A483-451A-8F7A-5D9CAD52AA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="7830" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>Task Import Template</t>
   </si>
@@ -276,129 +276,6 @@
   <si>
     <t>Chores</t>
   </si>
-  <si>
-    <t>Test Task 1</t>
-  </si>
-  <si>
-    <t>Pick up groceries after work (don’t forget milk and eggs)</t>
-  </si>
-  <si>
-    <t>Test Task 2</t>
-  </si>
-  <si>
-    <t>Call doctor’s office to reschedule appointment</t>
-  </si>
-  <si>
-    <t>Test Task 3</t>
-  </si>
-  <si>
-    <t>Follow up with Sarah about weekend plans</t>
-  </si>
-  <si>
-    <t>Test Task 4</t>
-  </si>
-  <si>
-    <t>Start laundry before dinner</t>
-  </si>
-  <si>
-    <t>Test Task 5</t>
-  </si>
-  <si>
-    <t>Pay electric bill before due date</t>
-  </si>
-  <si>
-    <t>Test Task 6</t>
-  </si>
-  <si>
-    <t>Clean out fridge and throw away expired food</t>
-  </si>
-  <si>
-    <t>Test Task 7</t>
-  </si>
-  <si>
-    <t>Water plants in the living room</t>
-  </si>
-  <si>
-    <t>Test Task 8</t>
-  </si>
-  <si>
-    <t>Take dog for a longer walk today</t>
-  </si>
-  <si>
-    <t>Test Task 9</t>
-  </si>
-  <si>
-    <t>School</t>
-  </si>
-  <si>
-    <t>Prep lunches for the next couple of days</t>
-  </si>
-  <si>
-    <t>Test Task 10</t>
-  </si>
-  <si>
-    <t>Check calendar and plan out the week</t>
-  </si>
-  <si>
-    <t>Test Task 11</t>
-  </si>
-  <si>
-    <t>Send birthday message to Mike</t>
-  </si>
-  <si>
-    <t>Test Task 12</t>
-  </si>
-  <si>
-    <t>Organize desk and get rid of clutter</t>
-  </si>
-  <si>
-    <t>Test Task 13</t>
-  </si>
-  <si>
-    <t>Look into booking summer vacation</t>
-  </si>
-  <si>
-    <t>Test Task 14</t>
-  </si>
-  <si>
-    <t>Finish reading current book</t>
-  </si>
-  <si>
-    <t>Test Task 15</t>
-  </si>
-  <si>
-    <t>Try new recipe for dinner tonight</t>
-  </si>
-  <si>
-    <t>Test Task 16</t>
-  </si>
-  <si>
-    <t>Set aside time to work out</t>
-  </si>
-  <si>
-    <t>Test Task 17</t>
-  </si>
-  <si>
-    <t>Back up photos from phone</t>
-  </si>
-  <si>
-    <t>Test Task 18</t>
-  </si>
-  <si>
-    <t>Return package at the post office</t>
-  </si>
-  <si>
-    <t>Test Task 19</t>
-  </si>
-  <si>
-    <t>Make list of things needed for the house</t>
-  </si>
-  <si>
-    <t>Test Task 20</t>
-  </si>
-  <si>
-    <t>Relax and take a break — no work tonight</t>
-  </si>
 </sst>
 </file>
 
@@ -491,6 +368,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -498,8 +377,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -816,30 +693,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -871,583 +748,154 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="9">
-        <v>46160</v>
-      </c>
-      <c r="D4" s="10">
-        <v>46129.385416666664</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>6</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="9">
-        <v>46161</v>
-      </c>
-      <c r="D5" s="10">
-        <v>46130.597222222219</v>
-      </c>
-      <c r="E5" s="10">
-        <v>46131.340277777781</v>
-      </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
-      <c r="H5" t="s">
-        <v>41</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="9">
-        <v>46162</v>
-      </c>
-      <c r="D6" s="10">
-        <v>46131.3125</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6">
-        <v>52</v>
-      </c>
-      <c r="H6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="9">
-        <v>46163</v>
-      </c>
-      <c r="D7" s="10">
-        <v>46132.697916666664</v>
-      </c>
-      <c r="E7" s="10">
-        <v>46133.697916666664</v>
-      </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7">
-        <v>49</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="9">
-        <v>46164</v>
-      </c>
-      <c r="D8" s="10">
-        <v>46133.420138888891</v>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8">
-        <v>7</v>
-      </c>
-      <c r="G8">
-        <v>25</v>
-      </c>
-      <c r="H8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="9">
-        <v>46165</v>
-      </c>
-      <c r="D9" s="10">
-        <v>46134.527777777781</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="G9">
-        <v>24</v>
-      </c>
-      <c r="H9" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="9">
-        <v>46166</v>
-      </c>
-      <c r="D10" s="10">
-        <v>46135.333333333336</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>37</v>
-      </c>
-      <c r="H10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="9">
-        <v>46167</v>
-      </c>
-      <c r="D11" s="10">
-        <v>46136.756944444445</v>
-      </c>
-      <c r="E11" s="10">
-        <v>46137.284722222219</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>9</v>
-      </c>
-      <c r="H11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="9">
-        <v>46168</v>
-      </c>
-      <c r="D12" s="10">
-        <v>46137.496527777781</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>18</v>
-      </c>
-      <c r="H12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" t="b">
-        <v>1</v>
-      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="9">
-        <v>46169</v>
-      </c>
-      <c r="D13" s="10">
-        <v>46138.649305555555</v>
-      </c>
-      <c r="E13" s="10">
-        <v>46139.708333333336</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>52</v>
-      </c>
-      <c r="H13" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" t="b">
-        <v>1</v>
-      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="9">
-        <v>46170</v>
-      </c>
-      <c r="D14" s="10">
-        <v>46139.263888888891</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>50</v>
-      </c>
-      <c r="H14" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="9">
-        <v>46171</v>
-      </c>
-      <c r="D15" s="10">
-        <v>46140.552083333336</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>36</v>
-      </c>
-      <c r="H15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="9">
-        <v>46172</v>
-      </c>
-      <c r="D16" s="10">
-        <v>46141.725694444445</v>
-      </c>
-      <c r="E16" s="10"/>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16">
-        <v>53</v>
-      </c>
-      <c r="H16" t="s">
-        <v>64</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="9">
-        <v>46173</v>
-      </c>
-      <c r="D17" s="10">
-        <v>46142.409722222219</v>
-      </c>
-      <c r="E17" s="10">
-        <v>46143.427083333336</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
-      </c>
-      <c r="G17">
-        <v>22</v>
-      </c>
-      <c r="H17" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="9">
-        <v>46174</v>
-      </c>
-      <c r="D18" s="10">
-        <v>46143.586805555555</v>
-      </c>
-      <c r="E18" s="10"/>
-      <c r="G18">
-        <v>2</v>
-      </c>
-      <c r="H18" t="s">
-        <v>68</v>
-      </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="9">
-        <v>46175</v>
-      </c>
-      <c r="D19" s="10">
-        <v>46144.322916666664</v>
-      </c>
-      <c r="E19" s="10"/>
-      <c r="G19">
-        <v>23</v>
-      </c>
-      <c r="H19" t="s">
-        <v>70</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="9">
-        <v>46176</v>
-      </c>
-      <c r="D20" s="10">
-        <v>46145.798611111109</v>
-      </c>
-      <c r="E20" s="10"/>
-      <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20">
-        <v>17</v>
-      </c>
-      <c r="H20" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="9">
-        <v>46177</v>
-      </c>
-      <c r="D21" s="10">
-        <v>46146.4375</v>
-      </c>
-      <c r="E21" s="10"/>
-      <c r="F21">
-        <v>2</v>
-      </c>
-      <c r="G21">
-        <v>15</v>
-      </c>
-      <c r="H21" t="s">
-        <v>74</v>
-      </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="9">
-        <v>46178</v>
-      </c>
-      <c r="D22" s="10">
-        <v>46147.579861111109</v>
-      </c>
-      <c r="E22" s="10"/>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>7</v>
-      </c>
-      <c r="H22" t="s">
-        <v>76</v>
-      </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="9">
-        <v>46179</v>
-      </c>
-      <c r="D23" s="10">
-        <v>46148.350694444445</v>
-      </c>
-      <c r="E23" s="10"/>
-      <c r="F23">
-        <v>3</v>
-      </c>
-      <c r="G23">
-        <v>43</v>
-      </c>
-      <c r="H23" t="s">
-        <v>78</v>
-      </c>
-      <c r="I23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="I29" s="2"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>

--- a/tracker/static/tracker/task_import_template.xlsx
+++ b/tracker/static/tracker/task_import_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frige\PycharmProjects\task-tracker\tracker\static\tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E19664F-A483-451A-8F7A-5D9CAD52AA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CDAAA8-6824-4C1B-94BF-74BE27F1F6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="7830" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -166,9 +166,6 @@
     <t>Task Import Template</t>
   </si>
   <si>
-    <t>Use this sheet to prepare entries for CSV import. Keep due_date as YYYY-MM-DD. Keep start_at/end_at as YYYY-MM-DD HH:MM. Row 4 is an example; delete it before saving if not needed.</t>
-  </si>
-  <si>
     <t>title</t>
   </si>
   <si>
@@ -276,6 +273,32 @@
   <si>
     <t>Chores</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Use this sheet to prepare entries for CSV import. See the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Instructions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sheet of this document for validation rules and an example row.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -285,7 +308,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +332,14 @@
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -679,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:I1003"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -707,7 +738,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -720,31 +751,31 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,5866 +879,5881 @@
       <c r="E23" s="7"/>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
       <c r="I39" s="2"/>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
       <c r="I42" s="2"/>
     </row>
     <row r="43" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
       <c r="I43" s="2"/>
     </row>
     <row r="44" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
       <c r="I44" s="2"/>
     </row>
     <row r="45" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
       <c r="I45" s="2"/>
     </row>
     <row r="46" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
       <c r="I46" s="2"/>
     </row>
     <row r="47" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
       <c r="I48" s="2"/>
     </row>
     <row r="49" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
       <c r="I49" s="2"/>
     </row>
     <row r="50" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
       <c r="I50" s="2"/>
     </row>
     <row r="51" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
       <c r="I51" s="2"/>
     </row>
     <row r="52" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
       <c r="I52" s="2"/>
     </row>
     <row r="53" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
       <c r="I53" s="2"/>
     </row>
     <row r="54" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
       <c r="I54" s="2"/>
     </row>
     <row r="55" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
       <c r="I55" s="2"/>
     </row>
     <row r="56" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
       <c r="I56" s="2"/>
     </row>
     <row r="57" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
       <c r="I57" s="2"/>
     </row>
     <row r="58" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
       <c r="I58" s="2"/>
     </row>
     <row r="59" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
       <c r="I59" s="2"/>
     </row>
     <row r="60" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
       <c r="I60" s="2"/>
     </row>
     <row r="61" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
       <c r="I61" s="2"/>
     </row>
     <row r="62" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
       <c r="I62" s="2"/>
     </row>
     <row r="63" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
       <c r="I63" s="2"/>
     </row>
     <row r="64" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
       <c r="I64" s="2"/>
     </row>
     <row r="65" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
       <c r="I65" s="2"/>
     </row>
     <row r="66" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
       <c r="I66" s="2"/>
     </row>
     <row r="67" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
       <c r="I67" s="2"/>
     </row>
     <row r="68" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
       <c r="I68" s="2"/>
     </row>
     <row r="69" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
       <c r="I69" s="2"/>
     </row>
     <row r="70" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
       <c r="I70" s="2"/>
     </row>
     <row r="71" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
       <c r="I71" s="2"/>
     </row>
     <row r="72" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
       <c r="I72" s="2"/>
     </row>
     <row r="73" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
       <c r="I73" s="2"/>
     </row>
     <row r="74" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
       <c r="I74" s="2"/>
     </row>
     <row r="75" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
       <c r="I75" s="2"/>
     </row>
     <row r="76" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
       <c r="I76" s="2"/>
     </row>
     <row r="77" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
       <c r="I77" s="2"/>
     </row>
     <row r="78" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
       <c r="I78" s="2"/>
     </row>
     <row r="79" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
       <c r="I79" s="2"/>
     </row>
     <row r="80" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
       <c r="I80" s="2"/>
     </row>
     <row r="81" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
       <c r="I81" s="2"/>
     </row>
     <row r="82" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
       <c r="I82" s="2"/>
     </row>
     <row r="83" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
       <c r="I83" s="2"/>
     </row>
     <row r="84" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
       <c r="I84" s="2"/>
     </row>
     <row r="85" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
       <c r="I85" s="2"/>
     </row>
     <row r="86" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
       <c r="I86" s="2"/>
     </row>
     <row r="87" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
       <c r="I87" s="2"/>
     </row>
     <row r="88" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
       <c r="I88" s="2"/>
     </row>
     <row r="89" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
       <c r="I89" s="2"/>
     </row>
     <row r="90" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
       <c r="I90" s="2"/>
     </row>
     <row r="91" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
       <c r="I91" s="2"/>
     </row>
     <row r="92" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
       <c r="I92" s="2"/>
     </row>
     <row r="93" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
       <c r="I93" s="2"/>
     </row>
     <row r="94" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
       <c r="I94" s="2"/>
     </row>
     <row r="95" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
       <c r="I95" s="2"/>
     </row>
     <row r="96" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
       <c r="I96" s="2"/>
     </row>
     <row r="97" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
       <c r="I97" s="2"/>
     </row>
     <row r="98" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
       <c r="I98" s="2"/>
     </row>
     <row r="99" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
       <c r="I99" s="2"/>
     </row>
     <row r="100" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
       <c r="I100" s="2"/>
     </row>
     <row r="101" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
       <c r="I101" s="2"/>
     </row>
     <row r="102" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
       <c r="I102" s="2"/>
     </row>
     <row r="103" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
       <c r="I103" s="2"/>
     </row>
     <row r="104" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
       <c r="I104" s="2"/>
     </row>
     <row r="105" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
       <c r="I105" s="2"/>
     </row>
     <row r="106" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
       <c r="I106" s="2"/>
     </row>
     <row r="107" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
       <c r="I107" s="2"/>
     </row>
     <row r="108" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
       <c r="I108" s="2"/>
     </row>
     <row r="109" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
       <c r="I109" s="2"/>
     </row>
     <row r="110" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
       <c r="I110" s="2"/>
     </row>
     <row r="111" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
       <c r="I111" s="2"/>
     </row>
     <row r="112" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
       <c r="I112" s="2"/>
     </row>
     <row r="113" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
       <c r="I113" s="2"/>
     </row>
     <row r="114" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
       <c r="I114" s="2"/>
     </row>
     <row r="115" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
       <c r="I115" s="2"/>
     </row>
     <row r="116" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
       <c r="I116" s="2"/>
     </row>
     <row r="117" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
+      <c r="C117" s="6"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
       <c r="I117" s="2"/>
     </row>
     <row r="118" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="7"/>
       <c r="I118" s="2"/>
     </row>
     <row r="119" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
       <c r="I119" s="2"/>
     </row>
     <row r="120" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
       <c r="I120" s="2"/>
     </row>
     <row r="121" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
+      <c r="C121" s="6"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
       <c r="I121" s="2"/>
     </row>
     <row r="122" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
       <c r="I122" s="2"/>
     </row>
     <row r="123" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
+      <c r="C123" s="6"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
       <c r="I123" s="2"/>
     </row>
     <row r="124" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
       <c r="I124" s="2"/>
     </row>
     <row r="125" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
+      <c r="C125" s="6"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
       <c r="I125" s="2"/>
     </row>
     <row r="126" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
+      <c r="C126" s="6"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
       <c r="I126" s="2"/>
     </row>
     <row r="127" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
+      <c r="C127" s="6"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
       <c r="I127" s="2"/>
     </row>
     <row r="128" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
+      <c r="C128" s="6"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
       <c r="I128" s="2"/>
     </row>
     <row r="129" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
+      <c r="C129" s="6"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
       <c r="I129" s="2"/>
     </row>
     <row r="130" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
+      <c r="C130" s="6"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
       <c r="I130" s="2"/>
     </row>
     <row r="131" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
+      <c r="C131" s="6"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
       <c r="I131" s="2"/>
     </row>
     <row r="132" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
       <c r="I132" s="2"/>
     </row>
     <row r="133" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
+      <c r="C133" s="6"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
       <c r="I133" s="2"/>
     </row>
     <row r="134" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
       <c r="I134" s="2"/>
     </row>
     <row r="135" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
+      <c r="C135" s="6"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
       <c r="I135" s="2"/>
     </row>
     <row r="136" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
+      <c r="C136" s="6"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
       <c r="I136" s="2"/>
     </row>
     <row r="137" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
+      <c r="C137" s="6"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
       <c r="I137" s="2"/>
     </row>
     <row r="138" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
+      <c r="C138" s="6"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
       <c r="I138" s="2"/>
     </row>
     <row r="139" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
+      <c r="C139" s="6"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
       <c r="I139" s="2"/>
     </row>
     <row r="140" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
+      <c r="C140" s="6"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
       <c r="I140" s="2"/>
     </row>
     <row r="141" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="2"/>
+      <c r="C141" s="6"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
       <c r="I141" s="2"/>
     </row>
     <row r="142" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
+      <c r="C142" s="6"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
       <c r="I142" s="2"/>
     </row>
     <row r="143" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
+      <c r="C143" s="6"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
       <c r="I143" s="2"/>
     </row>
     <row r="144" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
+      <c r="C144" s="6"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="7"/>
       <c r="I144" s="2"/>
     </row>
     <row r="145" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="C145" s="6"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
       <c r="I145" s="2"/>
     </row>
     <row r="146" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
+      <c r="C146" s="6"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
       <c r="I146" s="2"/>
     </row>
     <row r="147" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="C147" s="6"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
       <c r="I147" s="2"/>
     </row>
     <row r="148" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2"/>
+      <c r="C148" s="6"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
       <c r="I148" s="2"/>
     </row>
     <row r="149" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
+      <c r="C149" s="6"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
       <c r="I149" s="2"/>
     </row>
     <row r="150" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2"/>
+      <c r="C150" s="6"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
       <c r="I150" s="2"/>
     </row>
     <row r="151" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
-      <c r="E151" s="2"/>
+      <c r="C151" s="6"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
       <c r="I151" s="2"/>
     </row>
     <row r="152" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
-      <c r="E152" s="2"/>
+      <c r="C152" s="6"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
       <c r="I152" s="2"/>
     </row>
     <row r="153" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
-      <c r="E153" s="2"/>
+      <c r="C153" s="6"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
       <c r="I153" s="2"/>
     </row>
     <row r="154" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
-      <c r="E154" s="2"/>
+      <c r="C154" s="6"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
       <c r="I154" s="2"/>
     </row>
     <row r="155" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
-      <c r="E155" s="2"/>
+      <c r="C155" s="6"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
       <c r="I155" s="2"/>
     </row>
     <row r="156" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
-      <c r="E156" s="2"/>
+      <c r="C156" s="6"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
       <c r="I156" s="2"/>
     </row>
     <row r="157" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
-      <c r="E157" s="2"/>
+      <c r="C157" s="6"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
       <c r="I157" s="2"/>
     </row>
     <row r="158" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
-      <c r="E158" s="2"/>
+      <c r="C158" s="6"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
       <c r="I158" s="2"/>
     </row>
     <row r="159" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
-      <c r="E159" s="2"/>
+      <c r="C159" s="6"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
       <c r="I159" s="2"/>
     </row>
     <row r="160" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C160" s="2"/>
-      <c r="D160" s="2"/>
-      <c r="E160" s="2"/>
+      <c r="C160" s="6"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
       <c r="I160" s="2"/>
     </row>
     <row r="161" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
-      <c r="E161" s="2"/>
+      <c r="C161" s="6"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
       <c r="I161" s="2"/>
     </row>
     <row r="162" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
+      <c r="C162" s="6"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
       <c r="I162" s="2"/>
     </row>
     <row r="163" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
-      <c r="E163" s="2"/>
+      <c r="C163" s="6"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
       <c r="I163" s="2"/>
     </row>
     <row r="164" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
+      <c r="C164" s="6"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
       <c r="I164" s="2"/>
     </row>
     <row r="165" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C165" s="2"/>
-      <c r="D165" s="2"/>
-      <c r="E165" s="2"/>
+      <c r="C165" s="6"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
       <c r="I165" s="2"/>
     </row>
     <row r="166" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C166" s="2"/>
-      <c r="D166" s="2"/>
-      <c r="E166" s="2"/>
+      <c r="C166" s="6"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
       <c r="I166" s="2"/>
     </row>
     <row r="167" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C167" s="2"/>
-      <c r="D167" s="2"/>
-      <c r="E167" s="2"/>
+      <c r="C167" s="6"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
       <c r="I167" s="2"/>
     </row>
     <row r="168" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C168" s="2"/>
-      <c r="D168" s="2"/>
-      <c r="E168" s="2"/>
+      <c r="C168" s="6"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
       <c r="I168" s="2"/>
     </row>
     <row r="169" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C169" s="2"/>
-      <c r="D169" s="2"/>
-      <c r="E169" s="2"/>
+      <c r="C169" s="6"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
       <c r="I169" s="2"/>
     </row>
     <row r="170" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C170" s="2"/>
-      <c r="D170" s="2"/>
-      <c r="E170" s="2"/>
+      <c r="C170" s="6"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
       <c r="I170" s="2"/>
     </row>
     <row r="171" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
-      <c r="E171" s="2"/>
+      <c r="C171" s="6"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
       <c r="I171" s="2"/>
     </row>
     <row r="172" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
+      <c r="C172" s="6"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
       <c r="I172" s="2"/>
     </row>
     <row r="173" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
+      <c r="C173" s="6"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
       <c r="I173" s="2"/>
     </row>
     <row r="174" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C174" s="2"/>
-      <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
+      <c r="C174" s="6"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
       <c r="I174" s="2"/>
     </row>
     <row r="175" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
-      <c r="E175" s="2"/>
+      <c r="C175" s="6"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
       <c r="I175" s="2"/>
     </row>
     <row r="176" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
+      <c r="C176" s="6"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="7"/>
       <c r="I176" s="2"/>
     </row>
     <row r="177" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C177" s="2"/>
-      <c r="D177" s="2"/>
-      <c r="E177" s="2"/>
+      <c r="C177" s="6"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
       <c r="I177" s="2"/>
     </row>
     <row r="178" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C178" s="2"/>
-      <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
+      <c r="C178" s="6"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
       <c r="I178" s="2"/>
     </row>
     <row r="179" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C179" s="2"/>
-      <c r="D179" s="2"/>
-      <c r="E179" s="2"/>
+      <c r="C179" s="6"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="7"/>
       <c r="I179" s="2"/>
     </row>
     <row r="180" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C180" s="2"/>
-      <c r="D180" s="2"/>
-      <c r="E180" s="2"/>
+      <c r="C180" s="6"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="7"/>
       <c r="I180" s="2"/>
     </row>
     <row r="181" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C181" s="2"/>
-      <c r="D181" s="2"/>
-      <c r="E181" s="2"/>
+      <c r="C181" s="6"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="7"/>
       <c r="I181" s="2"/>
     </row>
     <row r="182" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C182" s="2"/>
-      <c r="D182" s="2"/>
-      <c r="E182" s="2"/>
+      <c r="C182" s="6"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="7"/>
       <c r="I182" s="2"/>
     </row>
     <row r="183" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
-      <c r="E183" s="2"/>
+      <c r="C183" s="6"/>
+      <c r="D183" s="7"/>
+      <c r="E183" s="7"/>
       <c r="I183" s="2"/>
     </row>
     <row r="184" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
-      <c r="E184" s="2"/>
+      <c r="C184" s="6"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="7"/>
       <c r="I184" s="2"/>
     </row>
     <row r="185" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
-      <c r="E185" s="2"/>
+      <c r="C185" s="6"/>
+      <c r="D185" s="7"/>
+      <c r="E185" s="7"/>
       <c r="I185" s="2"/>
     </row>
     <row r="186" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
+      <c r="C186" s="6"/>
+      <c r="D186" s="7"/>
+      <c r="E186" s="7"/>
       <c r="I186" s="2"/>
     </row>
     <row r="187" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
-      <c r="E187" s="2"/>
+      <c r="C187" s="6"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
       <c r="I187" s="2"/>
     </row>
     <row r="188" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
-      <c r="E188" s="2"/>
+      <c r="C188" s="6"/>
+      <c r="D188" s="7"/>
+      <c r="E188" s="7"/>
       <c r="I188" s="2"/>
     </row>
     <row r="189" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C189" s="2"/>
-      <c r="D189" s="2"/>
-      <c r="E189" s="2"/>
+      <c r="C189" s="6"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
       <c r="I189" s="2"/>
     </row>
     <row r="190" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
-      <c r="E190" s="2"/>
+      <c r="C190" s="6"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
       <c r="I190" s="2"/>
     </row>
     <row r="191" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C191" s="2"/>
-      <c r="D191" s="2"/>
-      <c r="E191" s="2"/>
+      <c r="C191" s="6"/>
+      <c r="D191" s="7"/>
+      <c r="E191" s="7"/>
       <c r="I191" s="2"/>
     </row>
     <row r="192" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C192" s="2"/>
-      <c r="D192" s="2"/>
-      <c r="E192" s="2"/>
+      <c r="C192" s="6"/>
+      <c r="D192" s="7"/>
+      <c r="E192" s="7"/>
       <c r="I192" s="2"/>
     </row>
     <row r="193" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
+      <c r="C193" s="6"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
       <c r="I193" s="2"/>
     </row>
     <row r="194" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C194" s="2"/>
-      <c r="D194" s="2"/>
-      <c r="E194" s="2"/>
+      <c r="C194" s="6"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
       <c r="I194" s="2"/>
     </row>
     <row r="195" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
-      <c r="E195" s="2"/>
+      <c r="C195" s="6"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
       <c r="I195" s="2"/>
     </row>
     <row r="196" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
+      <c r="C196" s="6"/>
+      <c r="D196" s="7"/>
+      <c r="E196" s="7"/>
       <c r="I196" s="2"/>
     </row>
     <row r="197" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
-      <c r="E197" s="2"/>
+      <c r="C197" s="6"/>
+      <c r="D197" s="7"/>
+      <c r="E197" s="7"/>
       <c r="I197" s="2"/>
     </row>
     <row r="198" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
-      <c r="E198" s="2"/>
+      <c r="C198" s="6"/>
+      <c r="D198" s="7"/>
+      <c r="E198" s="7"/>
       <c r="I198" s="2"/>
     </row>
     <row r="199" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
-      <c r="E199" s="2"/>
+      <c r="C199" s="6"/>
+      <c r="D199" s="7"/>
+      <c r="E199" s="7"/>
       <c r="I199" s="2"/>
     </row>
     <row r="200" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
+      <c r="C200" s="6"/>
+      <c r="D200" s="7"/>
+      <c r="E200" s="7"/>
       <c r="I200" s="2"/>
     </row>
     <row r="201" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C201" s="2"/>
-      <c r="D201" s="2"/>
-      <c r="E201" s="2"/>
+      <c r="C201" s="6"/>
+      <c r="D201" s="7"/>
+      <c r="E201" s="7"/>
       <c r="I201" s="2"/>
     </row>
     <row r="202" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C202" s="2"/>
-      <c r="D202" s="2"/>
-      <c r="E202" s="2"/>
+      <c r="C202" s="6"/>
+      <c r="D202" s="7"/>
+      <c r="E202" s="7"/>
       <c r="I202" s="2"/>
     </row>
     <row r="203" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C203" s="2"/>
-      <c r="D203" s="2"/>
-      <c r="E203" s="2"/>
+      <c r="C203" s="6"/>
+      <c r="D203" s="7"/>
+      <c r="E203" s="7"/>
       <c r="I203" s="2"/>
     </row>
     <row r="204" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
+      <c r="C204" s="6"/>
+      <c r="D204" s="7"/>
+      <c r="E204" s="7"/>
       <c r="I204" s="2"/>
     </row>
     <row r="205" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
+      <c r="C205" s="6"/>
+      <c r="D205" s="7"/>
+      <c r="E205" s="7"/>
       <c r="I205" s="2"/>
     </row>
     <row r="206" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C206" s="2"/>
-      <c r="D206" s="2"/>
-      <c r="E206" s="2"/>
+      <c r="C206" s="6"/>
+      <c r="D206" s="7"/>
+      <c r="E206" s="7"/>
       <c r="I206" s="2"/>
     </row>
     <row r="207" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C207" s="2"/>
-      <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
+      <c r="C207" s="6"/>
+      <c r="D207" s="7"/>
+      <c r="E207" s="7"/>
       <c r="I207" s="2"/>
     </row>
     <row r="208" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
+      <c r="C208" s="6"/>
+      <c r="D208" s="7"/>
+      <c r="E208" s="7"/>
       <c r="I208" s="2"/>
     </row>
     <row r="209" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C209" s="2"/>
-      <c r="D209" s="2"/>
-      <c r="E209" s="2"/>
+      <c r="C209" s="6"/>
+      <c r="D209" s="7"/>
+      <c r="E209" s="7"/>
       <c r="I209" s="2"/>
     </row>
     <row r="210" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
-      <c r="E210" s="2"/>
+      <c r="C210" s="6"/>
+      <c r="D210" s="7"/>
+      <c r="E210" s="7"/>
       <c r="I210" s="2"/>
     </row>
     <row r="211" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C211" s="2"/>
-      <c r="D211" s="2"/>
-      <c r="E211" s="2"/>
+      <c r="C211" s="6"/>
+      <c r="D211" s="7"/>
+      <c r="E211" s="7"/>
       <c r="I211" s="2"/>
     </row>
     <row r="212" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C212" s="2"/>
-      <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
+      <c r="C212" s="6"/>
+      <c r="D212" s="7"/>
+      <c r="E212" s="7"/>
       <c r="I212" s="2"/>
     </row>
     <row r="213" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C213" s="2"/>
-      <c r="D213" s="2"/>
-      <c r="E213" s="2"/>
+      <c r="C213" s="6"/>
+      <c r="D213" s="7"/>
+      <c r="E213" s="7"/>
       <c r="I213" s="2"/>
     </row>
     <row r="214" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
-      <c r="E214" s="2"/>
+      <c r="C214" s="6"/>
+      <c r="D214" s="7"/>
+      <c r="E214" s="7"/>
       <c r="I214" s="2"/>
     </row>
     <row r="215" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C215" s="2"/>
-      <c r="D215" s="2"/>
-      <c r="E215" s="2"/>
+      <c r="C215" s="6"/>
+      <c r="D215" s="7"/>
+      <c r="E215" s="7"/>
       <c r="I215" s="2"/>
     </row>
     <row r="216" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C216" s="2"/>
-      <c r="D216" s="2"/>
-      <c r="E216" s="2"/>
+      <c r="C216" s="6"/>
+      <c r="D216" s="7"/>
+      <c r="E216" s="7"/>
       <c r="I216" s="2"/>
     </row>
     <row r="217" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
-      <c r="E217" s="2"/>
+      <c r="C217" s="6"/>
+      <c r="D217" s="7"/>
+      <c r="E217" s="7"/>
       <c r="I217" s="2"/>
     </row>
     <row r="218" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C218" s="2"/>
-      <c r="D218" s="2"/>
-      <c r="E218" s="2"/>
+      <c r="C218" s="6"/>
+      <c r="D218" s="7"/>
+      <c r="E218" s="7"/>
       <c r="I218" s="2"/>
     </row>
     <row r="219" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C219" s="2"/>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
+      <c r="C219" s="6"/>
+      <c r="D219" s="7"/>
+      <c r="E219" s="7"/>
       <c r="I219" s="2"/>
     </row>
     <row r="220" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C220" s="2"/>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
+      <c r="C220" s="6"/>
+      <c r="D220" s="7"/>
+      <c r="E220" s="7"/>
       <c r="I220" s="2"/>
     </row>
     <row r="221" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
+      <c r="C221" s="6"/>
+      <c r="D221" s="7"/>
+      <c r="E221" s="7"/>
       <c r="I221" s="2"/>
     </row>
     <row r="222" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
+      <c r="C222" s="6"/>
+      <c r="D222" s="7"/>
+      <c r="E222" s="7"/>
       <c r="I222" s="2"/>
     </row>
     <row r="223" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
+      <c r="C223" s="6"/>
+      <c r="D223" s="7"/>
+      <c r="E223" s="7"/>
       <c r="I223" s="2"/>
     </row>
     <row r="224" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C224" s="2"/>
-      <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
+      <c r="C224" s="6"/>
+      <c r="D224" s="7"/>
+      <c r="E224" s="7"/>
       <c r="I224" s="2"/>
     </row>
     <row r="225" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C225" s="2"/>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
+      <c r="C225" s="6"/>
+      <c r="D225" s="7"/>
+      <c r="E225" s="7"/>
       <c r="I225" s="2"/>
     </row>
     <row r="226" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C226" s="2"/>
-      <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
+      <c r="C226" s="6"/>
+      <c r="D226" s="7"/>
+      <c r="E226" s="7"/>
       <c r="I226" s="2"/>
     </row>
     <row r="227" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C227" s="2"/>
-      <c r="D227" s="2"/>
-      <c r="E227" s="2"/>
+      <c r="C227" s="6"/>
+      <c r="D227" s="7"/>
+      <c r="E227" s="7"/>
       <c r="I227" s="2"/>
     </row>
     <row r="228" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C228" s="2"/>
-      <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
+      <c r="C228" s="6"/>
+      <c r="D228" s="7"/>
+      <c r="E228" s="7"/>
       <c r="I228" s="2"/>
     </row>
     <row r="229" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C229" s="2"/>
-      <c r="D229" s="2"/>
-      <c r="E229" s="2"/>
+      <c r="C229" s="6"/>
+      <c r="D229" s="7"/>
+      <c r="E229" s="7"/>
       <c r="I229" s="2"/>
     </row>
     <row r="230" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C230" s="2"/>
-      <c r="D230" s="2"/>
-      <c r="E230" s="2"/>
+      <c r="C230" s="6"/>
+      <c r="D230" s="7"/>
+      <c r="E230" s="7"/>
       <c r="I230" s="2"/>
     </row>
     <row r="231" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C231" s="2"/>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
+      <c r="C231" s="6"/>
+      <c r="D231" s="7"/>
+      <c r="E231" s="7"/>
       <c r="I231" s="2"/>
     </row>
     <row r="232" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C232" s="2"/>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
+      <c r="C232" s="6"/>
+      <c r="D232" s="7"/>
+      <c r="E232" s="7"/>
       <c r="I232" s="2"/>
     </row>
     <row r="233" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C233" s="2"/>
-      <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
+      <c r="C233" s="6"/>
+      <c r="D233" s="7"/>
+      <c r="E233" s="7"/>
       <c r="I233" s="2"/>
     </row>
     <row r="234" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C234" s="2"/>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
+      <c r="C234" s="6"/>
+      <c r="D234" s="7"/>
+      <c r="E234" s="7"/>
       <c r="I234" s="2"/>
     </row>
     <row r="235" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C235" s="2"/>
-      <c r="D235" s="2"/>
-      <c r="E235" s="2"/>
+      <c r="C235" s="6"/>
+      <c r="D235" s="7"/>
+      <c r="E235" s="7"/>
       <c r="I235" s="2"/>
     </row>
     <row r="236" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C236" s="2"/>
-      <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
+      <c r="C236" s="6"/>
+      <c r="D236" s="7"/>
+      <c r="E236" s="7"/>
       <c r="I236" s="2"/>
     </row>
     <row r="237" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C237" s="2"/>
-      <c r="D237" s="2"/>
-      <c r="E237" s="2"/>
+      <c r="C237" s="6"/>
+      <c r="D237" s="7"/>
+      <c r="E237" s="7"/>
       <c r="I237" s="2"/>
     </row>
     <row r="238" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C238" s="2"/>
-      <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
+      <c r="C238" s="6"/>
+      <c r="D238" s="7"/>
+      <c r="E238" s="7"/>
       <c r="I238" s="2"/>
     </row>
     <row r="239" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C239" s="2"/>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
+      <c r="C239" s="6"/>
+      <c r="D239" s="7"/>
+      <c r="E239" s="7"/>
       <c r="I239" s="2"/>
     </row>
     <row r="240" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
+      <c r="C240" s="6"/>
+      <c r="D240" s="7"/>
+      <c r="E240" s="7"/>
       <c r="I240" s="2"/>
     </row>
     <row r="241" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
+      <c r="C241" s="6"/>
+      <c r="D241" s="7"/>
+      <c r="E241" s="7"/>
       <c r="I241" s="2"/>
     </row>
     <row r="242" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
+      <c r="C242" s="6"/>
+      <c r="D242" s="7"/>
+      <c r="E242" s="7"/>
       <c r="I242" s="2"/>
     </row>
     <row r="243" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
+      <c r="C243" s="6"/>
+      <c r="D243" s="7"/>
+      <c r="E243" s="7"/>
       <c r="I243" s="2"/>
     </row>
     <row r="244" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
+      <c r="C244" s="6"/>
+      <c r="D244" s="7"/>
+      <c r="E244" s="7"/>
       <c r="I244" s="2"/>
     </row>
     <row r="245" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
+      <c r="C245" s="6"/>
+      <c r="D245" s="7"/>
+      <c r="E245" s="7"/>
       <c r="I245" s="2"/>
     </row>
     <row r="246" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
+      <c r="C246" s="6"/>
+      <c r="D246" s="7"/>
+      <c r="E246" s="7"/>
       <c r="I246" s="2"/>
     </row>
     <row r="247" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
+      <c r="C247" s="6"/>
+      <c r="D247" s="7"/>
+      <c r="E247" s="7"/>
       <c r="I247" s="2"/>
     </row>
     <row r="248" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
+      <c r="C248" s="6"/>
+      <c r="D248" s="7"/>
+      <c r="E248" s="7"/>
       <c r="I248" s="2"/>
     </row>
     <row r="249" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
+      <c r="C249" s="6"/>
+      <c r="D249" s="7"/>
+      <c r="E249" s="7"/>
       <c r="I249" s="2"/>
     </row>
     <row r="250" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
+      <c r="C250" s="6"/>
+      <c r="D250" s="7"/>
+      <c r="E250" s="7"/>
       <c r="I250" s="2"/>
     </row>
     <row r="251" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C251" s="2"/>
-      <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
+      <c r="C251" s="6"/>
+      <c r="D251" s="7"/>
+      <c r="E251" s="7"/>
       <c r="I251" s="2"/>
     </row>
     <row r="252" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C252" s="2"/>
-      <c r="D252" s="2"/>
-      <c r="E252" s="2"/>
+      <c r="C252" s="6"/>
+      <c r="D252" s="7"/>
+      <c r="E252" s="7"/>
       <c r="I252" s="2"/>
     </row>
     <row r="253" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C253" s="2"/>
-      <c r="D253" s="2"/>
-      <c r="E253" s="2"/>
+      <c r="C253" s="6"/>
+      <c r="D253" s="7"/>
+      <c r="E253" s="7"/>
       <c r="I253" s="2"/>
     </row>
     <row r="254" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C254" s="2"/>
-      <c r="D254" s="2"/>
-      <c r="E254" s="2"/>
+      <c r="C254" s="6"/>
+      <c r="D254" s="7"/>
+      <c r="E254" s="7"/>
       <c r="I254" s="2"/>
     </row>
     <row r="255" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C255" s="2"/>
-      <c r="D255" s="2"/>
-      <c r="E255" s="2"/>
+      <c r="C255" s="6"/>
+      <c r="D255" s="7"/>
+      <c r="E255" s="7"/>
       <c r="I255" s="2"/>
     </row>
     <row r="256" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
-      <c r="E256" s="2"/>
+      <c r="C256" s="6"/>
+      <c r="D256" s="7"/>
+      <c r="E256" s="7"/>
       <c r="I256" s="2"/>
     </row>
     <row r="257" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C257" s="2"/>
-      <c r="D257" s="2"/>
-      <c r="E257" s="2"/>
+      <c r="C257" s="6"/>
+      <c r="D257" s="7"/>
+      <c r="E257" s="7"/>
       <c r="I257" s="2"/>
     </row>
     <row r="258" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
-      <c r="E258" s="2"/>
+      <c r="C258" s="6"/>
+      <c r="D258" s="7"/>
+      <c r="E258" s="7"/>
       <c r="I258" s="2"/>
     </row>
     <row r="259" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
+      <c r="C259" s="6"/>
+      <c r="D259" s="7"/>
+      <c r="E259" s="7"/>
       <c r="I259" s="2"/>
     </row>
     <row r="260" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C260" s="2"/>
-      <c r="D260" s="2"/>
-      <c r="E260" s="2"/>
+      <c r="C260" s="6"/>
+      <c r="D260" s="7"/>
+      <c r="E260" s="7"/>
       <c r="I260" s="2"/>
     </row>
     <row r="261" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C261" s="2"/>
-      <c r="D261" s="2"/>
-      <c r="E261" s="2"/>
+      <c r="C261" s="6"/>
+      <c r="D261" s="7"/>
+      <c r="E261" s="7"/>
       <c r="I261" s="2"/>
     </row>
     <row r="262" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C262" s="2"/>
-      <c r="D262" s="2"/>
-      <c r="E262" s="2"/>
+      <c r="C262" s="6"/>
+      <c r="D262" s="7"/>
+      <c r="E262" s="7"/>
       <c r="I262" s="2"/>
     </row>
     <row r="263" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C263" s="2"/>
-      <c r="D263" s="2"/>
-      <c r="E263" s="2"/>
+      <c r="C263" s="6"/>
+      <c r="D263" s="7"/>
+      <c r="E263" s="7"/>
       <c r="I263" s="2"/>
     </row>
     <row r="264" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C264" s="2"/>
-      <c r="D264" s="2"/>
-      <c r="E264" s="2"/>
+      <c r="C264" s="6"/>
+      <c r="D264" s="7"/>
+      <c r="E264" s="7"/>
       <c r="I264" s="2"/>
     </row>
     <row r="265" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C265" s="2"/>
-      <c r="D265" s="2"/>
-      <c r="E265" s="2"/>
+      <c r="C265" s="6"/>
+      <c r="D265" s="7"/>
+      <c r="E265" s="7"/>
       <c r="I265" s="2"/>
     </row>
     <row r="266" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C266" s="2"/>
-      <c r="D266" s="2"/>
-      <c r="E266" s="2"/>
+      <c r="C266" s="6"/>
+      <c r="D266" s="7"/>
+      <c r="E266" s="7"/>
       <c r="I266" s="2"/>
     </row>
     <row r="267" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C267" s="2"/>
-      <c r="D267" s="2"/>
-      <c r="E267" s="2"/>
+      <c r="C267" s="6"/>
+      <c r="D267" s="7"/>
+      <c r="E267" s="7"/>
       <c r="I267" s="2"/>
     </row>
     <row r="268" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C268" s="2"/>
-      <c r="D268" s="2"/>
-      <c r="E268" s="2"/>
+      <c r="C268" s="6"/>
+      <c r="D268" s="7"/>
+      <c r="E268" s="7"/>
       <c r="I268" s="2"/>
     </row>
     <row r="269" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C269" s="2"/>
-      <c r="D269" s="2"/>
-      <c r="E269" s="2"/>
+      <c r="C269" s="6"/>
+      <c r="D269" s="7"/>
+      <c r="E269" s="7"/>
       <c r="I269" s="2"/>
     </row>
     <row r="270" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C270" s="2"/>
-      <c r="D270" s="2"/>
-      <c r="E270" s="2"/>
+      <c r="C270" s="6"/>
+      <c r="D270" s="7"/>
+      <c r="E270" s="7"/>
       <c r="I270" s="2"/>
     </row>
     <row r="271" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C271" s="2"/>
-      <c r="D271" s="2"/>
-      <c r="E271" s="2"/>
+      <c r="C271" s="6"/>
+      <c r="D271" s="7"/>
+      <c r="E271" s="7"/>
       <c r="I271" s="2"/>
     </row>
     <row r="272" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C272" s="2"/>
-      <c r="D272" s="2"/>
-      <c r="E272" s="2"/>
+      <c r="C272" s="6"/>
+      <c r="D272" s="7"/>
+      <c r="E272" s="7"/>
       <c r="I272" s="2"/>
     </row>
     <row r="273" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C273" s="2"/>
-      <c r="D273" s="2"/>
-      <c r="E273" s="2"/>
+      <c r="C273" s="6"/>
+      <c r="D273" s="7"/>
+      <c r="E273" s="7"/>
       <c r="I273" s="2"/>
     </row>
     <row r="274" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C274" s="2"/>
-      <c r="D274" s="2"/>
-      <c r="E274" s="2"/>
+      <c r="C274" s="6"/>
+      <c r="D274" s="7"/>
+      <c r="E274" s="7"/>
       <c r="I274" s="2"/>
     </row>
     <row r="275" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C275" s="2"/>
-      <c r="D275" s="2"/>
-      <c r="E275" s="2"/>
+      <c r="C275" s="6"/>
+      <c r="D275" s="7"/>
+      <c r="E275" s="7"/>
       <c r="I275" s="2"/>
     </row>
     <row r="276" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C276" s="2"/>
-      <c r="D276" s="2"/>
-      <c r="E276" s="2"/>
+      <c r="C276" s="6"/>
+      <c r="D276" s="7"/>
+      <c r="E276" s="7"/>
       <c r="I276" s="2"/>
     </row>
     <row r="277" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C277" s="2"/>
-      <c r="D277" s="2"/>
-      <c r="E277" s="2"/>
+      <c r="C277" s="6"/>
+      <c r="D277" s="7"/>
+      <c r="E277" s="7"/>
       <c r="I277" s="2"/>
     </row>
     <row r="278" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C278" s="2"/>
-      <c r="D278" s="2"/>
-      <c r="E278" s="2"/>
+      <c r="C278" s="6"/>
+      <c r="D278" s="7"/>
+      <c r="E278" s="7"/>
       <c r="I278" s="2"/>
     </row>
     <row r="279" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C279" s="2"/>
-      <c r="D279" s="2"/>
-      <c r="E279" s="2"/>
+      <c r="C279" s="6"/>
+      <c r="D279" s="7"/>
+      <c r="E279" s="7"/>
       <c r="I279" s="2"/>
     </row>
     <row r="280" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C280" s="2"/>
-      <c r="D280" s="2"/>
-      <c r="E280" s="2"/>
+      <c r="C280" s="6"/>
+      <c r="D280" s="7"/>
+      <c r="E280" s="7"/>
       <c r="I280" s="2"/>
     </row>
     <row r="281" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C281" s="2"/>
-      <c r="D281" s="2"/>
-      <c r="E281" s="2"/>
+      <c r="C281" s="6"/>
+      <c r="D281" s="7"/>
+      <c r="E281" s="7"/>
       <c r="I281" s="2"/>
     </row>
     <row r="282" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C282" s="2"/>
-      <c r="D282" s="2"/>
-      <c r="E282" s="2"/>
+      <c r="C282" s="6"/>
+      <c r="D282" s="7"/>
+      <c r="E282" s="7"/>
       <c r="I282" s="2"/>
     </row>
     <row r="283" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C283" s="2"/>
-      <c r="D283" s="2"/>
-      <c r="E283" s="2"/>
+      <c r="C283" s="6"/>
+      <c r="D283" s="7"/>
+      <c r="E283" s="7"/>
       <c r="I283" s="2"/>
     </row>
     <row r="284" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C284" s="2"/>
-      <c r="D284" s="2"/>
-      <c r="E284" s="2"/>
+      <c r="C284" s="6"/>
+      <c r="D284" s="7"/>
+      <c r="E284" s="7"/>
       <c r="I284" s="2"/>
     </row>
     <row r="285" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C285" s="2"/>
-      <c r="D285" s="2"/>
-      <c r="E285" s="2"/>
+      <c r="C285" s="6"/>
+      <c r="D285" s="7"/>
+      <c r="E285" s="7"/>
       <c r="I285" s="2"/>
     </row>
     <row r="286" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C286" s="2"/>
-      <c r="D286" s="2"/>
-      <c r="E286" s="2"/>
+      <c r="C286" s="6"/>
+      <c r="D286" s="7"/>
+      <c r="E286" s="7"/>
       <c r="I286" s="2"/>
     </row>
     <row r="287" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C287" s="2"/>
-      <c r="D287" s="2"/>
-      <c r="E287" s="2"/>
+      <c r="C287" s="6"/>
+      <c r="D287" s="7"/>
+      <c r="E287" s="7"/>
       <c r="I287" s="2"/>
     </row>
     <row r="288" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C288" s="2"/>
-      <c r="D288" s="2"/>
-      <c r="E288" s="2"/>
+      <c r="C288" s="6"/>
+      <c r="D288" s="7"/>
+      <c r="E288" s="7"/>
       <c r="I288" s="2"/>
     </row>
     <row r="289" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C289" s="2"/>
-      <c r="D289" s="2"/>
-      <c r="E289" s="2"/>
+      <c r="C289" s="6"/>
+      <c r="D289" s="7"/>
+      <c r="E289" s="7"/>
       <c r="I289" s="2"/>
     </row>
     <row r="290" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C290" s="2"/>
-      <c r="D290" s="2"/>
-      <c r="E290" s="2"/>
+      <c r="C290" s="6"/>
+      <c r="D290" s="7"/>
+      <c r="E290" s="7"/>
       <c r="I290" s="2"/>
     </row>
     <row r="291" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C291" s="2"/>
-      <c r="D291" s="2"/>
-      <c r="E291" s="2"/>
+      <c r="C291" s="6"/>
+      <c r="D291" s="7"/>
+      <c r="E291" s="7"/>
       <c r="I291" s="2"/>
     </row>
     <row r="292" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C292" s="2"/>
-      <c r="D292" s="2"/>
-      <c r="E292" s="2"/>
+      <c r="C292" s="6"/>
+      <c r="D292" s="7"/>
+      <c r="E292" s="7"/>
       <c r="I292" s="2"/>
     </row>
     <row r="293" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C293" s="2"/>
-      <c r="D293" s="2"/>
-      <c r="E293" s="2"/>
+      <c r="C293" s="6"/>
+      <c r="D293" s="7"/>
+      <c r="E293" s="7"/>
       <c r="I293" s="2"/>
     </row>
     <row r="294" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C294" s="2"/>
-      <c r="D294" s="2"/>
-      <c r="E294" s="2"/>
+      <c r="C294" s="6"/>
+      <c r="D294" s="7"/>
+      <c r="E294" s="7"/>
       <c r="I294" s="2"/>
     </row>
     <row r="295" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C295" s="2"/>
-      <c r="D295" s="2"/>
-      <c r="E295" s="2"/>
+      <c r="C295" s="6"/>
+      <c r="D295" s="7"/>
+      <c r="E295" s="7"/>
       <c r="I295" s="2"/>
     </row>
     <row r="296" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C296" s="2"/>
-      <c r="D296" s="2"/>
-      <c r="E296" s="2"/>
+      <c r="C296" s="6"/>
+      <c r="D296" s="7"/>
+      <c r="E296" s="7"/>
       <c r="I296" s="2"/>
     </row>
     <row r="297" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C297" s="2"/>
-      <c r="D297" s="2"/>
-      <c r="E297" s="2"/>
+      <c r="C297" s="6"/>
+      <c r="D297" s="7"/>
+      <c r="E297" s="7"/>
       <c r="I297" s="2"/>
     </row>
     <row r="298" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C298" s="2"/>
-      <c r="D298" s="2"/>
-      <c r="E298" s="2"/>
+      <c r="C298" s="6"/>
+      <c r="D298" s="7"/>
+      <c r="E298" s="7"/>
       <c r="I298" s="2"/>
     </row>
     <row r="299" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C299" s="2"/>
-      <c r="D299" s="2"/>
-      <c r="E299" s="2"/>
+      <c r="C299" s="6"/>
+      <c r="D299" s="7"/>
+      <c r="E299" s="7"/>
       <c r="I299" s="2"/>
     </row>
     <row r="300" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C300" s="2"/>
-      <c r="D300" s="2"/>
-      <c r="E300" s="2"/>
+      <c r="C300" s="6"/>
+      <c r="D300" s="7"/>
+      <c r="E300" s="7"/>
       <c r="I300" s="2"/>
     </row>
     <row r="301" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C301" s="2"/>
-      <c r="D301" s="2"/>
-      <c r="E301" s="2"/>
+      <c r="C301" s="6"/>
+      <c r="D301" s="7"/>
+      <c r="E301" s="7"/>
       <c r="I301" s="2"/>
     </row>
     <row r="302" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C302" s="2"/>
-      <c r="D302" s="2"/>
-      <c r="E302" s="2"/>
+      <c r="C302" s="6"/>
+      <c r="D302" s="7"/>
+      <c r="E302" s="7"/>
       <c r="I302" s="2"/>
     </row>
     <row r="303" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C303" s="2"/>
-      <c r="D303" s="2"/>
-      <c r="E303" s="2"/>
+      <c r="C303" s="6"/>
+      <c r="D303" s="7"/>
+      <c r="E303" s="7"/>
       <c r="I303" s="2"/>
     </row>
     <row r="304" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C304" s="2"/>
-      <c r="D304" s="2"/>
-      <c r="E304" s="2"/>
+      <c r="C304" s="6"/>
+      <c r="D304" s="7"/>
+      <c r="E304" s="7"/>
       <c r="I304" s="2"/>
     </row>
     <row r="305" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C305" s="2"/>
-      <c r="D305" s="2"/>
-      <c r="E305" s="2"/>
+      <c r="C305" s="6"/>
+      <c r="D305" s="7"/>
+      <c r="E305" s="7"/>
       <c r="I305" s="2"/>
     </row>
     <row r="306" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C306" s="2"/>
-      <c r="D306" s="2"/>
-      <c r="E306" s="2"/>
+      <c r="C306" s="6"/>
+      <c r="D306" s="7"/>
+      <c r="E306" s="7"/>
       <c r="I306" s="2"/>
     </row>
     <row r="307" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C307" s="2"/>
-      <c r="D307" s="2"/>
-      <c r="E307" s="2"/>
+      <c r="C307" s="6"/>
+      <c r="D307" s="7"/>
+      <c r="E307" s="7"/>
       <c r="I307" s="2"/>
     </row>
     <row r="308" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C308" s="2"/>
-      <c r="D308" s="2"/>
-      <c r="E308" s="2"/>
+      <c r="C308" s="6"/>
+      <c r="D308" s="7"/>
+      <c r="E308" s="7"/>
       <c r="I308" s="2"/>
     </row>
     <row r="309" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C309" s="2"/>
-      <c r="D309" s="2"/>
-      <c r="E309" s="2"/>
+      <c r="C309" s="6"/>
+      <c r="D309" s="7"/>
+      <c r="E309" s="7"/>
       <c r="I309" s="2"/>
     </row>
     <row r="310" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C310" s="2"/>
-      <c r="D310" s="2"/>
-      <c r="E310" s="2"/>
+      <c r="C310" s="6"/>
+      <c r="D310" s="7"/>
+      <c r="E310" s="7"/>
       <c r="I310" s="2"/>
     </row>
     <row r="311" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C311" s="2"/>
-      <c r="D311" s="2"/>
-      <c r="E311" s="2"/>
+      <c r="C311" s="6"/>
+      <c r="D311" s="7"/>
+      <c r="E311" s="7"/>
       <c r="I311" s="2"/>
     </row>
     <row r="312" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C312" s="2"/>
-      <c r="D312" s="2"/>
-      <c r="E312" s="2"/>
+      <c r="C312" s="6"/>
+      <c r="D312" s="7"/>
+      <c r="E312" s="7"/>
       <c r="I312" s="2"/>
     </row>
     <row r="313" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C313" s="2"/>
-      <c r="D313" s="2"/>
-      <c r="E313" s="2"/>
+      <c r="C313" s="6"/>
+      <c r="D313" s="7"/>
+      <c r="E313" s="7"/>
       <c r="I313" s="2"/>
     </row>
     <row r="314" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C314" s="2"/>
-      <c r="D314" s="2"/>
-      <c r="E314" s="2"/>
+      <c r="C314" s="6"/>
+      <c r="D314" s="7"/>
+      <c r="E314" s="7"/>
       <c r="I314" s="2"/>
     </row>
     <row r="315" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C315" s="2"/>
-      <c r="D315" s="2"/>
-      <c r="E315" s="2"/>
+      <c r="C315" s="6"/>
+      <c r="D315" s="7"/>
+      <c r="E315" s="7"/>
       <c r="I315" s="2"/>
     </row>
     <row r="316" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C316" s="2"/>
-      <c r="D316" s="2"/>
-      <c r="E316" s="2"/>
+      <c r="C316" s="6"/>
+      <c r="D316" s="7"/>
+      <c r="E316" s="7"/>
       <c r="I316" s="2"/>
     </row>
     <row r="317" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C317" s="2"/>
-      <c r="D317" s="2"/>
-      <c r="E317" s="2"/>
+      <c r="C317" s="6"/>
+      <c r="D317" s="7"/>
+      <c r="E317" s="7"/>
       <c r="I317" s="2"/>
     </row>
     <row r="318" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C318" s="2"/>
-      <c r="D318" s="2"/>
-      <c r="E318" s="2"/>
+      <c r="C318" s="6"/>
+      <c r="D318" s="7"/>
+      <c r="E318" s="7"/>
       <c r="I318" s="2"/>
     </row>
     <row r="319" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C319" s="2"/>
-      <c r="D319" s="2"/>
-      <c r="E319" s="2"/>
+      <c r="C319" s="6"/>
+      <c r="D319" s="7"/>
+      <c r="E319" s="7"/>
       <c r="I319" s="2"/>
     </row>
     <row r="320" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C320" s="2"/>
-      <c r="D320" s="2"/>
-      <c r="E320" s="2"/>
+      <c r="C320" s="6"/>
+      <c r="D320" s="7"/>
+      <c r="E320" s="7"/>
       <c r="I320" s="2"/>
     </row>
     <row r="321" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C321" s="2"/>
-      <c r="D321" s="2"/>
-      <c r="E321" s="2"/>
+      <c r="C321" s="6"/>
+      <c r="D321" s="7"/>
+      <c r="E321" s="7"/>
       <c r="I321" s="2"/>
     </row>
     <row r="322" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C322" s="2"/>
-      <c r="D322" s="2"/>
-      <c r="E322" s="2"/>
+      <c r="C322" s="6"/>
+      <c r="D322" s="7"/>
+      <c r="E322" s="7"/>
       <c r="I322" s="2"/>
     </row>
     <row r="323" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C323" s="2"/>
-      <c r="D323" s="2"/>
-      <c r="E323" s="2"/>
+      <c r="C323" s="6"/>
+      <c r="D323" s="7"/>
+      <c r="E323" s="7"/>
       <c r="I323" s="2"/>
     </row>
     <row r="324" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C324" s="2"/>
-      <c r="D324" s="2"/>
-      <c r="E324" s="2"/>
+      <c r="C324" s="6"/>
+      <c r="D324" s="7"/>
+      <c r="E324" s="7"/>
       <c r="I324" s="2"/>
     </row>
     <row r="325" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C325" s="2"/>
-      <c r="D325" s="2"/>
-      <c r="E325" s="2"/>
+      <c r="C325" s="6"/>
+      <c r="D325" s="7"/>
+      <c r="E325" s="7"/>
       <c r="I325" s="2"/>
     </row>
     <row r="326" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C326" s="2"/>
-      <c r="D326" s="2"/>
-      <c r="E326" s="2"/>
+      <c r="C326" s="6"/>
+      <c r="D326" s="7"/>
+      <c r="E326" s="7"/>
       <c r="I326" s="2"/>
     </row>
     <row r="327" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C327" s="2"/>
-      <c r="D327" s="2"/>
-      <c r="E327" s="2"/>
+      <c r="C327" s="6"/>
+      <c r="D327" s="7"/>
+      <c r="E327" s="7"/>
       <c r="I327" s="2"/>
     </row>
     <row r="328" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C328" s="2"/>
-      <c r="D328" s="2"/>
-      <c r="E328" s="2"/>
+      <c r="C328" s="6"/>
+      <c r="D328" s="7"/>
+      <c r="E328" s="7"/>
       <c r="I328" s="2"/>
     </row>
     <row r="329" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C329" s="2"/>
-      <c r="D329" s="2"/>
-      <c r="E329" s="2"/>
+      <c r="C329" s="6"/>
+      <c r="D329" s="7"/>
+      <c r="E329" s="7"/>
       <c r="I329" s="2"/>
     </row>
     <row r="330" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C330" s="2"/>
-      <c r="D330" s="2"/>
-      <c r="E330" s="2"/>
+      <c r="C330" s="6"/>
+      <c r="D330" s="7"/>
+      <c r="E330" s="7"/>
       <c r="I330" s="2"/>
     </row>
     <row r="331" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C331" s="2"/>
-      <c r="D331" s="2"/>
-      <c r="E331" s="2"/>
+      <c r="C331" s="6"/>
+      <c r="D331" s="7"/>
+      <c r="E331" s="7"/>
       <c r="I331" s="2"/>
     </row>
     <row r="332" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C332" s="2"/>
-      <c r="D332" s="2"/>
-      <c r="E332" s="2"/>
+      <c r="C332" s="6"/>
+      <c r="D332" s="7"/>
+      <c r="E332" s="7"/>
       <c r="I332" s="2"/>
     </row>
     <row r="333" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C333" s="2"/>
-      <c r="D333" s="2"/>
-      <c r="E333" s="2"/>
+      <c r="C333" s="6"/>
+      <c r="D333" s="7"/>
+      <c r="E333" s="7"/>
       <c r="I333" s="2"/>
     </row>
     <row r="334" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C334" s="2"/>
-      <c r="D334" s="2"/>
-      <c r="E334" s="2"/>
+      <c r="C334" s="6"/>
+      <c r="D334" s="7"/>
+      <c r="E334" s="7"/>
       <c r="I334" s="2"/>
     </row>
     <row r="335" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C335" s="2"/>
-      <c r="D335" s="2"/>
-      <c r="E335" s="2"/>
+      <c r="C335" s="6"/>
+      <c r="D335" s="7"/>
+      <c r="E335" s="7"/>
       <c r="I335" s="2"/>
     </row>
     <row r="336" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C336" s="2"/>
-      <c r="D336" s="2"/>
-      <c r="E336" s="2"/>
+      <c r="C336" s="6"/>
+      <c r="D336" s="7"/>
+      <c r="E336" s="7"/>
       <c r="I336" s="2"/>
     </row>
     <row r="337" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C337" s="2"/>
-      <c r="D337" s="2"/>
-      <c r="E337" s="2"/>
+      <c r="C337" s="6"/>
+      <c r="D337" s="7"/>
+      <c r="E337" s="7"/>
       <c r="I337" s="2"/>
     </row>
     <row r="338" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C338" s="2"/>
-      <c r="D338" s="2"/>
-      <c r="E338" s="2"/>
+      <c r="C338" s="6"/>
+      <c r="D338" s="7"/>
+      <c r="E338" s="7"/>
       <c r="I338" s="2"/>
     </row>
     <row r="339" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C339" s="2"/>
-      <c r="D339" s="2"/>
-      <c r="E339" s="2"/>
+      <c r="C339" s="6"/>
+      <c r="D339" s="7"/>
+      <c r="E339" s="7"/>
       <c r="I339" s="2"/>
     </row>
     <row r="340" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C340" s="2"/>
-      <c r="D340" s="2"/>
-      <c r="E340" s="2"/>
+      <c r="C340" s="6"/>
+      <c r="D340" s="7"/>
+      <c r="E340" s="7"/>
       <c r="I340" s="2"/>
     </row>
     <row r="341" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C341" s="2"/>
-      <c r="D341" s="2"/>
-      <c r="E341" s="2"/>
+      <c r="C341" s="6"/>
+      <c r="D341" s="7"/>
+      <c r="E341" s="7"/>
       <c r="I341" s="2"/>
     </row>
     <row r="342" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C342" s="2"/>
-      <c r="D342" s="2"/>
-      <c r="E342" s="2"/>
+      <c r="C342" s="6"/>
+      <c r="D342" s="7"/>
+      <c r="E342" s="7"/>
       <c r="I342" s="2"/>
     </row>
     <row r="343" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C343" s="2"/>
-      <c r="D343" s="2"/>
-      <c r="E343" s="2"/>
+      <c r="C343" s="6"/>
+      <c r="D343" s="7"/>
+      <c r="E343" s="7"/>
       <c r="I343" s="2"/>
     </row>
     <row r="344" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C344" s="2"/>
-      <c r="D344" s="2"/>
-      <c r="E344" s="2"/>
+      <c r="C344" s="6"/>
+      <c r="D344" s="7"/>
+      <c r="E344" s="7"/>
       <c r="I344" s="2"/>
     </row>
     <row r="345" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C345" s="2"/>
-      <c r="D345" s="2"/>
-      <c r="E345" s="2"/>
+      <c r="C345" s="6"/>
+      <c r="D345" s="7"/>
+      <c r="E345" s="7"/>
       <c r="I345" s="2"/>
     </row>
     <row r="346" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C346" s="2"/>
-      <c r="D346" s="2"/>
-      <c r="E346" s="2"/>
+      <c r="C346" s="6"/>
+      <c r="D346" s="7"/>
+      <c r="E346" s="7"/>
       <c r="I346" s="2"/>
     </row>
     <row r="347" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C347" s="2"/>
-      <c r="D347" s="2"/>
-      <c r="E347" s="2"/>
+      <c r="C347" s="6"/>
+      <c r="D347" s="7"/>
+      <c r="E347" s="7"/>
       <c r="I347" s="2"/>
     </row>
     <row r="348" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C348" s="2"/>
-      <c r="D348" s="2"/>
-      <c r="E348" s="2"/>
+      <c r="C348" s="6"/>
+      <c r="D348" s="7"/>
+      <c r="E348" s="7"/>
       <c r="I348" s="2"/>
     </row>
     <row r="349" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C349" s="2"/>
-      <c r="D349" s="2"/>
-      <c r="E349" s="2"/>
+      <c r="C349" s="6"/>
+      <c r="D349" s="7"/>
+      <c r="E349" s="7"/>
       <c r="I349" s="2"/>
     </row>
     <row r="350" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C350" s="2"/>
-      <c r="D350" s="2"/>
-      <c r="E350" s="2"/>
+      <c r="C350" s="6"/>
+      <c r="D350" s="7"/>
+      <c r="E350" s="7"/>
       <c r="I350" s="2"/>
     </row>
     <row r="351" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C351" s="2"/>
-      <c r="D351" s="2"/>
-      <c r="E351" s="2"/>
+      <c r="C351" s="6"/>
+      <c r="D351" s="7"/>
+      <c r="E351" s="7"/>
       <c r="I351" s="2"/>
     </row>
     <row r="352" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C352" s="2"/>
-      <c r="D352" s="2"/>
-      <c r="E352" s="2"/>
+      <c r="C352" s="6"/>
+      <c r="D352" s="7"/>
+      <c r="E352" s="7"/>
       <c r="I352" s="2"/>
     </row>
     <row r="353" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C353" s="2"/>
-      <c r="D353" s="2"/>
-      <c r="E353" s="2"/>
+      <c r="C353" s="6"/>
+      <c r="D353" s="7"/>
+      <c r="E353" s="7"/>
       <c r="I353" s="2"/>
     </row>
     <row r="354" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C354" s="2"/>
-      <c r="D354" s="2"/>
-      <c r="E354" s="2"/>
+      <c r="C354" s="6"/>
+      <c r="D354" s="7"/>
+      <c r="E354" s="7"/>
       <c r="I354" s="2"/>
     </row>
     <row r="355" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C355" s="2"/>
-      <c r="D355" s="2"/>
-      <c r="E355" s="2"/>
+      <c r="C355" s="6"/>
+      <c r="D355" s="7"/>
+      <c r="E355" s="7"/>
       <c r="I355" s="2"/>
     </row>
     <row r="356" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C356" s="2"/>
-      <c r="D356" s="2"/>
-      <c r="E356" s="2"/>
+      <c r="C356" s="6"/>
+      <c r="D356" s="7"/>
+      <c r="E356" s="7"/>
       <c r="I356" s="2"/>
     </row>
     <row r="357" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C357" s="2"/>
-      <c r="D357" s="2"/>
-      <c r="E357" s="2"/>
+      <c r="C357" s="6"/>
+      <c r="D357" s="7"/>
+      <c r="E357" s="7"/>
       <c r="I357" s="2"/>
     </row>
     <row r="358" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C358" s="2"/>
-      <c r="D358" s="2"/>
-      <c r="E358" s="2"/>
+      <c r="C358" s="6"/>
+      <c r="D358" s="7"/>
+      <c r="E358" s="7"/>
       <c r="I358" s="2"/>
     </row>
     <row r="359" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C359" s="2"/>
-      <c r="D359" s="2"/>
-      <c r="E359" s="2"/>
+      <c r="C359" s="6"/>
+      <c r="D359" s="7"/>
+      <c r="E359" s="7"/>
       <c r="I359" s="2"/>
     </row>
     <row r="360" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C360" s="2"/>
-      <c r="D360" s="2"/>
-      <c r="E360" s="2"/>
+      <c r="C360" s="6"/>
+      <c r="D360" s="7"/>
+      <c r="E360" s="7"/>
       <c r="I360" s="2"/>
     </row>
     <row r="361" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C361" s="2"/>
-      <c r="D361" s="2"/>
-      <c r="E361" s="2"/>
+      <c r="C361" s="6"/>
+      <c r="D361" s="7"/>
+      <c r="E361" s="7"/>
       <c r="I361" s="2"/>
     </row>
     <row r="362" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C362" s="2"/>
-      <c r="D362" s="2"/>
-      <c r="E362" s="2"/>
+      <c r="C362" s="6"/>
+      <c r="D362" s="7"/>
+      <c r="E362" s="7"/>
       <c r="I362" s="2"/>
     </row>
     <row r="363" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C363" s="2"/>
-      <c r="D363" s="2"/>
-      <c r="E363" s="2"/>
+      <c r="C363" s="6"/>
+      <c r="D363" s="7"/>
+      <c r="E363" s="7"/>
       <c r="I363" s="2"/>
     </row>
     <row r="364" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C364" s="2"/>
-      <c r="D364" s="2"/>
-      <c r="E364" s="2"/>
+      <c r="C364" s="6"/>
+      <c r="D364" s="7"/>
+      <c r="E364" s="7"/>
       <c r="I364" s="2"/>
     </row>
     <row r="365" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C365" s="2"/>
-      <c r="D365" s="2"/>
-      <c r="E365" s="2"/>
+      <c r="C365" s="6"/>
+      <c r="D365" s="7"/>
+      <c r="E365" s="7"/>
       <c r="I365" s="2"/>
     </row>
     <row r="366" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C366" s="2"/>
-      <c r="D366" s="2"/>
-      <c r="E366" s="2"/>
+      <c r="C366" s="6"/>
+      <c r="D366" s="7"/>
+      <c r="E366" s="7"/>
       <c r="I366" s="2"/>
     </row>
     <row r="367" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C367" s="2"/>
-      <c r="D367" s="2"/>
-      <c r="E367" s="2"/>
+      <c r="C367" s="6"/>
+      <c r="D367" s="7"/>
+      <c r="E367" s="7"/>
       <c r="I367" s="2"/>
     </row>
     <row r="368" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C368" s="2"/>
-      <c r="D368" s="2"/>
-      <c r="E368" s="2"/>
+      <c r="C368" s="6"/>
+      <c r="D368" s="7"/>
+      <c r="E368" s="7"/>
       <c r="I368" s="2"/>
     </row>
     <row r="369" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C369" s="2"/>
-      <c r="D369" s="2"/>
-      <c r="E369" s="2"/>
+      <c r="C369" s="6"/>
+      <c r="D369" s="7"/>
+      <c r="E369" s="7"/>
       <c r="I369" s="2"/>
     </row>
     <row r="370" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C370" s="2"/>
-      <c r="D370" s="2"/>
-      <c r="E370" s="2"/>
+      <c r="C370" s="6"/>
+      <c r="D370" s="7"/>
+      <c r="E370" s="7"/>
       <c r="I370" s="2"/>
     </row>
     <row r="371" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C371" s="2"/>
-      <c r="D371" s="2"/>
-      <c r="E371" s="2"/>
+      <c r="C371" s="6"/>
+      <c r="D371" s="7"/>
+      <c r="E371" s="7"/>
       <c r="I371" s="2"/>
     </row>
     <row r="372" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C372" s="2"/>
-      <c r="D372" s="2"/>
-      <c r="E372" s="2"/>
+      <c r="C372" s="6"/>
+      <c r="D372" s="7"/>
+      <c r="E372" s="7"/>
       <c r="I372" s="2"/>
     </row>
     <row r="373" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C373" s="2"/>
-      <c r="D373" s="2"/>
-      <c r="E373" s="2"/>
+      <c r="C373" s="6"/>
+      <c r="D373" s="7"/>
+      <c r="E373" s="7"/>
       <c r="I373" s="2"/>
     </row>
     <row r="374" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C374" s="2"/>
-      <c r="D374" s="2"/>
-      <c r="E374" s="2"/>
+      <c r="C374" s="6"/>
+      <c r="D374" s="7"/>
+      <c r="E374" s="7"/>
       <c r="I374" s="2"/>
     </row>
     <row r="375" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C375" s="2"/>
-      <c r="D375" s="2"/>
-      <c r="E375" s="2"/>
+      <c r="C375" s="6"/>
+      <c r="D375" s="7"/>
+      <c r="E375" s="7"/>
       <c r="I375" s="2"/>
     </row>
     <row r="376" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C376" s="2"/>
-      <c r="D376" s="2"/>
-      <c r="E376" s="2"/>
+      <c r="C376" s="6"/>
+      <c r="D376" s="7"/>
+      <c r="E376" s="7"/>
       <c r="I376" s="2"/>
     </row>
     <row r="377" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C377" s="2"/>
-      <c r="D377" s="2"/>
-      <c r="E377" s="2"/>
+      <c r="C377" s="6"/>
+      <c r="D377" s="7"/>
+      <c r="E377" s="7"/>
       <c r="I377" s="2"/>
     </row>
     <row r="378" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C378" s="2"/>
-      <c r="D378" s="2"/>
-      <c r="E378" s="2"/>
+      <c r="C378" s="6"/>
+      <c r="D378" s="7"/>
+      <c r="E378" s="7"/>
       <c r="I378" s="2"/>
     </row>
     <row r="379" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C379" s="2"/>
-      <c r="D379" s="2"/>
-      <c r="E379" s="2"/>
+      <c r="C379" s="6"/>
+      <c r="D379" s="7"/>
+      <c r="E379" s="7"/>
       <c r="I379" s="2"/>
     </row>
     <row r="380" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C380" s="2"/>
-      <c r="D380" s="2"/>
-      <c r="E380" s="2"/>
+      <c r="C380" s="6"/>
+      <c r="D380" s="7"/>
+      <c r="E380" s="7"/>
       <c r="I380" s="2"/>
     </row>
     <row r="381" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C381" s="2"/>
-      <c r="D381" s="2"/>
-      <c r="E381" s="2"/>
+      <c r="C381" s="6"/>
+      <c r="D381" s="7"/>
+      <c r="E381" s="7"/>
       <c r="I381" s="2"/>
     </row>
     <row r="382" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C382" s="2"/>
-      <c r="D382" s="2"/>
-      <c r="E382" s="2"/>
+      <c r="C382" s="6"/>
+      <c r="D382" s="7"/>
+      <c r="E382" s="7"/>
       <c r="I382" s="2"/>
     </row>
     <row r="383" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C383" s="2"/>
-      <c r="D383" s="2"/>
-      <c r="E383" s="2"/>
+      <c r="C383" s="6"/>
+      <c r="D383" s="7"/>
+      <c r="E383" s="7"/>
       <c r="I383" s="2"/>
     </row>
     <row r="384" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C384" s="2"/>
-      <c r="D384" s="2"/>
-      <c r="E384" s="2"/>
+      <c r="C384" s="6"/>
+      <c r="D384" s="7"/>
+      <c r="E384" s="7"/>
       <c r="I384" s="2"/>
     </row>
     <row r="385" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C385" s="2"/>
-      <c r="D385" s="2"/>
-      <c r="E385" s="2"/>
+      <c r="C385" s="6"/>
+      <c r="D385" s="7"/>
+      <c r="E385" s="7"/>
       <c r="I385" s="2"/>
     </row>
     <row r="386" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C386" s="2"/>
-      <c r="D386" s="2"/>
-      <c r="E386" s="2"/>
+      <c r="C386" s="6"/>
+      <c r="D386" s="7"/>
+      <c r="E386" s="7"/>
       <c r="I386" s="2"/>
     </row>
     <row r="387" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C387" s="2"/>
-      <c r="D387" s="2"/>
-      <c r="E387" s="2"/>
+      <c r="C387" s="6"/>
+      <c r="D387" s="7"/>
+      <c r="E387" s="7"/>
       <c r="I387" s="2"/>
     </row>
     <row r="388" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C388" s="2"/>
-      <c r="D388" s="2"/>
-      <c r="E388" s="2"/>
+      <c r="C388" s="6"/>
+      <c r="D388" s="7"/>
+      <c r="E388" s="7"/>
       <c r="I388" s="2"/>
     </row>
     <row r="389" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C389" s="2"/>
-      <c r="D389" s="2"/>
-      <c r="E389" s="2"/>
+      <c r="C389" s="6"/>
+      <c r="D389" s="7"/>
+      <c r="E389" s="7"/>
       <c r="I389" s="2"/>
     </row>
     <row r="390" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C390" s="2"/>
-      <c r="D390" s="2"/>
-      <c r="E390" s="2"/>
+      <c r="C390" s="6"/>
+      <c r="D390" s="7"/>
+      <c r="E390" s="7"/>
       <c r="I390" s="2"/>
     </row>
     <row r="391" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C391" s="2"/>
-      <c r="D391" s="2"/>
-      <c r="E391" s="2"/>
+      <c r="C391" s="6"/>
+      <c r="D391" s="7"/>
+      <c r="E391" s="7"/>
       <c r="I391" s="2"/>
     </row>
     <row r="392" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C392" s="2"/>
-      <c r="D392" s="2"/>
-      <c r="E392" s="2"/>
+      <c r="C392" s="6"/>
+      <c r="D392" s="7"/>
+      <c r="E392" s="7"/>
       <c r="I392" s="2"/>
     </row>
     <row r="393" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C393" s="2"/>
-      <c r="D393" s="2"/>
-      <c r="E393" s="2"/>
+      <c r="C393" s="6"/>
+      <c r="D393" s="7"/>
+      <c r="E393" s="7"/>
       <c r="I393" s="2"/>
     </row>
     <row r="394" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C394" s="2"/>
-      <c r="D394" s="2"/>
-      <c r="E394" s="2"/>
+      <c r="C394" s="6"/>
+      <c r="D394" s="7"/>
+      <c r="E394" s="7"/>
       <c r="I394" s="2"/>
     </row>
     <row r="395" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C395" s="2"/>
-      <c r="D395" s="2"/>
-      <c r="E395" s="2"/>
+      <c r="C395" s="6"/>
+      <c r="D395" s="7"/>
+      <c r="E395" s="7"/>
       <c r="I395" s="2"/>
     </row>
     <row r="396" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C396" s="2"/>
-      <c r="D396" s="2"/>
-      <c r="E396" s="2"/>
+      <c r="C396" s="6"/>
+      <c r="D396" s="7"/>
+      <c r="E396" s="7"/>
       <c r="I396" s="2"/>
     </row>
     <row r="397" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C397" s="2"/>
-      <c r="D397" s="2"/>
-      <c r="E397" s="2"/>
+      <c r="C397" s="6"/>
+      <c r="D397" s="7"/>
+      <c r="E397" s="7"/>
       <c r="I397" s="2"/>
     </row>
     <row r="398" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C398" s="2"/>
-      <c r="D398" s="2"/>
-      <c r="E398" s="2"/>
+      <c r="C398" s="6"/>
+      <c r="D398" s="7"/>
+      <c r="E398" s="7"/>
       <c r="I398" s="2"/>
     </row>
     <row r="399" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C399" s="2"/>
-      <c r="D399" s="2"/>
-      <c r="E399" s="2"/>
+      <c r="C399" s="6"/>
+      <c r="D399" s="7"/>
+      <c r="E399" s="7"/>
       <c r="I399" s="2"/>
     </row>
     <row r="400" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C400" s="2"/>
-      <c r="D400" s="2"/>
-      <c r="E400" s="2"/>
+      <c r="C400" s="6"/>
+      <c r="D400" s="7"/>
+      <c r="E400" s="7"/>
       <c r="I400" s="2"/>
     </row>
     <row r="401" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C401" s="2"/>
-      <c r="D401" s="2"/>
-      <c r="E401" s="2"/>
+      <c r="C401" s="6"/>
+      <c r="D401" s="7"/>
+      <c r="E401" s="7"/>
       <c r="I401" s="2"/>
     </row>
     <row r="402" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C402" s="2"/>
-      <c r="D402" s="2"/>
-      <c r="E402" s="2"/>
+      <c r="C402" s="6"/>
+      <c r="D402" s="7"/>
+      <c r="E402" s="7"/>
       <c r="I402" s="2"/>
     </row>
     <row r="403" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C403" s="2"/>
-      <c r="D403" s="2"/>
-      <c r="E403" s="2"/>
+      <c r="C403" s="6"/>
+      <c r="D403" s="7"/>
+      <c r="E403" s="7"/>
       <c r="I403" s="2"/>
     </row>
     <row r="404" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C404" s="2"/>
-      <c r="D404" s="2"/>
-      <c r="E404" s="2"/>
+      <c r="C404" s="6"/>
+      <c r="D404" s="7"/>
+      <c r="E404" s="7"/>
       <c r="I404" s="2"/>
     </row>
     <row r="405" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C405" s="2"/>
-      <c r="D405" s="2"/>
-      <c r="E405" s="2"/>
+      <c r="C405" s="6"/>
+      <c r="D405" s="7"/>
+      <c r="E405" s="7"/>
       <c r="I405" s="2"/>
     </row>
     <row r="406" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C406" s="2"/>
-      <c r="D406" s="2"/>
-      <c r="E406" s="2"/>
+      <c r="C406" s="6"/>
+      <c r="D406" s="7"/>
+      <c r="E406" s="7"/>
       <c r="I406" s="2"/>
     </row>
     <row r="407" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C407" s="2"/>
-      <c r="D407" s="2"/>
-      <c r="E407" s="2"/>
+      <c r="C407" s="6"/>
+      <c r="D407" s="7"/>
+      <c r="E407" s="7"/>
       <c r="I407" s="2"/>
     </row>
     <row r="408" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C408" s="2"/>
-      <c r="D408" s="2"/>
-      <c r="E408" s="2"/>
+      <c r="C408" s="6"/>
+      <c r="D408" s="7"/>
+      <c r="E408" s="7"/>
       <c r="I408" s="2"/>
     </row>
     <row r="409" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C409" s="2"/>
-      <c r="D409" s="2"/>
-      <c r="E409" s="2"/>
+      <c r="C409" s="6"/>
+      <c r="D409" s="7"/>
+      <c r="E409" s="7"/>
       <c r="I409" s="2"/>
     </row>
     <row r="410" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C410" s="2"/>
-      <c r="D410" s="2"/>
-      <c r="E410" s="2"/>
+      <c r="C410" s="6"/>
+      <c r="D410" s="7"/>
+      <c r="E410" s="7"/>
       <c r="I410" s="2"/>
     </row>
     <row r="411" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C411" s="2"/>
-      <c r="D411" s="2"/>
-      <c r="E411" s="2"/>
+      <c r="C411" s="6"/>
+      <c r="D411" s="7"/>
+      <c r="E411" s="7"/>
       <c r="I411" s="2"/>
     </row>
     <row r="412" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C412" s="2"/>
-      <c r="D412" s="2"/>
-      <c r="E412" s="2"/>
+      <c r="C412" s="6"/>
+      <c r="D412" s="7"/>
+      <c r="E412" s="7"/>
       <c r="I412" s="2"/>
     </row>
     <row r="413" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C413" s="2"/>
-      <c r="D413" s="2"/>
-      <c r="E413" s="2"/>
+      <c r="C413" s="6"/>
+      <c r="D413" s="7"/>
+      <c r="E413" s="7"/>
       <c r="I413" s="2"/>
     </row>
     <row r="414" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C414" s="2"/>
-      <c r="D414" s="2"/>
-      <c r="E414" s="2"/>
+      <c r="C414" s="6"/>
+      <c r="D414" s="7"/>
+      <c r="E414" s="7"/>
       <c r="I414" s="2"/>
     </row>
     <row r="415" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C415" s="2"/>
-      <c r="D415" s="2"/>
-      <c r="E415" s="2"/>
+      <c r="C415" s="6"/>
+      <c r="D415" s="7"/>
+      <c r="E415" s="7"/>
       <c r="I415" s="2"/>
     </row>
     <row r="416" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C416" s="2"/>
-      <c r="D416" s="2"/>
-      <c r="E416" s="2"/>
+      <c r="C416" s="6"/>
+      <c r="D416" s="7"/>
+      <c r="E416" s="7"/>
       <c r="I416" s="2"/>
     </row>
     <row r="417" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C417" s="2"/>
-      <c r="D417" s="2"/>
-      <c r="E417" s="2"/>
+      <c r="C417" s="6"/>
+      <c r="D417" s="7"/>
+      <c r="E417" s="7"/>
       <c r="I417" s="2"/>
     </row>
     <row r="418" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C418" s="2"/>
-      <c r="D418" s="2"/>
-      <c r="E418" s="2"/>
+      <c r="C418" s="6"/>
+      <c r="D418" s="7"/>
+      <c r="E418" s="7"/>
       <c r="I418" s="2"/>
     </row>
     <row r="419" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C419" s="2"/>
-      <c r="D419" s="2"/>
-      <c r="E419" s="2"/>
+      <c r="C419" s="6"/>
+      <c r="D419" s="7"/>
+      <c r="E419" s="7"/>
       <c r="I419" s="2"/>
     </row>
     <row r="420" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C420" s="2"/>
-      <c r="D420" s="2"/>
-      <c r="E420" s="2"/>
+      <c r="C420" s="6"/>
+      <c r="D420" s="7"/>
+      <c r="E420" s="7"/>
       <c r="I420" s="2"/>
     </row>
     <row r="421" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C421" s="2"/>
-      <c r="D421" s="2"/>
-      <c r="E421" s="2"/>
+      <c r="C421" s="6"/>
+      <c r="D421" s="7"/>
+      <c r="E421" s="7"/>
       <c r="I421" s="2"/>
     </row>
     <row r="422" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C422" s="2"/>
-      <c r="D422" s="2"/>
-      <c r="E422" s="2"/>
+      <c r="C422" s="6"/>
+      <c r="D422" s="7"/>
+      <c r="E422" s="7"/>
       <c r="I422" s="2"/>
     </row>
     <row r="423" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C423" s="2"/>
-      <c r="D423" s="2"/>
-      <c r="E423" s="2"/>
+      <c r="C423" s="6"/>
+      <c r="D423" s="7"/>
+      <c r="E423" s="7"/>
       <c r="I423" s="2"/>
     </row>
     <row r="424" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C424" s="2"/>
-      <c r="D424" s="2"/>
-      <c r="E424" s="2"/>
+      <c r="C424" s="6"/>
+      <c r="D424" s="7"/>
+      <c r="E424" s="7"/>
       <c r="I424" s="2"/>
     </row>
     <row r="425" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C425" s="2"/>
-      <c r="D425" s="2"/>
-      <c r="E425" s="2"/>
+      <c r="C425" s="6"/>
+      <c r="D425" s="7"/>
+      <c r="E425" s="7"/>
       <c r="I425" s="2"/>
     </row>
     <row r="426" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C426" s="2"/>
-      <c r="D426" s="2"/>
-      <c r="E426" s="2"/>
+      <c r="C426" s="6"/>
+      <c r="D426" s="7"/>
+      <c r="E426" s="7"/>
       <c r="I426" s="2"/>
     </row>
     <row r="427" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C427" s="2"/>
-      <c r="D427" s="2"/>
-      <c r="E427" s="2"/>
+      <c r="C427" s="6"/>
+      <c r="D427" s="7"/>
+      <c r="E427" s="7"/>
       <c r="I427" s="2"/>
     </row>
     <row r="428" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C428" s="2"/>
-      <c r="D428" s="2"/>
-      <c r="E428" s="2"/>
+      <c r="C428" s="6"/>
+      <c r="D428" s="7"/>
+      <c r="E428" s="7"/>
       <c r="I428" s="2"/>
     </row>
     <row r="429" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C429" s="2"/>
-      <c r="D429" s="2"/>
-      <c r="E429" s="2"/>
+      <c r="C429" s="6"/>
+      <c r="D429" s="7"/>
+      <c r="E429" s="7"/>
       <c r="I429" s="2"/>
     </row>
     <row r="430" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C430" s="2"/>
-      <c r="D430" s="2"/>
-      <c r="E430" s="2"/>
+      <c r="C430" s="6"/>
+      <c r="D430" s="7"/>
+      <c r="E430" s="7"/>
       <c r="I430" s="2"/>
     </row>
     <row r="431" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C431" s="2"/>
-      <c r="D431" s="2"/>
-      <c r="E431" s="2"/>
+      <c r="C431" s="6"/>
+      <c r="D431" s="7"/>
+      <c r="E431" s="7"/>
       <c r="I431" s="2"/>
     </row>
     <row r="432" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C432" s="2"/>
-      <c r="D432" s="2"/>
-      <c r="E432" s="2"/>
+      <c r="C432" s="6"/>
+      <c r="D432" s="7"/>
+      <c r="E432" s="7"/>
       <c r="I432" s="2"/>
     </row>
     <row r="433" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C433" s="2"/>
-      <c r="D433" s="2"/>
-      <c r="E433" s="2"/>
+      <c r="C433" s="6"/>
+      <c r="D433" s="7"/>
+      <c r="E433" s="7"/>
       <c r="I433" s="2"/>
     </row>
     <row r="434" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C434" s="2"/>
-      <c r="D434" s="2"/>
-      <c r="E434" s="2"/>
+      <c r="C434" s="6"/>
+      <c r="D434" s="7"/>
+      <c r="E434" s="7"/>
       <c r="I434" s="2"/>
     </row>
     <row r="435" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C435" s="2"/>
-      <c r="D435" s="2"/>
-      <c r="E435" s="2"/>
+      <c r="C435" s="6"/>
+      <c r="D435" s="7"/>
+      <c r="E435" s="7"/>
       <c r="I435" s="2"/>
     </row>
     <row r="436" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C436" s="2"/>
-      <c r="D436" s="2"/>
-      <c r="E436" s="2"/>
+      <c r="C436" s="6"/>
+      <c r="D436" s="7"/>
+      <c r="E436" s="7"/>
       <c r="I436" s="2"/>
     </row>
     <row r="437" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C437" s="2"/>
-      <c r="D437" s="2"/>
-      <c r="E437" s="2"/>
+      <c r="C437" s="6"/>
+      <c r="D437" s="7"/>
+      <c r="E437" s="7"/>
       <c r="I437" s="2"/>
     </row>
     <row r="438" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C438" s="2"/>
-      <c r="D438" s="2"/>
-      <c r="E438" s="2"/>
+      <c r="C438" s="6"/>
+      <c r="D438" s="7"/>
+      <c r="E438" s="7"/>
       <c r="I438" s="2"/>
     </row>
     <row r="439" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C439" s="2"/>
-      <c r="D439" s="2"/>
-      <c r="E439" s="2"/>
+      <c r="C439" s="6"/>
+      <c r="D439" s="7"/>
+      <c r="E439" s="7"/>
       <c r="I439" s="2"/>
     </row>
     <row r="440" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C440" s="2"/>
-      <c r="D440" s="2"/>
-      <c r="E440" s="2"/>
+      <c r="C440" s="6"/>
+      <c r="D440" s="7"/>
+      <c r="E440" s="7"/>
       <c r="I440" s="2"/>
     </row>
     <row r="441" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C441" s="2"/>
-      <c r="D441" s="2"/>
-      <c r="E441" s="2"/>
+      <c r="C441" s="6"/>
+      <c r="D441" s="7"/>
+      <c r="E441" s="7"/>
       <c r="I441" s="2"/>
     </row>
     <row r="442" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C442" s="2"/>
-      <c r="D442" s="2"/>
-      <c r="E442" s="2"/>
+      <c r="C442" s="6"/>
+      <c r="D442" s="7"/>
+      <c r="E442" s="7"/>
       <c r="I442" s="2"/>
     </row>
     <row r="443" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C443" s="2"/>
-      <c r="D443" s="2"/>
-      <c r="E443" s="2"/>
+      <c r="C443" s="6"/>
+      <c r="D443" s="7"/>
+      <c r="E443" s="7"/>
       <c r="I443" s="2"/>
     </row>
     <row r="444" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C444" s="2"/>
-      <c r="D444" s="2"/>
-      <c r="E444" s="2"/>
+      <c r="C444" s="6"/>
+      <c r="D444" s="7"/>
+      <c r="E444" s="7"/>
       <c r="I444" s="2"/>
     </row>
     <row r="445" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C445" s="2"/>
-      <c r="D445" s="2"/>
-      <c r="E445" s="2"/>
+      <c r="C445" s="6"/>
+      <c r="D445" s="7"/>
+      <c r="E445" s="7"/>
       <c r="I445" s="2"/>
     </row>
     <row r="446" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C446" s="2"/>
-      <c r="D446" s="2"/>
-      <c r="E446" s="2"/>
+      <c r="C446" s="6"/>
+      <c r="D446" s="7"/>
+      <c r="E446" s="7"/>
       <c r="I446" s="2"/>
     </row>
     <row r="447" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C447" s="2"/>
-      <c r="D447" s="2"/>
-      <c r="E447" s="2"/>
+      <c r="C447" s="6"/>
+      <c r="D447" s="7"/>
+      <c r="E447" s="7"/>
       <c r="I447" s="2"/>
     </row>
     <row r="448" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C448" s="2"/>
-      <c r="D448" s="2"/>
-      <c r="E448" s="2"/>
+      <c r="C448" s="6"/>
+      <c r="D448" s="7"/>
+      <c r="E448" s="7"/>
       <c r="I448" s="2"/>
     </row>
     <row r="449" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C449" s="2"/>
-      <c r="D449" s="2"/>
-      <c r="E449" s="2"/>
+      <c r="C449" s="6"/>
+      <c r="D449" s="7"/>
+      <c r="E449" s="7"/>
       <c r="I449" s="2"/>
     </row>
     <row r="450" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C450" s="2"/>
-      <c r="D450" s="2"/>
-      <c r="E450" s="2"/>
+      <c r="C450" s="6"/>
+      <c r="D450" s="7"/>
+      <c r="E450" s="7"/>
       <c r="I450" s="2"/>
     </row>
     <row r="451" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C451" s="2"/>
-      <c r="D451" s="2"/>
-      <c r="E451" s="2"/>
+      <c r="C451" s="6"/>
+      <c r="D451" s="7"/>
+      <c r="E451" s="7"/>
       <c r="I451" s="2"/>
     </row>
     <row r="452" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C452" s="2"/>
-      <c r="D452" s="2"/>
-      <c r="E452" s="2"/>
+      <c r="C452" s="6"/>
+      <c r="D452" s="7"/>
+      <c r="E452" s="7"/>
       <c r="I452" s="2"/>
     </row>
     <row r="453" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C453" s="2"/>
-      <c r="D453" s="2"/>
-      <c r="E453" s="2"/>
+      <c r="C453" s="6"/>
+      <c r="D453" s="7"/>
+      <c r="E453" s="7"/>
       <c r="I453" s="2"/>
     </row>
     <row r="454" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C454" s="2"/>
-      <c r="D454" s="2"/>
-      <c r="E454" s="2"/>
+      <c r="C454" s="6"/>
+      <c r="D454" s="7"/>
+      <c r="E454" s="7"/>
       <c r="I454" s="2"/>
     </row>
     <row r="455" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C455" s="2"/>
-      <c r="D455" s="2"/>
-      <c r="E455" s="2"/>
+      <c r="C455" s="6"/>
+      <c r="D455" s="7"/>
+      <c r="E455" s="7"/>
       <c r="I455" s="2"/>
     </row>
     <row r="456" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C456" s="2"/>
-      <c r="D456" s="2"/>
-      <c r="E456" s="2"/>
+      <c r="C456" s="6"/>
+      <c r="D456" s="7"/>
+      <c r="E456" s="7"/>
       <c r="I456" s="2"/>
     </row>
     <row r="457" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C457" s="2"/>
-      <c r="D457" s="2"/>
-      <c r="E457" s="2"/>
+      <c r="C457" s="6"/>
+      <c r="D457" s="7"/>
+      <c r="E457" s="7"/>
       <c r="I457" s="2"/>
     </row>
     <row r="458" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C458" s="2"/>
-      <c r="D458" s="2"/>
-      <c r="E458" s="2"/>
+      <c r="C458" s="6"/>
+      <c r="D458" s="7"/>
+      <c r="E458" s="7"/>
       <c r="I458" s="2"/>
     </row>
     <row r="459" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C459" s="2"/>
-      <c r="D459" s="2"/>
-      <c r="E459" s="2"/>
+      <c r="C459" s="6"/>
+      <c r="D459" s="7"/>
+      <c r="E459" s="7"/>
       <c r="I459" s="2"/>
     </row>
     <row r="460" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C460" s="2"/>
-      <c r="D460" s="2"/>
-      <c r="E460" s="2"/>
+      <c r="C460" s="6"/>
+      <c r="D460" s="7"/>
+      <c r="E460" s="7"/>
       <c r="I460" s="2"/>
     </row>
     <row r="461" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C461" s="2"/>
-      <c r="D461" s="2"/>
-      <c r="E461" s="2"/>
+      <c r="C461" s="6"/>
+      <c r="D461" s="7"/>
+      <c r="E461" s="7"/>
       <c r="I461" s="2"/>
     </row>
     <row r="462" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C462" s="2"/>
-      <c r="D462" s="2"/>
-      <c r="E462" s="2"/>
+      <c r="C462" s="6"/>
+      <c r="D462" s="7"/>
+      <c r="E462" s="7"/>
       <c r="I462" s="2"/>
     </row>
     <row r="463" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C463" s="2"/>
-      <c r="D463" s="2"/>
-      <c r="E463" s="2"/>
+      <c r="C463" s="6"/>
+      <c r="D463" s="7"/>
+      <c r="E463" s="7"/>
       <c r="I463" s="2"/>
     </row>
     <row r="464" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C464" s="2"/>
-      <c r="D464" s="2"/>
-      <c r="E464" s="2"/>
+      <c r="C464" s="6"/>
+      <c r="D464" s="7"/>
+      <c r="E464" s="7"/>
       <c r="I464" s="2"/>
     </row>
     <row r="465" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C465" s="2"/>
-      <c r="D465" s="2"/>
-      <c r="E465" s="2"/>
+      <c r="C465" s="6"/>
+      <c r="D465" s="7"/>
+      <c r="E465" s="7"/>
       <c r="I465" s="2"/>
     </row>
     <row r="466" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C466" s="2"/>
-      <c r="D466" s="2"/>
-      <c r="E466" s="2"/>
+      <c r="C466" s="6"/>
+      <c r="D466" s="7"/>
+      <c r="E466" s="7"/>
       <c r="I466" s="2"/>
     </row>
     <row r="467" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C467" s="2"/>
-      <c r="D467" s="2"/>
-      <c r="E467" s="2"/>
+      <c r="C467" s="6"/>
+      <c r="D467" s="7"/>
+      <c r="E467" s="7"/>
       <c r="I467" s="2"/>
     </row>
     <row r="468" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C468" s="2"/>
-      <c r="D468" s="2"/>
-      <c r="E468" s="2"/>
+      <c r="C468" s="6"/>
+      <c r="D468" s="7"/>
+      <c r="E468" s="7"/>
       <c r="I468" s="2"/>
     </row>
     <row r="469" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C469" s="2"/>
-      <c r="D469" s="2"/>
-      <c r="E469" s="2"/>
+      <c r="C469" s="6"/>
+      <c r="D469" s="7"/>
+      <c r="E469" s="7"/>
       <c r="I469" s="2"/>
     </row>
     <row r="470" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C470" s="2"/>
-      <c r="D470" s="2"/>
-      <c r="E470" s="2"/>
+      <c r="C470" s="6"/>
+      <c r="D470" s="7"/>
+      <c r="E470" s="7"/>
       <c r="I470" s="2"/>
     </row>
     <row r="471" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C471" s="2"/>
-      <c r="D471" s="2"/>
-      <c r="E471" s="2"/>
+      <c r="C471" s="6"/>
+      <c r="D471" s="7"/>
+      <c r="E471" s="7"/>
       <c r="I471" s="2"/>
     </row>
     <row r="472" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C472" s="2"/>
-      <c r="D472" s="2"/>
-      <c r="E472" s="2"/>
+      <c r="C472" s="6"/>
+      <c r="D472" s="7"/>
+      <c r="E472" s="7"/>
       <c r="I472" s="2"/>
     </row>
     <row r="473" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C473" s="2"/>
-      <c r="D473" s="2"/>
-      <c r="E473" s="2"/>
+      <c r="C473" s="6"/>
+      <c r="D473" s="7"/>
+      <c r="E473" s="7"/>
       <c r="I473" s="2"/>
     </row>
     <row r="474" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C474" s="2"/>
-      <c r="D474" s="2"/>
-      <c r="E474" s="2"/>
+      <c r="C474" s="6"/>
+      <c r="D474" s="7"/>
+      <c r="E474" s="7"/>
       <c r="I474" s="2"/>
     </row>
     <row r="475" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C475" s="2"/>
-      <c r="D475" s="2"/>
-      <c r="E475" s="2"/>
+      <c r="C475" s="6"/>
+      <c r="D475" s="7"/>
+      <c r="E475" s="7"/>
       <c r="I475" s="2"/>
     </row>
     <row r="476" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C476" s="2"/>
-      <c r="D476" s="2"/>
-      <c r="E476" s="2"/>
+      <c r="C476" s="6"/>
+      <c r="D476" s="7"/>
+      <c r="E476" s="7"/>
       <c r="I476" s="2"/>
     </row>
     <row r="477" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C477" s="2"/>
-      <c r="D477" s="2"/>
-      <c r="E477" s="2"/>
+      <c r="C477" s="6"/>
+      <c r="D477" s="7"/>
+      <c r="E477" s="7"/>
       <c r="I477" s="2"/>
     </row>
     <row r="478" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C478" s="2"/>
-      <c r="D478" s="2"/>
-      <c r="E478" s="2"/>
+      <c r="C478" s="6"/>
+      <c r="D478" s="7"/>
+      <c r="E478" s="7"/>
       <c r="I478" s="2"/>
     </row>
     <row r="479" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C479" s="2"/>
-      <c r="D479" s="2"/>
-      <c r="E479" s="2"/>
+      <c r="C479" s="6"/>
+      <c r="D479" s="7"/>
+      <c r="E479" s="7"/>
       <c r="I479" s="2"/>
     </row>
     <row r="480" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C480" s="2"/>
-      <c r="D480" s="2"/>
-      <c r="E480" s="2"/>
+      <c r="C480" s="6"/>
+      <c r="D480" s="7"/>
+      <c r="E480" s="7"/>
       <c r="I480" s="2"/>
     </row>
     <row r="481" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C481" s="2"/>
-      <c r="D481" s="2"/>
-      <c r="E481" s="2"/>
+      <c r="C481" s="6"/>
+      <c r="D481" s="7"/>
+      <c r="E481" s="7"/>
       <c r="I481" s="2"/>
     </row>
     <row r="482" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C482" s="2"/>
-      <c r="D482" s="2"/>
-      <c r="E482" s="2"/>
+      <c r="C482" s="6"/>
+      <c r="D482" s="7"/>
+      <c r="E482" s="7"/>
       <c r="I482" s="2"/>
     </row>
     <row r="483" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C483" s="2"/>
-      <c r="D483" s="2"/>
-      <c r="E483" s="2"/>
+      <c r="C483" s="6"/>
+      <c r="D483" s="7"/>
+      <c r="E483" s="7"/>
       <c r="I483" s="2"/>
     </row>
     <row r="484" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C484" s="2"/>
-      <c r="D484" s="2"/>
-      <c r="E484" s="2"/>
+      <c r="C484" s="6"/>
+      <c r="D484" s="7"/>
+      <c r="E484" s="7"/>
       <c r="I484" s="2"/>
     </row>
     <row r="485" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C485" s="2"/>
-      <c r="D485" s="2"/>
-      <c r="E485" s="2"/>
+      <c r="C485" s="6"/>
+      <c r="D485" s="7"/>
+      <c r="E485" s="7"/>
       <c r="I485" s="2"/>
     </row>
     <row r="486" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C486" s="2"/>
-      <c r="D486" s="2"/>
-      <c r="E486" s="2"/>
+      <c r="C486" s="6"/>
+      <c r="D486" s="7"/>
+      <c r="E486" s="7"/>
       <c r="I486" s="2"/>
     </row>
     <row r="487" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C487" s="2"/>
-      <c r="D487" s="2"/>
-      <c r="E487" s="2"/>
+      <c r="C487" s="6"/>
+      <c r="D487" s="7"/>
+      <c r="E487" s="7"/>
       <c r="I487" s="2"/>
     </row>
     <row r="488" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C488" s="2"/>
-      <c r="D488" s="2"/>
-      <c r="E488" s="2"/>
+      <c r="C488" s="6"/>
+      <c r="D488" s="7"/>
+      <c r="E488" s="7"/>
       <c r="I488" s="2"/>
     </row>
     <row r="489" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C489" s="2"/>
-      <c r="D489" s="2"/>
-      <c r="E489" s="2"/>
+      <c r="C489" s="6"/>
+      <c r="D489" s="7"/>
+      <c r="E489" s="7"/>
       <c r="I489" s="2"/>
     </row>
     <row r="490" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C490" s="2"/>
-      <c r="D490" s="2"/>
-      <c r="E490" s="2"/>
+      <c r="C490" s="6"/>
+      <c r="D490" s="7"/>
+      <c r="E490" s="7"/>
       <c r="I490" s="2"/>
     </row>
     <row r="491" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C491" s="2"/>
-      <c r="D491" s="2"/>
-      <c r="E491" s="2"/>
+      <c r="C491" s="6"/>
+      <c r="D491" s="7"/>
+      <c r="E491" s="7"/>
       <c r="I491" s="2"/>
     </row>
     <row r="492" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C492" s="2"/>
-      <c r="D492" s="2"/>
-      <c r="E492" s="2"/>
+      <c r="C492" s="6"/>
+      <c r="D492" s="7"/>
+      <c r="E492" s="7"/>
       <c r="I492" s="2"/>
     </row>
     <row r="493" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C493" s="2"/>
-      <c r="D493" s="2"/>
-      <c r="E493" s="2"/>
+      <c r="C493" s="6"/>
+      <c r="D493" s="7"/>
+      <c r="E493" s="7"/>
       <c r="I493" s="2"/>
     </row>
     <row r="494" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C494" s="2"/>
-      <c r="D494" s="2"/>
-      <c r="E494" s="2"/>
+      <c r="C494" s="6"/>
+      <c r="D494" s="7"/>
+      <c r="E494" s="7"/>
       <c r="I494" s="2"/>
     </row>
     <row r="495" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C495" s="2"/>
-      <c r="D495" s="2"/>
-      <c r="E495" s="2"/>
+      <c r="C495" s="6"/>
+      <c r="D495" s="7"/>
+      <c r="E495" s="7"/>
       <c r="I495" s="2"/>
     </row>
     <row r="496" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C496" s="2"/>
-      <c r="D496" s="2"/>
-      <c r="E496" s="2"/>
+      <c r="C496" s="6"/>
+      <c r="D496" s="7"/>
+      <c r="E496" s="7"/>
       <c r="I496" s="2"/>
     </row>
     <row r="497" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C497" s="2"/>
-      <c r="D497" s="2"/>
-      <c r="E497" s="2"/>
+      <c r="C497" s="6"/>
+      <c r="D497" s="7"/>
+      <c r="E497" s="7"/>
       <c r="I497" s="2"/>
     </row>
     <row r="498" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C498" s="2"/>
-      <c r="D498" s="2"/>
-      <c r="E498" s="2"/>
+      <c r="C498" s="6"/>
+      <c r="D498" s="7"/>
+      <c r="E498" s="7"/>
       <c r="I498" s="2"/>
     </row>
     <row r="499" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C499" s="2"/>
-      <c r="D499" s="2"/>
-      <c r="E499" s="2"/>
+      <c r="C499" s="6"/>
+      <c r="D499" s="7"/>
+      <c r="E499" s="7"/>
       <c r="I499" s="2"/>
     </row>
     <row r="500" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C500" s="2"/>
-      <c r="D500" s="2"/>
-      <c r="E500" s="2"/>
+      <c r="C500" s="6"/>
+      <c r="D500" s="7"/>
+      <c r="E500" s="7"/>
       <c r="I500" s="2"/>
     </row>
     <row r="501" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C501" s="2"/>
-      <c r="D501" s="2"/>
-      <c r="E501" s="2"/>
+      <c r="C501" s="6"/>
+      <c r="D501" s="7"/>
+      <c r="E501" s="7"/>
       <c r="I501" s="2"/>
     </row>
     <row r="502" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C502" s="2"/>
-      <c r="D502" s="2"/>
-      <c r="E502" s="2"/>
+      <c r="C502" s="6"/>
+      <c r="D502" s="7"/>
+      <c r="E502" s="7"/>
       <c r="I502" s="2"/>
     </row>
     <row r="503" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C503" s="2"/>
-      <c r="D503" s="2"/>
-      <c r="E503" s="2"/>
+      <c r="C503" s="6"/>
+      <c r="D503" s="7"/>
+      <c r="E503" s="7"/>
       <c r="I503" s="2"/>
     </row>
     <row r="504" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C504" s="2"/>
-      <c r="D504" s="2"/>
-      <c r="E504" s="2"/>
+      <c r="C504" s="6"/>
+      <c r="D504" s="7"/>
+      <c r="E504" s="7"/>
       <c r="I504" s="2"/>
     </row>
     <row r="505" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C505" s="2"/>
-      <c r="D505" s="2"/>
-      <c r="E505" s="2"/>
+      <c r="C505" s="6"/>
+      <c r="D505" s="7"/>
+      <c r="E505" s="7"/>
       <c r="I505" s="2"/>
     </row>
     <row r="506" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C506" s="2"/>
-      <c r="D506" s="2"/>
-      <c r="E506" s="2"/>
+      <c r="C506" s="6"/>
+      <c r="D506" s="7"/>
+      <c r="E506" s="7"/>
       <c r="I506" s="2"/>
     </row>
     <row r="507" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C507" s="2"/>
-      <c r="D507" s="2"/>
-      <c r="E507" s="2"/>
+      <c r="C507" s="6"/>
+      <c r="D507" s="7"/>
+      <c r="E507" s="7"/>
       <c r="I507" s="2"/>
     </row>
     <row r="508" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C508" s="2"/>
-      <c r="D508" s="2"/>
-      <c r="E508" s="2"/>
+      <c r="C508" s="6"/>
+      <c r="D508" s="7"/>
+      <c r="E508" s="7"/>
       <c r="I508" s="2"/>
     </row>
     <row r="509" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C509" s="2"/>
-      <c r="D509" s="2"/>
-      <c r="E509" s="2"/>
+      <c r="C509" s="6"/>
+      <c r="D509" s="7"/>
+      <c r="E509" s="7"/>
       <c r="I509" s="2"/>
     </row>
     <row r="510" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C510" s="2"/>
-      <c r="D510" s="2"/>
-      <c r="E510" s="2"/>
+      <c r="C510" s="6"/>
+      <c r="D510" s="7"/>
+      <c r="E510" s="7"/>
       <c r="I510" s="2"/>
     </row>
     <row r="511" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C511" s="2"/>
-      <c r="D511" s="2"/>
-      <c r="E511" s="2"/>
+      <c r="C511" s="6"/>
+      <c r="D511" s="7"/>
+      <c r="E511" s="7"/>
       <c r="I511" s="2"/>
     </row>
     <row r="512" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C512" s="2"/>
-      <c r="D512" s="2"/>
-      <c r="E512" s="2"/>
+      <c r="C512" s="6"/>
+      <c r="D512" s="7"/>
+      <c r="E512" s="7"/>
       <c r="I512" s="2"/>
     </row>
     <row r="513" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C513" s="2"/>
-      <c r="D513" s="2"/>
-      <c r="E513" s="2"/>
+      <c r="C513" s="6"/>
+      <c r="D513" s="7"/>
+      <c r="E513" s="7"/>
       <c r="I513" s="2"/>
     </row>
     <row r="514" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C514" s="2"/>
-      <c r="D514" s="2"/>
-      <c r="E514" s="2"/>
+      <c r="C514" s="6"/>
+      <c r="D514" s="7"/>
+      <c r="E514" s="7"/>
       <c r="I514" s="2"/>
     </row>
     <row r="515" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C515" s="2"/>
-      <c r="D515" s="2"/>
-      <c r="E515" s="2"/>
+      <c r="C515" s="6"/>
+      <c r="D515" s="7"/>
+      <c r="E515" s="7"/>
       <c r="I515" s="2"/>
     </row>
     <row r="516" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C516" s="2"/>
-      <c r="D516" s="2"/>
-      <c r="E516" s="2"/>
+      <c r="C516" s="6"/>
+      <c r="D516" s="7"/>
+      <c r="E516" s="7"/>
       <c r="I516" s="2"/>
     </row>
     <row r="517" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C517" s="2"/>
-      <c r="D517" s="2"/>
-      <c r="E517" s="2"/>
+      <c r="C517" s="6"/>
+      <c r="D517" s="7"/>
+      <c r="E517" s="7"/>
       <c r="I517" s="2"/>
     </row>
     <row r="518" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C518" s="2"/>
-      <c r="D518" s="2"/>
-      <c r="E518" s="2"/>
+      <c r="C518" s="6"/>
+      <c r="D518" s="7"/>
+      <c r="E518" s="7"/>
       <c r="I518" s="2"/>
     </row>
     <row r="519" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C519" s="2"/>
-      <c r="D519" s="2"/>
-      <c r="E519" s="2"/>
+      <c r="C519" s="6"/>
+      <c r="D519" s="7"/>
+      <c r="E519" s="7"/>
       <c r="I519" s="2"/>
     </row>
     <row r="520" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C520" s="2"/>
-      <c r="D520" s="2"/>
-      <c r="E520" s="2"/>
+      <c r="C520" s="6"/>
+      <c r="D520" s="7"/>
+      <c r="E520" s="7"/>
       <c r="I520" s="2"/>
     </row>
     <row r="521" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C521" s="2"/>
-      <c r="D521" s="2"/>
-      <c r="E521" s="2"/>
+      <c r="C521" s="6"/>
+      <c r="D521" s="7"/>
+      <c r="E521" s="7"/>
       <c r="I521" s="2"/>
     </row>
     <row r="522" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C522" s="2"/>
-      <c r="D522" s="2"/>
-      <c r="E522" s="2"/>
+      <c r="C522" s="6"/>
+      <c r="D522" s="7"/>
+      <c r="E522" s="7"/>
       <c r="I522" s="2"/>
     </row>
     <row r="523" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C523" s="2"/>
-      <c r="D523" s="2"/>
-      <c r="E523" s="2"/>
+      <c r="C523" s="6"/>
+      <c r="D523" s="7"/>
+      <c r="E523" s="7"/>
       <c r="I523" s="2"/>
     </row>
     <row r="524" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C524" s="2"/>
-      <c r="D524" s="2"/>
-      <c r="E524" s="2"/>
+      <c r="C524" s="6"/>
+      <c r="D524" s="7"/>
+      <c r="E524" s="7"/>
       <c r="I524" s="2"/>
     </row>
     <row r="525" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C525" s="2"/>
-      <c r="D525" s="2"/>
-      <c r="E525" s="2"/>
+      <c r="C525" s="6"/>
+      <c r="D525" s="7"/>
+      <c r="E525" s="7"/>
       <c r="I525" s="2"/>
     </row>
     <row r="526" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C526" s="2"/>
-      <c r="D526" s="2"/>
-      <c r="E526" s="2"/>
+      <c r="C526" s="6"/>
+      <c r="D526" s="7"/>
+      <c r="E526" s="7"/>
       <c r="I526" s="2"/>
     </row>
     <row r="527" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C527" s="2"/>
-      <c r="D527" s="2"/>
-      <c r="E527" s="2"/>
+      <c r="C527" s="6"/>
+      <c r="D527" s="7"/>
+      <c r="E527" s="7"/>
       <c r="I527" s="2"/>
     </row>
     <row r="528" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C528" s="2"/>
-      <c r="D528" s="2"/>
-      <c r="E528" s="2"/>
+      <c r="C528" s="6"/>
+      <c r="D528" s="7"/>
+      <c r="E528" s="7"/>
       <c r="I528" s="2"/>
     </row>
     <row r="529" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C529" s="2"/>
-      <c r="D529" s="2"/>
-      <c r="E529" s="2"/>
+      <c r="C529" s="6"/>
+      <c r="D529" s="7"/>
+      <c r="E529" s="7"/>
       <c r="I529" s="2"/>
     </row>
     <row r="530" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C530" s="2"/>
-      <c r="D530" s="2"/>
-      <c r="E530" s="2"/>
+      <c r="C530" s="6"/>
+      <c r="D530" s="7"/>
+      <c r="E530" s="7"/>
       <c r="I530" s="2"/>
     </row>
     <row r="531" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C531" s="2"/>
-      <c r="D531" s="2"/>
-      <c r="E531" s="2"/>
+      <c r="C531" s="6"/>
+      <c r="D531" s="7"/>
+      <c r="E531" s="7"/>
       <c r="I531" s="2"/>
     </row>
     <row r="532" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C532" s="2"/>
-      <c r="D532" s="2"/>
-      <c r="E532" s="2"/>
+      <c r="C532" s="6"/>
+      <c r="D532" s="7"/>
+      <c r="E532" s="7"/>
       <c r="I532" s="2"/>
     </row>
     <row r="533" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C533" s="2"/>
-      <c r="D533" s="2"/>
-      <c r="E533" s="2"/>
+      <c r="C533" s="6"/>
+      <c r="D533" s="7"/>
+      <c r="E533" s="7"/>
       <c r="I533" s="2"/>
     </row>
     <row r="534" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C534" s="2"/>
-      <c r="D534" s="2"/>
-      <c r="E534" s="2"/>
+      <c r="C534" s="6"/>
+      <c r="D534" s="7"/>
+      <c r="E534" s="7"/>
       <c r="I534" s="2"/>
     </row>
     <row r="535" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C535" s="2"/>
-      <c r="D535" s="2"/>
-      <c r="E535" s="2"/>
+      <c r="C535" s="6"/>
+      <c r="D535" s="7"/>
+      <c r="E535" s="7"/>
       <c r="I535" s="2"/>
     </row>
     <row r="536" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C536" s="2"/>
-      <c r="D536" s="2"/>
-      <c r="E536" s="2"/>
+      <c r="C536" s="6"/>
+      <c r="D536" s="7"/>
+      <c r="E536" s="7"/>
       <c r="I536" s="2"/>
     </row>
     <row r="537" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C537" s="2"/>
-      <c r="D537" s="2"/>
-      <c r="E537" s="2"/>
+      <c r="C537" s="6"/>
+      <c r="D537" s="7"/>
+      <c r="E537" s="7"/>
       <c r="I537" s="2"/>
     </row>
     <row r="538" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C538" s="2"/>
-      <c r="D538" s="2"/>
-      <c r="E538" s="2"/>
+      <c r="C538" s="6"/>
+      <c r="D538" s="7"/>
+      <c r="E538" s="7"/>
       <c r="I538" s="2"/>
     </row>
     <row r="539" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C539" s="2"/>
-      <c r="D539" s="2"/>
-      <c r="E539" s="2"/>
+      <c r="C539" s="6"/>
+      <c r="D539" s="7"/>
+      <c r="E539" s="7"/>
       <c r="I539" s="2"/>
     </row>
     <row r="540" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C540" s="2"/>
-      <c r="D540" s="2"/>
-      <c r="E540" s="2"/>
+      <c r="C540" s="6"/>
+      <c r="D540" s="7"/>
+      <c r="E540" s="7"/>
       <c r="I540" s="2"/>
     </row>
     <row r="541" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C541" s="2"/>
-      <c r="D541" s="2"/>
-      <c r="E541" s="2"/>
+      <c r="C541" s="6"/>
+      <c r="D541" s="7"/>
+      <c r="E541" s="7"/>
       <c r="I541" s="2"/>
     </row>
     <row r="542" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C542" s="2"/>
-      <c r="D542" s="2"/>
-      <c r="E542" s="2"/>
+      <c r="C542" s="6"/>
+      <c r="D542" s="7"/>
+      <c r="E542" s="7"/>
       <c r="I542" s="2"/>
     </row>
     <row r="543" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C543" s="2"/>
-      <c r="D543" s="2"/>
-      <c r="E543" s="2"/>
+      <c r="C543" s="6"/>
+      <c r="D543" s="7"/>
+      <c r="E543" s="7"/>
       <c r="I543" s="2"/>
     </row>
     <row r="544" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C544" s="2"/>
-      <c r="D544" s="2"/>
-      <c r="E544" s="2"/>
+      <c r="C544" s="6"/>
+      <c r="D544" s="7"/>
+      <c r="E544" s="7"/>
       <c r="I544" s="2"/>
     </row>
     <row r="545" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C545" s="2"/>
-      <c r="D545" s="2"/>
-      <c r="E545" s="2"/>
+      <c r="C545" s="6"/>
+      <c r="D545" s="7"/>
+      <c r="E545" s="7"/>
       <c r="I545" s="2"/>
     </row>
     <row r="546" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C546" s="2"/>
-      <c r="D546" s="2"/>
-      <c r="E546" s="2"/>
+      <c r="C546" s="6"/>
+      <c r="D546" s="7"/>
+      <c r="E546" s="7"/>
       <c r="I546" s="2"/>
     </row>
     <row r="547" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C547" s="2"/>
-      <c r="D547" s="2"/>
-      <c r="E547" s="2"/>
+      <c r="C547" s="6"/>
+      <c r="D547" s="7"/>
+      <c r="E547" s="7"/>
       <c r="I547" s="2"/>
     </row>
     <row r="548" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C548" s="2"/>
-      <c r="D548" s="2"/>
-      <c r="E548" s="2"/>
+      <c r="C548" s="6"/>
+      <c r="D548" s="7"/>
+      <c r="E548" s="7"/>
       <c r="I548" s="2"/>
     </row>
     <row r="549" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C549" s="2"/>
-      <c r="D549" s="2"/>
-      <c r="E549" s="2"/>
+      <c r="C549" s="6"/>
+      <c r="D549" s="7"/>
+      <c r="E549" s="7"/>
       <c r="I549" s="2"/>
     </row>
     <row r="550" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C550" s="2"/>
-      <c r="D550" s="2"/>
-      <c r="E550" s="2"/>
+      <c r="C550" s="6"/>
+      <c r="D550" s="7"/>
+      <c r="E550" s="7"/>
       <c r="I550" s="2"/>
     </row>
     <row r="551" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C551" s="2"/>
-      <c r="D551" s="2"/>
-      <c r="E551" s="2"/>
+      <c r="C551" s="6"/>
+      <c r="D551" s="7"/>
+      <c r="E551" s="7"/>
       <c r="I551" s="2"/>
     </row>
     <row r="552" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C552" s="2"/>
-      <c r="D552" s="2"/>
-      <c r="E552" s="2"/>
+      <c r="C552" s="6"/>
+      <c r="D552" s="7"/>
+      <c r="E552" s="7"/>
       <c r="I552" s="2"/>
     </row>
     <row r="553" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C553" s="2"/>
-      <c r="D553" s="2"/>
-      <c r="E553" s="2"/>
+      <c r="C553" s="6"/>
+      <c r="D553" s="7"/>
+      <c r="E553" s="7"/>
       <c r="I553" s="2"/>
     </row>
     <row r="554" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C554" s="2"/>
-      <c r="D554" s="2"/>
-      <c r="E554" s="2"/>
+      <c r="C554" s="6"/>
+      <c r="D554" s="7"/>
+      <c r="E554" s="7"/>
       <c r="I554" s="2"/>
     </row>
     <row r="555" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C555" s="2"/>
-      <c r="D555" s="2"/>
-      <c r="E555" s="2"/>
+      <c r="C555" s="6"/>
+      <c r="D555" s="7"/>
+      <c r="E555" s="7"/>
       <c r="I555" s="2"/>
     </row>
     <row r="556" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C556" s="2"/>
-      <c r="D556" s="2"/>
-      <c r="E556" s="2"/>
+      <c r="C556" s="6"/>
+      <c r="D556" s="7"/>
+      <c r="E556" s="7"/>
       <c r="I556" s="2"/>
     </row>
     <row r="557" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C557" s="2"/>
-      <c r="D557" s="2"/>
-      <c r="E557" s="2"/>
+      <c r="C557" s="6"/>
+      <c r="D557" s="7"/>
+      <c r="E557" s="7"/>
       <c r="I557" s="2"/>
     </row>
     <row r="558" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C558" s="2"/>
-      <c r="D558" s="2"/>
-      <c r="E558" s="2"/>
+      <c r="C558" s="6"/>
+      <c r="D558" s="7"/>
+      <c r="E558" s="7"/>
       <c r="I558" s="2"/>
     </row>
     <row r="559" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C559" s="2"/>
-      <c r="D559" s="2"/>
-      <c r="E559" s="2"/>
+      <c r="C559" s="6"/>
+      <c r="D559" s="7"/>
+      <c r="E559" s="7"/>
       <c r="I559" s="2"/>
     </row>
     <row r="560" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C560" s="2"/>
-      <c r="D560" s="2"/>
-      <c r="E560" s="2"/>
+      <c r="C560" s="6"/>
+      <c r="D560" s="7"/>
+      <c r="E560" s="7"/>
       <c r="I560" s="2"/>
     </row>
     <row r="561" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C561" s="2"/>
-      <c r="D561" s="2"/>
-      <c r="E561" s="2"/>
+      <c r="C561" s="6"/>
+      <c r="D561" s="7"/>
+      <c r="E561" s="7"/>
       <c r="I561" s="2"/>
     </row>
     <row r="562" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C562" s="2"/>
-      <c r="D562" s="2"/>
-      <c r="E562" s="2"/>
+      <c r="C562" s="6"/>
+      <c r="D562" s="7"/>
+      <c r="E562" s="7"/>
       <c r="I562" s="2"/>
     </row>
     <row r="563" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C563" s="2"/>
-      <c r="D563" s="2"/>
-      <c r="E563" s="2"/>
+      <c r="C563" s="6"/>
+      <c r="D563" s="7"/>
+      <c r="E563" s="7"/>
       <c r="I563" s="2"/>
     </row>
     <row r="564" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C564" s="2"/>
-      <c r="D564" s="2"/>
-      <c r="E564" s="2"/>
+      <c r="C564" s="6"/>
+      <c r="D564" s="7"/>
+      <c r="E564" s="7"/>
       <c r="I564" s="2"/>
     </row>
     <row r="565" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C565" s="2"/>
-      <c r="D565" s="2"/>
-      <c r="E565" s="2"/>
+      <c r="C565" s="6"/>
+      <c r="D565" s="7"/>
+      <c r="E565" s="7"/>
       <c r="I565" s="2"/>
     </row>
     <row r="566" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C566" s="2"/>
-      <c r="D566" s="2"/>
-      <c r="E566" s="2"/>
+      <c r="C566" s="6"/>
+      <c r="D566" s="7"/>
+      <c r="E566" s="7"/>
       <c r="I566" s="2"/>
     </row>
     <row r="567" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C567" s="2"/>
-      <c r="D567" s="2"/>
-      <c r="E567" s="2"/>
+      <c r="C567" s="6"/>
+      <c r="D567" s="7"/>
+      <c r="E567" s="7"/>
       <c r="I567" s="2"/>
     </row>
     <row r="568" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C568" s="2"/>
-      <c r="D568" s="2"/>
-      <c r="E568" s="2"/>
+      <c r="C568" s="6"/>
+      <c r="D568" s="7"/>
+      <c r="E568" s="7"/>
       <c r="I568" s="2"/>
     </row>
     <row r="569" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C569" s="2"/>
-      <c r="D569" s="2"/>
-      <c r="E569" s="2"/>
+      <c r="C569" s="6"/>
+      <c r="D569" s="7"/>
+      <c r="E569" s="7"/>
       <c r="I569" s="2"/>
     </row>
     <row r="570" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C570" s="2"/>
-      <c r="D570" s="2"/>
-      <c r="E570" s="2"/>
+      <c r="C570" s="6"/>
+      <c r="D570" s="7"/>
+      <c r="E570" s="7"/>
       <c r="I570" s="2"/>
     </row>
     <row r="571" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C571" s="2"/>
-      <c r="D571" s="2"/>
-      <c r="E571" s="2"/>
+      <c r="C571" s="6"/>
+      <c r="D571" s="7"/>
+      <c r="E571" s="7"/>
       <c r="I571" s="2"/>
     </row>
     <row r="572" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C572" s="2"/>
-      <c r="D572" s="2"/>
-      <c r="E572" s="2"/>
+      <c r="C572" s="6"/>
+      <c r="D572" s="7"/>
+      <c r="E572" s="7"/>
       <c r="I572" s="2"/>
     </row>
     <row r="573" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C573" s="2"/>
-      <c r="D573" s="2"/>
-      <c r="E573" s="2"/>
+      <c r="C573" s="6"/>
+      <c r="D573" s="7"/>
+      <c r="E573" s="7"/>
       <c r="I573" s="2"/>
     </row>
     <row r="574" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C574" s="2"/>
-      <c r="D574" s="2"/>
-      <c r="E574" s="2"/>
+      <c r="C574" s="6"/>
+      <c r="D574" s="7"/>
+      <c r="E574" s="7"/>
       <c r="I574" s="2"/>
     </row>
     <row r="575" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C575" s="2"/>
-      <c r="D575" s="2"/>
-      <c r="E575" s="2"/>
+      <c r="C575" s="6"/>
+      <c r="D575" s="7"/>
+      <c r="E575" s="7"/>
       <c r="I575" s="2"/>
     </row>
     <row r="576" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C576" s="2"/>
-      <c r="D576" s="2"/>
-      <c r="E576" s="2"/>
+      <c r="C576" s="6"/>
+      <c r="D576" s="7"/>
+      <c r="E576" s="7"/>
       <c r="I576" s="2"/>
     </row>
     <row r="577" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C577" s="2"/>
-      <c r="D577" s="2"/>
-      <c r="E577" s="2"/>
+      <c r="C577" s="6"/>
+      <c r="D577" s="7"/>
+      <c r="E577" s="7"/>
       <c r="I577" s="2"/>
     </row>
     <row r="578" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C578" s="2"/>
-      <c r="D578" s="2"/>
-      <c r="E578" s="2"/>
+      <c r="C578" s="6"/>
+      <c r="D578" s="7"/>
+      <c r="E578" s="7"/>
       <c r="I578" s="2"/>
     </row>
     <row r="579" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C579" s="2"/>
-      <c r="D579" s="2"/>
-      <c r="E579" s="2"/>
+      <c r="C579" s="6"/>
+      <c r="D579" s="7"/>
+      <c r="E579" s="7"/>
       <c r="I579" s="2"/>
     </row>
     <row r="580" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C580" s="2"/>
-      <c r="D580" s="2"/>
-      <c r="E580" s="2"/>
+      <c r="C580" s="6"/>
+      <c r="D580" s="7"/>
+      <c r="E580" s="7"/>
       <c r="I580" s="2"/>
     </row>
     <row r="581" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C581" s="2"/>
-      <c r="D581" s="2"/>
-      <c r="E581" s="2"/>
+      <c r="C581" s="6"/>
+      <c r="D581" s="7"/>
+      <c r="E581" s="7"/>
       <c r="I581" s="2"/>
     </row>
     <row r="582" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C582" s="2"/>
-      <c r="D582" s="2"/>
-      <c r="E582" s="2"/>
+      <c r="C582" s="6"/>
+      <c r="D582" s="7"/>
+      <c r="E582" s="7"/>
       <c r="I582" s="2"/>
     </row>
     <row r="583" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C583" s="2"/>
-      <c r="D583" s="2"/>
-      <c r="E583" s="2"/>
+      <c r="C583" s="6"/>
+      <c r="D583" s="7"/>
+      <c r="E583" s="7"/>
       <c r="I583" s="2"/>
     </row>
     <row r="584" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C584" s="2"/>
-      <c r="D584" s="2"/>
-      <c r="E584" s="2"/>
+      <c r="C584" s="6"/>
+      <c r="D584" s="7"/>
+      <c r="E584" s="7"/>
       <c r="I584" s="2"/>
     </row>
     <row r="585" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C585" s="2"/>
-      <c r="D585" s="2"/>
-      <c r="E585" s="2"/>
+      <c r="C585" s="6"/>
+      <c r="D585" s="7"/>
+      <c r="E585" s="7"/>
       <c r="I585" s="2"/>
     </row>
     <row r="586" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C586" s="2"/>
-      <c r="D586" s="2"/>
-      <c r="E586" s="2"/>
+      <c r="C586" s="6"/>
+      <c r="D586" s="7"/>
+      <c r="E586" s="7"/>
       <c r="I586" s="2"/>
     </row>
     <row r="587" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C587" s="2"/>
-      <c r="D587" s="2"/>
-      <c r="E587" s="2"/>
+      <c r="C587" s="6"/>
+      <c r="D587" s="7"/>
+      <c r="E587" s="7"/>
       <c r="I587" s="2"/>
     </row>
     <row r="588" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C588" s="2"/>
-      <c r="D588" s="2"/>
-      <c r="E588" s="2"/>
+      <c r="C588" s="6"/>
+      <c r="D588" s="7"/>
+      <c r="E588" s="7"/>
       <c r="I588" s="2"/>
     </row>
     <row r="589" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C589" s="2"/>
-      <c r="D589" s="2"/>
-      <c r="E589" s="2"/>
+      <c r="C589" s="6"/>
+      <c r="D589" s="7"/>
+      <c r="E589" s="7"/>
       <c r="I589" s="2"/>
     </row>
     <row r="590" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C590" s="2"/>
-      <c r="D590" s="2"/>
-      <c r="E590" s="2"/>
+      <c r="C590" s="6"/>
+      <c r="D590" s="7"/>
+      <c r="E590" s="7"/>
       <c r="I590" s="2"/>
     </row>
     <row r="591" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C591" s="2"/>
-      <c r="D591" s="2"/>
-      <c r="E591" s="2"/>
+      <c r="C591" s="6"/>
+      <c r="D591" s="7"/>
+      <c r="E591" s="7"/>
       <c r="I591" s="2"/>
     </row>
     <row r="592" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C592" s="2"/>
-      <c r="D592" s="2"/>
-      <c r="E592" s="2"/>
+      <c r="C592" s="6"/>
+      <c r="D592" s="7"/>
+      <c r="E592" s="7"/>
       <c r="I592" s="2"/>
     </row>
     <row r="593" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C593" s="2"/>
-      <c r="D593" s="2"/>
-      <c r="E593" s="2"/>
+      <c r="C593" s="6"/>
+      <c r="D593" s="7"/>
+      <c r="E593" s="7"/>
       <c r="I593" s="2"/>
     </row>
     <row r="594" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C594" s="2"/>
-      <c r="D594" s="2"/>
-      <c r="E594" s="2"/>
+      <c r="C594" s="6"/>
+      <c r="D594" s="7"/>
+      <c r="E594" s="7"/>
       <c r="I594" s="2"/>
     </row>
     <row r="595" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C595" s="2"/>
-      <c r="D595" s="2"/>
-      <c r="E595" s="2"/>
+      <c r="C595" s="6"/>
+      <c r="D595" s="7"/>
+      <c r="E595" s="7"/>
       <c r="I595" s="2"/>
     </row>
     <row r="596" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C596" s="2"/>
-      <c r="D596" s="2"/>
-      <c r="E596" s="2"/>
+      <c r="C596" s="6"/>
+      <c r="D596" s="7"/>
+      <c r="E596" s="7"/>
       <c r="I596" s="2"/>
     </row>
     <row r="597" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C597" s="2"/>
-      <c r="D597" s="2"/>
-      <c r="E597" s="2"/>
+      <c r="C597" s="6"/>
+      <c r="D597" s="7"/>
+      <c r="E597" s="7"/>
       <c r="I597" s="2"/>
     </row>
     <row r="598" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C598" s="2"/>
-      <c r="D598" s="2"/>
-      <c r="E598" s="2"/>
+      <c r="C598" s="6"/>
+      <c r="D598" s="7"/>
+      <c r="E598" s="7"/>
       <c r="I598" s="2"/>
     </row>
     <row r="599" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C599" s="2"/>
-      <c r="D599" s="2"/>
-      <c r="E599" s="2"/>
+      <c r="C599" s="6"/>
+      <c r="D599" s="7"/>
+      <c r="E599" s="7"/>
       <c r="I599" s="2"/>
     </row>
     <row r="600" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C600" s="2"/>
-      <c r="D600" s="2"/>
-      <c r="E600" s="2"/>
+      <c r="C600" s="6"/>
+      <c r="D600" s="7"/>
+      <c r="E600" s="7"/>
       <c r="I600" s="2"/>
     </row>
     <row r="601" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C601" s="2"/>
-      <c r="D601" s="2"/>
-      <c r="E601" s="2"/>
+      <c r="C601" s="6"/>
+      <c r="D601" s="7"/>
+      <c r="E601" s="7"/>
       <c r="I601" s="2"/>
     </row>
     <row r="602" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C602" s="2"/>
-      <c r="D602" s="2"/>
-      <c r="E602" s="2"/>
+      <c r="C602" s="6"/>
+      <c r="D602" s="7"/>
+      <c r="E602" s="7"/>
       <c r="I602" s="2"/>
     </row>
     <row r="603" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C603" s="2"/>
-      <c r="D603" s="2"/>
-      <c r="E603" s="2"/>
+      <c r="C603" s="6"/>
+      <c r="D603" s="7"/>
+      <c r="E603" s="7"/>
       <c r="I603" s="2"/>
     </row>
     <row r="604" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C604" s="2"/>
-      <c r="D604" s="2"/>
-      <c r="E604" s="2"/>
+      <c r="C604" s="6"/>
+      <c r="D604" s="7"/>
+      <c r="E604" s="7"/>
       <c r="I604" s="2"/>
     </row>
     <row r="605" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C605" s="2"/>
-      <c r="D605" s="2"/>
-      <c r="E605" s="2"/>
+      <c r="C605" s="6"/>
+      <c r="D605" s="7"/>
+      <c r="E605" s="7"/>
       <c r="I605" s="2"/>
     </row>
     <row r="606" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C606" s="2"/>
-      <c r="D606" s="2"/>
-      <c r="E606" s="2"/>
+      <c r="C606" s="6"/>
+      <c r="D606" s="7"/>
+      <c r="E606" s="7"/>
       <c r="I606" s="2"/>
     </row>
     <row r="607" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C607" s="2"/>
-      <c r="D607" s="2"/>
-      <c r="E607" s="2"/>
+      <c r="C607" s="6"/>
+      <c r="D607" s="7"/>
+      <c r="E607" s="7"/>
       <c r="I607" s="2"/>
     </row>
     <row r="608" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C608" s="2"/>
-      <c r="D608" s="2"/>
-      <c r="E608" s="2"/>
+      <c r="C608" s="6"/>
+      <c r="D608" s="7"/>
+      <c r="E608" s="7"/>
       <c r="I608" s="2"/>
     </row>
     <row r="609" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C609" s="2"/>
-      <c r="D609" s="2"/>
-      <c r="E609" s="2"/>
+      <c r="C609" s="6"/>
+      <c r="D609" s="7"/>
+      <c r="E609" s="7"/>
       <c r="I609" s="2"/>
     </row>
     <row r="610" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C610" s="2"/>
-      <c r="D610" s="2"/>
-      <c r="E610" s="2"/>
+      <c r="C610" s="6"/>
+      <c r="D610" s="7"/>
+      <c r="E610" s="7"/>
       <c r="I610" s="2"/>
     </row>
     <row r="611" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C611" s="2"/>
-      <c r="D611" s="2"/>
-      <c r="E611" s="2"/>
+      <c r="C611" s="6"/>
+      <c r="D611" s="7"/>
+      <c r="E611" s="7"/>
       <c r="I611" s="2"/>
     </row>
     <row r="612" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C612" s="2"/>
-      <c r="D612" s="2"/>
-      <c r="E612" s="2"/>
+      <c r="C612" s="6"/>
+      <c r="D612" s="7"/>
+      <c r="E612" s="7"/>
       <c r="I612" s="2"/>
     </row>
     <row r="613" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C613" s="2"/>
-      <c r="D613" s="2"/>
-      <c r="E613" s="2"/>
+      <c r="C613" s="6"/>
+      <c r="D613" s="7"/>
+      <c r="E613" s="7"/>
       <c r="I613" s="2"/>
     </row>
     <row r="614" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C614" s="2"/>
-      <c r="D614" s="2"/>
-      <c r="E614" s="2"/>
+      <c r="C614" s="6"/>
+      <c r="D614" s="7"/>
+      <c r="E614" s="7"/>
       <c r="I614" s="2"/>
     </row>
     <row r="615" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C615" s="2"/>
-      <c r="D615" s="2"/>
-      <c r="E615" s="2"/>
+      <c r="C615" s="6"/>
+      <c r="D615" s="7"/>
+      <c r="E615" s="7"/>
       <c r="I615" s="2"/>
     </row>
     <row r="616" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C616" s="2"/>
-      <c r="D616" s="2"/>
-      <c r="E616" s="2"/>
+      <c r="C616" s="6"/>
+      <c r="D616" s="7"/>
+      <c r="E616" s="7"/>
       <c r="I616" s="2"/>
     </row>
     <row r="617" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C617" s="2"/>
-      <c r="D617" s="2"/>
-      <c r="E617" s="2"/>
+      <c r="C617" s="6"/>
+      <c r="D617" s="7"/>
+      <c r="E617" s="7"/>
       <c r="I617" s="2"/>
     </row>
     <row r="618" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C618" s="2"/>
-      <c r="D618" s="2"/>
-      <c r="E618" s="2"/>
+      <c r="C618" s="6"/>
+      <c r="D618" s="7"/>
+      <c r="E618" s="7"/>
       <c r="I618" s="2"/>
     </row>
     <row r="619" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C619" s="2"/>
-      <c r="D619" s="2"/>
-      <c r="E619" s="2"/>
+      <c r="C619" s="6"/>
+      <c r="D619" s="7"/>
+      <c r="E619" s="7"/>
       <c r="I619" s="2"/>
     </row>
     <row r="620" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C620" s="2"/>
-      <c r="D620" s="2"/>
-      <c r="E620" s="2"/>
+      <c r="C620" s="6"/>
+      <c r="D620" s="7"/>
+      <c r="E620" s="7"/>
       <c r="I620" s="2"/>
     </row>
     <row r="621" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C621" s="2"/>
-      <c r="D621" s="2"/>
-      <c r="E621" s="2"/>
+      <c r="C621" s="6"/>
+      <c r="D621" s="7"/>
+      <c r="E621" s="7"/>
       <c r="I621" s="2"/>
     </row>
     <row r="622" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C622" s="2"/>
-      <c r="D622" s="2"/>
-      <c r="E622" s="2"/>
+      <c r="C622" s="6"/>
+      <c r="D622" s="7"/>
+      <c r="E622" s="7"/>
       <c r="I622" s="2"/>
     </row>
     <row r="623" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C623" s="2"/>
-      <c r="D623" s="2"/>
-      <c r="E623" s="2"/>
+      <c r="C623" s="6"/>
+      <c r="D623" s="7"/>
+      <c r="E623" s="7"/>
       <c r="I623" s="2"/>
     </row>
     <row r="624" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C624" s="2"/>
-      <c r="D624" s="2"/>
-      <c r="E624" s="2"/>
+      <c r="C624" s="6"/>
+      <c r="D624" s="7"/>
+      <c r="E624" s="7"/>
       <c r="I624" s="2"/>
     </row>
     <row r="625" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C625" s="2"/>
-      <c r="D625" s="2"/>
-      <c r="E625" s="2"/>
+      <c r="C625" s="6"/>
+      <c r="D625" s="7"/>
+      <c r="E625" s="7"/>
       <c r="I625" s="2"/>
     </row>
     <row r="626" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C626" s="2"/>
-      <c r="D626" s="2"/>
-      <c r="E626" s="2"/>
+      <c r="C626" s="6"/>
+      <c r="D626" s="7"/>
+      <c r="E626" s="7"/>
       <c r="I626" s="2"/>
     </row>
     <row r="627" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C627" s="2"/>
-      <c r="D627" s="2"/>
-      <c r="E627" s="2"/>
+      <c r="C627" s="6"/>
+      <c r="D627" s="7"/>
+      <c r="E627" s="7"/>
       <c r="I627" s="2"/>
     </row>
     <row r="628" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C628" s="2"/>
-      <c r="D628" s="2"/>
-      <c r="E628" s="2"/>
+      <c r="C628" s="6"/>
+      <c r="D628" s="7"/>
+      <c r="E628" s="7"/>
       <c r="I628" s="2"/>
     </row>
     <row r="629" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C629" s="2"/>
-      <c r="D629" s="2"/>
-      <c r="E629" s="2"/>
+      <c r="C629" s="6"/>
+      <c r="D629" s="7"/>
+      <c r="E629" s="7"/>
       <c r="I629" s="2"/>
     </row>
     <row r="630" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C630" s="2"/>
-      <c r="D630" s="2"/>
-      <c r="E630" s="2"/>
+      <c r="C630" s="6"/>
+      <c r="D630" s="7"/>
+      <c r="E630" s="7"/>
       <c r="I630" s="2"/>
     </row>
     <row r="631" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C631" s="2"/>
-      <c r="D631" s="2"/>
-      <c r="E631" s="2"/>
+      <c r="C631" s="6"/>
+      <c r="D631" s="7"/>
+      <c r="E631" s="7"/>
       <c r="I631" s="2"/>
     </row>
     <row r="632" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C632" s="2"/>
-      <c r="D632" s="2"/>
-      <c r="E632" s="2"/>
+      <c r="C632" s="6"/>
+      <c r="D632" s="7"/>
+      <c r="E632" s="7"/>
       <c r="I632" s="2"/>
     </row>
     <row r="633" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C633" s="2"/>
-      <c r="D633" s="2"/>
-      <c r="E633" s="2"/>
+      <c r="C633" s="6"/>
+      <c r="D633" s="7"/>
+      <c r="E633" s="7"/>
       <c r="I633" s="2"/>
     </row>
     <row r="634" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C634" s="2"/>
-      <c r="D634" s="2"/>
-      <c r="E634" s="2"/>
+      <c r="C634" s="6"/>
+      <c r="D634" s="7"/>
+      <c r="E634" s="7"/>
       <c r="I634" s="2"/>
     </row>
     <row r="635" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C635" s="2"/>
-      <c r="D635" s="2"/>
-      <c r="E635" s="2"/>
+      <c r="C635" s="6"/>
+      <c r="D635" s="7"/>
+      <c r="E635" s="7"/>
       <c r="I635" s="2"/>
     </row>
     <row r="636" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C636" s="2"/>
-      <c r="D636" s="2"/>
-      <c r="E636" s="2"/>
+      <c r="C636" s="6"/>
+      <c r="D636" s="7"/>
+      <c r="E636" s="7"/>
       <c r="I636" s="2"/>
     </row>
     <row r="637" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C637" s="2"/>
-      <c r="D637" s="2"/>
-      <c r="E637" s="2"/>
+      <c r="C637" s="6"/>
+      <c r="D637" s="7"/>
+      <c r="E637" s="7"/>
       <c r="I637" s="2"/>
     </row>
     <row r="638" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C638" s="2"/>
-      <c r="D638" s="2"/>
-      <c r="E638" s="2"/>
+      <c r="C638" s="6"/>
+      <c r="D638" s="7"/>
+      <c r="E638" s="7"/>
       <c r="I638" s="2"/>
     </row>
     <row r="639" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C639" s="2"/>
-      <c r="D639" s="2"/>
-      <c r="E639" s="2"/>
+      <c r="C639" s="6"/>
+      <c r="D639" s="7"/>
+      <c r="E639" s="7"/>
       <c r="I639" s="2"/>
     </row>
     <row r="640" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C640" s="2"/>
-      <c r="D640" s="2"/>
-      <c r="E640" s="2"/>
+      <c r="C640" s="6"/>
+      <c r="D640" s="7"/>
+      <c r="E640" s="7"/>
       <c r="I640" s="2"/>
     </row>
     <row r="641" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C641" s="2"/>
-      <c r="D641" s="2"/>
-      <c r="E641" s="2"/>
+      <c r="C641" s="6"/>
+      <c r="D641" s="7"/>
+      <c r="E641" s="7"/>
       <c r="I641" s="2"/>
     </row>
     <row r="642" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C642" s="2"/>
-      <c r="D642" s="2"/>
-      <c r="E642" s="2"/>
+      <c r="C642" s="6"/>
+      <c r="D642" s="7"/>
+      <c r="E642" s="7"/>
       <c r="I642" s="2"/>
     </row>
     <row r="643" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C643" s="2"/>
-      <c r="D643" s="2"/>
-      <c r="E643" s="2"/>
+      <c r="C643" s="6"/>
+      <c r="D643" s="7"/>
+      <c r="E643" s="7"/>
       <c r="I643" s="2"/>
     </row>
     <row r="644" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C644" s="2"/>
-      <c r="D644" s="2"/>
-      <c r="E644" s="2"/>
+      <c r="C644" s="6"/>
+      <c r="D644" s="7"/>
+      <c r="E644" s="7"/>
       <c r="I644" s="2"/>
     </row>
     <row r="645" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C645" s="2"/>
-      <c r="D645" s="2"/>
-      <c r="E645" s="2"/>
+      <c r="C645" s="6"/>
+      <c r="D645" s="7"/>
+      <c r="E645" s="7"/>
       <c r="I645" s="2"/>
     </row>
     <row r="646" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C646" s="2"/>
-      <c r="D646" s="2"/>
-      <c r="E646" s="2"/>
+      <c r="C646" s="6"/>
+      <c r="D646" s="7"/>
+      <c r="E646" s="7"/>
       <c r="I646" s="2"/>
     </row>
     <row r="647" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C647" s="2"/>
-      <c r="D647" s="2"/>
-      <c r="E647" s="2"/>
+      <c r="C647" s="6"/>
+      <c r="D647" s="7"/>
+      <c r="E647" s="7"/>
       <c r="I647" s="2"/>
     </row>
     <row r="648" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C648" s="2"/>
-      <c r="D648" s="2"/>
-      <c r="E648" s="2"/>
+      <c r="C648" s="6"/>
+      <c r="D648" s="7"/>
+      <c r="E648" s="7"/>
       <c r="I648" s="2"/>
     </row>
     <row r="649" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C649" s="2"/>
-      <c r="D649" s="2"/>
-      <c r="E649" s="2"/>
+      <c r="C649" s="6"/>
+      <c r="D649" s="7"/>
+      <c r="E649" s="7"/>
       <c r="I649" s="2"/>
     </row>
     <row r="650" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C650" s="2"/>
-      <c r="D650" s="2"/>
-      <c r="E650" s="2"/>
+      <c r="C650" s="6"/>
+      <c r="D650" s="7"/>
+      <c r="E650" s="7"/>
       <c r="I650" s="2"/>
     </row>
     <row r="651" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C651" s="2"/>
-      <c r="D651" s="2"/>
-      <c r="E651" s="2"/>
+      <c r="C651" s="6"/>
+      <c r="D651" s="7"/>
+      <c r="E651" s="7"/>
       <c r="I651" s="2"/>
     </row>
     <row r="652" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C652" s="2"/>
-      <c r="D652" s="2"/>
-      <c r="E652" s="2"/>
+      <c r="C652" s="6"/>
+      <c r="D652" s="7"/>
+      <c r="E652" s="7"/>
       <c r="I652" s="2"/>
     </row>
     <row r="653" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C653" s="2"/>
-      <c r="D653" s="2"/>
-      <c r="E653" s="2"/>
+      <c r="C653" s="6"/>
+      <c r="D653" s="7"/>
+      <c r="E653" s="7"/>
       <c r="I653" s="2"/>
     </row>
     <row r="654" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C654" s="2"/>
-      <c r="D654" s="2"/>
-      <c r="E654" s="2"/>
+      <c r="C654" s="6"/>
+      <c r="D654" s="7"/>
+      <c r="E654" s="7"/>
       <c r="I654" s="2"/>
     </row>
     <row r="655" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C655" s="2"/>
-      <c r="D655" s="2"/>
-      <c r="E655" s="2"/>
+      <c r="C655" s="6"/>
+      <c r="D655" s="7"/>
+      <c r="E655" s="7"/>
       <c r="I655" s="2"/>
     </row>
     <row r="656" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C656" s="2"/>
-      <c r="D656" s="2"/>
-      <c r="E656" s="2"/>
+      <c r="C656" s="6"/>
+      <c r="D656" s="7"/>
+      <c r="E656" s="7"/>
       <c r="I656" s="2"/>
     </row>
     <row r="657" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C657" s="2"/>
-      <c r="D657" s="2"/>
-      <c r="E657" s="2"/>
+      <c r="C657" s="6"/>
+      <c r="D657" s="7"/>
+      <c r="E657" s="7"/>
       <c r="I657" s="2"/>
     </row>
     <row r="658" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C658" s="2"/>
-      <c r="D658" s="2"/>
-      <c r="E658" s="2"/>
+      <c r="C658" s="6"/>
+      <c r="D658" s="7"/>
+      <c r="E658" s="7"/>
       <c r="I658" s="2"/>
     </row>
     <row r="659" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C659" s="2"/>
-      <c r="D659" s="2"/>
-      <c r="E659" s="2"/>
+      <c r="C659" s="6"/>
+      <c r="D659" s="7"/>
+      <c r="E659" s="7"/>
       <c r="I659" s="2"/>
     </row>
     <row r="660" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C660" s="2"/>
-      <c r="D660" s="2"/>
-      <c r="E660" s="2"/>
+      <c r="C660" s="6"/>
+      <c r="D660" s="7"/>
+      <c r="E660" s="7"/>
       <c r="I660" s="2"/>
     </row>
     <row r="661" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C661" s="2"/>
-      <c r="D661" s="2"/>
-      <c r="E661" s="2"/>
+      <c r="C661" s="6"/>
+      <c r="D661" s="7"/>
+      <c r="E661" s="7"/>
       <c r="I661" s="2"/>
     </row>
     <row r="662" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C662" s="2"/>
-      <c r="D662" s="2"/>
-      <c r="E662" s="2"/>
+      <c r="C662" s="6"/>
+      <c r="D662" s="7"/>
+      <c r="E662" s="7"/>
       <c r="I662" s="2"/>
     </row>
     <row r="663" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C663" s="2"/>
-      <c r="D663" s="2"/>
-      <c r="E663" s="2"/>
+      <c r="C663" s="6"/>
+      <c r="D663" s="7"/>
+      <c r="E663" s="7"/>
       <c r="I663" s="2"/>
     </row>
     <row r="664" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C664" s="2"/>
-      <c r="D664" s="2"/>
-      <c r="E664" s="2"/>
+      <c r="C664" s="6"/>
+      <c r="D664" s="7"/>
+      <c r="E664" s="7"/>
       <c r="I664" s="2"/>
     </row>
     <row r="665" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C665" s="2"/>
-      <c r="D665" s="2"/>
-      <c r="E665" s="2"/>
+      <c r="C665" s="6"/>
+      <c r="D665" s="7"/>
+      <c r="E665" s="7"/>
       <c r="I665" s="2"/>
     </row>
     <row r="666" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C666" s="2"/>
-      <c r="D666" s="2"/>
-      <c r="E666" s="2"/>
+      <c r="C666" s="6"/>
+      <c r="D666" s="7"/>
+      <c r="E666" s="7"/>
       <c r="I666" s="2"/>
     </row>
     <row r="667" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C667" s="2"/>
-      <c r="D667" s="2"/>
-      <c r="E667" s="2"/>
+      <c r="C667" s="6"/>
+      <c r="D667" s="7"/>
+      <c r="E667" s="7"/>
       <c r="I667" s="2"/>
     </row>
     <row r="668" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C668" s="2"/>
-      <c r="D668" s="2"/>
-      <c r="E668" s="2"/>
+      <c r="C668" s="6"/>
+      <c r="D668" s="7"/>
+      <c r="E668" s="7"/>
       <c r="I668" s="2"/>
     </row>
     <row r="669" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C669" s="2"/>
-      <c r="D669" s="2"/>
-      <c r="E669" s="2"/>
+      <c r="C669" s="6"/>
+      <c r="D669" s="7"/>
+      <c r="E669" s="7"/>
       <c r="I669" s="2"/>
     </row>
     <row r="670" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C670" s="2"/>
-      <c r="D670" s="2"/>
-      <c r="E670" s="2"/>
+      <c r="C670" s="6"/>
+      <c r="D670" s="7"/>
+      <c r="E670" s="7"/>
       <c r="I670" s="2"/>
     </row>
     <row r="671" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C671" s="2"/>
-      <c r="D671" s="2"/>
-      <c r="E671" s="2"/>
+      <c r="C671" s="6"/>
+      <c r="D671" s="7"/>
+      <c r="E671" s="7"/>
       <c r="I671" s="2"/>
     </row>
     <row r="672" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C672" s="2"/>
-      <c r="D672" s="2"/>
-      <c r="E672" s="2"/>
+      <c r="C672" s="6"/>
+      <c r="D672" s="7"/>
+      <c r="E672" s="7"/>
       <c r="I672" s="2"/>
     </row>
     <row r="673" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C673" s="2"/>
-      <c r="D673" s="2"/>
-      <c r="E673" s="2"/>
+      <c r="C673" s="6"/>
+      <c r="D673" s="7"/>
+      <c r="E673" s="7"/>
       <c r="I673" s="2"/>
     </row>
     <row r="674" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C674" s="2"/>
-      <c r="D674" s="2"/>
-      <c r="E674" s="2"/>
+      <c r="C674" s="6"/>
+      <c r="D674" s="7"/>
+      <c r="E674" s="7"/>
       <c r="I674" s="2"/>
     </row>
     <row r="675" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C675" s="2"/>
-      <c r="D675" s="2"/>
-      <c r="E675" s="2"/>
+      <c r="C675" s="6"/>
+      <c r="D675" s="7"/>
+      <c r="E675" s="7"/>
       <c r="I675" s="2"/>
     </row>
     <row r="676" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C676" s="2"/>
-      <c r="D676" s="2"/>
-      <c r="E676" s="2"/>
+      <c r="C676" s="6"/>
+      <c r="D676" s="7"/>
+      <c r="E676" s="7"/>
       <c r="I676" s="2"/>
     </row>
     <row r="677" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C677" s="2"/>
-      <c r="D677" s="2"/>
-      <c r="E677" s="2"/>
+      <c r="C677" s="6"/>
+      <c r="D677" s="7"/>
+      <c r="E677" s="7"/>
       <c r="I677" s="2"/>
     </row>
     <row r="678" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C678" s="2"/>
-      <c r="D678" s="2"/>
-      <c r="E678" s="2"/>
+      <c r="C678" s="6"/>
+      <c r="D678" s="7"/>
+      <c r="E678" s="7"/>
       <c r="I678" s="2"/>
     </row>
     <row r="679" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C679" s="2"/>
-      <c r="D679" s="2"/>
-      <c r="E679" s="2"/>
+      <c r="C679" s="6"/>
+      <c r="D679" s="7"/>
+      <c r="E679" s="7"/>
       <c r="I679" s="2"/>
     </row>
     <row r="680" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C680" s="2"/>
-      <c r="D680" s="2"/>
-      <c r="E680" s="2"/>
+      <c r="C680" s="6"/>
+      <c r="D680" s="7"/>
+      <c r="E680" s="7"/>
       <c r="I680" s="2"/>
     </row>
     <row r="681" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C681" s="2"/>
-      <c r="D681" s="2"/>
-      <c r="E681" s="2"/>
+      <c r="C681" s="6"/>
+      <c r="D681" s="7"/>
+      <c r="E681" s="7"/>
       <c r="I681" s="2"/>
     </row>
     <row r="682" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C682" s="2"/>
-      <c r="D682" s="2"/>
-      <c r="E682" s="2"/>
+      <c r="C682" s="6"/>
+      <c r="D682" s="7"/>
+      <c r="E682" s="7"/>
       <c r="I682" s="2"/>
     </row>
     <row r="683" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C683" s="2"/>
-      <c r="D683" s="2"/>
-      <c r="E683" s="2"/>
+      <c r="C683" s="6"/>
+      <c r="D683" s="7"/>
+      <c r="E683" s="7"/>
       <c r="I683" s="2"/>
     </row>
     <row r="684" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C684" s="2"/>
-      <c r="D684" s="2"/>
-      <c r="E684" s="2"/>
+      <c r="C684" s="6"/>
+      <c r="D684" s="7"/>
+      <c r="E684" s="7"/>
       <c r="I684" s="2"/>
     </row>
     <row r="685" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C685" s="2"/>
-      <c r="D685" s="2"/>
-      <c r="E685" s="2"/>
+      <c r="C685" s="6"/>
+      <c r="D685" s="7"/>
+      <c r="E685" s="7"/>
       <c r="I685" s="2"/>
     </row>
     <row r="686" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C686" s="2"/>
-      <c r="D686" s="2"/>
-      <c r="E686" s="2"/>
+      <c r="C686" s="6"/>
+      <c r="D686" s="7"/>
+      <c r="E686" s="7"/>
       <c r="I686" s="2"/>
     </row>
     <row r="687" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C687" s="2"/>
-      <c r="D687" s="2"/>
-      <c r="E687" s="2"/>
+      <c r="C687" s="6"/>
+      <c r="D687" s="7"/>
+      <c r="E687" s="7"/>
       <c r="I687" s="2"/>
     </row>
     <row r="688" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C688" s="2"/>
-      <c r="D688" s="2"/>
-      <c r="E688" s="2"/>
+      <c r="C688" s="6"/>
+      <c r="D688" s="7"/>
+      <c r="E688" s="7"/>
       <c r="I688" s="2"/>
     </row>
     <row r="689" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C689" s="2"/>
-      <c r="D689" s="2"/>
-      <c r="E689" s="2"/>
+      <c r="C689" s="6"/>
+      <c r="D689" s="7"/>
+      <c r="E689" s="7"/>
       <c r="I689" s="2"/>
     </row>
     <row r="690" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C690" s="2"/>
-      <c r="D690" s="2"/>
-      <c r="E690" s="2"/>
+      <c r="C690" s="6"/>
+      <c r="D690" s="7"/>
+      <c r="E690" s="7"/>
       <c r="I690" s="2"/>
     </row>
     <row r="691" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C691" s="2"/>
-      <c r="D691" s="2"/>
-      <c r="E691" s="2"/>
+      <c r="C691" s="6"/>
+      <c r="D691" s="7"/>
+      <c r="E691" s="7"/>
       <c r="I691" s="2"/>
     </row>
     <row r="692" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C692" s="2"/>
-      <c r="D692" s="2"/>
-      <c r="E692" s="2"/>
+      <c r="C692" s="6"/>
+      <c r="D692" s="7"/>
+      <c r="E692" s="7"/>
       <c r="I692" s="2"/>
     </row>
     <row r="693" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C693" s="2"/>
-      <c r="D693" s="2"/>
-      <c r="E693" s="2"/>
+      <c r="C693" s="6"/>
+      <c r="D693" s="7"/>
+      <c r="E693" s="7"/>
       <c r="I693" s="2"/>
     </row>
     <row r="694" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C694" s="2"/>
-      <c r="D694" s="2"/>
-      <c r="E694" s="2"/>
+      <c r="C694" s="6"/>
+      <c r="D694" s="7"/>
+      <c r="E694" s="7"/>
       <c r="I694" s="2"/>
     </row>
     <row r="695" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C695" s="2"/>
-      <c r="D695" s="2"/>
-      <c r="E695" s="2"/>
+      <c r="C695" s="6"/>
+      <c r="D695" s="7"/>
+      <c r="E695" s="7"/>
       <c r="I695" s="2"/>
     </row>
     <row r="696" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C696" s="2"/>
-      <c r="D696" s="2"/>
-      <c r="E696" s="2"/>
+      <c r="C696" s="6"/>
+      <c r="D696" s="7"/>
+      <c r="E696" s="7"/>
       <c r="I696" s="2"/>
     </row>
     <row r="697" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C697" s="2"/>
-      <c r="D697" s="2"/>
-      <c r="E697" s="2"/>
+      <c r="C697" s="6"/>
+      <c r="D697" s="7"/>
+      <c r="E697" s="7"/>
       <c r="I697" s="2"/>
     </row>
     <row r="698" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C698" s="2"/>
-      <c r="D698" s="2"/>
-      <c r="E698" s="2"/>
+      <c r="C698" s="6"/>
+      <c r="D698" s="7"/>
+      <c r="E698" s="7"/>
       <c r="I698" s="2"/>
     </row>
     <row r="699" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C699" s="2"/>
-      <c r="D699" s="2"/>
-      <c r="E699" s="2"/>
+      <c r="C699" s="6"/>
+      <c r="D699" s="7"/>
+      <c r="E699" s="7"/>
       <c r="I699" s="2"/>
     </row>
     <row r="700" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C700" s="2"/>
-      <c r="D700" s="2"/>
-      <c r="E700" s="2"/>
+      <c r="C700" s="6"/>
+      <c r="D700" s="7"/>
+      <c r="E700" s="7"/>
       <c r="I700" s="2"/>
     </row>
     <row r="701" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C701" s="2"/>
-      <c r="D701" s="2"/>
-      <c r="E701" s="2"/>
+      <c r="C701" s="6"/>
+      <c r="D701" s="7"/>
+      <c r="E701" s="7"/>
       <c r="I701" s="2"/>
     </row>
     <row r="702" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C702" s="2"/>
-      <c r="D702" s="2"/>
-      <c r="E702" s="2"/>
+      <c r="C702" s="6"/>
+      <c r="D702" s="7"/>
+      <c r="E702" s="7"/>
       <c r="I702" s="2"/>
     </row>
     <row r="703" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C703" s="2"/>
-      <c r="D703" s="2"/>
-      <c r="E703" s="2"/>
+      <c r="C703" s="6"/>
+      <c r="D703" s="7"/>
+      <c r="E703" s="7"/>
       <c r="I703" s="2"/>
     </row>
     <row r="704" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C704" s="2"/>
-      <c r="D704" s="2"/>
-      <c r="E704" s="2"/>
+      <c r="C704" s="6"/>
+      <c r="D704" s="7"/>
+      <c r="E704" s="7"/>
       <c r="I704" s="2"/>
     </row>
     <row r="705" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C705" s="2"/>
-      <c r="D705" s="2"/>
-      <c r="E705" s="2"/>
+      <c r="C705" s="6"/>
+      <c r="D705" s="7"/>
+      <c r="E705" s="7"/>
       <c r="I705" s="2"/>
     </row>
     <row r="706" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C706" s="2"/>
-      <c r="D706" s="2"/>
-      <c r="E706" s="2"/>
+      <c r="C706" s="6"/>
+      <c r="D706" s="7"/>
+      <c r="E706" s="7"/>
       <c r="I706" s="2"/>
     </row>
     <row r="707" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C707" s="2"/>
-      <c r="D707" s="2"/>
-      <c r="E707" s="2"/>
+      <c r="C707" s="6"/>
+      <c r="D707" s="7"/>
+      <c r="E707" s="7"/>
       <c r="I707" s="2"/>
     </row>
     <row r="708" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C708" s="2"/>
-      <c r="D708" s="2"/>
-      <c r="E708" s="2"/>
+      <c r="C708" s="6"/>
+      <c r="D708" s="7"/>
+      <c r="E708" s="7"/>
       <c r="I708" s="2"/>
     </row>
     <row r="709" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C709" s="2"/>
-      <c r="D709" s="2"/>
-      <c r="E709" s="2"/>
+      <c r="C709" s="6"/>
+      <c r="D709" s="7"/>
+      <c r="E709" s="7"/>
       <c r="I709" s="2"/>
     </row>
     <row r="710" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C710" s="2"/>
-      <c r="D710" s="2"/>
-      <c r="E710" s="2"/>
+      <c r="C710" s="6"/>
+      <c r="D710" s="7"/>
+      <c r="E710" s="7"/>
       <c r="I710" s="2"/>
     </row>
     <row r="711" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C711" s="2"/>
-      <c r="D711" s="2"/>
-      <c r="E711" s="2"/>
+      <c r="C711" s="6"/>
+      <c r="D711" s="7"/>
+      <c r="E711" s="7"/>
       <c r="I711" s="2"/>
     </row>
     <row r="712" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C712" s="2"/>
-      <c r="D712" s="2"/>
-      <c r="E712" s="2"/>
+      <c r="C712" s="6"/>
+      <c r="D712" s="7"/>
+      <c r="E712" s="7"/>
       <c r="I712" s="2"/>
     </row>
     <row r="713" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C713" s="2"/>
-      <c r="D713" s="2"/>
-      <c r="E713" s="2"/>
+      <c r="C713" s="6"/>
+      <c r="D713" s="7"/>
+      <c r="E713" s="7"/>
       <c r="I713" s="2"/>
     </row>
     <row r="714" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C714" s="2"/>
-      <c r="D714" s="2"/>
-      <c r="E714" s="2"/>
+      <c r="C714" s="6"/>
+      <c r="D714" s="7"/>
+      <c r="E714" s="7"/>
       <c r="I714" s="2"/>
     </row>
     <row r="715" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C715" s="2"/>
-      <c r="D715" s="2"/>
-      <c r="E715" s="2"/>
+      <c r="C715" s="6"/>
+      <c r="D715" s="7"/>
+      <c r="E715" s="7"/>
       <c r="I715" s="2"/>
     </row>
     <row r="716" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C716" s="2"/>
-      <c r="D716" s="2"/>
-      <c r="E716" s="2"/>
+      <c r="C716" s="6"/>
+      <c r="D716" s="7"/>
+      <c r="E716" s="7"/>
       <c r="I716" s="2"/>
     </row>
     <row r="717" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C717" s="2"/>
-      <c r="D717" s="2"/>
-      <c r="E717" s="2"/>
+      <c r="C717" s="6"/>
+      <c r="D717" s="7"/>
+      <c r="E717" s="7"/>
       <c r="I717" s="2"/>
     </row>
     <row r="718" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C718" s="2"/>
-      <c r="D718" s="2"/>
-      <c r="E718" s="2"/>
+      <c r="C718" s="6"/>
+      <c r="D718" s="7"/>
+      <c r="E718" s="7"/>
       <c r="I718" s="2"/>
     </row>
     <row r="719" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C719" s="2"/>
-      <c r="D719" s="2"/>
-      <c r="E719" s="2"/>
+      <c r="C719" s="6"/>
+      <c r="D719" s="7"/>
+      <c r="E719" s="7"/>
       <c r="I719" s="2"/>
     </row>
     <row r="720" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C720" s="2"/>
-      <c r="D720" s="2"/>
-      <c r="E720" s="2"/>
+      <c r="C720" s="6"/>
+      <c r="D720" s="7"/>
+      <c r="E720" s="7"/>
       <c r="I720" s="2"/>
     </row>
     <row r="721" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C721" s="2"/>
-      <c r="D721" s="2"/>
-      <c r="E721" s="2"/>
+      <c r="C721" s="6"/>
+      <c r="D721" s="7"/>
+      <c r="E721" s="7"/>
       <c r="I721" s="2"/>
     </row>
     <row r="722" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C722" s="2"/>
-      <c r="D722" s="2"/>
-      <c r="E722" s="2"/>
+      <c r="C722" s="6"/>
+      <c r="D722" s="7"/>
+      <c r="E722" s="7"/>
       <c r="I722" s="2"/>
     </row>
     <row r="723" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C723" s="2"/>
-      <c r="D723" s="2"/>
-      <c r="E723" s="2"/>
+      <c r="C723" s="6"/>
+      <c r="D723" s="7"/>
+      <c r="E723" s="7"/>
       <c r="I723" s="2"/>
     </row>
     <row r="724" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C724" s="2"/>
-      <c r="D724" s="2"/>
-      <c r="E724" s="2"/>
+      <c r="C724" s="6"/>
+      <c r="D724" s="7"/>
+      <c r="E724" s="7"/>
       <c r="I724" s="2"/>
     </row>
     <row r="725" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C725" s="2"/>
-      <c r="D725" s="2"/>
-      <c r="E725" s="2"/>
+      <c r="C725" s="6"/>
+      <c r="D725" s="7"/>
+      <c r="E725" s="7"/>
       <c r="I725" s="2"/>
     </row>
     <row r="726" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C726" s="2"/>
-      <c r="D726" s="2"/>
-      <c r="E726" s="2"/>
+      <c r="C726" s="6"/>
+      <c r="D726" s="7"/>
+      <c r="E726" s="7"/>
       <c r="I726" s="2"/>
     </row>
     <row r="727" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C727" s="2"/>
-      <c r="D727" s="2"/>
-      <c r="E727" s="2"/>
+      <c r="C727" s="6"/>
+      <c r="D727" s="7"/>
+      <c r="E727" s="7"/>
       <c r="I727" s="2"/>
     </row>
     <row r="728" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C728" s="2"/>
-      <c r="D728" s="2"/>
-      <c r="E728" s="2"/>
+      <c r="C728" s="6"/>
+      <c r="D728" s="7"/>
+      <c r="E728" s="7"/>
       <c r="I728" s="2"/>
     </row>
     <row r="729" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C729" s="2"/>
-      <c r="D729" s="2"/>
-      <c r="E729" s="2"/>
+      <c r="C729" s="6"/>
+      <c r="D729" s="7"/>
+      <c r="E729" s="7"/>
       <c r="I729" s="2"/>
     </row>
     <row r="730" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C730" s="2"/>
-      <c r="D730" s="2"/>
-      <c r="E730" s="2"/>
+      <c r="C730" s="6"/>
+      <c r="D730" s="7"/>
+      <c r="E730" s="7"/>
       <c r="I730" s="2"/>
     </row>
     <row r="731" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C731" s="2"/>
-      <c r="D731" s="2"/>
-      <c r="E731" s="2"/>
+      <c r="C731" s="6"/>
+      <c r="D731" s="7"/>
+      <c r="E731" s="7"/>
       <c r="I731" s="2"/>
     </row>
     <row r="732" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C732" s="2"/>
-      <c r="D732" s="2"/>
-      <c r="E732" s="2"/>
+      <c r="C732" s="6"/>
+      <c r="D732" s="7"/>
+      <c r="E732" s="7"/>
       <c r="I732" s="2"/>
     </row>
     <row r="733" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C733" s="2"/>
-      <c r="D733" s="2"/>
-      <c r="E733" s="2"/>
+      <c r="C733" s="6"/>
+      <c r="D733" s="7"/>
+      <c r="E733" s="7"/>
       <c r="I733" s="2"/>
     </row>
     <row r="734" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C734" s="2"/>
-      <c r="D734" s="2"/>
-      <c r="E734" s="2"/>
+      <c r="C734" s="6"/>
+      <c r="D734" s="7"/>
+      <c r="E734" s="7"/>
       <c r="I734" s="2"/>
     </row>
     <row r="735" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C735" s="2"/>
-      <c r="D735" s="2"/>
-      <c r="E735" s="2"/>
+      <c r="C735" s="6"/>
+      <c r="D735" s="7"/>
+      <c r="E735" s="7"/>
       <c r="I735" s="2"/>
     </row>
     <row r="736" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C736" s="2"/>
-      <c r="D736" s="2"/>
-      <c r="E736" s="2"/>
+      <c r="C736" s="6"/>
+      <c r="D736" s="7"/>
+      <c r="E736" s="7"/>
       <c r="I736" s="2"/>
     </row>
     <row r="737" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C737" s="2"/>
-      <c r="D737" s="2"/>
-      <c r="E737" s="2"/>
+      <c r="C737" s="6"/>
+      <c r="D737" s="7"/>
+      <c r="E737" s="7"/>
       <c r="I737" s="2"/>
     </row>
     <row r="738" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C738" s="2"/>
-      <c r="D738" s="2"/>
-      <c r="E738" s="2"/>
+      <c r="C738" s="6"/>
+      <c r="D738" s="7"/>
+      <c r="E738" s="7"/>
       <c r="I738" s="2"/>
     </row>
     <row r="739" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C739" s="2"/>
-      <c r="D739" s="2"/>
-      <c r="E739" s="2"/>
+      <c r="C739" s="6"/>
+      <c r="D739" s="7"/>
+      <c r="E739" s="7"/>
       <c r="I739" s="2"/>
     </row>
     <row r="740" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C740" s="2"/>
-      <c r="D740" s="2"/>
-      <c r="E740" s="2"/>
+      <c r="C740" s="6"/>
+      <c r="D740" s="7"/>
+      <c r="E740" s="7"/>
       <c r="I740" s="2"/>
     </row>
     <row r="741" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C741" s="2"/>
-      <c r="D741" s="2"/>
-      <c r="E741" s="2"/>
+      <c r="C741" s="6"/>
+      <c r="D741" s="7"/>
+      <c r="E741" s="7"/>
       <c r="I741" s="2"/>
     </row>
     <row r="742" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C742" s="2"/>
-      <c r="D742" s="2"/>
-      <c r="E742" s="2"/>
+      <c r="C742" s="6"/>
+      <c r="D742" s="7"/>
+      <c r="E742" s="7"/>
       <c r="I742" s="2"/>
     </row>
     <row r="743" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C743" s="2"/>
-      <c r="D743" s="2"/>
-      <c r="E743" s="2"/>
+      <c r="C743" s="6"/>
+      <c r="D743" s="7"/>
+      <c r="E743" s="7"/>
       <c r="I743" s="2"/>
     </row>
     <row r="744" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C744" s="2"/>
-      <c r="D744" s="2"/>
-      <c r="E744" s="2"/>
+      <c r="C744" s="6"/>
+      <c r="D744" s="7"/>
+      <c r="E744" s="7"/>
       <c r="I744" s="2"/>
     </row>
     <row r="745" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C745" s="2"/>
-      <c r="D745" s="2"/>
-      <c r="E745" s="2"/>
+      <c r="C745" s="6"/>
+      <c r="D745" s="7"/>
+      <c r="E745" s="7"/>
       <c r="I745" s="2"/>
     </row>
     <row r="746" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C746" s="2"/>
-      <c r="D746" s="2"/>
-      <c r="E746" s="2"/>
+      <c r="C746" s="6"/>
+      <c r="D746" s="7"/>
+      <c r="E746" s="7"/>
       <c r="I746" s="2"/>
     </row>
     <row r="747" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C747" s="2"/>
-      <c r="D747" s="2"/>
-      <c r="E747" s="2"/>
+      <c r="C747" s="6"/>
+      <c r="D747" s="7"/>
+      <c r="E747" s="7"/>
       <c r="I747" s="2"/>
     </row>
     <row r="748" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C748" s="2"/>
-      <c r="D748" s="2"/>
-      <c r="E748" s="2"/>
+      <c r="C748" s="6"/>
+      <c r="D748" s="7"/>
+      <c r="E748" s="7"/>
       <c r="I748" s="2"/>
     </row>
     <row r="749" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C749" s="2"/>
-      <c r="D749" s="2"/>
-      <c r="E749" s="2"/>
+      <c r="C749" s="6"/>
+      <c r="D749" s="7"/>
+      <c r="E749" s="7"/>
       <c r="I749" s="2"/>
     </row>
     <row r="750" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C750" s="2"/>
-      <c r="D750" s="2"/>
-      <c r="E750" s="2"/>
+      <c r="C750" s="6"/>
+      <c r="D750" s="7"/>
+      <c r="E750" s="7"/>
       <c r="I750" s="2"/>
     </row>
     <row r="751" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C751" s="2"/>
-      <c r="D751" s="2"/>
-      <c r="E751" s="2"/>
+      <c r="C751" s="6"/>
+      <c r="D751" s="7"/>
+      <c r="E751" s="7"/>
       <c r="I751" s="2"/>
     </row>
     <row r="752" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C752" s="2"/>
-      <c r="D752" s="2"/>
-      <c r="E752" s="2"/>
+      <c r="C752" s="6"/>
+      <c r="D752" s="7"/>
+      <c r="E752" s="7"/>
       <c r="I752" s="2"/>
     </row>
     <row r="753" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C753" s="2"/>
-      <c r="D753" s="2"/>
-      <c r="E753" s="2"/>
+      <c r="C753" s="6"/>
+      <c r="D753" s="7"/>
+      <c r="E753" s="7"/>
       <c r="I753" s="2"/>
     </row>
     <row r="754" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C754" s="2"/>
-      <c r="D754" s="2"/>
-      <c r="E754" s="2"/>
+      <c r="C754" s="6"/>
+      <c r="D754" s="7"/>
+      <c r="E754" s="7"/>
       <c r="I754" s="2"/>
     </row>
     <row r="755" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C755" s="2"/>
-      <c r="D755" s="2"/>
-      <c r="E755" s="2"/>
+      <c r="C755" s="6"/>
+      <c r="D755" s="7"/>
+      <c r="E755" s="7"/>
       <c r="I755" s="2"/>
     </row>
     <row r="756" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C756" s="2"/>
-      <c r="D756" s="2"/>
-      <c r="E756" s="2"/>
+      <c r="C756" s="6"/>
+      <c r="D756" s="7"/>
+      <c r="E756" s="7"/>
       <c r="I756" s="2"/>
     </row>
     <row r="757" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C757" s="2"/>
-      <c r="D757" s="2"/>
-      <c r="E757" s="2"/>
+      <c r="C757" s="6"/>
+      <c r="D757" s="7"/>
+      <c r="E757" s="7"/>
       <c r="I757" s="2"/>
     </row>
     <row r="758" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C758" s="2"/>
-      <c r="D758" s="2"/>
-      <c r="E758" s="2"/>
+      <c r="C758" s="6"/>
+      <c r="D758" s="7"/>
+      <c r="E758" s="7"/>
       <c r="I758" s="2"/>
     </row>
     <row r="759" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C759" s="2"/>
-      <c r="D759" s="2"/>
-      <c r="E759" s="2"/>
+      <c r="C759" s="6"/>
+      <c r="D759" s="7"/>
+      <c r="E759" s="7"/>
       <c r="I759" s="2"/>
     </row>
     <row r="760" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C760" s="2"/>
-      <c r="D760" s="2"/>
-      <c r="E760" s="2"/>
+      <c r="C760" s="6"/>
+      <c r="D760" s="7"/>
+      <c r="E760" s="7"/>
       <c r="I760" s="2"/>
     </row>
     <row r="761" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C761" s="2"/>
-      <c r="D761" s="2"/>
-      <c r="E761" s="2"/>
+      <c r="C761" s="6"/>
+      <c r="D761" s="7"/>
+      <c r="E761" s="7"/>
       <c r="I761" s="2"/>
     </row>
     <row r="762" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C762" s="2"/>
-      <c r="D762" s="2"/>
-      <c r="E762" s="2"/>
+      <c r="C762" s="6"/>
+      <c r="D762" s="7"/>
+      <c r="E762" s="7"/>
       <c r="I762" s="2"/>
     </row>
     <row r="763" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C763" s="2"/>
-      <c r="D763" s="2"/>
-      <c r="E763" s="2"/>
+      <c r="C763" s="6"/>
+      <c r="D763" s="7"/>
+      <c r="E763" s="7"/>
       <c r="I763" s="2"/>
     </row>
     <row r="764" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C764" s="2"/>
-      <c r="D764" s="2"/>
-      <c r="E764" s="2"/>
+      <c r="C764" s="6"/>
+      <c r="D764" s="7"/>
+      <c r="E764" s="7"/>
       <c r="I764" s="2"/>
     </row>
     <row r="765" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C765" s="2"/>
-      <c r="D765" s="2"/>
-      <c r="E765" s="2"/>
+      <c r="C765" s="6"/>
+      <c r="D765" s="7"/>
+      <c r="E765" s="7"/>
       <c r="I765" s="2"/>
     </row>
     <row r="766" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C766" s="2"/>
-      <c r="D766" s="2"/>
-      <c r="E766" s="2"/>
+      <c r="C766" s="6"/>
+      <c r="D766" s="7"/>
+      <c r="E766" s="7"/>
       <c r="I766" s="2"/>
     </row>
     <row r="767" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C767" s="2"/>
-      <c r="D767" s="2"/>
-      <c r="E767" s="2"/>
+      <c r="C767" s="6"/>
+      <c r="D767" s="7"/>
+      <c r="E767" s="7"/>
       <c r="I767" s="2"/>
     </row>
     <row r="768" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C768" s="2"/>
-      <c r="D768" s="2"/>
-      <c r="E768" s="2"/>
+      <c r="C768" s="6"/>
+      <c r="D768" s="7"/>
+      <c r="E768" s="7"/>
       <c r="I768" s="2"/>
     </row>
     <row r="769" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C769" s="2"/>
-      <c r="D769" s="2"/>
-      <c r="E769" s="2"/>
+      <c r="C769" s="6"/>
+      <c r="D769" s="7"/>
+      <c r="E769" s="7"/>
       <c r="I769" s="2"/>
     </row>
     <row r="770" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C770" s="2"/>
-      <c r="D770" s="2"/>
-      <c r="E770" s="2"/>
+      <c r="C770" s="6"/>
+      <c r="D770" s="7"/>
+      <c r="E770" s="7"/>
       <c r="I770" s="2"/>
     </row>
     <row r="771" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C771" s="2"/>
-      <c r="D771" s="2"/>
-      <c r="E771" s="2"/>
+      <c r="C771" s="6"/>
+      <c r="D771" s="7"/>
+      <c r="E771" s="7"/>
       <c r="I771" s="2"/>
     </row>
     <row r="772" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C772" s="2"/>
-      <c r="D772" s="2"/>
-      <c r="E772" s="2"/>
+      <c r="C772" s="6"/>
+      <c r="D772" s="7"/>
+      <c r="E772" s="7"/>
       <c r="I772" s="2"/>
     </row>
     <row r="773" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C773" s="2"/>
-      <c r="D773" s="2"/>
-      <c r="E773" s="2"/>
+      <c r="C773" s="6"/>
+      <c r="D773" s="7"/>
+      <c r="E773" s="7"/>
       <c r="I773" s="2"/>
     </row>
     <row r="774" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C774" s="2"/>
-      <c r="D774" s="2"/>
-      <c r="E774" s="2"/>
+      <c r="C774" s="6"/>
+      <c r="D774" s="7"/>
+      <c r="E774" s="7"/>
       <c r="I774" s="2"/>
     </row>
     <row r="775" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C775" s="2"/>
-      <c r="D775" s="2"/>
-      <c r="E775" s="2"/>
+      <c r="C775" s="6"/>
+      <c r="D775" s="7"/>
+      <c r="E775" s="7"/>
       <c r="I775" s="2"/>
     </row>
     <row r="776" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C776" s="2"/>
-      <c r="D776" s="2"/>
-      <c r="E776" s="2"/>
+      <c r="C776" s="6"/>
+      <c r="D776" s="7"/>
+      <c r="E776" s="7"/>
       <c r="I776" s="2"/>
     </row>
     <row r="777" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C777" s="2"/>
-      <c r="D777" s="2"/>
-      <c r="E777" s="2"/>
+      <c r="C777" s="6"/>
+      <c r="D777" s="7"/>
+      <c r="E777" s="7"/>
       <c r="I777" s="2"/>
     </row>
     <row r="778" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C778" s="2"/>
-      <c r="D778" s="2"/>
-      <c r="E778" s="2"/>
+      <c r="C778" s="6"/>
+      <c r="D778" s="7"/>
+      <c r="E778" s="7"/>
       <c r="I778" s="2"/>
     </row>
     <row r="779" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C779" s="2"/>
-      <c r="D779" s="2"/>
-      <c r="E779" s="2"/>
+      <c r="C779" s="6"/>
+      <c r="D779" s="7"/>
+      <c r="E779" s="7"/>
       <c r="I779" s="2"/>
     </row>
     <row r="780" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C780" s="2"/>
-      <c r="D780" s="2"/>
-      <c r="E780" s="2"/>
+      <c r="C780" s="6"/>
+      <c r="D780" s="7"/>
+      <c r="E780" s="7"/>
       <c r="I780" s="2"/>
     </row>
     <row r="781" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C781" s="2"/>
-      <c r="D781" s="2"/>
-      <c r="E781" s="2"/>
+      <c r="C781" s="6"/>
+      <c r="D781" s="7"/>
+      <c r="E781" s="7"/>
       <c r="I781" s="2"/>
     </row>
     <row r="782" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C782" s="2"/>
-      <c r="D782" s="2"/>
-      <c r="E782" s="2"/>
+      <c r="C782" s="6"/>
+      <c r="D782" s="7"/>
+      <c r="E782" s="7"/>
       <c r="I782" s="2"/>
     </row>
     <row r="783" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C783" s="2"/>
-      <c r="D783" s="2"/>
-      <c r="E783" s="2"/>
+      <c r="C783" s="6"/>
+      <c r="D783" s="7"/>
+      <c r="E783" s="7"/>
       <c r="I783" s="2"/>
     </row>
     <row r="784" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C784" s="2"/>
-      <c r="D784" s="2"/>
-      <c r="E784" s="2"/>
+      <c r="C784" s="6"/>
+      <c r="D784" s="7"/>
+      <c r="E784" s="7"/>
       <c r="I784" s="2"/>
     </row>
     <row r="785" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C785" s="2"/>
-      <c r="D785" s="2"/>
-      <c r="E785" s="2"/>
+      <c r="C785" s="6"/>
+      <c r="D785" s="7"/>
+      <c r="E785" s="7"/>
       <c r="I785" s="2"/>
     </row>
     <row r="786" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C786" s="2"/>
-      <c r="D786" s="2"/>
-      <c r="E786" s="2"/>
+      <c r="C786" s="6"/>
+      <c r="D786" s="7"/>
+      <c r="E786" s="7"/>
       <c r="I786" s="2"/>
     </row>
     <row r="787" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C787" s="2"/>
-      <c r="D787" s="2"/>
-      <c r="E787" s="2"/>
+      <c r="C787" s="6"/>
+      <c r="D787" s="7"/>
+      <c r="E787" s="7"/>
       <c r="I787" s="2"/>
     </row>
     <row r="788" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C788" s="2"/>
-      <c r="D788" s="2"/>
-      <c r="E788" s="2"/>
+      <c r="C788" s="6"/>
+      <c r="D788" s="7"/>
+      <c r="E788" s="7"/>
       <c r="I788" s="2"/>
     </row>
     <row r="789" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C789" s="2"/>
-      <c r="D789" s="2"/>
-      <c r="E789" s="2"/>
+      <c r="C789" s="6"/>
+      <c r="D789" s="7"/>
+      <c r="E789" s="7"/>
       <c r="I789" s="2"/>
     </row>
     <row r="790" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C790" s="2"/>
-      <c r="D790" s="2"/>
-      <c r="E790" s="2"/>
+      <c r="C790" s="6"/>
+      <c r="D790" s="7"/>
+      <c r="E790" s="7"/>
       <c r="I790" s="2"/>
     </row>
     <row r="791" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C791" s="2"/>
-      <c r="D791" s="2"/>
-      <c r="E791" s="2"/>
+      <c r="C791" s="6"/>
+      <c r="D791" s="7"/>
+      <c r="E791" s="7"/>
       <c r="I791" s="2"/>
     </row>
     <row r="792" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C792" s="2"/>
-      <c r="D792" s="2"/>
-      <c r="E792" s="2"/>
+      <c r="C792" s="6"/>
+      <c r="D792" s="7"/>
+      <c r="E792" s="7"/>
       <c r="I792" s="2"/>
     </row>
     <row r="793" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C793" s="2"/>
-      <c r="D793" s="2"/>
-      <c r="E793" s="2"/>
+      <c r="C793" s="6"/>
+      <c r="D793" s="7"/>
+      <c r="E793" s="7"/>
       <c r="I793" s="2"/>
     </row>
     <row r="794" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C794" s="2"/>
-      <c r="D794" s="2"/>
-      <c r="E794" s="2"/>
+      <c r="C794" s="6"/>
+      <c r="D794" s="7"/>
+      <c r="E794" s="7"/>
       <c r="I794" s="2"/>
     </row>
     <row r="795" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C795" s="2"/>
-      <c r="D795" s="2"/>
-      <c r="E795" s="2"/>
+      <c r="C795" s="6"/>
+      <c r="D795" s="7"/>
+      <c r="E795" s="7"/>
       <c r="I795" s="2"/>
     </row>
     <row r="796" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C796" s="2"/>
-      <c r="D796" s="2"/>
-      <c r="E796" s="2"/>
+      <c r="C796" s="6"/>
+      <c r="D796" s="7"/>
+      <c r="E796" s="7"/>
       <c r="I796" s="2"/>
     </row>
     <row r="797" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C797" s="2"/>
-      <c r="D797" s="2"/>
-      <c r="E797" s="2"/>
+      <c r="C797" s="6"/>
+      <c r="D797" s="7"/>
+      <c r="E797" s="7"/>
       <c r="I797" s="2"/>
     </row>
     <row r="798" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C798" s="2"/>
-      <c r="D798" s="2"/>
-      <c r="E798" s="2"/>
+      <c r="C798" s="6"/>
+      <c r="D798" s="7"/>
+      <c r="E798" s="7"/>
       <c r="I798" s="2"/>
     </row>
     <row r="799" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C799" s="2"/>
-      <c r="D799" s="2"/>
-      <c r="E799" s="2"/>
+      <c r="C799" s="6"/>
+      <c r="D799" s="7"/>
+      <c r="E799" s="7"/>
       <c r="I799" s="2"/>
     </row>
     <row r="800" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C800" s="2"/>
-      <c r="D800" s="2"/>
-      <c r="E800" s="2"/>
+      <c r="C800" s="6"/>
+      <c r="D800" s="7"/>
+      <c r="E800" s="7"/>
       <c r="I800" s="2"/>
     </row>
     <row r="801" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C801" s="2"/>
-      <c r="D801" s="2"/>
-      <c r="E801" s="2"/>
+      <c r="C801" s="6"/>
+      <c r="D801" s="7"/>
+      <c r="E801" s="7"/>
       <c r="I801" s="2"/>
     </row>
     <row r="802" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C802" s="2"/>
-      <c r="D802" s="2"/>
-      <c r="E802" s="2"/>
+      <c r="C802" s="6"/>
+      <c r="D802" s="7"/>
+      <c r="E802" s="7"/>
       <c r="I802" s="2"/>
     </row>
     <row r="803" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C803" s="2"/>
-      <c r="D803" s="2"/>
-      <c r="E803" s="2"/>
+      <c r="C803" s="6"/>
+      <c r="D803" s="7"/>
+      <c r="E803" s="7"/>
       <c r="I803" s="2"/>
     </row>
     <row r="804" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C804" s="2"/>
-      <c r="D804" s="2"/>
-      <c r="E804" s="2"/>
+      <c r="C804" s="6"/>
+      <c r="D804" s="7"/>
+      <c r="E804" s="7"/>
       <c r="I804" s="2"/>
     </row>
     <row r="805" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C805" s="2"/>
-      <c r="D805" s="2"/>
-      <c r="E805" s="2"/>
+      <c r="C805" s="6"/>
+      <c r="D805" s="7"/>
+      <c r="E805" s="7"/>
       <c r="I805" s="2"/>
     </row>
     <row r="806" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C806" s="2"/>
-      <c r="D806" s="2"/>
-      <c r="E806" s="2"/>
+      <c r="C806" s="6"/>
+      <c r="D806" s="7"/>
+      <c r="E806" s="7"/>
       <c r="I806" s="2"/>
     </row>
     <row r="807" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C807" s="2"/>
-      <c r="D807" s="2"/>
-      <c r="E807" s="2"/>
+      <c r="C807" s="6"/>
+      <c r="D807" s="7"/>
+      <c r="E807" s="7"/>
       <c r="I807" s="2"/>
     </row>
     <row r="808" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C808" s="2"/>
-      <c r="D808" s="2"/>
-      <c r="E808" s="2"/>
+      <c r="C808" s="6"/>
+      <c r="D808" s="7"/>
+      <c r="E808" s="7"/>
       <c r="I808" s="2"/>
     </row>
     <row r="809" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C809" s="2"/>
-      <c r="D809" s="2"/>
-      <c r="E809" s="2"/>
+      <c r="C809" s="6"/>
+      <c r="D809" s="7"/>
+      <c r="E809" s="7"/>
       <c r="I809" s="2"/>
     </row>
     <row r="810" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C810" s="2"/>
-      <c r="D810" s="2"/>
-      <c r="E810" s="2"/>
+      <c r="C810" s="6"/>
+      <c r="D810" s="7"/>
+      <c r="E810" s="7"/>
       <c r="I810" s="2"/>
     </row>
     <row r="811" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C811" s="2"/>
-      <c r="D811" s="2"/>
-      <c r="E811" s="2"/>
+      <c r="C811" s="6"/>
+      <c r="D811" s="7"/>
+      <c r="E811" s="7"/>
       <c r="I811" s="2"/>
     </row>
     <row r="812" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C812" s="2"/>
-      <c r="D812" s="2"/>
-      <c r="E812" s="2"/>
+      <c r="C812" s="6"/>
+      <c r="D812" s="7"/>
+      <c r="E812" s="7"/>
       <c r="I812" s="2"/>
     </row>
     <row r="813" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C813" s="2"/>
-      <c r="D813" s="2"/>
-      <c r="E813" s="2"/>
+      <c r="C813" s="6"/>
+      <c r="D813" s="7"/>
+      <c r="E813" s="7"/>
       <c r="I813" s="2"/>
     </row>
     <row r="814" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C814" s="2"/>
-      <c r="D814" s="2"/>
-      <c r="E814" s="2"/>
+      <c r="C814" s="6"/>
+      <c r="D814" s="7"/>
+      <c r="E814" s="7"/>
       <c r="I814" s="2"/>
     </row>
     <row r="815" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C815" s="2"/>
-      <c r="D815" s="2"/>
-      <c r="E815" s="2"/>
+      <c r="C815" s="6"/>
+      <c r="D815" s="7"/>
+      <c r="E815" s="7"/>
       <c r="I815" s="2"/>
     </row>
     <row r="816" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C816" s="2"/>
-      <c r="D816" s="2"/>
-      <c r="E816" s="2"/>
+      <c r="C816" s="6"/>
+      <c r="D816" s="7"/>
+      <c r="E816" s="7"/>
       <c r="I816" s="2"/>
     </row>
     <row r="817" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C817" s="2"/>
-      <c r="D817" s="2"/>
-      <c r="E817" s="2"/>
+      <c r="C817" s="6"/>
+      <c r="D817" s="7"/>
+      <c r="E817" s="7"/>
       <c r="I817" s="2"/>
     </row>
     <row r="818" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C818" s="2"/>
-      <c r="D818" s="2"/>
-      <c r="E818" s="2"/>
+      <c r="C818" s="6"/>
+      <c r="D818" s="7"/>
+      <c r="E818" s="7"/>
       <c r="I818" s="2"/>
     </row>
     <row r="819" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C819" s="2"/>
-      <c r="D819" s="2"/>
-      <c r="E819" s="2"/>
+      <c r="C819" s="6"/>
+      <c r="D819" s="7"/>
+      <c r="E819" s="7"/>
       <c r="I819" s="2"/>
     </row>
     <row r="820" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C820" s="2"/>
-      <c r="D820" s="2"/>
-      <c r="E820" s="2"/>
+      <c r="C820" s="6"/>
+      <c r="D820" s="7"/>
+      <c r="E820" s="7"/>
       <c r="I820" s="2"/>
     </row>
     <row r="821" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C821" s="2"/>
-      <c r="D821" s="2"/>
-      <c r="E821" s="2"/>
+      <c r="C821" s="6"/>
+      <c r="D821" s="7"/>
+      <c r="E821" s="7"/>
       <c r="I821" s="2"/>
     </row>
     <row r="822" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C822" s="2"/>
-      <c r="D822" s="2"/>
-      <c r="E822" s="2"/>
+      <c r="C822" s="6"/>
+      <c r="D822" s="7"/>
+      <c r="E822" s="7"/>
       <c r="I822" s="2"/>
     </row>
     <row r="823" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C823" s="2"/>
-      <c r="D823" s="2"/>
-      <c r="E823" s="2"/>
+      <c r="C823" s="6"/>
+      <c r="D823" s="7"/>
+      <c r="E823" s="7"/>
       <c r="I823" s="2"/>
     </row>
     <row r="824" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C824" s="2"/>
-      <c r="D824" s="2"/>
-      <c r="E824" s="2"/>
+      <c r="C824" s="6"/>
+      <c r="D824" s="7"/>
+      <c r="E824" s="7"/>
       <c r="I824" s="2"/>
     </row>
     <row r="825" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C825" s="2"/>
-      <c r="D825" s="2"/>
-      <c r="E825" s="2"/>
+      <c r="C825" s="6"/>
+      <c r="D825" s="7"/>
+      <c r="E825" s="7"/>
       <c r="I825" s="2"/>
     </row>
     <row r="826" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C826" s="2"/>
-      <c r="D826" s="2"/>
-      <c r="E826" s="2"/>
+      <c r="C826" s="6"/>
+      <c r="D826" s="7"/>
+      <c r="E826" s="7"/>
       <c r="I826" s="2"/>
     </row>
     <row r="827" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C827" s="2"/>
-      <c r="D827" s="2"/>
-      <c r="E827" s="2"/>
+      <c r="C827" s="6"/>
+      <c r="D827" s="7"/>
+      <c r="E827" s="7"/>
       <c r="I827" s="2"/>
     </row>
     <row r="828" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C828" s="2"/>
-      <c r="D828" s="2"/>
-      <c r="E828" s="2"/>
+      <c r="C828" s="6"/>
+      <c r="D828" s="7"/>
+      <c r="E828" s="7"/>
       <c r="I828" s="2"/>
     </row>
     <row r="829" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C829" s="2"/>
-      <c r="D829" s="2"/>
-      <c r="E829" s="2"/>
+      <c r="C829" s="6"/>
+      <c r="D829" s="7"/>
+      <c r="E829" s="7"/>
       <c r="I829" s="2"/>
     </row>
     <row r="830" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C830" s="2"/>
-      <c r="D830" s="2"/>
-      <c r="E830" s="2"/>
+      <c r="C830" s="6"/>
+      <c r="D830" s="7"/>
+      <c r="E830" s="7"/>
       <c r="I830" s="2"/>
     </row>
     <row r="831" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C831" s="2"/>
-      <c r="D831" s="2"/>
-      <c r="E831" s="2"/>
+      <c r="C831" s="6"/>
+      <c r="D831" s="7"/>
+      <c r="E831" s="7"/>
       <c r="I831" s="2"/>
     </row>
     <row r="832" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C832" s="2"/>
-      <c r="D832" s="2"/>
-      <c r="E832" s="2"/>
+      <c r="C832" s="6"/>
+      <c r="D832" s="7"/>
+      <c r="E832" s="7"/>
       <c r="I832" s="2"/>
     </row>
     <row r="833" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C833" s="2"/>
-      <c r="D833" s="2"/>
-      <c r="E833" s="2"/>
+      <c r="C833" s="6"/>
+      <c r="D833" s="7"/>
+      <c r="E833" s="7"/>
       <c r="I833" s="2"/>
     </row>
     <row r="834" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C834" s="2"/>
-      <c r="D834" s="2"/>
-      <c r="E834" s="2"/>
+      <c r="C834" s="6"/>
+      <c r="D834" s="7"/>
+      <c r="E834" s="7"/>
       <c r="I834" s="2"/>
     </row>
     <row r="835" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C835" s="2"/>
-      <c r="D835" s="2"/>
-      <c r="E835" s="2"/>
+      <c r="C835" s="6"/>
+      <c r="D835" s="7"/>
+      <c r="E835" s="7"/>
       <c r="I835" s="2"/>
     </row>
     <row r="836" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C836" s="2"/>
-      <c r="D836" s="2"/>
-      <c r="E836" s="2"/>
+      <c r="C836" s="6"/>
+      <c r="D836" s="7"/>
+      <c r="E836" s="7"/>
       <c r="I836" s="2"/>
     </row>
     <row r="837" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C837" s="2"/>
-      <c r="D837" s="2"/>
-      <c r="E837" s="2"/>
+      <c r="C837" s="6"/>
+      <c r="D837" s="7"/>
+      <c r="E837" s="7"/>
       <c r="I837" s="2"/>
     </row>
     <row r="838" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C838" s="2"/>
-      <c r="D838" s="2"/>
-      <c r="E838" s="2"/>
+      <c r="C838" s="6"/>
+      <c r="D838" s="7"/>
+      <c r="E838" s="7"/>
       <c r="I838" s="2"/>
     </row>
     <row r="839" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C839" s="2"/>
-      <c r="D839" s="2"/>
-      <c r="E839" s="2"/>
+      <c r="C839" s="6"/>
+      <c r="D839" s="7"/>
+      <c r="E839" s="7"/>
       <c r="I839" s="2"/>
     </row>
     <row r="840" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C840" s="2"/>
-      <c r="D840" s="2"/>
-      <c r="E840" s="2"/>
+      <c r="C840" s="6"/>
+      <c r="D840" s="7"/>
+      <c r="E840" s="7"/>
       <c r="I840" s="2"/>
     </row>
     <row r="841" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C841" s="2"/>
-      <c r="D841" s="2"/>
-      <c r="E841" s="2"/>
+      <c r="C841" s="6"/>
+      <c r="D841" s="7"/>
+      <c r="E841" s="7"/>
       <c r="I841" s="2"/>
     </row>
     <row r="842" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C842" s="2"/>
-      <c r="D842" s="2"/>
-      <c r="E842" s="2"/>
+      <c r="C842" s="6"/>
+      <c r="D842" s="7"/>
+      <c r="E842" s="7"/>
       <c r="I842" s="2"/>
     </row>
     <row r="843" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C843" s="2"/>
-      <c r="D843" s="2"/>
-      <c r="E843" s="2"/>
+      <c r="C843" s="6"/>
+      <c r="D843" s="7"/>
+      <c r="E843" s="7"/>
       <c r="I843" s="2"/>
     </row>
     <row r="844" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C844" s="2"/>
-      <c r="D844" s="2"/>
-      <c r="E844" s="2"/>
+      <c r="C844" s="6"/>
+      <c r="D844" s="7"/>
+      <c r="E844" s="7"/>
       <c r="I844" s="2"/>
     </row>
     <row r="845" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C845" s="2"/>
-      <c r="D845" s="2"/>
-      <c r="E845" s="2"/>
+      <c r="C845" s="6"/>
+      <c r="D845" s="7"/>
+      <c r="E845" s="7"/>
       <c r="I845" s="2"/>
     </row>
     <row r="846" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C846" s="2"/>
-      <c r="D846" s="2"/>
-      <c r="E846" s="2"/>
+      <c r="C846" s="6"/>
+      <c r="D846" s="7"/>
+      <c r="E846" s="7"/>
       <c r="I846" s="2"/>
     </row>
     <row r="847" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C847" s="2"/>
-      <c r="D847" s="2"/>
-      <c r="E847" s="2"/>
+      <c r="C847" s="6"/>
+      <c r="D847" s="7"/>
+      <c r="E847" s="7"/>
       <c r="I847" s="2"/>
     </row>
     <row r="848" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C848" s="2"/>
-      <c r="D848" s="2"/>
-      <c r="E848" s="2"/>
+      <c r="C848" s="6"/>
+      <c r="D848" s="7"/>
+      <c r="E848" s="7"/>
       <c r="I848" s="2"/>
     </row>
     <row r="849" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C849" s="2"/>
-      <c r="D849" s="2"/>
-      <c r="E849" s="2"/>
+      <c r="C849" s="6"/>
+      <c r="D849" s="7"/>
+      <c r="E849" s="7"/>
       <c r="I849" s="2"/>
     </row>
     <row r="850" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C850" s="2"/>
-      <c r="D850" s="2"/>
-      <c r="E850" s="2"/>
+      <c r="C850" s="6"/>
+      <c r="D850" s="7"/>
+      <c r="E850" s="7"/>
       <c r="I850" s="2"/>
     </row>
     <row r="851" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C851" s="2"/>
-      <c r="D851" s="2"/>
-      <c r="E851" s="2"/>
+      <c r="C851" s="6"/>
+      <c r="D851" s="7"/>
+      <c r="E851" s="7"/>
       <c r="I851" s="2"/>
     </row>
     <row r="852" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C852" s="2"/>
-      <c r="D852" s="2"/>
-      <c r="E852" s="2"/>
+      <c r="C852" s="6"/>
+      <c r="D852" s="7"/>
+      <c r="E852" s="7"/>
       <c r="I852" s="2"/>
     </row>
     <row r="853" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C853" s="2"/>
-      <c r="D853" s="2"/>
-      <c r="E853" s="2"/>
+      <c r="C853" s="6"/>
+      <c r="D853" s="7"/>
+      <c r="E853" s="7"/>
       <c r="I853" s="2"/>
     </row>
     <row r="854" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C854" s="2"/>
-      <c r="D854" s="2"/>
-      <c r="E854" s="2"/>
+      <c r="C854" s="6"/>
+      <c r="D854" s="7"/>
+      <c r="E854" s="7"/>
       <c r="I854" s="2"/>
     </row>
     <row r="855" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C855" s="2"/>
-      <c r="D855" s="2"/>
-      <c r="E855" s="2"/>
+      <c r="C855" s="6"/>
+      <c r="D855" s="7"/>
+      <c r="E855" s="7"/>
       <c r="I855" s="2"/>
     </row>
     <row r="856" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C856" s="2"/>
-      <c r="D856" s="2"/>
-      <c r="E856" s="2"/>
+      <c r="C856" s="6"/>
+      <c r="D856" s="7"/>
+      <c r="E856" s="7"/>
       <c r="I856" s="2"/>
     </row>
     <row r="857" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C857" s="2"/>
-      <c r="D857" s="2"/>
-      <c r="E857" s="2"/>
+      <c r="C857" s="6"/>
+      <c r="D857" s="7"/>
+      <c r="E857" s="7"/>
       <c r="I857" s="2"/>
     </row>
     <row r="858" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C858" s="2"/>
-      <c r="D858" s="2"/>
-      <c r="E858" s="2"/>
+      <c r="C858" s="6"/>
+      <c r="D858" s="7"/>
+      <c r="E858" s="7"/>
       <c r="I858" s="2"/>
     </row>
     <row r="859" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C859" s="2"/>
-      <c r="D859" s="2"/>
-      <c r="E859" s="2"/>
+      <c r="C859" s="6"/>
+      <c r="D859" s="7"/>
+      <c r="E859" s="7"/>
       <c r="I859" s="2"/>
     </row>
     <row r="860" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C860" s="2"/>
-      <c r="D860" s="2"/>
-      <c r="E860" s="2"/>
+      <c r="C860" s="6"/>
+      <c r="D860" s="7"/>
+      <c r="E860" s="7"/>
       <c r="I860" s="2"/>
     </row>
     <row r="861" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C861" s="2"/>
-      <c r="D861" s="2"/>
-      <c r="E861" s="2"/>
+      <c r="C861" s="6"/>
+      <c r="D861" s="7"/>
+      <c r="E861" s="7"/>
       <c r="I861" s="2"/>
     </row>
     <row r="862" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C862" s="2"/>
-      <c r="D862" s="2"/>
-      <c r="E862" s="2"/>
+      <c r="C862" s="6"/>
+      <c r="D862" s="7"/>
+      <c r="E862" s="7"/>
       <c r="I862" s="2"/>
     </row>
     <row r="863" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C863" s="2"/>
-      <c r="D863" s="2"/>
-      <c r="E863" s="2"/>
+      <c r="C863" s="6"/>
+      <c r="D863" s="7"/>
+      <c r="E863" s="7"/>
       <c r="I863" s="2"/>
     </row>
     <row r="864" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C864" s="2"/>
-      <c r="D864" s="2"/>
-      <c r="E864" s="2"/>
+      <c r="C864" s="6"/>
+      <c r="D864" s="7"/>
+      <c r="E864" s="7"/>
       <c r="I864" s="2"/>
     </row>
     <row r="865" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C865" s="2"/>
-      <c r="D865" s="2"/>
-      <c r="E865" s="2"/>
+      <c r="C865" s="6"/>
+      <c r="D865" s="7"/>
+      <c r="E865" s="7"/>
       <c r="I865" s="2"/>
     </row>
     <row r="866" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C866" s="2"/>
-      <c r="D866" s="2"/>
-      <c r="E866" s="2"/>
+      <c r="C866" s="6"/>
+      <c r="D866" s="7"/>
+      <c r="E866" s="7"/>
       <c r="I866" s="2"/>
     </row>
     <row r="867" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C867" s="2"/>
-      <c r="D867" s="2"/>
-      <c r="E867" s="2"/>
+      <c r="C867" s="6"/>
+      <c r="D867" s="7"/>
+      <c r="E867" s="7"/>
       <c r="I867" s="2"/>
     </row>
     <row r="868" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C868" s="2"/>
-      <c r="D868" s="2"/>
-      <c r="E868" s="2"/>
+      <c r="C868" s="6"/>
+      <c r="D868" s="7"/>
+      <c r="E868" s="7"/>
       <c r="I868" s="2"/>
     </row>
     <row r="869" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C869" s="2"/>
-      <c r="D869" s="2"/>
-      <c r="E869" s="2"/>
+      <c r="C869" s="6"/>
+      <c r="D869" s="7"/>
+      <c r="E869" s="7"/>
       <c r="I869" s="2"/>
     </row>
     <row r="870" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C870" s="2"/>
-      <c r="D870" s="2"/>
-      <c r="E870" s="2"/>
+      <c r="C870" s="6"/>
+      <c r="D870" s="7"/>
+      <c r="E870" s="7"/>
       <c r="I870" s="2"/>
     </row>
     <row r="871" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C871" s="2"/>
-      <c r="D871" s="2"/>
-      <c r="E871" s="2"/>
+      <c r="C871" s="6"/>
+      <c r="D871" s="7"/>
+      <c r="E871" s="7"/>
       <c r="I871" s="2"/>
     </row>
     <row r="872" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C872" s="2"/>
-      <c r="D872" s="2"/>
-      <c r="E872" s="2"/>
+      <c r="C872" s="6"/>
+      <c r="D872" s="7"/>
+      <c r="E872" s="7"/>
       <c r="I872" s="2"/>
     </row>
     <row r="873" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C873" s="2"/>
-      <c r="D873" s="2"/>
-      <c r="E873" s="2"/>
+      <c r="C873" s="6"/>
+      <c r="D873" s="7"/>
+      <c r="E873" s="7"/>
       <c r="I873" s="2"/>
     </row>
     <row r="874" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C874" s="2"/>
-      <c r="D874" s="2"/>
-      <c r="E874" s="2"/>
+      <c r="C874" s="6"/>
+      <c r="D874" s="7"/>
+      <c r="E874" s="7"/>
       <c r="I874" s="2"/>
     </row>
     <row r="875" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C875" s="2"/>
-      <c r="D875" s="2"/>
-      <c r="E875" s="2"/>
+      <c r="C875" s="6"/>
+      <c r="D875" s="7"/>
+      <c r="E875" s="7"/>
       <c r="I875" s="2"/>
     </row>
     <row r="876" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C876" s="2"/>
-      <c r="D876" s="2"/>
-      <c r="E876" s="2"/>
+      <c r="C876" s="6"/>
+      <c r="D876" s="7"/>
+      <c r="E876" s="7"/>
       <c r="I876" s="2"/>
     </row>
     <row r="877" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C877" s="2"/>
-      <c r="D877" s="2"/>
-      <c r="E877" s="2"/>
+      <c r="C877" s="6"/>
+      <c r="D877" s="7"/>
+      <c r="E877" s="7"/>
       <c r="I877" s="2"/>
     </row>
     <row r="878" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C878" s="2"/>
-      <c r="D878" s="2"/>
-      <c r="E878" s="2"/>
+      <c r="C878" s="6"/>
+      <c r="D878" s="7"/>
+      <c r="E878" s="7"/>
       <c r="I878" s="2"/>
     </row>
     <row r="879" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C879" s="2"/>
-      <c r="D879" s="2"/>
-      <c r="E879" s="2"/>
+      <c r="C879" s="6"/>
+      <c r="D879" s="7"/>
+      <c r="E879" s="7"/>
       <c r="I879" s="2"/>
     </row>
     <row r="880" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C880" s="2"/>
-      <c r="D880" s="2"/>
-      <c r="E880" s="2"/>
+      <c r="C880" s="6"/>
+      <c r="D880" s="7"/>
+      <c r="E880" s="7"/>
       <c r="I880" s="2"/>
     </row>
     <row r="881" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C881" s="2"/>
-      <c r="D881" s="2"/>
-      <c r="E881" s="2"/>
+      <c r="C881" s="6"/>
+      <c r="D881" s="7"/>
+      <c r="E881" s="7"/>
       <c r="I881" s="2"/>
     </row>
     <row r="882" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C882" s="2"/>
-      <c r="D882" s="2"/>
-      <c r="E882" s="2"/>
+      <c r="C882" s="6"/>
+      <c r="D882" s="7"/>
+      <c r="E882" s="7"/>
       <c r="I882" s="2"/>
     </row>
     <row r="883" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C883" s="2"/>
-      <c r="D883" s="2"/>
-      <c r="E883" s="2"/>
+      <c r="C883" s="6"/>
+      <c r="D883" s="7"/>
+      <c r="E883" s="7"/>
       <c r="I883" s="2"/>
     </row>
     <row r="884" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C884" s="2"/>
-      <c r="D884" s="2"/>
-      <c r="E884" s="2"/>
+      <c r="C884" s="6"/>
+      <c r="D884" s="7"/>
+      <c r="E884" s="7"/>
       <c r="I884" s="2"/>
     </row>
     <row r="885" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C885" s="2"/>
-      <c r="D885" s="2"/>
-      <c r="E885" s="2"/>
+      <c r="C885" s="6"/>
+      <c r="D885" s="7"/>
+      <c r="E885" s="7"/>
       <c r="I885" s="2"/>
     </row>
     <row r="886" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C886" s="2"/>
-      <c r="D886" s="2"/>
-      <c r="E886" s="2"/>
+      <c r="C886" s="6"/>
+      <c r="D886" s="7"/>
+      <c r="E886" s="7"/>
       <c r="I886" s="2"/>
     </row>
     <row r="887" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C887" s="2"/>
-      <c r="D887" s="2"/>
-      <c r="E887" s="2"/>
+      <c r="C887" s="6"/>
+      <c r="D887" s="7"/>
+      <c r="E887" s="7"/>
       <c r="I887" s="2"/>
     </row>
     <row r="888" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C888" s="2"/>
-      <c r="D888" s="2"/>
-      <c r="E888" s="2"/>
+      <c r="C888" s="6"/>
+      <c r="D888" s="7"/>
+      <c r="E888" s="7"/>
       <c r="I888" s="2"/>
     </row>
     <row r="889" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C889" s="2"/>
-      <c r="D889" s="2"/>
-      <c r="E889" s="2"/>
+      <c r="C889" s="6"/>
+      <c r="D889" s="7"/>
+      <c r="E889" s="7"/>
       <c r="I889" s="2"/>
     </row>
     <row r="890" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C890" s="2"/>
-      <c r="D890" s="2"/>
-      <c r="E890" s="2"/>
+      <c r="C890" s="6"/>
+      <c r="D890" s="7"/>
+      <c r="E890" s="7"/>
       <c r="I890" s="2"/>
     </row>
     <row r="891" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C891" s="2"/>
-      <c r="D891" s="2"/>
-      <c r="E891" s="2"/>
+      <c r="C891" s="6"/>
+      <c r="D891" s="7"/>
+      <c r="E891" s="7"/>
       <c r="I891" s="2"/>
     </row>
     <row r="892" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C892" s="2"/>
-      <c r="D892" s="2"/>
-      <c r="E892" s="2"/>
+      <c r="C892" s="6"/>
+      <c r="D892" s="7"/>
+      <c r="E892" s="7"/>
       <c r="I892" s="2"/>
     </row>
     <row r="893" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C893" s="2"/>
-      <c r="D893" s="2"/>
-      <c r="E893" s="2"/>
+      <c r="C893" s="6"/>
+      <c r="D893" s="7"/>
+      <c r="E893" s="7"/>
       <c r="I893" s="2"/>
     </row>
     <row r="894" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C894" s="2"/>
-      <c r="D894" s="2"/>
-      <c r="E894" s="2"/>
+      <c r="C894" s="6"/>
+      <c r="D894" s="7"/>
+      <c r="E894" s="7"/>
       <c r="I894" s="2"/>
     </row>
     <row r="895" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C895" s="2"/>
-      <c r="D895" s="2"/>
-      <c r="E895" s="2"/>
+      <c r="C895" s="6"/>
+      <c r="D895" s="7"/>
+      <c r="E895" s="7"/>
       <c r="I895" s="2"/>
     </row>
     <row r="896" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C896" s="2"/>
-      <c r="D896" s="2"/>
-      <c r="E896" s="2"/>
+      <c r="C896" s="6"/>
+      <c r="D896" s="7"/>
+      <c r="E896" s="7"/>
       <c r="I896" s="2"/>
     </row>
     <row r="897" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C897" s="2"/>
-      <c r="D897" s="2"/>
-      <c r="E897" s="2"/>
+      <c r="C897" s="6"/>
+      <c r="D897" s="7"/>
+      <c r="E897" s="7"/>
       <c r="I897" s="2"/>
     </row>
     <row r="898" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C898" s="2"/>
-      <c r="D898" s="2"/>
-      <c r="E898" s="2"/>
+      <c r="C898" s="6"/>
+      <c r="D898" s="7"/>
+      <c r="E898" s="7"/>
       <c r="I898" s="2"/>
     </row>
     <row r="899" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C899" s="2"/>
-      <c r="D899" s="2"/>
-      <c r="E899" s="2"/>
+      <c r="C899" s="6"/>
+      <c r="D899" s="7"/>
+      <c r="E899" s="7"/>
       <c r="I899" s="2"/>
     </row>
     <row r="900" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C900" s="2"/>
-      <c r="D900" s="2"/>
-      <c r="E900" s="2"/>
+      <c r="C900" s="6"/>
+      <c r="D900" s="7"/>
+      <c r="E900" s="7"/>
       <c r="I900" s="2"/>
     </row>
     <row r="901" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C901" s="2"/>
-      <c r="D901" s="2"/>
-      <c r="E901" s="2"/>
+      <c r="C901" s="6"/>
+      <c r="D901" s="7"/>
+      <c r="E901" s="7"/>
       <c r="I901" s="2"/>
     </row>
     <row r="902" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C902" s="2"/>
-      <c r="D902" s="2"/>
-      <c r="E902" s="2"/>
+      <c r="C902" s="6"/>
+      <c r="D902" s="7"/>
+      <c r="E902" s="7"/>
       <c r="I902" s="2"/>
     </row>
     <row r="903" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C903" s="2"/>
-      <c r="D903" s="2"/>
-      <c r="E903" s="2"/>
+      <c r="C903" s="6"/>
+      <c r="D903" s="7"/>
+      <c r="E903" s="7"/>
       <c r="I903" s="2"/>
     </row>
     <row r="904" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C904" s="2"/>
-      <c r="D904" s="2"/>
-      <c r="E904" s="2"/>
+      <c r="C904" s="6"/>
+      <c r="D904" s="7"/>
+      <c r="E904" s="7"/>
       <c r="I904" s="2"/>
     </row>
     <row r="905" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C905" s="2"/>
-      <c r="D905" s="2"/>
-      <c r="E905" s="2"/>
+      <c r="C905" s="6"/>
+      <c r="D905" s="7"/>
+      <c r="E905" s="7"/>
       <c r="I905" s="2"/>
     </row>
     <row r="906" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C906" s="2"/>
-      <c r="D906" s="2"/>
-      <c r="E906" s="2"/>
+      <c r="C906" s="6"/>
+      <c r="D906" s="7"/>
+      <c r="E906" s="7"/>
       <c r="I906" s="2"/>
     </row>
     <row r="907" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C907" s="2"/>
-      <c r="D907" s="2"/>
-      <c r="E907" s="2"/>
+      <c r="C907" s="6"/>
+      <c r="D907" s="7"/>
+      <c r="E907" s="7"/>
       <c r="I907" s="2"/>
     </row>
     <row r="908" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C908" s="2"/>
-      <c r="D908" s="2"/>
-      <c r="E908" s="2"/>
+      <c r="C908" s="6"/>
+      <c r="D908" s="7"/>
+      <c r="E908" s="7"/>
       <c r="I908" s="2"/>
     </row>
     <row r="909" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C909" s="2"/>
-      <c r="D909" s="2"/>
-      <c r="E909" s="2"/>
+      <c r="C909" s="6"/>
+      <c r="D909" s="7"/>
+      <c r="E909" s="7"/>
       <c r="I909" s="2"/>
     </row>
     <row r="910" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C910" s="2"/>
-      <c r="D910" s="2"/>
-      <c r="E910" s="2"/>
+      <c r="C910" s="6"/>
+      <c r="D910" s="7"/>
+      <c r="E910" s="7"/>
       <c r="I910" s="2"/>
     </row>
     <row r="911" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C911" s="2"/>
-      <c r="D911" s="2"/>
-      <c r="E911" s="2"/>
+      <c r="C911" s="6"/>
+      <c r="D911" s="7"/>
+      <c r="E911" s="7"/>
       <c r="I911" s="2"/>
     </row>
     <row r="912" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C912" s="2"/>
-      <c r="D912" s="2"/>
-      <c r="E912" s="2"/>
+      <c r="C912" s="6"/>
+      <c r="D912" s="7"/>
+      <c r="E912" s="7"/>
       <c r="I912" s="2"/>
     </row>
     <row r="913" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C913" s="2"/>
-      <c r="D913" s="2"/>
-      <c r="E913" s="2"/>
+      <c r="C913" s="6"/>
+      <c r="D913" s="7"/>
+      <c r="E913" s="7"/>
       <c r="I913" s="2"/>
     </row>
     <row r="914" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C914" s="2"/>
-      <c r="D914" s="2"/>
-      <c r="E914" s="2"/>
+      <c r="C914" s="6"/>
+      <c r="D914" s="7"/>
+      <c r="E914" s="7"/>
       <c r="I914" s="2"/>
     </row>
     <row r="915" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C915" s="2"/>
-      <c r="D915" s="2"/>
-      <c r="E915" s="2"/>
+      <c r="C915" s="6"/>
+      <c r="D915" s="7"/>
+      <c r="E915" s="7"/>
       <c r="I915" s="2"/>
     </row>
     <row r="916" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C916" s="2"/>
-      <c r="D916" s="2"/>
-      <c r="E916" s="2"/>
+      <c r="C916" s="6"/>
+      <c r="D916" s="7"/>
+      <c r="E916" s="7"/>
       <c r="I916" s="2"/>
     </row>
     <row r="917" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C917" s="2"/>
-      <c r="D917" s="2"/>
-      <c r="E917" s="2"/>
+      <c r="C917" s="6"/>
+      <c r="D917" s="7"/>
+      <c r="E917" s="7"/>
       <c r="I917" s="2"/>
     </row>
     <row r="918" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C918" s="2"/>
-      <c r="D918" s="2"/>
-      <c r="E918" s="2"/>
+      <c r="C918" s="6"/>
+      <c r="D918" s="7"/>
+      <c r="E918" s="7"/>
       <c r="I918" s="2"/>
     </row>
     <row r="919" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C919" s="2"/>
-      <c r="D919" s="2"/>
-      <c r="E919" s="2"/>
+      <c r="C919" s="6"/>
+      <c r="D919" s="7"/>
+      <c r="E919" s="7"/>
       <c r="I919" s="2"/>
     </row>
     <row r="920" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C920" s="2"/>
-      <c r="D920" s="2"/>
-      <c r="E920" s="2"/>
+      <c r="C920" s="6"/>
+      <c r="D920" s="7"/>
+      <c r="E920" s="7"/>
       <c r="I920" s="2"/>
     </row>
     <row r="921" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C921" s="2"/>
-      <c r="D921" s="2"/>
-      <c r="E921" s="2"/>
+      <c r="C921" s="6"/>
+      <c r="D921" s="7"/>
+      <c r="E921" s="7"/>
       <c r="I921" s="2"/>
     </row>
     <row r="922" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C922" s="2"/>
-      <c r="D922" s="2"/>
-      <c r="E922" s="2"/>
+      <c r="C922" s="6"/>
+      <c r="D922" s="7"/>
+      <c r="E922" s="7"/>
       <c r="I922" s="2"/>
     </row>
     <row r="923" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C923" s="2"/>
-      <c r="D923" s="2"/>
-      <c r="E923" s="2"/>
+      <c r="C923" s="6"/>
+      <c r="D923" s="7"/>
+      <c r="E923" s="7"/>
       <c r="I923" s="2"/>
     </row>
     <row r="924" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C924" s="2"/>
-      <c r="D924" s="2"/>
-      <c r="E924" s="2"/>
+      <c r="C924" s="6"/>
+      <c r="D924" s="7"/>
+      <c r="E924" s="7"/>
       <c r="I924" s="2"/>
     </row>
     <row r="925" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C925" s="2"/>
-      <c r="D925" s="2"/>
-      <c r="E925" s="2"/>
+      <c r="C925" s="6"/>
+      <c r="D925" s="7"/>
+      <c r="E925" s="7"/>
       <c r="I925" s="2"/>
     </row>
     <row r="926" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C926" s="2"/>
-      <c r="D926" s="2"/>
-      <c r="E926" s="2"/>
+      <c r="C926" s="6"/>
+      <c r="D926" s="7"/>
+      <c r="E926" s="7"/>
       <c r="I926" s="2"/>
     </row>
     <row r="927" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C927" s="2"/>
-      <c r="D927" s="2"/>
-      <c r="E927" s="2"/>
+      <c r="C927" s="6"/>
+      <c r="D927" s="7"/>
+      <c r="E927" s="7"/>
       <c r="I927" s="2"/>
     </row>
     <row r="928" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C928" s="2"/>
-      <c r="D928" s="2"/>
-      <c r="E928" s="2"/>
+      <c r="C928" s="6"/>
+      <c r="D928" s="7"/>
+      <c r="E928" s="7"/>
       <c r="I928" s="2"/>
     </row>
     <row r="929" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C929" s="2"/>
-      <c r="D929" s="2"/>
-      <c r="E929" s="2"/>
+      <c r="C929" s="6"/>
+      <c r="D929" s="7"/>
+      <c r="E929" s="7"/>
       <c r="I929" s="2"/>
     </row>
     <row r="930" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C930" s="2"/>
-      <c r="D930" s="2"/>
-      <c r="E930" s="2"/>
+      <c r="C930" s="6"/>
+      <c r="D930" s="7"/>
+      <c r="E930" s="7"/>
       <c r="I930" s="2"/>
     </row>
     <row r="931" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C931" s="2"/>
-      <c r="D931" s="2"/>
-      <c r="E931" s="2"/>
+      <c r="C931" s="6"/>
+      <c r="D931" s="7"/>
+      <c r="E931" s="7"/>
       <c r="I931" s="2"/>
     </row>
     <row r="932" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C932" s="2"/>
-      <c r="D932" s="2"/>
-      <c r="E932" s="2"/>
+      <c r="C932" s="6"/>
+      <c r="D932" s="7"/>
+      <c r="E932" s="7"/>
       <c r="I932" s="2"/>
     </row>
     <row r="933" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C933" s="2"/>
-      <c r="D933" s="2"/>
-      <c r="E933" s="2"/>
+      <c r="C933" s="6"/>
+      <c r="D933" s="7"/>
+      <c r="E933" s="7"/>
       <c r="I933" s="2"/>
     </row>
     <row r="934" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C934" s="2"/>
-      <c r="D934" s="2"/>
-      <c r="E934" s="2"/>
+      <c r="C934" s="6"/>
+      <c r="D934" s="7"/>
+      <c r="E934" s="7"/>
       <c r="I934" s="2"/>
     </row>
     <row r="935" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C935" s="2"/>
-      <c r="D935" s="2"/>
-      <c r="E935" s="2"/>
+      <c r="C935" s="6"/>
+      <c r="D935" s="7"/>
+      <c r="E935" s="7"/>
       <c r="I935" s="2"/>
     </row>
     <row r="936" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C936" s="2"/>
-      <c r="D936" s="2"/>
-      <c r="E936" s="2"/>
+      <c r="C936" s="6"/>
+      <c r="D936" s="7"/>
+      <c r="E936" s="7"/>
       <c r="I936" s="2"/>
     </row>
     <row r="937" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C937" s="2"/>
-      <c r="D937" s="2"/>
-      <c r="E937" s="2"/>
+      <c r="C937" s="6"/>
+      <c r="D937" s="7"/>
+      <c r="E937" s="7"/>
       <c r="I937" s="2"/>
     </row>
     <row r="938" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C938" s="2"/>
-      <c r="D938" s="2"/>
-      <c r="E938" s="2"/>
+      <c r="C938" s="6"/>
+      <c r="D938" s="7"/>
+      <c r="E938" s="7"/>
       <c r="I938" s="2"/>
     </row>
     <row r="939" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C939" s="2"/>
-      <c r="D939" s="2"/>
-      <c r="E939" s="2"/>
+      <c r="C939" s="6"/>
+      <c r="D939" s="7"/>
+      <c r="E939" s="7"/>
       <c r="I939" s="2"/>
     </row>
     <row r="940" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C940" s="2"/>
-      <c r="D940" s="2"/>
-      <c r="E940" s="2"/>
+      <c r="C940" s="6"/>
+      <c r="D940" s="7"/>
+      <c r="E940" s="7"/>
       <c r="I940" s="2"/>
     </row>
     <row r="941" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C941" s="2"/>
-      <c r="D941" s="2"/>
-      <c r="E941" s="2"/>
+      <c r="C941" s="6"/>
+      <c r="D941" s="7"/>
+      <c r="E941" s="7"/>
       <c r="I941" s="2"/>
     </row>
     <row r="942" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C942" s="2"/>
-      <c r="D942" s="2"/>
-      <c r="E942" s="2"/>
+      <c r="C942" s="6"/>
+      <c r="D942" s="7"/>
+      <c r="E942" s="7"/>
       <c r="I942" s="2"/>
     </row>
     <row r="943" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C943" s="2"/>
-      <c r="D943" s="2"/>
-      <c r="E943" s="2"/>
+      <c r="C943" s="6"/>
+      <c r="D943" s="7"/>
+      <c r="E943" s="7"/>
       <c r="I943" s="2"/>
     </row>
     <row r="944" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C944" s="2"/>
-      <c r="D944" s="2"/>
-      <c r="E944" s="2"/>
+      <c r="C944" s="6"/>
+      <c r="D944" s="7"/>
+      <c r="E944" s="7"/>
       <c r="I944" s="2"/>
     </row>
     <row r="945" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C945" s="2"/>
-      <c r="D945" s="2"/>
-      <c r="E945" s="2"/>
+      <c r="C945" s="6"/>
+      <c r="D945" s="7"/>
+      <c r="E945" s="7"/>
       <c r="I945" s="2"/>
     </row>
     <row r="946" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C946" s="2"/>
-      <c r="D946" s="2"/>
-      <c r="E946" s="2"/>
+      <c r="C946" s="6"/>
+      <c r="D946" s="7"/>
+      <c r="E946" s="7"/>
       <c r="I946" s="2"/>
     </row>
     <row r="947" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C947" s="2"/>
-      <c r="D947" s="2"/>
-      <c r="E947" s="2"/>
+      <c r="C947" s="6"/>
+      <c r="D947" s="7"/>
+      <c r="E947" s="7"/>
       <c r="I947" s="2"/>
     </row>
     <row r="948" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C948" s="2"/>
-      <c r="D948" s="2"/>
-      <c r="E948" s="2"/>
+      <c r="C948" s="6"/>
+      <c r="D948" s="7"/>
+      <c r="E948" s="7"/>
       <c r="I948" s="2"/>
     </row>
     <row r="949" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C949" s="2"/>
-      <c r="D949" s="2"/>
-      <c r="E949" s="2"/>
+      <c r="C949" s="6"/>
+      <c r="D949" s="7"/>
+      <c r="E949" s="7"/>
       <c r="I949" s="2"/>
     </row>
     <row r="950" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C950" s="2"/>
-      <c r="D950" s="2"/>
-      <c r="E950" s="2"/>
+      <c r="C950" s="6"/>
+      <c r="D950" s="7"/>
+      <c r="E950" s="7"/>
       <c r="I950" s="2"/>
     </row>
     <row r="951" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C951" s="2"/>
-      <c r="D951" s="2"/>
-      <c r="E951" s="2"/>
+      <c r="C951" s="6"/>
+      <c r="D951" s="7"/>
+      <c r="E951" s="7"/>
       <c r="I951" s="2"/>
     </row>
     <row r="952" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C952" s="2"/>
-      <c r="D952" s="2"/>
-      <c r="E952" s="2"/>
+      <c r="C952" s="6"/>
+      <c r="D952" s="7"/>
+      <c r="E952" s="7"/>
       <c r="I952" s="2"/>
     </row>
     <row r="953" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C953" s="2"/>
-      <c r="D953" s="2"/>
-      <c r="E953" s="2"/>
+      <c r="C953" s="6"/>
+      <c r="D953" s="7"/>
+      <c r="E953" s="7"/>
       <c r="I953" s="2"/>
     </row>
     <row r="954" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C954" s="2"/>
-      <c r="D954" s="2"/>
-      <c r="E954" s="2"/>
+      <c r="C954" s="6"/>
+      <c r="D954" s="7"/>
+      <c r="E954" s="7"/>
       <c r="I954" s="2"/>
     </row>
     <row r="955" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C955" s="2"/>
-      <c r="D955" s="2"/>
-      <c r="E955" s="2"/>
+      <c r="C955" s="6"/>
+      <c r="D955" s="7"/>
+      <c r="E955" s="7"/>
       <c r="I955" s="2"/>
     </row>
     <row r="956" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C956" s="2"/>
-      <c r="D956" s="2"/>
-      <c r="E956" s="2"/>
+      <c r="C956" s="6"/>
+      <c r="D956" s="7"/>
+      <c r="E956" s="7"/>
       <c r="I956" s="2"/>
     </row>
     <row r="957" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C957" s="2"/>
-      <c r="D957" s="2"/>
-      <c r="E957" s="2"/>
+      <c r="C957" s="6"/>
+      <c r="D957" s="7"/>
+      <c r="E957" s="7"/>
       <c r="I957" s="2"/>
     </row>
     <row r="958" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C958" s="2"/>
-      <c r="D958" s="2"/>
-      <c r="E958" s="2"/>
+      <c r="C958" s="6"/>
+      <c r="D958" s="7"/>
+      <c r="E958" s="7"/>
       <c r="I958" s="2"/>
     </row>
     <row r="959" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C959" s="2"/>
-      <c r="D959" s="2"/>
-      <c r="E959" s="2"/>
+      <c r="C959" s="6"/>
+      <c r="D959" s="7"/>
+      <c r="E959" s="7"/>
       <c r="I959" s="2"/>
     </row>
     <row r="960" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C960" s="2"/>
-      <c r="D960" s="2"/>
-      <c r="E960" s="2"/>
+      <c r="C960" s="6"/>
+      <c r="D960" s="7"/>
+      <c r="E960" s="7"/>
       <c r="I960" s="2"/>
     </row>
     <row r="961" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C961" s="2"/>
-      <c r="D961" s="2"/>
-      <c r="E961" s="2"/>
+      <c r="C961" s="6"/>
+      <c r="D961" s="7"/>
+      <c r="E961" s="7"/>
       <c r="I961" s="2"/>
     </row>
     <row r="962" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C962" s="2"/>
-      <c r="D962" s="2"/>
-      <c r="E962" s="2"/>
+      <c r="C962" s="6"/>
+      <c r="D962" s="7"/>
+      <c r="E962" s="7"/>
       <c r="I962" s="2"/>
     </row>
     <row r="963" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C963" s="2"/>
-      <c r="D963" s="2"/>
-      <c r="E963" s="2"/>
+      <c r="C963" s="6"/>
+      <c r="D963" s="7"/>
+      <c r="E963" s="7"/>
       <c r="I963" s="2"/>
     </row>
     <row r="964" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C964" s="2"/>
-      <c r="D964" s="2"/>
-      <c r="E964" s="2"/>
+      <c r="C964" s="6"/>
+      <c r="D964" s="7"/>
+      <c r="E964" s="7"/>
       <c r="I964" s="2"/>
     </row>
     <row r="965" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C965" s="2"/>
-      <c r="D965" s="2"/>
-      <c r="E965" s="2"/>
+      <c r="C965" s="6"/>
+      <c r="D965" s="7"/>
+      <c r="E965" s="7"/>
       <c r="I965" s="2"/>
     </row>
     <row r="966" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C966" s="2"/>
-      <c r="D966" s="2"/>
-      <c r="E966" s="2"/>
+      <c r="C966" s="6"/>
+      <c r="D966" s="7"/>
+      <c r="E966" s="7"/>
       <c r="I966" s="2"/>
     </row>
     <row r="967" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C967" s="2"/>
-      <c r="D967" s="2"/>
-      <c r="E967" s="2"/>
+      <c r="C967" s="6"/>
+      <c r="D967" s="7"/>
+      <c r="E967" s="7"/>
       <c r="I967" s="2"/>
     </row>
     <row r="968" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C968" s="2"/>
-      <c r="D968" s="2"/>
-      <c r="E968" s="2"/>
+      <c r="C968" s="6"/>
+      <c r="D968" s="7"/>
+      <c r="E968" s="7"/>
       <c r="I968" s="2"/>
     </row>
     <row r="969" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C969" s="2"/>
-      <c r="D969" s="2"/>
-      <c r="E969" s="2"/>
+      <c r="C969" s="6"/>
+      <c r="D969" s="7"/>
+      <c r="E969" s="7"/>
       <c r="I969" s="2"/>
     </row>
     <row r="970" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C970" s="2"/>
-      <c r="D970" s="2"/>
-      <c r="E970" s="2"/>
+      <c r="C970" s="6"/>
+      <c r="D970" s="7"/>
+      <c r="E970" s="7"/>
       <c r="I970" s="2"/>
     </row>
     <row r="971" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C971" s="2"/>
-      <c r="D971" s="2"/>
-      <c r="E971" s="2"/>
+      <c r="C971" s="6"/>
+      <c r="D971" s="7"/>
+      <c r="E971" s="7"/>
       <c r="I971" s="2"/>
     </row>
     <row r="972" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C972" s="2"/>
-      <c r="D972" s="2"/>
-      <c r="E972" s="2"/>
+      <c r="C972" s="6"/>
+      <c r="D972" s="7"/>
+      <c r="E972" s="7"/>
       <c r="I972" s="2"/>
     </row>
     <row r="973" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C973" s="2"/>
-      <c r="D973" s="2"/>
-      <c r="E973" s="2"/>
+      <c r="C973" s="6"/>
+      <c r="D973" s="7"/>
+      <c r="E973" s="7"/>
       <c r="I973" s="2"/>
     </row>
     <row r="974" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C974" s="2"/>
-      <c r="D974" s="2"/>
-      <c r="E974" s="2"/>
+      <c r="C974" s="6"/>
+      <c r="D974" s="7"/>
+      <c r="E974" s="7"/>
       <c r="I974" s="2"/>
     </row>
     <row r="975" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C975" s="2"/>
-      <c r="D975" s="2"/>
-      <c r="E975" s="2"/>
+      <c r="C975" s="6"/>
+      <c r="D975" s="7"/>
+      <c r="E975" s="7"/>
       <c r="I975" s="2"/>
     </row>
     <row r="976" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C976" s="2"/>
-      <c r="D976" s="2"/>
-      <c r="E976" s="2"/>
+      <c r="C976" s="6"/>
+      <c r="D976" s="7"/>
+      <c r="E976" s="7"/>
       <c r="I976" s="2"/>
     </row>
     <row r="977" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C977" s="2"/>
-      <c r="D977" s="2"/>
-      <c r="E977" s="2"/>
+      <c r="C977" s="6"/>
+      <c r="D977" s="7"/>
+      <c r="E977" s="7"/>
       <c r="I977" s="2"/>
     </row>
     <row r="978" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C978" s="2"/>
-      <c r="D978" s="2"/>
-      <c r="E978" s="2"/>
+      <c r="C978" s="6"/>
+      <c r="D978" s="7"/>
+      <c r="E978" s="7"/>
       <c r="I978" s="2"/>
     </row>
     <row r="979" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C979" s="2"/>
-      <c r="D979" s="2"/>
-      <c r="E979" s="2"/>
+      <c r="C979" s="6"/>
+      <c r="D979" s="7"/>
+      <c r="E979" s="7"/>
       <c r="I979" s="2"/>
     </row>
     <row r="980" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C980" s="2"/>
-      <c r="D980" s="2"/>
-      <c r="E980" s="2"/>
+      <c r="C980" s="6"/>
+      <c r="D980" s="7"/>
+      <c r="E980" s="7"/>
       <c r="I980" s="2"/>
     </row>
     <row r="981" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C981" s="2"/>
-      <c r="D981" s="2"/>
-      <c r="E981" s="2"/>
+      <c r="C981" s="6"/>
+      <c r="D981" s="7"/>
+      <c r="E981" s="7"/>
       <c r="I981" s="2"/>
     </row>
     <row r="982" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C982" s="2"/>
-      <c r="D982" s="2"/>
-      <c r="E982" s="2"/>
+      <c r="C982" s="6"/>
+      <c r="D982" s="7"/>
+      <c r="E982" s="7"/>
       <c r="I982" s="2"/>
     </row>
     <row r="983" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C983" s="2"/>
-      <c r="D983" s="2"/>
-      <c r="E983" s="2"/>
+      <c r="C983" s="6"/>
+      <c r="D983" s="7"/>
+      <c r="E983" s="7"/>
       <c r="I983" s="2"/>
     </row>
     <row r="984" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C984" s="2"/>
-      <c r="D984" s="2"/>
-      <c r="E984" s="2"/>
+      <c r="C984" s="6"/>
+      <c r="D984" s="7"/>
+      <c r="E984" s="7"/>
       <c r="I984" s="2"/>
     </row>
     <row r="985" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C985" s="2"/>
-      <c r="D985" s="2"/>
-      <c r="E985" s="2"/>
+      <c r="C985" s="6"/>
+      <c r="D985" s="7"/>
+      <c r="E985" s="7"/>
       <c r="I985" s="2"/>
     </row>
     <row r="986" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C986" s="2"/>
-      <c r="D986" s="2"/>
-      <c r="E986" s="2"/>
+      <c r="C986" s="6"/>
+      <c r="D986" s="7"/>
+      <c r="E986" s="7"/>
       <c r="I986" s="2"/>
     </row>
     <row r="987" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C987" s="2"/>
-      <c r="D987" s="2"/>
-      <c r="E987" s="2"/>
+      <c r="C987" s="6"/>
+      <c r="D987" s="7"/>
+      <c r="E987" s="7"/>
       <c r="I987" s="2"/>
     </row>
     <row r="988" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C988" s="2"/>
-      <c r="D988" s="2"/>
-      <c r="E988" s="2"/>
+      <c r="C988" s="6"/>
+      <c r="D988" s="7"/>
+      <c r="E988" s="7"/>
       <c r="I988" s="2"/>
     </row>
     <row r="989" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C989" s="2"/>
-      <c r="D989" s="2"/>
-      <c r="E989" s="2"/>
+      <c r="C989" s="6"/>
+      <c r="D989" s="7"/>
+      <c r="E989" s="7"/>
       <c r="I989" s="2"/>
     </row>
     <row r="990" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C990" s="2"/>
-      <c r="D990" s="2"/>
-      <c r="E990" s="2"/>
+      <c r="C990" s="6"/>
+      <c r="D990" s="7"/>
+      <c r="E990" s="7"/>
       <c r="I990" s="2"/>
     </row>
     <row r="991" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C991" s="2"/>
-      <c r="D991" s="2"/>
-      <c r="E991" s="2"/>
+      <c r="C991" s="6"/>
+      <c r="D991" s="7"/>
+      <c r="E991" s="7"/>
       <c r="I991" s="2"/>
     </row>
     <row r="992" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C992" s="2"/>
-      <c r="D992" s="2"/>
-      <c r="E992" s="2"/>
+      <c r="C992" s="6"/>
+      <c r="D992" s="7"/>
+      <c r="E992" s="7"/>
       <c r="I992" s="2"/>
     </row>
     <row r="993" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C993" s="2"/>
-      <c r="D993" s="2"/>
-      <c r="E993" s="2"/>
+      <c r="C993" s="6"/>
+      <c r="D993" s="7"/>
+      <c r="E993" s="7"/>
       <c r="I993" s="2"/>
     </row>
     <row r="994" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C994" s="2"/>
-      <c r="D994" s="2"/>
-      <c r="E994" s="2"/>
+      <c r="C994" s="6"/>
+      <c r="D994" s="7"/>
+      <c r="E994" s="7"/>
       <c r="I994" s="2"/>
     </row>
     <row r="995" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C995" s="2"/>
-      <c r="D995" s="2"/>
-      <c r="E995" s="2"/>
+      <c r="C995" s="6"/>
+      <c r="D995" s="7"/>
+      <c r="E995" s="7"/>
       <c r="I995" s="2"/>
     </row>
     <row r="996" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C996" s="2"/>
-      <c r="D996" s="2"/>
-      <c r="E996" s="2"/>
+      <c r="C996" s="6"/>
+      <c r="D996" s="7"/>
+      <c r="E996" s="7"/>
       <c r="I996" s="2"/>
     </row>
     <row r="997" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C997" s="2"/>
-      <c r="D997" s="2"/>
-      <c r="E997" s="2"/>
+      <c r="C997" s="6"/>
+      <c r="D997" s="7"/>
+      <c r="E997" s="7"/>
       <c r="I997" s="2"/>
     </row>
     <row r="998" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C998" s="2"/>
-      <c r="D998" s="2"/>
-      <c r="E998" s="2"/>
+      <c r="C998" s="6"/>
+      <c r="D998" s="7"/>
+      <c r="E998" s="7"/>
       <c r="I998" s="2"/>
     </row>
     <row r="999" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C999" s="2"/>
-      <c r="D999" s="2"/>
-      <c r="E999" s="2"/>
+      <c r="C999" s="6"/>
+      <c r="D999" s="7"/>
+      <c r="E999" s="7"/>
       <c r="I999" s="2"/>
     </row>
     <row r="1000" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C1000" s="2"/>
-      <c r="D1000" s="2"/>
-      <c r="E1000" s="2"/>
+      <c r="C1000" s="6"/>
+      <c r="D1000" s="7"/>
+      <c r="E1000" s="7"/>
       <c r="I1000" s="2"/>
+    </row>
+    <row r="1001" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C1001" s="6"/>
+      <c r="D1001" s="7"/>
+      <c r="E1001" s="7"/>
+    </row>
+    <row r="1002" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C1002" s="6"/>
+      <c r="D1002" s="7"/>
+      <c r="E1002" s="7"/>
+    </row>
+    <row r="1003" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="C1003" s="6"/>
+      <c r="D1003" s="7"/>
+      <c r="E1003" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I1000" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -6726,11 +6772,11 @@
       <formula1>0</formula1>
       <formula2>59</formula2>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid due_date" error="Use YYYY-MM-DD, for example 2026-05-19." sqref="C4:C1000" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>OR(C4="",AND(LEN(C4)=10,MID(C4,5,1)="-",MID(C4,8,1)="-",ISNUMBER(--LEFT(C4,4)),ISNUMBER(--MID(C4,6,2)),ISNUMBER(--RIGHT(C4,2))))</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid due_date" error="Use YYYY-MM-DD, for example 2026-05-19." sqref="C4:C1003" xr:uid="{600EFB90-C93A-4852-9C0C-737760A23221}">
+      <formula1>OR(C4="",ISNUMBER(C4),AND(LEN(C4)=10,MID(C4,5,1)="-",MID(C4,8,1)="-",ISNUMBER(--LEFT(C4,4)),ISNUMBER(--MID(C4,6,2)),ISNUMBER(--RIGHT(C4,2))))</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid datetime" error="Use YYYY-MM-DD HH:MM, for example 2026-04-18 14:20." sqref="D4:E1000" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>OR(D4="",AND(LEN(D4)=16,MID(D4,5,1)="-",MID(D4,8,1)="-",MID(D4,11,1)=" ",MID(D4,14,1)=":",ISNUMBER(--LEFT(D4,4)),ISNUMBER(--MID(D4,6,2)),ISNUMBER(--MID(D4,9,2)),ISNUMBER(--MID(D4,12,2)),ISNUMBER(--RIGHT(D4,2))))</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid datetime" error="Use YYYY-MM-DD HH:MM, for example 2026-04-18 14:20." sqref="D4:E1003" xr:uid="{8BEE0597-75FC-4518-81AF-B4C79FEED218}">
+      <formula1>OR(D4="",ISNUMBER(D4),AND(LEN(D4)=16,MID(D4,5,1)="-",MID(D4,8,1)="-",MID(D4,11,1)=" ",MID(D4,14,1)=":",ISNUMBER(--LEFT(D4,4)),ISNUMBER(--MID(D4,6,2)),ISNUMBER(--MID(D4,9,2)),ISNUMBER(--MID(D4,12,2)),ISNUMBER(--RIGHT(D4,2))))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6755,93 +6801,93 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-    </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="H12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="I12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="4" t="s">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>15</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -6850,10 +6896,10 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -6872,60 +6918,60 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C2" s="5" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-    </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/tracker/static/tracker/task_import_template.xlsx
+++ b/tracker/static/tracker/task_import_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frige\PycharmProjects\task-tracker\tracker\static\tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CDAAA8-6824-4C1B-94BF-74BE27F1F6EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A18911-5B1C-442A-B87A-9622A3132DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32460" yWindow="11070" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>Task Import Template</t>
   </si>
@@ -205,9 +205,6 @@
     <t>2026-04-18 14:20</t>
   </si>
   <si>
-    <t>2026-04-18 14:35</t>
-  </si>
-  <si>
     <t>Reschedule annual appointment</t>
   </si>
   <si>
@@ -245,9 +242,6 @@
   </si>
   <si>
     <t>Tip</t>
-  </si>
-  <si>
-    <t>Users can create categories inside the app, so categories here are flexible.</t>
   </si>
   <si>
     <t>Work</t>
@@ -298,6 +292,9 @@
       </rPr>
       <t xml:space="preserve"> sheet of this document for validation rules and an example row.</t>
     </r>
+  </si>
+  <si>
+    <t>Users can create categories inside the app as well, so categories here are optional.</t>
   </si>
 </sst>
 </file>
@@ -365,7 +362,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -382,11 +379,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -396,9 +408,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -406,6 +415,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -724,30 +738,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
-        <v>37</v>
+      <c r="A2" s="9" t="s">
+        <v>35</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -779,5981 +793,5981 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C11" s="6"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C14" s="6"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C15" s="6"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C16" s="6"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C22" s="6"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C24" s="6"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C29" s="6"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C30" s="6"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
       <c r="I30" s="2"/>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C31" s="6"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
       <c r="I31" s="2"/>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C32" s="6"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C33" s="6"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C34" s="6"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C36" s="6"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C37" s="6"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C38" s="6"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C39" s="6"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
       <c r="I39" s="2"/>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C40" s="6"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C41" s="6"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C42" s="6"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
       <c r="I42" s="2"/>
     </row>
     <row r="43" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C43" s="6"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
       <c r="I43" s="2"/>
     </row>
     <row r="44" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
       <c r="I44" s="2"/>
     </row>
     <row r="45" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C45" s="6"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
       <c r="I45" s="2"/>
     </row>
     <row r="46" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C46" s="6"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
       <c r="I46" s="2"/>
     </row>
     <row r="47" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C47" s="6"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C48" s="6"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
       <c r="I48" s="2"/>
     </row>
     <row r="49" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C49" s="6"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
       <c r="I49" s="2"/>
     </row>
     <row r="50" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C50" s="6"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
       <c r="I50" s="2"/>
     </row>
     <row r="51" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C51" s="6"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
       <c r="I51" s="2"/>
     </row>
     <row r="52" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C52" s="6"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
       <c r="I52" s="2"/>
     </row>
     <row r="53" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C53" s="6"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
       <c r="I53" s="2"/>
     </row>
     <row r="54" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C54" s="6"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
       <c r="I54" s="2"/>
     </row>
     <row r="55" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C55" s="6"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
       <c r="I55" s="2"/>
     </row>
     <row r="56" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C56" s="6"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
       <c r="I56" s="2"/>
     </row>
     <row r="57" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C57" s="6"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
       <c r="I57" s="2"/>
     </row>
     <row r="58" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C58" s="6"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
       <c r="I58" s="2"/>
     </row>
     <row r="59" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C59" s="6"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
       <c r="I59" s="2"/>
     </row>
     <row r="60" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C60" s="6"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
       <c r="I60" s="2"/>
     </row>
     <row r="61" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C61" s="6"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
       <c r="I61" s="2"/>
     </row>
     <row r="62" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C62" s="6"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
       <c r="I62" s="2"/>
     </row>
     <row r="63" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C63" s="6"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
       <c r="I63" s="2"/>
     </row>
     <row r="64" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C64" s="6"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
       <c r="I64" s="2"/>
     </row>
     <row r="65" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C65" s="6"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
       <c r="I65" s="2"/>
     </row>
     <row r="66" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C66" s="6"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
       <c r="I66" s="2"/>
     </row>
     <row r="67" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C67" s="6"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
       <c r="I67" s="2"/>
     </row>
     <row r="68" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C68" s="6"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
       <c r="I68" s="2"/>
     </row>
     <row r="69" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C69" s="6"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
       <c r="I69" s="2"/>
     </row>
     <row r="70" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C70" s="6"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
       <c r="I70" s="2"/>
     </row>
     <row r="71" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C71" s="6"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
       <c r="I71" s="2"/>
     </row>
     <row r="72" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C72" s="6"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
       <c r="I72" s="2"/>
     </row>
     <row r="73" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C73" s="6"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
       <c r="I73" s="2"/>
     </row>
     <row r="74" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C74" s="6"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
       <c r="I74" s="2"/>
     </row>
     <row r="75" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C75" s="6"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
       <c r="I75" s="2"/>
     </row>
     <row r="76" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C76" s="6"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
       <c r="I76" s="2"/>
     </row>
     <row r="77" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C77" s="6"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
       <c r="I77" s="2"/>
     </row>
     <row r="78" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C78" s="6"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="7"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
       <c r="I78" s="2"/>
     </row>
     <row r="79" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C79" s="6"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
       <c r="I79" s="2"/>
     </row>
     <row r="80" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C80" s="6"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
       <c r="I80" s="2"/>
     </row>
     <row r="81" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C81" s="6"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
       <c r="I81" s="2"/>
     </row>
     <row r="82" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C82" s="6"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
       <c r="I82" s="2"/>
     </row>
     <row r="83" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C83" s="6"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
       <c r="I83" s="2"/>
     </row>
     <row r="84" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C84" s="6"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
       <c r="I84" s="2"/>
     </row>
     <row r="85" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C85" s="6"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
       <c r="I85" s="2"/>
     </row>
     <row r="86" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C86" s="6"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
       <c r="I86" s="2"/>
     </row>
     <row r="87" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C87" s="6"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
       <c r="I87" s="2"/>
     </row>
     <row r="88" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C88" s="6"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
       <c r="I88" s="2"/>
     </row>
     <row r="89" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C89" s="6"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
       <c r="I89" s="2"/>
     </row>
     <row r="90" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C90" s="6"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="7"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
       <c r="I90" s="2"/>
     </row>
     <row r="91" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C91" s="6"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
       <c r="I91" s="2"/>
     </row>
     <row r="92" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C92" s="6"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
       <c r="I92" s="2"/>
     </row>
     <row r="93" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C93" s="6"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
       <c r="I93" s="2"/>
     </row>
     <row r="94" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C94" s="6"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
       <c r="I94" s="2"/>
     </row>
     <row r="95" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C95" s="6"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
       <c r="I95" s="2"/>
     </row>
     <row r="96" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C96" s="6"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
       <c r="I96" s="2"/>
     </row>
     <row r="97" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C97" s="6"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
       <c r="I97" s="2"/>
     </row>
     <row r="98" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C98" s="6"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
       <c r="I98" s="2"/>
     </row>
     <row r="99" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C99" s="6"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
       <c r="I99" s="2"/>
     </row>
     <row r="100" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C100" s="6"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
       <c r="I100" s="2"/>
     </row>
     <row r="101" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C101" s="6"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
       <c r="I101" s="2"/>
     </row>
     <row r="102" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C102" s="6"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
       <c r="I102" s="2"/>
     </row>
     <row r="103" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C103" s="6"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="7"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
       <c r="I103" s="2"/>
     </row>
     <row r="104" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C104" s="6"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="7"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
       <c r="I104" s="2"/>
     </row>
     <row r="105" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C105" s="6"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="7"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
       <c r="I105" s="2"/>
     </row>
     <row r="106" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C106" s="6"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
       <c r="I106" s="2"/>
     </row>
     <row r="107" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C107" s="6"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="7"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
       <c r="I107" s="2"/>
     </row>
     <row r="108" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C108" s="6"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="7"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
       <c r="I108" s="2"/>
     </row>
     <row r="109" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C109" s="6"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="7"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
       <c r="I109" s="2"/>
     </row>
     <row r="110" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C110" s="6"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
       <c r="I110" s="2"/>
     </row>
     <row r="111" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C111" s="6"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="7"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
       <c r="I111" s="2"/>
     </row>
     <row r="112" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C112" s="6"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
       <c r="I112" s="2"/>
     </row>
     <row r="113" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C113" s="6"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="7"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
       <c r="I113" s="2"/>
     </row>
     <row r="114" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C114" s="6"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="7"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
       <c r="I114" s="2"/>
     </row>
     <row r="115" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C115" s="6"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="7"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
       <c r="I115" s="2"/>
     </row>
     <row r="116" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C116" s="6"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="7"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
       <c r="I116" s="2"/>
     </row>
     <row r="117" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C117" s="6"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="7"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="6"/>
+      <c r="E117" s="6"/>
       <c r="I117" s="2"/>
     </row>
     <row r="118" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C118" s="6"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="7"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
       <c r="I118" s="2"/>
     </row>
     <row r="119" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C119" s="6"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="7"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
       <c r="I119" s="2"/>
     </row>
     <row r="120" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C120" s="6"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="6"/>
       <c r="I120" s="2"/>
     </row>
     <row r="121" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C121" s="6"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="7"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="6"/>
+      <c r="E121" s="6"/>
       <c r="I121" s="2"/>
     </row>
     <row r="122" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C122" s="6"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="7"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="6"/>
       <c r="I122" s="2"/>
     </row>
     <row r="123" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C123" s="6"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="7"/>
+      <c r="C123" s="5"/>
+      <c r="D123" s="6"/>
+      <c r="E123" s="6"/>
       <c r="I123" s="2"/>
     </row>
     <row r="124" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C124" s="6"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="6"/>
       <c r="I124" s="2"/>
     </row>
     <row r="125" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C125" s="6"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="6"/>
+      <c r="E125" s="6"/>
       <c r="I125" s="2"/>
     </row>
     <row r="126" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C126" s="6"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="7"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="6"/>
+      <c r="E126" s="6"/>
       <c r="I126" s="2"/>
     </row>
     <row r="127" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C127" s="6"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="6"/>
+      <c r="E127" s="6"/>
       <c r="I127" s="2"/>
     </row>
     <row r="128" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C128" s="6"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="7"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
       <c r="I128" s="2"/>
     </row>
     <row r="129" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C129" s="6"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="7"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="6"/>
+      <c r="E129" s="6"/>
       <c r="I129" s="2"/>
     </row>
     <row r="130" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C130" s="6"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="6"/>
+      <c r="E130" s="6"/>
       <c r="I130" s="2"/>
     </row>
     <row r="131" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C131" s="6"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="7"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="6"/>
+      <c r="E131" s="6"/>
       <c r="I131" s="2"/>
     </row>
     <row r="132" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C132" s="6"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
       <c r="I132" s="2"/>
     </row>
     <row r="133" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C133" s="6"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="7"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
       <c r="I133" s="2"/>
     </row>
     <row r="134" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C134" s="6"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="7"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
       <c r="I134" s="2"/>
     </row>
     <row r="135" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C135" s="6"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="7"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
       <c r="I135" s="2"/>
     </row>
     <row r="136" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C136" s="6"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
+      <c r="C136" s="5"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
       <c r="I136" s="2"/>
     </row>
     <row r="137" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C137" s="6"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
       <c r="I137" s="2"/>
     </row>
     <row r="138" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C138" s="6"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
       <c r="I138" s="2"/>
     </row>
     <row r="139" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C139" s="6"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
       <c r="I139" s="2"/>
     </row>
     <row r="140" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C140" s="6"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="7"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
       <c r="I140" s="2"/>
     </row>
     <row r="141" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C141" s="6"/>
-      <c r="D141" s="7"/>
-      <c r="E141" s="7"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="6"/>
+      <c r="E141" s="6"/>
       <c r="I141" s="2"/>
     </row>
     <row r="142" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C142" s="6"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="7"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6"/>
       <c r="I142" s="2"/>
     </row>
     <row r="143" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C143" s="6"/>
-      <c r="D143" s="7"/>
-      <c r="E143" s="7"/>
+      <c r="C143" s="5"/>
+      <c r="D143" s="6"/>
+      <c r="E143" s="6"/>
       <c r="I143" s="2"/>
     </row>
     <row r="144" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C144" s="6"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="7"/>
+      <c r="C144" s="5"/>
+      <c r="D144" s="6"/>
+      <c r="E144" s="6"/>
       <c r="I144" s="2"/>
     </row>
     <row r="145" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C145" s="6"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="7"/>
+      <c r="C145" s="5"/>
+      <c r="D145" s="6"/>
+      <c r="E145" s="6"/>
       <c r="I145" s="2"/>
     </row>
     <row r="146" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C146" s="6"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
+      <c r="C146" s="5"/>
+      <c r="D146" s="6"/>
+      <c r="E146" s="6"/>
       <c r="I146" s="2"/>
     </row>
     <row r="147" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C147" s="6"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
+      <c r="C147" s="5"/>
+      <c r="D147" s="6"/>
+      <c r="E147" s="6"/>
       <c r="I147" s="2"/>
     </row>
     <row r="148" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C148" s="6"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="6"/>
+      <c r="E148" s="6"/>
       <c r="I148" s="2"/>
     </row>
     <row r="149" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C149" s="6"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="7"/>
+      <c r="C149" s="5"/>
+      <c r="D149" s="6"/>
+      <c r="E149" s="6"/>
       <c r="I149" s="2"/>
     </row>
     <row r="150" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C150" s="6"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="7"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="6"/>
+      <c r="E150" s="6"/>
       <c r="I150" s="2"/>
     </row>
     <row r="151" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C151" s="6"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="6"/>
+      <c r="E151" s="6"/>
       <c r="I151" s="2"/>
     </row>
     <row r="152" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C152" s="6"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="6"/>
+      <c r="E152" s="6"/>
       <c r="I152" s="2"/>
     </row>
     <row r="153" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C153" s="6"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="7"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="6"/>
+      <c r="E153" s="6"/>
       <c r="I153" s="2"/>
     </row>
     <row r="154" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C154" s="6"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="7"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="6"/>
+      <c r="E154" s="6"/>
       <c r="I154" s="2"/>
     </row>
     <row r="155" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C155" s="6"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="7"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="6"/>
+      <c r="E155" s="6"/>
       <c r="I155" s="2"/>
     </row>
     <row r="156" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C156" s="6"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="7"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="6"/>
+      <c r="E156" s="6"/>
       <c r="I156" s="2"/>
     </row>
     <row r="157" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C157" s="6"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="6"/>
+      <c r="E157" s="6"/>
       <c r="I157" s="2"/>
     </row>
     <row r="158" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C158" s="6"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
+      <c r="C158" s="5"/>
+      <c r="D158" s="6"/>
+      <c r="E158" s="6"/>
       <c r="I158" s="2"/>
     </row>
     <row r="159" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C159" s="6"/>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="6"/>
+      <c r="E159" s="6"/>
       <c r="I159" s="2"/>
     </row>
     <row r="160" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C160" s="6"/>
-      <c r="D160" s="7"/>
-      <c r="E160" s="7"/>
+      <c r="C160" s="5"/>
+      <c r="D160" s="6"/>
+      <c r="E160" s="6"/>
       <c r="I160" s="2"/>
     </row>
     <row r="161" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C161" s="6"/>
-      <c r="D161" s="7"/>
-      <c r="E161" s="7"/>
+      <c r="C161" s="5"/>
+      <c r="D161" s="6"/>
+      <c r="E161" s="6"/>
       <c r="I161" s="2"/>
     </row>
     <row r="162" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C162" s="6"/>
-      <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
+      <c r="C162" s="5"/>
+      <c r="D162" s="6"/>
+      <c r="E162" s="6"/>
       <c r="I162" s="2"/>
     </row>
     <row r="163" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C163" s="6"/>
-      <c r="D163" s="7"/>
-      <c r="E163" s="7"/>
+      <c r="C163" s="5"/>
+      <c r="D163" s="6"/>
+      <c r="E163" s="6"/>
       <c r="I163" s="2"/>
     </row>
     <row r="164" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C164" s="6"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
+      <c r="C164" s="5"/>
+      <c r="D164" s="6"/>
+      <c r="E164" s="6"/>
       <c r="I164" s="2"/>
     </row>
     <row r="165" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C165" s="6"/>
-      <c r="D165" s="7"/>
-      <c r="E165" s="7"/>
+      <c r="C165" s="5"/>
+      <c r="D165" s="6"/>
+      <c r="E165" s="6"/>
       <c r="I165" s="2"/>
     </row>
     <row r="166" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C166" s="6"/>
-      <c r="D166" s="7"/>
-      <c r="E166" s="7"/>
+      <c r="C166" s="5"/>
+      <c r="D166" s="6"/>
+      <c r="E166" s="6"/>
       <c r="I166" s="2"/>
     </row>
     <row r="167" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C167" s="6"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
+      <c r="C167" s="5"/>
+      <c r="D167" s="6"/>
+      <c r="E167" s="6"/>
       <c r="I167" s="2"/>
     </row>
     <row r="168" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C168" s="6"/>
-      <c r="D168" s="7"/>
-      <c r="E168" s="7"/>
+      <c r="C168" s="5"/>
+      <c r="D168" s="6"/>
+      <c r="E168" s="6"/>
       <c r="I168" s="2"/>
     </row>
     <row r="169" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C169" s="6"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="6"/>
+      <c r="E169" s="6"/>
       <c r="I169" s="2"/>
     </row>
     <row r="170" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C170" s="6"/>
-      <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
+      <c r="C170" s="5"/>
+      <c r="D170" s="6"/>
+      <c r="E170" s="6"/>
       <c r="I170" s="2"/>
     </row>
     <row r="171" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C171" s="6"/>
-      <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
+      <c r="C171" s="5"/>
+      <c r="D171" s="6"/>
+      <c r="E171" s="6"/>
       <c r="I171" s="2"/>
     </row>
     <row r="172" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C172" s="6"/>
-      <c r="D172" s="7"/>
-      <c r="E172" s="7"/>
+      <c r="C172" s="5"/>
+      <c r="D172" s="6"/>
+      <c r="E172" s="6"/>
       <c r="I172" s="2"/>
     </row>
     <row r="173" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C173" s="6"/>
-      <c r="D173" s="7"/>
-      <c r="E173" s="7"/>
+      <c r="C173" s="5"/>
+      <c r="D173" s="6"/>
+      <c r="E173" s="6"/>
       <c r="I173" s="2"/>
     </row>
     <row r="174" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C174" s="6"/>
-      <c r="D174" s="7"/>
-      <c r="E174" s="7"/>
+      <c r="C174" s="5"/>
+      <c r="D174" s="6"/>
+      <c r="E174" s="6"/>
       <c r="I174" s="2"/>
     </row>
     <row r="175" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C175" s="6"/>
-      <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
+      <c r="C175" s="5"/>
+      <c r="D175" s="6"/>
+      <c r="E175" s="6"/>
       <c r="I175" s="2"/>
     </row>
     <row r="176" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C176" s="6"/>
-      <c r="D176" s="7"/>
-      <c r="E176" s="7"/>
+      <c r="C176" s="5"/>
+      <c r="D176" s="6"/>
+      <c r="E176" s="6"/>
       <c r="I176" s="2"/>
     </row>
     <row r="177" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C177" s="6"/>
-      <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
+      <c r="C177" s="5"/>
+      <c r="D177" s="6"/>
+      <c r="E177" s="6"/>
       <c r="I177" s="2"/>
     </row>
     <row r="178" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C178" s="6"/>
-      <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
+      <c r="C178" s="5"/>
+      <c r="D178" s="6"/>
+      <c r="E178" s="6"/>
       <c r="I178" s="2"/>
     </row>
     <row r="179" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C179" s="6"/>
-      <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
+      <c r="C179" s="5"/>
+      <c r="D179" s="6"/>
+      <c r="E179" s="6"/>
       <c r="I179" s="2"/>
     </row>
     <row r="180" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C180" s="6"/>
-      <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
+      <c r="C180" s="5"/>
+      <c r="D180" s="6"/>
+      <c r="E180" s="6"/>
       <c r="I180" s="2"/>
     </row>
     <row r="181" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C181" s="6"/>
-      <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
+      <c r="C181" s="5"/>
+      <c r="D181" s="6"/>
+      <c r="E181" s="6"/>
       <c r="I181" s="2"/>
     </row>
     <row r="182" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C182" s="6"/>
-      <c r="D182" s="7"/>
-      <c r="E182" s="7"/>
+      <c r="C182" s="5"/>
+      <c r="D182" s="6"/>
+      <c r="E182" s="6"/>
       <c r="I182" s="2"/>
     </row>
     <row r="183" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C183" s="6"/>
-      <c r="D183" s="7"/>
-      <c r="E183" s="7"/>
+      <c r="C183" s="5"/>
+      <c r="D183" s="6"/>
+      <c r="E183" s="6"/>
       <c r="I183" s="2"/>
     </row>
     <row r="184" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C184" s="6"/>
-      <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
+      <c r="C184" s="5"/>
+      <c r="D184" s="6"/>
+      <c r="E184" s="6"/>
       <c r="I184" s="2"/>
     </row>
     <row r="185" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C185" s="6"/>
-      <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
+      <c r="C185" s="5"/>
+      <c r="D185" s="6"/>
+      <c r="E185" s="6"/>
       <c r="I185" s="2"/>
     </row>
     <row r="186" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C186" s="6"/>
-      <c r="D186" s="7"/>
-      <c r="E186" s="7"/>
+      <c r="C186" s="5"/>
+      <c r="D186" s="6"/>
+      <c r="E186" s="6"/>
       <c r="I186" s="2"/>
     </row>
     <row r="187" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C187" s="6"/>
-      <c r="D187" s="7"/>
-      <c r="E187" s="7"/>
+      <c r="C187" s="5"/>
+      <c r="D187" s="6"/>
+      <c r="E187" s="6"/>
       <c r="I187" s="2"/>
     </row>
     <row r="188" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C188" s="6"/>
-      <c r="D188" s="7"/>
-      <c r="E188" s="7"/>
+      <c r="C188" s="5"/>
+      <c r="D188" s="6"/>
+      <c r="E188" s="6"/>
       <c r="I188" s="2"/>
     </row>
     <row r="189" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C189" s="6"/>
-      <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
+      <c r="C189" s="5"/>
+      <c r="D189" s="6"/>
+      <c r="E189" s="6"/>
       <c r="I189" s="2"/>
     </row>
     <row r="190" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C190" s="6"/>
-      <c r="D190" s="7"/>
-      <c r="E190" s="7"/>
+      <c r="C190" s="5"/>
+      <c r="D190" s="6"/>
+      <c r="E190" s="6"/>
       <c r="I190" s="2"/>
     </row>
     <row r="191" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C191" s="6"/>
-      <c r="D191" s="7"/>
-      <c r="E191" s="7"/>
+      <c r="C191" s="5"/>
+      <c r="D191" s="6"/>
+      <c r="E191" s="6"/>
       <c r="I191" s="2"/>
     </row>
     <row r="192" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C192" s="6"/>
-      <c r="D192" s="7"/>
-      <c r="E192" s="7"/>
+      <c r="C192" s="5"/>
+      <c r="D192" s="6"/>
+      <c r="E192" s="6"/>
       <c r="I192" s="2"/>
     </row>
     <row r="193" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C193" s="6"/>
-      <c r="D193" s="7"/>
-      <c r="E193" s="7"/>
+      <c r="C193" s="5"/>
+      <c r="D193" s="6"/>
+      <c r="E193" s="6"/>
       <c r="I193" s="2"/>
     </row>
     <row r="194" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C194" s="6"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
+      <c r="C194" s="5"/>
+      <c r="D194" s="6"/>
+      <c r="E194" s="6"/>
       <c r="I194" s="2"/>
     </row>
     <row r="195" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C195" s="6"/>
-      <c r="D195" s="7"/>
-      <c r="E195" s="7"/>
+      <c r="C195" s="5"/>
+      <c r="D195" s="6"/>
+      <c r="E195" s="6"/>
       <c r="I195" s="2"/>
     </row>
     <row r="196" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C196" s="6"/>
-      <c r="D196" s="7"/>
-      <c r="E196" s="7"/>
+      <c r="C196" s="5"/>
+      <c r="D196" s="6"/>
+      <c r="E196" s="6"/>
       <c r="I196" s="2"/>
     </row>
     <row r="197" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C197" s="6"/>
-      <c r="D197" s="7"/>
-      <c r="E197" s="7"/>
+      <c r="C197" s="5"/>
+      <c r="D197" s="6"/>
+      <c r="E197" s="6"/>
       <c r="I197" s="2"/>
     </row>
     <row r="198" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C198" s="6"/>
-      <c r="D198" s="7"/>
-      <c r="E198" s="7"/>
+      <c r="C198" s="5"/>
+      <c r="D198" s="6"/>
+      <c r="E198" s="6"/>
       <c r="I198" s="2"/>
     </row>
     <row r="199" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C199" s="6"/>
-      <c r="D199" s="7"/>
-      <c r="E199" s="7"/>
+      <c r="C199" s="5"/>
+      <c r="D199" s="6"/>
+      <c r="E199" s="6"/>
       <c r="I199" s="2"/>
     </row>
     <row r="200" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C200" s="6"/>
-      <c r="D200" s="7"/>
-      <c r="E200" s="7"/>
+      <c r="C200" s="5"/>
+      <c r="D200" s="6"/>
+      <c r="E200" s="6"/>
       <c r="I200" s="2"/>
     </row>
     <row r="201" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C201" s="6"/>
-      <c r="D201" s="7"/>
-      <c r="E201" s="7"/>
+      <c r="C201" s="5"/>
+      <c r="D201" s="6"/>
+      <c r="E201" s="6"/>
       <c r="I201" s="2"/>
     </row>
     <row r="202" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C202" s="6"/>
-      <c r="D202" s="7"/>
-      <c r="E202" s="7"/>
+      <c r="C202" s="5"/>
+      <c r="D202" s="6"/>
+      <c r="E202" s="6"/>
       <c r="I202" s="2"/>
     </row>
     <row r="203" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C203" s="6"/>
-      <c r="D203" s="7"/>
-      <c r="E203" s="7"/>
+      <c r="C203" s="5"/>
+      <c r="D203" s="6"/>
+      <c r="E203" s="6"/>
       <c r="I203" s="2"/>
     </row>
     <row r="204" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C204" s="6"/>
-      <c r="D204" s="7"/>
-      <c r="E204" s="7"/>
+      <c r="C204" s="5"/>
+      <c r="D204" s="6"/>
+      <c r="E204" s="6"/>
       <c r="I204" s="2"/>
     </row>
     <row r="205" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C205" s="6"/>
-      <c r="D205" s="7"/>
-      <c r="E205" s="7"/>
+      <c r="C205" s="5"/>
+      <c r="D205" s="6"/>
+      <c r="E205" s="6"/>
       <c r="I205" s="2"/>
     </row>
     <row r="206" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C206" s="6"/>
-      <c r="D206" s="7"/>
-      <c r="E206" s="7"/>
+      <c r="C206" s="5"/>
+      <c r="D206" s="6"/>
+      <c r="E206" s="6"/>
       <c r="I206" s="2"/>
     </row>
     <row r="207" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C207" s="6"/>
-      <c r="D207" s="7"/>
-      <c r="E207" s="7"/>
+      <c r="C207" s="5"/>
+      <c r="D207" s="6"/>
+      <c r="E207" s="6"/>
       <c r="I207" s="2"/>
     </row>
     <row r="208" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C208" s="6"/>
-      <c r="D208" s="7"/>
-      <c r="E208" s="7"/>
+      <c r="C208" s="5"/>
+      <c r="D208" s="6"/>
+      <c r="E208" s="6"/>
       <c r="I208" s="2"/>
     </row>
     <row r="209" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C209" s="6"/>
-      <c r="D209" s="7"/>
-      <c r="E209" s="7"/>
+      <c r="C209" s="5"/>
+      <c r="D209" s="6"/>
+      <c r="E209" s="6"/>
       <c r="I209" s="2"/>
     </row>
     <row r="210" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C210" s="6"/>
-      <c r="D210" s="7"/>
-      <c r="E210" s="7"/>
+      <c r="C210" s="5"/>
+      <c r="D210" s="6"/>
+      <c r="E210" s="6"/>
       <c r="I210" s="2"/>
     </row>
     <row r="211" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C211" s="6"/>
-      <c r="D211" s="7"/>
-      <c r="E211" s="7"/>
+      <c r="C211" s="5"/>
+      <c r="D211" s="6"/>
+      <c r="E211" s="6"/>
       <c r="I211" s="2"/>
     </row>
     <row r="212" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C212" s="6"/>
-      <c r="D212" s="7"/>
-      <c r="E212" s="7"/>
+      <c r="C212" s="5"/>
+      <c r="D212" s="6"/>
+      <c r="E212" s="6"/>
       <c r="I212" s="2"/>
     </row>
     <row r="213" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C213" s="6"/>
-      <c r="D213" s="7"/>
-      <c r="E213" s="7"/>
+      <c r="C213" s="5"/>
+      <c r="D213" s="6"/>
+      <c r="E213" s="6"/>
       <c r="I213" s="2"/>
     </row>
     <row r="214" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C214" s="6"/>
-      <c r="D214" s="7"/>
-      <c r="E214" s="7"/>
+      <c r="C214" s="5"/>
+      <c r="D214" s="6"/>
+      <c r="E214" s="6"/>
       <c r="I214" s="2"/>
     </row>
     <row r="215" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C215" s="6"/>
-      <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
+      <c r="C215" s="5"/>
+      <c r="D215" s="6"/>
+      <c r="E215" s="6"/>
       <c r="I215" s="2"/>
     </row>
     <row r="216" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C216" s="6"/>
-      <c r="D216" s="7"/>
-      <c r="E216" s="7"/>
+      <c r="C216" s="5"/>
+      <c r="D216" s="6"/>
+      <c r="E216" s="6"/>
       <c r="I216" s="2"/>
     </row>
     <row r="217" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C217" s="6"/>
-      <c r="D217" s="7"/>
-      <c r="E217" s="7"/>
+      <c r="C217" s="5"/>
+      <c r="D217" s="6"/>
+      <c r="E217" s="6"/>
       <c r="I217" s="2"/>
     </row>
     <row r="218" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C218" s="6"/>
-      <c r="D218" s="7"/>
-      <c r="E218" s="7"/>
+      <c r="C218" s="5"/>
+      <c r="D218" s="6"/>
+      <c r="E218" s="6"/>
       <c r="I218" s="2"/>
     </row>
     <row r="219" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C219" s="6"/>
-      <c r="D219" s="7"/>
-      <c r="E219" s="7"/>
+      <c r="C219" s="5"/>
+      <c r="D219" s="6"/>
+      <c r="E219" s="6"/>
       <c r="I219" s="2"/>
     </row>
     <row r="220" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C220" s="6"/>
-      <c r="D220" s="7"/>
-      <c r="E220" s="7"/>
+      <c r="C220" s="5"/>
+      <c r="D220" s="6"/>
+      <c r="E220" s="6"/>
       <c r="I220" s="2"/>
     </row>
     <row r="221" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C221" s="6"/>
-      <c r="D221" s="7"/>
-      <c r="E221" s="7"/>
+      <c r="C221" s="5"/>
+      <c r="D221" s="6"/>
+      <c r="E221" s="6"/>
       <c r="I221" s="2"/>
     </row>
     <row r="222" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C222" s="6"/>
-      <c r="D222" s="7"/>
-      <c r="E222" s="7"/>
+      <c r="C222" s="5"/>
+      <c r="D222" s="6"/>
+      <c r="E222" s="6"/>
       <c r="I222" s="2"/>
     </row>
     <row r="223" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C223" s="6"/>
-      <c r="D223" s="7"/>
-      <c r="E223" s="7"/>
+      <c r="C223" s="5"/>
+      <c r="D223" s="6"/>
+      <c r="E223" s="6"/>
       <c r="I223" s="2"/>
     </row>
     <row r="224" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C224" s="6"/>
-      <c r="D224" s="7"/>
-      <c r="E224" s="7"/>
+      <c r="C224" s="5"/>
+      <c r="D224" s="6"/>
+      <c r="E224" s="6"/>
       <c r="I224" s="2"/>
     </row>
     <row r="225" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C225" s="6"/>
-      <c r="D225" s="7"/>
-      <c r="E225" s="7"/>
+      <c r="C225" s="5"/>
+      <c r="D225" s="6"/>
+      <c r="E225" s="6"/>
       <c r="I225" s="2"/>
     </row>
     <row r="226" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C226" s="6"/>
-      <c r="D226" s="7"/>
-      <c r="E226" s="7"/>
+      <c r="C226" s="5"/>
+      <c r="D226" s="6"/>
+      <c r="E226" s="6"/>
       <c r="I226" s="2"/>
     </row>
     <row r="227" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C227" s="6"/>
-      <c r="D227" s="7"/>
-      <c r="E227" s="7"/>
+      <c r="C227" s="5"/>
+      <c r="D227" s="6"/>
+      <c r="E227" s="6"/>
       <c r="I227" s="2"/>
     </row>
     <row r="228" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C228" s="6"/>
-      <c r="D228" s="7"/>
-      <c r="E228" s="7"/>
+      <c r="C228" s="5"/>
+      <c r="D228" s="6"/>
+      <c r="E228" s="6"/>
       <c r="I228" s="2"/>
     </row>
     <row r="229" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C229" s="6"/>
-      <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
+      <c r="C229" s="5"/>
+      <c r="D229" s="6"/>
+      <c r="E229" s="6"/>
       <c r="I229" s="2"/>
     </row>
     <row r="230" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C230" s="6"/>
-      <c r="D230" s="7"/>
-      <c r="E230" s="7"/>
+      <c r="C230" s="5"/>
+      <c r="D230" s="6"/>
+      <c r="E230" s="6"/>
       <c r="I230" s="2"/>
     </row>
     <row r="231" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C231" s="6"/>
-      <c r="D231" s="7"/>
-      <c r="E231" s="7"/>
+      <c r="C231" s="5"/>
+      <c r="D231" s="6"/>
+      <c r="E231" s="6"/>
       <c r="I231" s="2"/>
     </row>
     <row r="232" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C232" s="6"/>
-      <c r="D232" s="7"/>
-      <c r="E232" s="7"/>
+      <c r="C232" s="5"/>
+      <c r="D232" s="6"/>
+      <c r="E232" s="6"/>
       <c r="I232" s="2"/>
     </row>
     <row r="233" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C233" s="6"/>
-      <c r="D233" s="7"/>
-      <c r="E233" s="7"/>
+      <c r="C233" s="5"/>
+      <c r="D233" s="6"/>
+      <c r="E233" s="6"/>
       <c r="I233" s="2"/>
     </row>
     <row r="234" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C234" s="6"/>
-      <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
+      <c r="C234" s="5"/>
+      <c r="D234" s="6"/>
+      <c r="E234" s="6"/>
       <c r="I234" s="2"/>
     </row>
     <row r="235" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C235" s="6"/>
-      <c r="D235" s="7"/>
-      <c r="E235" s="7"/>
+      <c r="C235" s="5"/>
+      <c r="D235" s="6"/>
+      <c r="E235" s="6"/>
       <c r="I235" s="2"/>
     </row>
     <row r="236" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C236" s="6"/>
-      <c r="D236" s="7"/>
-      <c r="E236" s="7"/>
+      <c r="C236" s="5"/>
+      <c r="D236" s="6"/>
+      <c r="E236" s="6"/>
       <c r="I236" s="2"/>
     </row>
     <row r="237" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C237" s="6"/>
-      <c r="D237" s="7"/>
-      <c r="E237" s="7"/>
+      <c r="C237" s="5"/>
+      <c r="D237" s="6"/>
+      <c r="E237" s="6"/>
       <c r="I237" s="2"/>
     </row>
     <row r="238" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C238" s="6"/>
-      <c r="D238" s="7"/>
-      <c r="E238" s="7"/>
+      <c r="C238" s="5"/>
+      <c r="D238" s="6"/>
+      <c r="E238" s="6"/>
       <c r="I238" s="2"/>
     </row>
     <row r="239" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C239" s="6"/>
-      <c r="D239" s="7"/>
-      <c r="E239" s="7"/>
+      <c r="C239" s="5"/>
+      <c r="D239" s="6"/>
+      <c r="E239" s="6"/>
       <c r="I239" s="2"/>
     </row>
     <row r="240" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C240" s="6"/>
-      <c r="D240" s="7"/>
-      <c r="E240" s="7"/>
+      <c r="C240" s="5"/>
+      <c r="D240" s="6"/>
+      <c r="E240" s="6"/>
       <c r="I240" s="2"/>
     </row>
     <row r="241" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C241" s="6"/>
-      <c r="D241" s="7"/>
-      <c r="E241" s="7"/>
+      <c r="C241" s="5"/>
+      <c r="D241" s="6"/>
+      <c r="E241" s="6"/>
       <c r="I241" s="2"/>
     </row>
     <row r="242" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C242" s="6"/>
-      <c r="D242" s="7"/>
-      <c r="E242" s="7"/>
+      <c r="C242" s="5"/>
+      <c r="D242" s="6"/>
+      <c r="E242" s="6"/>
       <c r="I242" s="2"/>
     </row>
     <row r="243" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C243" s="6"/>
-      <c r="D243" s="7"/>
-      <c r="E243" s="7"/>
+      <c r="C243" s="5"/>
+      <c r="D243" s="6"/>
+      <c r="E243" s="6"/>
       <c r="I243" s="2"/>
     </row>
     <row r="244" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C244" s="6"/>
-      <c r="D244" s="7"/>
-      <c r="E244" s="7"/>
+      <c r="C244" s="5"/>
+      <c r="D244" s="6"/>
+      <c r="E244" s="6"/>
       <c r="I244" s="2"/>
     </row>
     <row r="245" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C245" s="6"/>
-      <c r="D245" s="7"/>
-      <c r="E245" s="7"/>
+      <c r="C245" s="5"/>
+      <c r="D245" s="6"/>
+      <c r="E245" s="6"/>
       <c r="I245" s="2"/>
     </row>
     <row r="246" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C246" s="6"/>
-      <c r="D246" s="7"/>
-      <c r="E246" s="7"/>
+      <c r="C246" s="5"/>
+      <c r="D246" s="6"/>
+      <c r="E246" s="6"/>
       <c r="I246" s="2"/>
     </row>
     <row r="247" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C247" s="6"/>
-      <c r="D247" s="7"/>
-      <c r="E247" s="7"/>
+      <c r="C247" s="5"/>
+      <c r="D247" s="6"/>
+      <c r="E247" s="6"/>
       <c r="I247" s="2"/>
     </row>
     <row r="248" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C248" s="6"/>
-      <c r="D248" s="7"/>
-      <c r="E248" s="7"/>
+      <c r="C248" s="5"/>
+      <c r="D248" s="6"/>
+      <c r="E248" s="6"/>
       <c r="I248" s="2"/>
     </row>
     <row r="249" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C249" s="6"/>
-      <c r="D249" s="7"/>
-      <c r="E249" s="7"/>
+      <c r="C249" s="5"/>
+      <c r="D249" s="6"/>
+      <c r="E249" s="6"/>
       <c r="I249" s="2"/>
     </row>
     <row r="250" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C250" s="6"/>
-      <c r="D250" s="7"/>
-      <c r="E250" s="7"/>
+      <c r="C250" s="5"/>
+      <c r="D250" s="6"/>
+      <c r="E250" s="6"/>
       <c r="I250" s="2"/>
     </row>
     <row r="251" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C251" s="6"/>
-      <c r="D251" s="7"/>
-      <c r="E251" s="7"/>
+      <c r="C251" s="5"/>
+      <c r="D251" s="6"/>
+      <c r="E251" s="6"/>
       <c r="I251" s="2"/>
     </row>
     <row r="252" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C252" s="6"/>
-      <c r="D252" s="7"/>
-      <c r="E252" s="7"/>
+      <c r="C252" s="5"/>
+      <c r="D252" s="6"/>
+      <c r="E252" s="6"/>
       <c r="I252" s="2"/>
     </row>
     <row r="253" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C253" s="6"/>
-      <c r="D253" s="7"/>
-      <c r="E253" s="7"/>
+      <c r="C253" s="5"/>
+      <c r="D253" s="6"/>
+      <c r="E253" s="6"/>
       <c r="I253" s="2"/>
     </row>
     <row r="254" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C254" s="6"/>
-      <c r="D254" s="7"/>
-      <c r="E254" s="7"/>
+      <c r="C254" s="5"/>
+      <c r="D254" s="6"/>
+      <c r="E254" s="6"/>
       <c r="I254" s="2"/>
     </row>
     <row r="255" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C255" s="6"/>
-      <c r="D255" s="7"/>
-      <c r="E255" s="7"/>
+      <c r="C255" s="5"/>
+      <c r="D255" s="6"/>
+      <c r="E255" s="6"/>
       <c r="I255" s="2"/>
     </row>
     <row r="256" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C256" s="6"/>
-      <c r="D256" s="7"/>
-      <c r="E256" s="7"/>
+      <c r="C256" s="5"/>
+      <c r="D256" s="6"/>
+      <c r="E256" s="6"/>
       <c r="I256" s="2"/>
     </row>
     <row r="257" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C257" s="6"/>
-      <c r="D257" s="7"/>
-      <c r="E257" s="7"/>
+      <c r="C257" s="5"/>
+      <c r="D257" s="6"/>
+      <c r="E257" s="6"/>
       <c r="I257" s="2"/>
     </row>
     <row r="258" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C258" s="6"/>
-      <c r="D258" s="7"/>
-      <c r="E258" s="7"/>
+      <c r="C258" s="5"/>
+      <c r="D258" s="6"/>
+      <c r="E258" s="6"/>
       <c r="I258" s="2"/>
     </row>
     <row r="259" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C259" s="6"/>
-      <c r="D259" s="7"/>
-      <c r="E259" s="7"/>
+      <c r="C259" s="5"/>
+      <c r="D259" s="6"/>
+      <c r="E259" s="6"/>
       <c r="I259" s="2"/>
     </row>
     <row r="260" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C260" s="6"/>
-      <c r="D260" s="7"/>
-      <c r="E260" s="7"/>
+      <c r="C260" s="5"/>
+      <c r="D260" s="6"/>
+      <c r="E260" s="6"/>
       <c r="I260" s="2"/>
     </row>
     <row r="261" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C261" s="6"/>
-      <c r="D261" s="7"/>
-      <c r="E261" s="7"/>
+      <c r="C261" s="5"/>
+      <c r="D261" s="6"/>
+      <c r="E261" s="6"/>
       <c r="I261" s="2"/>
     </row>
     <row r="262" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C262" s="6"/>
-      <c r="D262" s="7"/>
-      <c r="E262" s="7"/>
+      <c r="C262" s="5"/>
+      <c r="D262" s="6"/>
+      <c r="E262" s="6"/>
       <c r="I262" s="2"/>
     </row>
     <row r="263" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C263" s="6"/>
-      <c r="D263" s="7"/>
-      <c r="E263" s="7"/>
+      <c r="C263" s="5"/>
+      <c r="D263" s="6"/>
+      <c r="E263" s="6"/>
       <c r="I263" s="2"/>
     </row>
     <row r="264" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C264" s="6"/>
-      <c r="D264" s="7"/>
-      <c r="E264" s="7"/>
+      <c r="C264" s="5"/>
+      <c r="D264" s="6"/>
+      <c r="E264" s="6"/>
       <c r="I264" s="2"/>
     </row>
     <row r="265" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C265" s="6"/>
-      <c r="D265" s="7"/>
-      <c r="E265" s="7"/>
+      <c r="C265" s="5"/>
+      <c r="D265" s="6"/>
+      <c r="E265" s="6"/>
       <c r="I265" s="2"/>
     </row>
     <row r="266" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C266" s="6"/>
-      <c r="D266" s="7"/>
-      <c r="E266" s="7"/>
+      <c r="C266" s="5"/>
+      <c r="D266" s="6"/>
+      <c r="E266" s="6"/>
       <c r="I266" s="2"/>
     </row>
     <row r="267" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C267" s="6"/>
-      <c r="D267" s="7"/>
-      <c r="E267" s="7"/>
+      <c r="C267" s="5"/>
+      <c r="D267" s="6"/>
+      <c r="E267" s="6"/>
       <c r="I267" s="2"/>
     </row>
     <row r="268" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C268" s="6"/>
-      <c r="D268" s="7"/>
-      <c r="E268" s="7"/>
+      <c r="C268" s="5"/>
+      <c r="D268" s="6"/>
+      <c r="E268" s="6"/>
       <c r="I268" s="2"/>
     </row>
     <row r="269" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C269" s="6"/>
-      <c r="D269" s="7"/>
-      <c r="E269" s="7"/>
+      <c r="C269" s="5"/>
+      <c r="D269" s="6"/>
+      <c r="E269" s="6"/>
       <c r="I269" s="2"/>
     </row>
     <row r="270" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C270" s="6"/>
-      <c r="D270" s="7"/>
-      <c r="E270" s="7"/>
+      <c r="C270" s="5"/>
+      <c r="D270" s="6"/>
+      <c r="E270" s="6"/>
       <c r="I270" s="2"/>
     </row>
     <row r="271" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C271" s="6"/>
-      <c r="D271" s="7"/>
-      <c r="E271" s="7"/>
+      <c r="C271" s="5"/>
+      <c r="D271" s="6"/>
+      <c r="E271" s="6"/>
       <c r="I271" s="2"/>
     </row>
     <row r="272" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C272" s="6"/>
-      <c r="D272" s="7"/>
-      <c r="E272" s="7"/>
+      <c r="C272" s="5"/>
+      <c r="D272" s="6"/>
+      <c r="E272" s="6"/>
       <c r="I272" s="2"/>
     </row>
     <row r="273" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C273" s="6"/>
-      <c r="D273" s="7"/>
-      <c r="E273" s="7"/>
+      <c r="C273" s="5"/>
+      <c r="D273" s="6"/>
+      <c r="E273" s="6"/>
       <c r="I273" s="2"/>
     </row>
     <row r="274" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C274" s="6"/>
-      <c r="D274" s="7"/>
-      <c r="E274" s="7"/>
+      <c r="C274" s="5"/>
+      <c r="D274" s="6"/>
+      <c r="E274" s="6"/>
       <c r="I274" s="2"/>
     </row>
     <row r="275" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C275" s="6"/>
-      <c r="D275" s="7"/>
-      <c r="E275" s="7"/>
+      <c r="C275" s="5"/>
+      <c r="D275" s="6"/>
+      <c r="E275" s="6"/>
       <c r="I275" s="2"/>
     </row>
     <row r="276" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C276" s="6"/>
-      <c r="D276" s="7"/>
-      <c r="E276" s="7"/>
+      <c r="C276" s="5"/>
+      <c r="D276" s="6"/>
+      <c r="E276" s="6"/>
       <c r="I276" s="2"/>
     </row>
     <row r="277" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C277" s="6"/>
-      <c r="D277" s="7"/>
-      <c r="E277" s="7"/>
+      <c r="C277" s="5"/>
+      <c r="D277" s="6"/>
+      <c r="E277" s="6"/>
       <c r="I277" s="2"/>
     </row>
     <row r="278" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C278" s="6"/>
-      <c r="D278" s="7"/>
-      <c r="E278" s="7"/>
+      <c r="C278" s="5"/>
+      <c r="D278" s="6"/>
+      <c r="E278" s="6"/>
       <c r="I278" s="2"/>
     </row>
     <row r="279" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C279" s="6"/>
-      <c r="D279" s="7"/>
-      <c r="E279" s="7"/>
+      <c r="C279" s="5"/>
+      <c r="D279" s="6"/>
+      <c r="E279" s="6"/>
       <c r="I279" s="2"/>
     </row>
     <row r="280" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C280" s="6"/>
-      <c r="D280" s="7"/>
-      <c r="E280" s="7"/>
+      <c r="C280" s="5"/>
+      <c r="D280" s="6"/>
+      <c r="E280" s="6"/>
       <c r="I280" s="2"/>
     </row>
     <row r="281" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C281" s="6"/>
-      <c r="D281" s="7"/>
-      <c r="E281" s="7"/>
+      <c r="C281" s="5"/>
+      <c r="D281" s="6"/>
+      <c r="E281" s="6"/>
       <c r="I281" s="2"/>
     </row>
     <row r="282" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C282" s="6"/>
-      <c r="D282" s="7"/>
-      <c r="E282" s="7"/>
+      <c r="C282" s="5"/>
+      <c r="D282" s="6"/>
+      <c r="E282" s="6"/>
       <c r="I282" s="2"/>
     </row>
     <row r="283" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C283" s="6"/>
-      <c r="D283" s="7"/>
-      <c r="E283" s="7"/>
+      <c r="C283" s="5"/>
+      <c r="D283" s="6"/>
+      <c r="E283" s="6"/>
       <c r="I283" s="2"/>
     </row>
     <row r="284" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C284" s="6"/>
-      <c r="D284" s="7"/>
-      <c r="E284" s="7"/>
+      <c r="C284" s="5"/>
+      <c r="D284" s="6"/>
+      <c r="E284" s="6"/>
       <c r="I284" s="2"/>
     </row>
     <row r="285" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C285" s="6"/>
-      <c r="D285" s="7"/>
-      <c r="E285" s="7"/>
+      <c r="C285" s="5"/>
+      <c r="D285" s="6"/>
+      <c r="E285" s="6"/>
       <c r="I285" s="2"/>
     </row>
     <row r="286" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C286" s="6"/>
-      <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
+      <c r="C286" s="5"/>
+      <c r="D286" s="6"/>
+      <c r="E286" s="6"/>
       <c r="I286" s="2"/>
     </row>
     <row r="287" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C287" s="6"/>
-      <c r="D287" s="7"/>
-      <c r="E287" s="7"/>
+      <c r="C287" s="5"/>
+      <c r="D287" s="6"/>
+      <c r="E287" s="6"/>
       <c r="I287" s="2"/>
     </row>
     <row r="288" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C288" s="6"/>
-      <c r="D288" s="7"/>
-      <c r="E288" s="7"/>
+      <c r="C288" s="5"/>
+      <c r="D288" s="6"/>
+      <c r="E288" s="6"/>
       <c r="I288" s="2"/>
     </row>
     <row r="289" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C289" s="6"/>
-      <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
+      <c r="C289" s="5"/>
+      <c r="D289" s="6"/>
+      <c r="E289" s="6"/>
       <c r="I289" s="2"/>
     </row>
     <row r="290" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C290" s="6"/>
-      <c r="D290" s="7"/>
-      <c r="E290" s="7"/>
+      <c r="C290" s="5"/>
+      <c r="D290" s="6"/>
+      <c r="E290" s="6"/>
       <c r="I290" s="2"/>
     </row>
     <row r="291" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C291" s="6"/>
-      <c r="D291" s="7"/>
-      <c r="E291" s="7"/>
+      <c r="C291" s="5"/>
+      <c r="D291" s="6"/>
+      <c r="E291" s="6"/>
       <c r="I291" s="2"/>
     </row>
     <row r="292" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C292" s="6"/>
-      <c r="D292" s="7"/>
-      <c r="E292" s="7"/>
+      <c r="C292" s="5"/>
+      <c r="D292" s="6"/>
+      <c r="E292" s="6"/>
       <c r="I292" s="2"/>
     </row>
     <row r="293" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C293" s="6"/>
-      <c r="D293" s="7"/>
-      <c r="E293" s="7"/>
+      <c r="C293" s="5"/>
+      <c r="D293" s="6"/>
+      <c r="E293" s="6"/>
       <c r="I293" s="2"/>
     </row>
     <row r="294" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C294" s="6"/>
-      <c r="D294" s="7"/>
-      <c r="E294" s="7"/>
+      <c r="C294" s="5"/>
+      <c r="D294" s="6"/>
+      <c r="E294" s="6"/>
       <c r="I294" s="2"/>
     </row>
     <row r="295" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C295" s="6"/>
-      <c r="D295" s="7"/>
-      <c r="E295" s="7"/>
+      <c r="C295" s="5"/>
+      <c r="D295" s="6"/>
+      <c r="E295" s="6"/>
       <c r="I295" s="2"/>
     </row>
     <row r="296" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C296" s="6"/>
-      <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
+      <c r="C296" s="5"/>
+      <c r="D296" s="6"/>
+      <c r="E296" s="6"/>
       <c r="I296" s="2"/>
     </row>
     <row r="297" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C297" s="6"/>
-      <c r="D297" s="7"/>
-      <c r="E297" s="7"/>
+      <c r="C297" s="5"/>
+      <c r="D297" s="6"/>
+      <c r="E297" s="6"/>
       <c r="I297" s="2"/>
     </row>
     <row r="298" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C298" s="6"/>
-      <c r="D298" s="7"/>
-      <c r="E298" s="7"/>
+      <c r="C298" s="5"/>
+      <c r="D298" s="6"/>
+      <c r="E298" s="6"/>
       <c r="I298" s="2"/>
     </row>
     <row r="299" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C299" s="6"/>
-      <c r="D299" s="7"/>
-      <c r="E299" s="7"/>
+      <c r="C299" s="5"/>
+      <c r="D299" s="6"/>
+      <c r="E299" s="6"/>
       <c r="I299" s="2"/>
     </row>
     <row r="300" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C300" s="6"/>
-      <c r="D300" s="7"/>
-      <c r="E300" s="7"/>
+      <c r="C300" s="5"/>
+      <c r="D300" s="6"/>
+      <c r="E300" s="6"/>
       <c r="I300" s="2"/>
     </row>
     <row r="301" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C301" s="6"/>
-      <c r="D301" s="7"/>
-      <c r="E301" s="7"/>
+      <c r="C301" s="5"/>
+      <c r="D301" s="6"/>
+      <c r="E301" s="6"/>
       <c r="I301" s="2"/>
     </row>
     <row r="302" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C302" s="6"/>
-      <c r="D302" s="7"/>
-      <c r="E302" s="7"/>
+      <c r="C302" s="5"/>
+      <c r="D302" s="6"/>
+      <c r="E302" s="6"/>
       <c r="I302" s="2"/>
     </row>
     <row r="303" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C303" s="6"/>
-      <c r="D303" s="7"/>
-      <c r="E303" s="7"/>
+      <c r="C303" s="5"/>
+      <c r="D303" s="6"/>
+      <c r="E303" s="6"/>
       <c r="I303" s="2"/>
     </row>
     <row r="304" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C304" s="6"/>
-      <c r="D304" s="7"/>
-      <c r="E304" s="7"/>
+      <c r="C304" s="5"/>
+      <c r="D304" s="6"/>
+      <c r="E304" s="6"/>
       <c r="I304" s="2"/>
     </row>
     <row r="305" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C305" s="6"/>
-      <c r="D305" s="7"/>
-      <c r="E305" s="7"/>
+      <c r="C305" s="5"/>
+      <c r="D305" s="6"/>
+      <c r="E305" s="6"/>
       <c r="I305" s="2"/>
     </row>
     <row r="306" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C306" s="6"/>
-      <c r="D306" s="7"/>
-      <c r="E306" s="7"/>
+      <c r="C306" s="5"/>
+      <c r="D306" s="6"/>
+      <c r="E306" s="6"/>
       <c r="I306" s="2"/>
     </row>
     <row r="307" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C307" s="6"/>
-      <c r="D307" s="7"/>
-      <c r="E307" s="7"/>
+      <c r="C307" s="5"/>
+      <c r="D307" s="6"/>
+      <c r="E307" s="6"/>
       <c r="I307" s="2"/>
     </row>
     <row r="308" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C308" s="6"/>
-      <c r="D308" s="7"/>
-      <c r="E308" s="7"/>
+      <c r="C308" s="5"/>
+      <c r="D308" s="6"/>
+      <c r="E308" s="6"/>
       <c r="I308" s="2"/>
     </row>
     <row r="309" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C309" s="6"/>
-      <c r="D309" s="7"/>
-      <c r="E309" s="7"/>
+      <c r="C309" s="5"/>
+      <c r="D309" s="6"/>
+      <c r="E309" s="6"/>
       <c r="I309" s="2"/>
     </row>
     <row r="310" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C310" s="6"/>
-      <c r="D310" s="7"/>
-      <c r="E310" s="7"/>
+      <c r="C310" s="5"/>
+      <c r="D310" s="6"/>
+      <c r="E310" s="6"/>
       <c r="I310" s="2"/>
     </row>
     <row r="311" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C311" s="6"/>
-      <c r="D311" s="7"/>
-      <c r="E311" s="7"/>
+      <c r="C311" s="5"/>
+      <c r="D311" s="6"/>
+      <c r="E311" s="6"/>
       <c r="I311" s="2"/>
     </row>
     <row r="312" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C312" s="6"/>
-      <c r="D312" s="7"/>
-      <c r="E312" s="7"/>
+      <c r="C312" s="5"/>
+      <c r="D312" s="6"/>
+      <c r="E312" s="6"/>
       <c r="I312" s="2"/>
     </row>
     <row r="313" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C313" s="6"/>
-      <c r="D313" s="7"/>
-      <c r="E313" s="7"/>
+      <c r="C313" s="5"/>
+      <c r="D313" s="6"/>
+      <c r="E313" s="6"/>
       <c r="I313" s="2"/>
     </row>
     <row r="314" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C314" s="6"/>
-      <c r="D314" s="7"/>
-      <c r="E314" s="7"/>
+      <c r="C314" s="5"/>
+      <c r="D314" s="6"/>
+      <c r="E314" s="6"/>
       <c r="I314" s="2"/>
     </row>
     <row r="315" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C315" s="6"/>
-      <c r="D315" s="7"/>
-      <c r="E315" s="7"/>
+      <c r="C315" s="5"/>
+      <c r="D315" s="6"/>
+      <c r="E315" s="6"/>
       <c r="I315" s="2"/>
     </row>
     <row r="316" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C316" s="6"/>
-      <c r="D316" s="7"/>
-      <c r="E316" s="7"/>
+      <c r="C316" s="5"/>
+      <c r="D316" s="6"/>
+      <c r="E316" s="6"/>
       <c r="I316" s="2"/>
     </row>
     <row r="317" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C317" s="6"/>
-      <c r="D317" s="7"/>
-      <c r="E317" s="7"/>
+      <c r="C317" s="5"/>
+      <c r="D317" s="6"/>
+      <c r="E317" s="6"/>
       <c r="I317" s="2"/>
     </row>
     <row r="318" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C318" s="6"/>
-      <c r="D318" s="7"/>
-      <c r="E318" s="7"/>
+      <c r="C318" s="5"/>
+      <c r="D318" s="6"/>
+      <c r="E318" s="6"/>
       <c r="I318" s="2"/>
     </row>
     <row r="319" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C319" s="6"/>
-      <c r="D319" s="7"/>
-      <c r="E319" s="7"/>
+      <c r="C319" s="5"/>
+      <c r="D319" s="6"/>
+      <c r="E319" s="6"/>
       <c r="I319" s="2"/>
     </row>
     <row r="320" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C320" s="6"/>
-      <c r="D320" s="7"/>
-      <c r="E320" s="7"/>
+      <c r="C320" s="5"/>
+      <c r="D320" s="6"/>
+      <c r="E320" s="6"/>
       <c r="I320" s="2"/>
     </row>
     <row r="321" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C321" s="6"/>
-      <c r="D321" s="7"/>
-      <c r="E321" s="7"/>
+      <c r="C321" s="5"/>
+      <c r="D321" s="6"/>
+      <c r="E321" s="6"/>
       <c r="I321" s="2"/>
     </row>
     <row r="322" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C322" s="6"/>
-      <c r="D322" s="7"/>
-      <c r="E322" s="7"/>
+      <c r="C322" s="5"/>
+      <c r="D322" s="6"/>
+      <c r="E322" s="6"/>
       <c r="I322" s="2"/>
     </row>
     <row r="323" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C323" s="6"/>
-      <c r="D323" s="7"/>
-      <c r="E323" s="7"/>
+      <c r="C323" s="5"/>
+      <c r="D323" s="6"/>
+      <c r="E323" s="6"/>
       <c r="I323" s="2"/>
     </row>
     <row r="324" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C324" s="6"/>
-      <c r="D324" s="7"/>
-      <c r="E324" s="7"/>
+      <c r="C324" s="5"/>
+      <c r="D324" s="6"/>
+      <c r="E324" s="6"/>
       <c r="I324" s="2"/>
     </row>
     <row r="325" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C325" s="6"/>
-      <c r="D325" s="7"/>
-      <c r="E325" s="7"/>
+      <c r="C325" s="5"/>
+      <c r="D325" s="6"/>
+      <c r="E325" s="6"/>
       <c r="I325" s="2"/>
     </row>
     <row r="326" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C326" s="6"/>
-      <c r="D326" s="7"/>
-      <c r="E326" s="7"/>
+      <c r="C326" s="5"/>
+      <c r="D326" s="6"/>
+      <c r="E326" s="6"/>
       <c r="I326" s="2"/>
     </row>
     <row r="327" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C327" s="6"/>
-      <c r="D327" s="7"/>
-      <c r="E327" s="7"/>
+      <c r="C327" s="5"/>
+      <c r="D327" s="6"/>
+      <c r="E327" s="6"/>
       <c r="I327" s="2"/>
     </row>
     <row r="328" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C328" s="6"/>
-      <c r="D328" s="7"/>
-      <c r="E328" s="7"/>
+      <c r="C328" s="5"/>
+      <c r="D328" s="6"/>
+      <c r="E328" s="6"/>
       <c r="I328" s="2"/>
     </row>
     <row r="329" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C329" s="6"/>
-      <c r="D329" s="7"/>
-      <c r="E329" s="7"/>
+      <c r="C329" s="5"/>
+      <c r="D329" s="6"/>
+      <c r="E329" s="6"/>
       <c r="I329" s="2"/>
     </row>
     <row r="330" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C330" s="6"/>
-      <c r="D330" s="7"/>
-      <c r="E330" s="7"/>
+      <c r="C330" s="5"/>
+      <c r="D330" s="6"/>
+      <c r="E330" s="6"/>
       <c r="I330" s="2"/>
     </row>
     <row r="331" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C331" s="6"/>
-      <c r="D331" s="7"/>
-      <c r="E331" s="7"/>
+      <c r="C331" s="5"/>
+      <c r="D331" s="6"/>
+      <c r="E331" s="6"/>
       <c r="I331" s="2"/>
     </row>
     <row r="332" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C332" s="6"/>
-      <c r="D332" s="7"/>
-      <c r="E332" s="7"/>
+      <c r="C332" s="5"/>
+      <c r="D332" s="6"/>
+      <c r="E332" s="6"/>
       <c r="I332" s="2"/>
     </row>
     <row r="333" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C333" s="6"/>
-      <c r="D333" s="7"/>
-      <c r="E333" s="7"/>
+      <c r="C333" s="5"/>
+      <c r="D333" s="6"/>
+      <c r="E333" s="6"/>
       <c r="I333" s="2"/>
     </row>
     <row r="334" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C334" s="6"/>
-      <c r="D334" s="7"/>
-      <c r="E334" s="7"/>
+      <c r="C334" s="5"/>
+      <c r="D334" s="6"/>
+      <c r="E334" s="6"/>
       <c r="I334" s="2"/>
     </row>
     <row r="335" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C335" s="6"/>
-      <c r="D335" s="7"/>
-      <c r="E335" s="7"/>
+      <c r="C335" s="5"/>
+      <c r="D335" s="6"/>
+      <c r="E335" s="6"/>
       <c r="I335" s="2"/>
     </row>
     <row r="336" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C336" s="6"/>
-      <c r="D336" s="7"/>
-      <c r="E336" s="7"/>
+      <c r="C336" s="5"/>
+      <c r="D336" s="6"/>
+      <c r="E336" s="6"/>
       <c r="I336" s="2"/>
     </row>
     <row r="337" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C337" s="6"/>
-      <c r="D337" s="7"/>
-      <c r="E337" s="7"/>
+      <c r="C337" s="5"/>
+      <c r="D337" s="6"/>
+      <c r="E337" s="6"/>
       <c r="I337" s="2"/>
     </row>
     <row r="338" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C338" s="6"/>
-      <c r="D338" s="7"/>
-      <c r="E338" s="7"/>
+      <c r="C338" s="5"/>
+      <c r="D338" s="6"/>
+      <c r="E338" s="6"/>
       <c r="I338" s="2"/>
     </row>
     <row r="339" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C339" s="6"/>
-      <c r="D339" s="7"/>
-      <c r="E339" s="7"/>
+      <c r="C339" s="5"/>
+      <c r="D339" s="6"/>
+      <c r="E339" s="6"/>
       <c r="I339" s="2"/>
     </row>
     <row r="340" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C340" s="6"/>
-      <c r="D340" s="7"/>
-      <c r="E340" s="7"/>
+      <c r="C340" s="5"/>
+      <c r="D340" s="6"/>
+      <c r="E340" s="6"/>
       <c r="I340" s="2"/>
     </row>
     <row r="341" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C341" s="6"/>
-      <c r="D341" s="7"/>
-      <c r="E341" s="7"/>
+      <c r="C341" s="5"/>
+      <c r="D341" s="6"/>
+      <c r="E341" s="6"/>
       <c r="I341" s="2"/>
     </row>
     <row r="342" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C342" s="6"/>
-      <c r="D342" s="7"/>
-      <c r="E342" s="7"/>
+      <c r="C342" s="5"/>
+      <c r="D342" s="6"/>
+      <c r="E342" s="6"/>
       <c r="I342" s="2"/>
     </row>
     <row r="343" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C343" s="6"/>
-      <c r="D343" s="7"/>
-      <c r="E343" s="7"/>
+      <c r="C343" s="5"/>
+      <c r="D343" s="6"/>
+      <c r="E343" s="6"/>
       <c r="I343" s="2"/>
     </row>
     <row r="344" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C344" s="6"/>
-      <c r="D344" s="7"/>
-      <c r="E344" s="7"/>
+      <c r="C344" s="5"/>
+      <c r="D344" s="6"/>
+      <c r="E344" s="6"/>
       <c r="I344" s="2"/>
     </row>
     <row r="345" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C345" s="6"/>
-      <c r="D345" s="7"/>
-      <c r="E345" s="7"/>
+      <c r="C345" s="5"/>
+      <c r="D345" s="6"/>
+      <c r="E345" s="6"/>
       <c r="I345" s="2"/>
     </row>
     <row r="346" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C346" s="6"/>
-      <c r="D346" s="7"/>
-      <c r="E346" s="7"/>
+      <c r="C346" s="5"/>
+      <c r="D346" s="6"/>
+      <c r="E346" s="6"/>
       <c r="I346" s="2"/>
     </row>
     <row r="347" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C347" s="6"/>
-      <c r="D347" s="7"/>
-      <c r="E347" s="7"/>
+      <c r="C347" s="5"/>
+      <c r="D347" s="6"/>
+      <c r="E347" s="6"/>
       <c r="I347" s="2"/>
     </row>
     <row r="348" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C348" s="6"/>
-      <c r="D348" s="7"/>
-      <c r="E348" s="7"/>
+      <c r="C348" s="5"/>
+      <c r="D348" s="6"/>
+      <c r="E348" s="6"/>
       <c r="I348" s="2"/>
     </row>
     <row r="349" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C349" s="6"/>
-      <c r="D349" s="7"/>
-      <c r="E349" s="7"/>
+      <c r="C349" s="5"/>
+      <c r="D349" s="6"/>
+      <c r="E349" s="6"/>
       <c r="I349" s="2"/>
     </row>
     <row r="350" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C350" s="6"/>
-      <c r="D350" s="7"/>
-      <c r="E350" s="7"/>
+      <c r="C350" s="5"/>
+      <c r="D350" s="6"/>
+      <c r="E350" s="6"/>
       <c r="I350" s="2"/>
     </row>
     <row r="351" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C351" s="6"/>
-      <c r="D351" s="7"/>
-      <c r="E351" s="7"/>
+      <c r="C351" s="5"/>
+      <c r="D351" s="6"/>
+      <c r="E351" s="6"/>
       <c r="I351" s="2"/>
     </row>
     <row r="352" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C352" s="6"/>
-      <c r="D352" s="7"/>
-      <c r="E352" s="7"/>
+      <c r="C352" s="5"/>
+      <c r="D352" s="6"/>
+      <c r="E352" s="6"/>
       <c r="I352" s="2"/>
     </row>
     <row r="353" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C353" s="6"/>
-      <c r="D353" s="7"/>
-      <c r="E353" s="7"/>
+      <c r="C353" s="5"/>
+      <c r="D353" s="6"/>
+      <c r="E353" s="6"/>
       <c r="I353" s="2"/>
     </row>
     <row r="354" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C354" s="6"/>
-      <c r="D354" s="7"/>
-      <c r="E354" s="7"/>
+      <c r="C354" s="5"/>
+      <c r="D354" s="6"/>
+      <c r="E354" s="6"/>
       <c r="I354" s="2"/>
     </row>
     <row r="355" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C355" s="6"/>
-      <c r="D355" s="7"/>
-      <c r="E355" s="7"/>
+      <c r="C355" s="5"/>
+      <c r="D355" s="6"/>
+      <c r="E355" s="6"/>
       <c r="I355" s="2"/>
     </row>
     <row r="356" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C356" s="6"/>
-      <c r="D356" s="7"/>
-      <c r="E356" s="7"/>
+      <c r="C356" s="5"/>
+      <c r="D356" s="6"/>
+      <c r="E356" s="6"/>
       <c r="I356" s="2"/>
     </row>
     <row r="357" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C357" s="6"/>
-      <c r="D357" s="7"/>
-      <c r="E357" s="7"/>
+      <c r="C357" s="5"/>
+      <c r="D357" s="6"/>
+      <c r="E357" s="6"/>
       <c r="I357" s="2"/>
     </row>
     <row r="358" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C358" s="6"/>
-      <c r="D358" s="7"/>
-      <c r="E358" s="7"/>
+      <c r="C358" s="5"/>
+      <c r="D358" s="6"/>
+      <c r="E358" s="6"/>
       <c r="I358" s="2"/>
     </row>
     <row r="359" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C359" s="6"/>
-      <c r="D359" s="7"/>
-      <c r="E359" s="7"/>
+      <c r="C359" s="5"/>
+      <c r="D359" s="6"/>
+      <c r="E359" s="6"/>
       <c r="I359" s="2"/>
     </row>
     <row r="360" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C360" s="6"/>
-      <c r="D360" s="7"/>
-      <c r="E360" s="7"/>
+      <c r="C360" s="5"/>
+      <c r="D360" s="6"/>
+      <c r="E360" s="6"/>
       <c r="I360" s="2"/>
     </row>
     <row r="361" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C361" s="6"/>
-      <c r="D361" s="7"/>
-      <c r="E361" s="7"/>
+      <c r="C361" s="5"/>
+      <c r="D361" s="6"/>
+      <c r="E361" s="6"/>
       <c r="I361" s="2"/>
     </row>
     <row r="362" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C362" s="6"/>
-      <c r="D362" s="7"/>
-      <c r="E362" s="7"/>
+      <c r="C362" s="5"/>
+      <c r="D362" s="6"/>
+      <c r="E362" s="6"/>
       <c r="I362" s="2"/>
     </row>
     <row r="363" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C363" s="6"/>
-      <c r="D363" s="7"/>
-      <c r="E363" s="7"/>
+      <c r="C363" s="5"/>
+      <c r="D363" s="6"/>
+      <c r="E363" s="6"/>
       <c r="I363" s="2"/>
     </row>
     <row r="364" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C364" s="6"/>
-      <c r="D364" s="7"/>
-      <c r="E364" s="7"/>
+      <c r="C364" s="5"/>
+      <c r="D364" s="6"/>
+      <c r="E364" s="6"/>
       <c r="I364" s="2"/>
     </row>
     <row r="365" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C365" s="6"/>
-      <c r="D365" s="7"/>
-      <c r="E365" s="7"/>
+      <c r="C365" s="5"/>
+      <c r="D365" s="6"/>
+      <c r="E365" s="6"/>
       <c r="I365" s="2"/>
     </row>
     <row r="366" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C366" s="6"/>
-      <c r="D366" s="7"/>
-      <c r="E366" s="7"/>
+      <c r="C366" s="5"/>
+      <c r="D366" s="6"/>
+      <c r="E366" s="6"/>
       <c r="I366" s="2"/>
     </row>
     <row r="367" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C367" s="6"/>
-      <c r="D367" s="7"/>
-      <c r="E367" s="7"/>
+      <c r="C367" s="5"/>
+      <c r="D367" s="6"/>
+      <c r="E367" s="6"/>
       <c r="I367" s="2"/>
     </row>
     <row r="368" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C368" s="6"/>
-      <c r="D368" s="7"/>
-      <c r="E368" s="7"/>
+      <c r="C368" s="5"/>
+      <c r="D368" s="6"/>
+      <c r="E368" s="6"/>
       <c r="I368" s="2"/>
     </row>
     <row r="369" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C369" s="6"/>
-      <c r="D369" s="7"/>
-      <c r="E369" s="7"/>
+      <c r="C369" s="5"/>
+      <c r="D369" s="6"/>
+      <c r="E369" s="6"/>
       <c r="I369" s="2"/>
     </row>
     <row r="370" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C370" s="6"/>
-      <c r="D370" s="7"/>
-      <c r="E370" s="7"/>
+      <c r="C370" s="5"/>
+      <c r="D370" s="6"/>
+      <c r="E370" s="6"/>
       <c r="I370" s="2"/>
     </row>
     <row r="371" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C371" s="6"/>
-      <c r="D371" s="7"/>
-      <c r="E371" s="7"/>
+      <c r="C371" s="5"/>
+      <c r="D371" s="6"/>
+      <c r="E371" s="6"/>
       <c r="I371" s="2"/>
     </row>
     <row r="372" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C372" s="6"/>
-      <c r="D372" s="7"/>
-      <c r="E372" s="7"/>
+      <c r="C372" s="5"/>
+      <c r="D372" s="6"/>
+      <c r="E372" s="6"/>
       <c r="I372" s="2"/>
     </row>
     <row r="373" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C373" s="6"/>
-      <c r="D373" s="7"/>
-      <c r="E373" s="7"/>
+      <c r="C373" s="5"/>
+      <c r="D373" s="6"/>
+      <c r="E373" s="6"/>
       <c r="I373" s="2"/>
     </row>
     <row r="374" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C374" s="6"/>
-      <c r="D374" s="7"/>
-      <c r="E374" s="7"/>
+      <c r="C374" s="5"/>
+      <c r="D374" s="6"/>
+      <c r="E374" s="6"/>
       <c r="I374" s="2"/>
     </row>
     <row r="375" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C375" s="6"/>
-      <c r="D375" s="7"/>
-      <c r="E375" s="7"/>
+      <c r="C375" s="5"/>
+      <c r="D375" s="6"/>
+      <c r="E375" s="6"/>
       <c r="I375" s="2"/>
     </row>
     <row r="376" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C376" s="6"/>
-      <c r="D376" s="7"/>
-      <c r="E376" s="7"/>
+      <c r="C376" s="5"/>
+      <c r="D376" s="6"/>
+      <c r="E376" s="6"/>
       <c r="I376" s="2"/>
     </row>
     <row r="377" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C377" s="6"/>
-      <c r="D377" s="7"/>
-      <c r="E377" s="7"/>
+      <c r="C377" s="5"/>
+      <c r="D377" s="6"/>
+      <c r="E377" s="6"/>
       <c r="I377" s="2"/>
     </row>
     <row r="378" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C378" s="6"/>
-      <c r="D378" s="7"/>
-      <c r="E378" s="7"/>
+      <c r="C378" s="5"/>
+      <c r="D378" s="6"/>
+      <c r="E378" s="6"/>
       <c r="I378" s="2"/>
     </row>
     <row r="379" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C379" s="6"/>
-      <c r="D379" s="7"/>
-      <c r="E379" s="7"/>
+      <c r="C379" s="5"/>
+      <c r="D379" s="6"/>
+      <c r="E379" s="6"/>
       <c r="I379" s="2"/>
     </row>
     <row r="380" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C380" s="6"/>
-      <c r="D380" s="7"/>
-      <c r="E380" s="7"/>
+      <c r="C380" s="5"/>
+      <c r="D380" s="6"/>
+      <c r="E380" s="6"/>
       <c r="I380" s="2"/>
     </row>
     <row r="381" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C381" s="6"/>
-      <c r="D381" s="7"/>
-      <c r="E381" s="7"/>
+      <c r="C381" s="5"/>
+      <c r="D381" s="6"/>
+      <c r="E381" s="6"/>
       <c r="I381" s="2"/>
     </row>
     <row r="382" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C382" s="6"/>
-      <c r="D382" s="7"/>
-      <c r="E382" s="7"/>
+      <c r="C382" s="5"/>
+      <c r="D382" s="6"/>
+      <c r="E382" s="6"/>
       <c r="I382" s="2"/>
     </row>
     <row r="383" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C383" s="6"/>
-      <c r="D383" s="7"/>
-      <c r="E383" s="7"/>
+      <c r="C383" s="5"/>
+      <c r="D383" s="6"/>
+      <c r="E383" s="6"/>
       <c r="I383" s="2"/>
     </row>
     <row r="384" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C384" s="6"/>
-      <c r="D384" s="7"/>
-      <c r="E384" s="7"/>
+      <c r="C384" s="5"/>
+      <c r="D384" s="6"/>
+      <c r="E384" s="6"/>
       <c r="I384" s="2"/>
     </row>
     <row r="385" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C385" s="6"/>
-      <c r="D385" s="7"/>
-      <c r="E385" s="7"/>
+      <c r="C385" s="5"/>
+      <c r="D385" s="6"/>
+      <c r="E385" s="6"/>
       <c r="I385" s="2"/>
     </row>
     <row r="386" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C386" s="6"/>
-      <c r="D386" s="7"/>
-      <c r="E386" s="7"/>
+      <c r="C386" s="5"/>
+      <c r="D386" s="6"/>
+      <c r="E386" s="6"/>
       <c r="I386" s="2"/>
     </row>
     <row r="387" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C387" s="6"/>
-      <c r="D387" s="7"/>
-      <c r="E387" s="7"/>
+      <c r="C387" s="5"/>
+      <c r="D387" s="6"/>
+      <c r="E387" s="6"/>
       <c r="I387" s="2"/>
     </row>
     <row r="388" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C388" s="6"/>
-      <c r="D388" s="7"/>
-      <c r="E388" s="7"/>
+      <c r="C388" s="5"/>
+      <c r="D388" s="6"/>
+      <c r="E388" s="6"/>
       <c r="I388" s="2"/>
     </row>
     <row r="389" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C389" s="6"/>
-      <c r="D389" s="7"/>
-      <c r="E389" s="7"/>
+      <c r="C389" s="5"/>
+      <c r="D389" s="6"/>
+      <c r="E389" s="6"/>
       <c r="I389" s="2"/>
     </row>
     <row r="390" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C390" s="6"/>
-      <c r="D390" s="7"/>
-      <c r="E390" s="7"/>
+      <c r="C390" s="5"/>
+      <c r="D390" s="6"/>
+      <c r="E390" s="6"/>
       <c r="I390" s="2"/>
     </row>
     <row r="391" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C391" s="6"/>
-      <c r="D391" s="7"/>
-      <c r="E391" s="7"/>
+      <c r="C391" s="5"/>
+      <c r="D391" s="6"/>
+      <c r="E391" s="6"/>
       <c r="I391" s="2"/>
     </row>
     <row r="392" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C392" s="6"/>
-      <c r="D392" s="7"/>
-      <c r="E392" s="7"/>
+      <c r="C392" s="5"/>
+      <c r="D392" s="6"/>
+      <c r="E392" s="6"/>
       <c r="I392" s="2"/>
     </row>
     <row r="393" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C393" s="6"/>
-      <c r="D393" s="7"/>
-      <c r="E393" s="7"/>
+      <c r="C393" s="5"/>
+      <c r="D393" s="6"/>
+      <c r="E393" s="6"/>
       <c r="I393" s="2"/>
     </row>
     <row r="394" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C394" s="6"/>
-      <c r="D394" s="7"/>
-      <c r="E394" s="7"/>
+      <c r="C394" s="5"/>
+      <c r="D394" s="6"/>
+      <c r="E394" s="6"/>
       <c r="I394" s="2"/>
     </row>
     <row r="395" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C395" s="6"/>
-      <c r="D395" s="7"/>
-      <c r="E395" s="7"/>
+      <c r="C395" s="5"/>
+      <c r="D395" s="6"/>
+      <c r="E395" s="6"/>
       <c r="I395" s="2"/>
     </row>
     <row r="396" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C396" s="6"/>
-      <c r="D396" s="7"/>
-      <c r="E396" s="7"/>
+      <c r="C396" s="5"/>
+      <c r="D396" s="6"/>
+      <c r="E396" s="6"/>
       <c r="I396" s="2"/>
     </row>
     <row r="397" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C397" s="6"/>
-      <c r="D397" s="7"/>
-      <c r="E397" s="7"/>
+      <c r="C397" s="5"/>
+      <c r="D397" s="6"/>
+      <c r="E397" s="6"/>
       <c r="I397" s="2"/>
     </row>
     <row r="398" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C398" s="6"/>
-      <c r="D398" s="7"/>
-      <c r="E398" s="7"/>
+      <c r="C398" s="5"/>
+      <c r="D398" s="6"/>
+      <c r="E398" s="6"/>
       <c r="I398" s="2"/>
     </row>
     <row r="399" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C399" s="6"/>
-      <c r="D399" s="7"/>
-      <c r="E399" s="7"/>
+      <c r="C399" s="5"/>
+      <c r="D399" s="6"/>
+      <c r="E399" s="6"/>
       <c r="I399" s="2"/>
     </row>
     <row r="400" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C400" s="6"/>
-      <c r="D400" s="7"/>
-      <c r="E400" s="7"/>
+      <c r="C400" s="5"/>
+      <c r="D400" s="6"/>
+      <c r="E400" s="6"/>
       <c r="I400" s="2"/>
     </row>
     <row r="401" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C401" s="6"/>
-      <c r="D401" s="7"/>
-      <c r="E401" s="7"/>
+      <c r="C401" s="5"/>
+      <c r="D401" s="6"/>
+      <c r="E401" s="6"/>
       <c r="I401" s="2"/>
     </row>
     <row r="402" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C402" s="6"/>
-      <c r="D402" s="7"/>
-      <c r="E402" s="7"/>
+      <c r="C402" s="5"/>
+      <c r="D402" s="6"/>
+      <c r="E402" s="6"/>
       <c r="I402" s="2"/>
     </row>
     <row r="403" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C403" s="6"/>
-      <c r="D403" s="7"/>
-      <c r="E403" s="7"/>
+      <c r="C403" s="5"/>
+      <c r="D403" s="6"/>
+      <c r="E403" s="6"/>
       <c r="I403" s="2"/>
     </row>
     <row r="404" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C404" s="6"/>
-      <c r="D404" s="7"/>
-      <c r="E404" s="7"/>
+      <c r="C404" s="5"/>
+      <c r="D404" s="6"/>
+      <c r="E404" s="6"/>
       <c r="I404" s="2"/>
     </row>
     <row r="405" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C405" s="6"/>
-      <c r="D405" s="7"/>
-      <c r="E405" s="7"/>
+      <c r="C405" s="5"/>
+      <c r="D405" s="6"/>
+      <c r="E405" s="6"/>
       <c r="I405" s="2"/>
     </row>
     <row r="406" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C406" s="6"/>
-      <c r="D406" s="7"/>
-      <c r="E406" s="7"/>
+      <c r="C406" s="5"/>
+      <c r="D406" s="6"/>
+      <c r="E406" s="6"/>
       <c r="I406" s="2"/>
     </row>
     <row r="407" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C407" s="6"/>
-      <c r="D407" s="7"/>
-      <c r="E407" s="7"/>
+      <c r="C407" s="5"/>
+      <c r="D407" s="6"/>
+      <c r="E407" s="6"/>
       <c r="I407" s="2"/>
     </row>
     <row r="408" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C408" s="6"/>
-      <c r="D408" s="7"/>
-      <c r="E408" s="7"/>
+      <c r="C408" s="5"/>
+      <c r="D408" s="6"/>
+      <c r="E408" s="6"/>
       <c r="I408" s="2"/>
     </row>
     <row r="409" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C409" s="6"/>
-      <c r="D409" s="7"/>
-      <c r="E409" s="7"/>
+      <c r="C409" s="5"/>
+      <c r="D409" s="6"/>
+      <c r="E409" s="6"/>
       <c r="I409" s="2"/>
     </row>
     <row r="410" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C410" s="6"/>
-      <c r="D410" s="7"/>
-      <c r="E410" s="7"/>
+      <c r="C410" s="5"/>
+      <c r="D410" s="6"/>
+      <c r="E410" s="6"/>
       <c r="I410" s="2"/>
     </row>
     <row r="411" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C411" s="6"/>
-      <c r="D411" s="7"/>
-      <c r="E411" s="7"/>
+      <c r="C411" s="5"/>
+      <c r="D411" s="6"/>
+      <c r="E411" s="6"/>
       <c r="I411" s="2"/>
     </row>
     <row r="412" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C412" s="6"/>
-      <c r="D412" s="7"/>
-      <c r="E412" s="7"/>
+      <c r="C412" s="5"/>
+      <c r="D412" s="6"/>
+      <c r="E412" s="6"/>
       <c r="I412" s="2"/>
     </row>
     <row r="413" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C413" s="6"/>
-      <c r="D413" s="7"/>
-      <c r="E413" s="7"/>
+      <c r="C413" s="5"/>
+      <c r="D413" s="6"/>
+      <c r="E413" s="6"/>
       <c r="I413" s="2"/>
     </row>
     <row r="414" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C414" s="6"/>
-      <c r="D414" s="7"/>
-      <c r="E414" s="7"/>
+      <c r="C414" s="5"/>
+      <c r="D414" s="6"/>
+      <c r="E414" s="6"/>
       <c r="I414" s="2"/>
     </row>
     <row r="415" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C415" s="6"/>
-      <c r="D415" s="7"/>
-      <c r="E415" s="7"/>
+      <c r="C415" s="5"/>
+      <c r="D415" s="6"/>
+      <c r="E415" s="6"/>
       <c r="I415" s="2"/>
     </row>
     <row r="416" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C416" s="6"/>
-      <c r="D416" s="7"/>
-      <c r="E416" s="7"/>
+      <c r="C416" s="5"/>
+      <c r="D416" s="6"/>
+      <c r="E416" s="6"/>
       <c r="I416" s="2"/>
     </row>
     <row r="417" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C417" s="6"/>
-      <c r="D417" s="7"/>
-      <c r="E417" s="7"/>
+      <c r="C417" s="5"/>
+      <c r="D417" s="6"/>
+      <c r="E417" s="6"/>
       <c r="I417" s="2"/>
     </row>
     <row r="418" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C418" s="6"/>
-      <c r="D418" s="7"/>
-      <c r="E418" s="7"/>
+      <c r="C418" s="5"/>
+      <c r="D418" s="6"/>
+      <c r="E418" s="6"/>
       <c r="I418" s="2"/>
     </row>
     <row r="419" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C419" s="6"/>
-      <c r="D419" s="7"/>
-      <c r="E419" s="7"/>
+      <c r="C419" s="5"/>
+      <c r="D419" s="6"/>
+      <c r="E419" s="6"/>
       <c r="I419" s="2"/>
     </row>
     <row r="420" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C420" s="6"/>
-      <c r="D420" s="7"/>
-      <c r="E420" s="7"/>
+      <c r="C420" s="5"/>
+      <c r="D420" s="6"/>
+      <c r="E420" s="6"/>
       <c r="I420" s="2"/>
     </row>
     <row r="421" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C421" s="6"/>
-      <c r="D421" s="7"/>
-      <c r="E421" s="7"/>
+      <c r="C421" s="5"/>
+      <c r="D421" s="6"/>
+      <c r="E421" s="6"/>
       <c r="I421" s="2"/>
     </row>
     <row r="422" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C422" s="6"/>
-      <c r="D422" s="7"/>
-      <c r="E422" s="7"/>
+      <c r="C422" s="5"/>
+      <c r="D422" s="6"/>
+      <c r="E422" s="6"/>
       <c r="I422" s="2"/>
     </row>
     <row r="423" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C423" s="6"/>
-      <c r="D423" s="7"/>
-      <c r="E423" s="7"/>
+      <c r="C423" s="5"/>
+      <c r="D423" s="6"/>
+      <c r="E423" s="6"/>
       <c r="I423" s="2"/>
     </row>
     <row r="424" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C424" s="6"/>
-      <c r="D424" s="7"/>
-      <c r="E424" s="7"/>
+      <c r="C424" s="5"/>
+      <c r="D424" s="6"/>
+      <c r="E424" s="6"/>
       <c r="I424" s="2"/>
     </row>
     <row r="425" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C425" s="6"/>
-      <c r="D425" s="7"/>
-      <c r="E425" s="7"/>
+      <c r="C425" s="5"/>
+      <c r="D425" s="6"/>
+      <c r="E425" s="6"/>
       <c r="I425" s="2"/>
     </row>
     <row r="426" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C426" s="6"/>
-      <c r="D426" s="7"/>
-      <c r="E426" s="7"/>
+      <c r="C426" s="5"/>
+      <c r="D426" s="6"/>
+      <c r="E426" s="6"/>
       <c r="I426" s="2"/>
     </row>
     <row r="427" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C427" s="6"/>
-      <c r="D427" s="7"/>
-      <c r="E427" s="7"/>
+      <c r="C427" s="5"/>
+      <c r="D427" s="6"/>
+      <c r="E427" s="6"/>
       <c r="I427" s="2"/>
     </row>
     <row r="428" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C428" s="6"/>
-      <c r="D428" s="7"/>
-      <c r="E428" s="7"/>
+      <c r="C428" s="5"/>
+      <c r="D428" s="6"/>
+      <c r="E428" s="6"/>
       <c r="I428" s="2"/>
     </row>
     <row r="429" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C429" s="6"/>
-      <c r="D429" s="7"/>
-      <c r="E429" s="7"/>
+      <c r="C429" s="5"/>
+      <c r="D429" s="6"/>
+      <c r="E429" s="6"/>
       <c r="I429" s="2"/>
     </row>
     <row r="430" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C430" s="6"/>
-      <c r="D430" s="7"/>
-      <c r="E430" s="7"/>
+      <c r="C430" s="5"/>
+      <c r="D430" s="6"/>
+      <c r="E430" s="6"/>
       <c r="I430" s="2"/>
     </row>
     <row r="431" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C431" s="6"/>
-      <c r="D431" s="7"/>
-      <c r="E431" s="7"/>
+      <c r="C431" s="5"/>
+      <c r="D431" s="6"/>
+      <c r="E431" s="6"/>
       <c r="I431" s="2"/>
     </row>
     <row r="432" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C432" s="6"/>
-      <c r="D432" s="7"/>
-      <c r="E432" s="7"/>
+      <c r="C432" s="5"/>
+      <c r="D432" s="6"/>
+      <c r="E432" s="6"/>
       <c r="I432" s="2"/>
     </row>
     <row r="433" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C433" s="6"/>
-      <c r="D433" s="7"/>
-      <c r="E433" s="7"/>
+      <c r="C433" s="5"/>
+      <c r="D433" s="6"/>
+      <c r="E433" s="6"/>
       <c r="I433" s="2"/>
     </row>
     <row r="434" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C434" s="6"/>
-      <c r="D434" s="7"/>
-      <c r="E434" s="7"/>
+      <c r="C434" s="5"/>
+      <c r="D434" s="6"/>
+      <c r="E434" s="6"/>
       <c r="I434" s="2"/>
     </row>
     <row r="435" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C435" s="6"/>
-      <c r="D435" s="7"/>
-      <c r="E435" s="7"/>
+      <c r="C435" s="5"/>
+      <c r="D435" s="6"/>
+      <c r="E435" s="6"/>
       <c r="I435" s="2"/>
     </row>
     <row r="436" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C436" s="6"/>
-      <c r="D436" s="7"/>
-      <c r="E436" s="7"/>
+      <c r="C436" s="5"/>
+      <c r="D436" s="6"/>
+      <c r="E436" s="6"/>
       <c r="I436" s="2"/>
     </row>
     <row r="437" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C437" s="6"/>
-      <c r="D437" s="7"/>
-      <c r="E437" s="7"/>
+      <c r="C437" s="5"/>
+      <c r="D437" s="6"/>
+      <c r="E437" s="6"/>
       <c r="I437" s="2"/>
     </row>
     <row r="438" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C438" s="6"/>
-      <c r="D438" s="7"/>
-      <c r="E438" s="7"/>
+      <c r="C438" s="5"/>
+      <c r="D438" s="6"/>
+      <c r="E438" s="6"/>
       <c r="I438" s="2"/>
     </row>
     <row r="439" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C439" s="6"/>
-      <c r="D439" s="7"/>
-      <c r="E439" s="7"/>
+      <c r="C439" s="5"/>
+      <c r="D439" s="6"/>
+      <c r="E439" s="6"/>
       <c r="I439" s="2"/>
     </row>
     <row r="440" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C440" s="6"/>
-      <c r="D440" s="7"/>
-      <c r="E440" s="7"/>
+      <c r="C440" s="5"/>
+      <c r="D440" s="6"/>
+      <c r="E440" s="6"/>
       <c r="I440" s="2"/>
     </row>
     <row r="441" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C441" s="6"/>
-      <c r="D441" s="7"/>
-      <c r="E441" s="7"/>
+      <c r="C441" s="5"/>
+      <c r="D441" s="6"/>
+      <c r="E441" s="6"/>
       <c r="I441" s="2"/>
     </row>
     <row r="442" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C442" s="6"/>
-      <c r="D442" s="7"/>
-      <c r="E442" s="7"/>
+      <c r="C442" s="5"/>
+      <c r="D442" s="6"/>
+      <c r="E442" s="6"/>
       <c r="I442" s="2"/>
     </row>
     <row r="443" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C443" s="6"/>
-      <c r="D443" s="7"/>
-      <c r="E443" s="7"/>
+      <c r="C443" s="5"/>
+      <c r="D443" s="6"/>
+      <c r="E443" s="6"/>
       <c r="I443" s="2"/>
     </row>
     <row r="444" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C444" s="6"/>
-      <c r="D444" s="7"/>
-      <c r="E444" s="7"/>
+      <c r="C444" s="5"/>
+      <c r="D444" s="6"/>
+      <c r="E444" s="6"/>
       <c r="I444" s="2"/>
     </row>
     <row r="445" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C445" s="6"/>
-      <c r="D445" s="7"/>
-      <c r="E445" s="7"/>
+      <c r="C445" s="5"/>
+      <c r="D445" s="6"/>
+      <c r="E445" s="6"/>
       <c r="I445" s="2"/>
     </row>
     <row r="446" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C446" s="6"/>
-      <c r="D446" s="7"/>
-      <c r="E446" s="7"/>
+      <c r="C446" s="5"/>
+      <c r="D446" s="6"/>
+      <c r="E446" s="6"/>
       <c r="I446" s="2"/>
     </row>
     <row r="447" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C447" s="6"/>
-      <c r="D447" s="7"/>
-      <c r="E447" s="7"/>
+      <c r="C447" s="5"/>
+      <c r="D447" s="6"/>
+      <c r="E447" s="6"/>
       <c r="I447" s="2"/>
     </row>
     <row r="448" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C448" s="6"/>
-      <c r="D448" s="7"/>
-      <c r="E448" s="7"/>
+      <c r="C448" s="5"/>
+      <c r="D448" s="6"/>
+      <c r="E448" s="6"/>
       <c r="I448" s="2"/>
     </row>
     <row r="449" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C449" s="6"/>
-      <c r="D449" s="7"/>
-      <c r="E449" s="7"/>
+      <c r="C449" s="5"/>
+      <c r="D449" s="6"/>
+      <c r="E449" s="6"/>
       <c r="I449" s="2"/>
     </row>
     <row r="450" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C450" s="6"/>
-      <c r="D450" s="7"/>
-      <c r="E450" s="7"/>
+      <c r="C450" s="5"/>
+      <c r="D450" s="6"/>
+      <c r="E450" s="6"/>
       <c r="I450" s="2"/>
     </row>
     <row r="451" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C451" s="6"/>
-      <c r="D451" s="7"/>
-      <c r="E451" s="7"/>
+      <c r="C451" s="5"/>
+      <c r="D451" s="6"/>
+      <c r="E451" s="6"/>
       <c r="I451" s="2"/>
     </row>
     <row r="452" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C452" s="6"/>
-      <c r="D452" s="7"/>
-      <c r="E452" s="7"/>
+      <c r="C452" s="5"/>
+      <c r="D452" s="6"/>
+      <c r="E452" s="6"/>
       <c r="I452" s="2"/>
     </row>
     <row r="453" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C453" s="6"/>
-      <c r="D453" s="7"/>
-      <c r="E453" s="7"/>
+      <c r="C453" s="5"/>
+      <c r="D453" s="6"/>
+      <c r="E453" s="6"/>
       <c r="I453" s="2"/>
     </row>
     <row r="454" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C454" s="6"/>
-      <c r="D454" s="7"/>
-      <c r="E454" s="7"/>
+      <c r="C454" s="5"/>
+      <c r="D454" s="6"/>
+      <c r="E454" s="6"/>
       <c r="I454" s="2"/>
     </row>
     <row r="455" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C455" s="6"/>
-      <c r="D455" s="7"/>
-      <c r="E455" s="7"/>
+      <c r="C455" s="5"/>
+      <c r="D455" s="6"/>
+      <c r="E455" s="6"/>
       <c r="I455" s="2"/>
     </row>
     <row r="456" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C456" s="6"/>
-      <c r="D456" s="7"/>
-      <c r="E456" s="7"/>
+      <c r="C456" s="5"/>
+      <c r="D456" s="6"/>
+      <c r="E456" s="6"/>
       <c r="I456" s="2"/>
     </row>
     <row r="457" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C457" s="6"/>
-      <c r="D457" s="7"/>
-      <c r="E457" s="7"/>
+      <c r="C457" s="5"/>
+      <c r="D457" s="6"/>
+      <c r="E457" s="6"/>
       <c r="I457" s="2"/>
     </row>
     <row r="458" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C458" s="6"/>
-      <c r="D458" s="7"/>
-      <c r="E458" s="7"/>
+      <c r="C458" s="5"/>
+      <c r="D458" s="6"/>
+      <c r="E458" s="6"/>
       <c r="I458" s="2"/>
     </row>
     <row r="459" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C459" s="6"/>
-      <c r="D459" s="7"/>
-      <c r="E459" s="7"/>
+      <c r="C459" s="5"/>
+      <c r="D459" s="6"/>
+      <c r="E459" s="6"/>
       <c r="I459" s="2"/>
     </row>
     <row r="460" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C460" s="6"/>
-      <c r="D460" s="7"/>
-      <c r="E460" s="7"/>
+      <c r="C460" s="5"/>
+      <c r="D460" s="6"/>
+      <c r="E460" s="6"/>
       <c r="I460" s="2"/>
     </row>
     <row r="461" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C461" s="6"/>
-      <c r="D461" s="7"/>
-      <c r="E461" s="7"/>
+      <c r="C461" s="5"/>
+      <c r="D461" s="6"/>
+      <c r="E461" s="6"/>
       <c r="I461" s="2"/>
     </row>
     <row r="462" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C462" s="6"/>
-      <c r="D462" s="7"/>
-      <c r="E462" s="7"/>
+      <c r="C462" s="5"/>
+      <c r="D462" s="6"/>
+      <c r="E462" s="6"/>
       <c r="I462" s="2"/>
     </row>
     <row r="463" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C463" s="6"/>
-      <c r="D463" s="7"/>
-      <c r="E463" s="7"/>
+      <c r="C463" s="5"/>
+      <c r="D463" s="6"/>
+      <c r="E463" s="6"/>
       <c r="I463" s="2"/>
     </row>
     <row r="464" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C464" s="6"/>
-      <c r="D464" s="7"/>
-      <c r="E464" s="7"/>
+      <c r="C464" s="5"/>
+      <c r="D464" s="6"/>
+      <c r="E464" s="6"/>
       <c r="I464" s="2"/>
     </row>
     <row r="465" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C465" s="6"/>
-      <c r="D465" s="7"/>
-      <c r="E465" s="7"/>
+      <c r="C465" s="5"/>
+      <c r="D465" s="6"/>
+      <c r="E465" s="6"/>
       <c r="I465" s="2"/>
     </row>
     <row r="466" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C466" s="6"/>
-      <c r="D466" s="7"/>
-      <c r="E466" s="7"/>
+      <c r="C466" s="5"/>
+      <c r="D466" s="6"/>
+      <c r="E466" s="6"/>
       <c r="I466" s="2"/>
     </row>
     <row r="467" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C467" s="6"/>
-      <c r="D467" s="7"/>
-      <c r="E467" s="7"/>
+      <c r="C467" s="5"/>
+      <c r="D467" s="6"/>
+      <c r="E467" s="6"/>
       <c r="I467" s="2"/>
     </row>
     <row r="468" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C468" s="6"/>
-      <c r="D468" s="7"/>
-      <c r="E468" s="7"/>
+      <c r="C468" s="5"/>
+      <c r="D468" s="6"/>
+      <c r="E468" s="6"/>
       <c r="I468" s="2"/>
     </row>
     <row r="469" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C469" s="6"/>
-      <c r="D469" s="7"/>
-      <c r="E469" s="7"/>
+      <c r="C469" s="5"/>
+      <c r="D469" s="6"/>
+      <c r="E469" s="6"/>
       <c r="I469" s="2"/>
     </row>
     <row r="470" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C470" s="6"/>
-      <c r="D470" s="7"/>
-      <c r="E470" s="7"/>
+      <c r="C470" s="5"/>
+      <c r="D470" s="6"/>
+      <c r="E470" s="6"/>
       <c r="I470" s="2"/>
     </row>
     <row r="471" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C471" s="6"/>
-      <c r="D471" s="7"/>
-      <c r="E471" s="7"/>
+      <c r="C471" s="5"/>
+      <c r="D471" s="6"/>
+      <c r="E471" s="6"/>
       <c r="I471" s="2"/>
     </row>
     <row r="472" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C472" s="6"/>
-      <c r="D472" s="7"/>
-      <c r="E472" s="7"/>
+      <c r="C472" s="5"/>
+      <c r="D472" s="6"/>
+      <c r="E472" s="6"/>
       <c r="I472" s="2"/>
     </row>
     <row r="473" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C473" s="6"/>
-      <c r="D473" s="7"/>
-      <c r="E473" s="7"/>
+      <c r="C473" s="5"/>
+      <c r="D473" s="6"/>
+      <c r="E473" s="6"/>
       <c r="I473" s="2"/>
     </row>
     <row r="474" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C474" s="6"/>
-      <c r="D474" s="7"/>
-      <c r="E474" s="7"/>
+      <c r="C474" s="5"/>
+      <c r="D474" s="6"/>
+      <c r="E474" s="6"/>
       <c r="I474" s="2"/>
     </row>
     <row r="475" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C475" s="6"/>
-      <c r="D475" s="7"/>
-      <c r="E475" s="7"/>
+      <c r="C475" s="5"/>
+      <c r="D475" s="6"/>
+      <c r="E475" s="6"/>
       <c r="I475" s="2"/>
     </row>
     <row r="476" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C476" s="6"/>
-      <c r="D476" s="7"/>
-      <c r="E476" s="7"/>
+      <c r="C476" s="5"/>
+      <c r="D476" s="6"/>
+      <c r="E476" s="6"/>
       <c r="I476" s="2"/>
     </row>
     <row r="477" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C477" s="6"/>
-      <c r="D477" s="7"/>
-      <c r="E477" s="7"/>
+      <c r="C477" s="5"/>
+      <c r="D477" s="6"/>
+      <c r="E477" s="6"/>
       <c r="I477" s="2"/>
     </row>
     <row r="478" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C478" s="6"/>
-      <c r="D478" s="7"/>
-      <c r="E478" s="7"/>
+      <c r="C478" s="5"/>
+      <c r="D478" s="6"/>
+      <c r="E478" s="6"/>
       <c r="I478" s="2"/>
     </row>
     <row r="479" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C479" s="6"/>
-      <c r="D479" s="7"/>
-      <c r="E479" s="7"/>
+      <c r="C479" s="5"/>
+      <c r="D479" s="6"/>
+      <c r="E479" s="6"/>
       <c r="I479" s="2"/>
     </row>
     <row r="480" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C480" s="6"/>
-      <c r="D480" s="7"/>
-      <c r="E480" s="7"/>
+      <c r="C480" s="5"/>
+      <c r="D480" s="6"/>
+      <c r="E480" s="6"/>
       <c r="I480" s="2"/>
     </row>
     <row r="481" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C481" s="6"/>
-      <c r="D481" s="7"/>
-      <c r="E481" s="7"/>
+      <c r="C481" s="5"/>
+      <c r="D481" s="6"/>
+      <c r="E481" s="6"/>
       <c r="I481" s="2"/>
     </row>
     <row r="482" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C482" s="6"/>
-      <c r="D482" s="7"/>
-      <c r="E482" s="7"/>
+      <c r="C482" s="5"/>
+      <c r="D482" s="6"/>
+      <c r="E482" s="6"/>
       <c r="I482" s="2"/>
     </row>
     <row r="483" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C483" s="6"/>
-      <c r="D483" s="7"/>
-      <c r="E483" s="7"/>
+      <c r="C483" s="5"/>
+      <c r="D483" s="6"/>
+      <c r="E483" s="6"/>
       <c r="I483" s="2"/>
     </row>
     <row r="484" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C484" s="6"/>
-      <c r="D484" s="7"/>
-      <c r="E484" s="7"/>
+      <c r="C484" s="5"/>
+      <c r="D484" s="6"/>
+      <c r="E484" s="6"/>
       <c r="I484" s="2"/>
     </row>
     <row r="485" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C485" s="6"/>
-      <c r="D485" s="7"/>
-      <c r="E485" s="7"/>
+      <c r="C485" s="5"/>
+      <c r="D485" s="6"/>
+      <c r="E485" s="6"/>
       <c r="I485" s="2"/>
     </row>
     <row r="486" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C486" s="6"/>
-      <c r="D486" s="7"/>
-      <c r="E486" s="7"/>
+      <c r="C486" s="5"/>
+      <c r="D486" s="6"/>
+      <c r="E486" s="6"/>
       <c r="I486" s="2"/>
     </row>
     <row r="487" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C487" s="6"/>
-      <c r="D487" s="7"/>
-      <c r="E487" s="7"/>
+      <c r="C487" s="5"/>
+      <c r="D487" s="6"/>
+      <c r="E487" s="6"/>
       <c r="I487" s="2"/>
     </row>
     <row r="488" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C488" s="6"/>
-      <c r="D488" s="7"/>
-      <c r="E488" s="7"/>
+      <c r="C488" s="5"/>
+      <c r="D488" s="6"/>
+      <c r="E488" s="6"/>
       <c r="I488" s="2"/>
     </row>
     <row r="489" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C489" s="6"/>
-      <c r="D489" s="7"/>
-      <c r="E489" s="7"/>
+      <c r="C489" s="5"/>
+      <c r="D489" s="6"/>
+      <c r="E489" s="6"/>
       <c r="I489" s="2"/>
     </row>
     <row r="490" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C490" s="6"/>
-      <c r="D490" s="7"/>
-      <c r="E490" s="7"/>
+      <c r="C490" s="5"/>
+      <c r="D490" s="6"/>
+      <c r="E490" s="6"/>
       <c r="I490" s="2"/>
     </row>
     <row r="491" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C491" s="6"/>
-      <c r="D491" s="7"/>
-      <c r="E491" s="7"/>
+      <c r="C491" s="5"/>
+      <c r="D491" s="6"/>
+      <c r="E491" s="6"/>
       <c r="I491" s="2"/>
     </row>
     <row r="492" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C492" s="6"/>
-      <c r="D492" s="7"/>
-      <c r="E492" s="7"/>
+      <c r="C492" s="5"/>
+      <c r="D492" s="6"/>
+      <c r="E492" s="6"/>
       <c r="I492" s="2"/>
     </row>
     <row r="493" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C493" s="6"/>
-      <c r="D493" s="7"/>
-      <c r="E493" s="7"/>
+      <c r="C493" s="5"/>
+      <c r="D493" s="6"/>
+      <c r="E493" s="6"/>
       <c r="I493" s="2"/>
     </row>
     <row r="494" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C494" s="6"/>
-      <c r="D494" s="7"/>
-      <c r="E494" s="7"/>
+      <c r="C494" s="5"/>
+      <c r="D494" s="6"/>
+      <c r="E494" s="6"/>
       <c r="I494" s="2"/>
     </row>
     <row r="495" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C495" s="6"/>
-      <c r="D495" s="7"/>
-      <c r="E495" s="7"/>
+      <c r="C495" s="5"/>
+      <c r="D495" s="6"/>
+      <c r="E495" s="6"/>
       <c r="I495" s="2"/>
     </row>
     <row r="496" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C496" s="6"/>
-      <c r="D496" s="7"/>
-      <c r="E496" s="7"/>
+      <c r="C496" s="5"/>
+      <c r="D496" s="6"/>
+      <c r="E496" s="6"/>
       <c r="I496" s="2"/>
     </row>
     <row r="497" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C497" s="6"/>
-      <c r="D497" s="7"/>
-      <c r="E497" s="7"/>
+      <c r="C497" s="5"/>
+      <c r="D497" s="6"/>
+      <c r="E497" s="6"/>
       <c r="I497" s="2"/>
     </row>
     <row r="498" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C498" s="6"/>
-      <c r="D498" s="7"/>
-      <c r="E498" s="7"/>
+      <c r="C498" s="5"/>
+      <c r="D498" s="6"/>
+      <c r="E498" s="6"/>
       <c r="I498" s="2"/>
     </row>
     <row r="499" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C499" s="6"/>
-      <c r="D499" s="7"/>
-      <c r="E499" s="7"/>
+      <c r="C499" s="5"/>
+      <c r="D499" s="6"/>
+      <c r="E499" s="6"/>
       <c r="I499" s="2"/>
     </row>
     <row r="500" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C500" s="6"/>
-      <c r="D500" s="7"/>
-      <c r="E500" s="7"/>
+      <c r="C500" s="5"/>
+      <c r="D500" s="6"/>
+      <c r="E500" s="6"/>
       <c r="I500" s="2"/>
     </row>
     <row r="501" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C501" s="6"/>
-      <c r="D501" s="7"/>
-      <c r="E501" s="7"/>
+      <c r="C501" s="5"/>
+      <c r="D501" s="6"/>
+      <c r="E501" s="6"/>
       <c r="I501" s="2"/>
     </row>
     <row r="502" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C502" s="6"/>
-      <c r="D502" s="7"/>
-      <c r="E502" s="7"/>
+      <c r="C502" s="5"/>
+      <c r="D502" s="6"/>
+      <c r="E502" s="6"/>
       <c r="I502" s="2"/>
     </row>
     <row r="503" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C503" s="6"/>
-      <c r="D503" s="7"/>
-      <c r="E503" s="7"/>
+      <c r="C503" s="5"/>
+      <c r="D503" s="6"/>
+      <c r="E503" s="6"/>
       <c r="I503" s="2"/>
     </row>
     <row r="504" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C504" s="6"/>
-      <c r="D504" s="7"/>
-      <c r="E504" s="7"/>
+      <c r="C504" s="5"/>
+      <c r="D504" s="6"/>
+      <c r="E504" s="6"/>
       <c r="I504" s="2"/>
     </row>
     <row r="505" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C505" s="6"/>
-      <c r="D505" s="7"/>
-      <c r="E505" s="7"/>
+      <c r="C505" s="5"/>
+      <c r="D505" s="6"/>
+      <c r="E505" s="6"/>
       <c r="I505" s="2"/>
     </row>
     <row r="506" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C506" s="6"/>
-      <c r="D506" s="7"/>
-      <c r="E506" s="7"/>
+      <c r="C506" s="5"/>
+      <c r="D506" s="6"/>
+      <c r="E506" s="6"/>
       <c r="I506" s="2"/>
     </row>
     <row r="507" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C507" s="6"/>
-      <c r="D507" s="7"/>
-      <c r="E507" s="7"/>
+      <c r="C507" s="5"/>
+      <c r="D507" s="6"/>
+      <c r="E507" s="6"/>
       <c r="I507" s="2"/>
     </row>
     <row r="508" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C508" s="6"/>
-      <c r="D508" s="7"/>
-      <c r="E508" s="7"/>
+      <c r="C508" s="5"/>
+      <c r="D508" s="6"/>
+      <c r="E508" s="6"/>
       <c r="I508" s="2"/>
     </row>
     <row r="509" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C509" s="6"/>
-      <c r="D509" s="7"/>
-      <c r="E509" s="7"/>
+      <c r="C509" s="5"/>
+      <c r="D509" s="6"/>
+      <c r="E509" s="6"/>
       <c r="I509" s="2"/>
     </row>
     <row r="510" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C510" s="6"/>
-      <c r="D510" s="7"/>
-      <c r="E510" s="7"/>
+      <c r="C510" s="5"/>
+      <c r="D510" s="6"/>
+      <c r="E510" s="6"/>
       <c r="I510" s="2"/>
     </row>
     <row r="511" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C511" s="6"/>
-      <c r="D511" s="7"/>
-      <c r="E511" s="7"/>
+      <c r="C511" s="5"/>
+      <c r="D511" s="6"/>
+      <c r="E511" s="6"/>
       <c r="I511" s="2"/>
     </row>
     <row r="512" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C512" s="6"/>
-      <c r="D512" s="7"/>
-      <c r="E512" s="7"/>
+      <c r="C512" s="5"/>
+      <c r="D512" s="6"/>
+      <c r="E512" s="6"/>
       <c r="I512" s="2"/>
     </row>
     <row r="513" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C513" s="6"/>
-      <c r="D513" s="7"/>
-      <c r="E513" s="7"/>
+      <c r="C513" s="5"/>
+      <c r="D513" s="6"/>
+      <c r="E513" s="6"/>
       <c r="I513" s="2"/>
     </row>
     <row r="514" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C514" s="6"/>
-      <c r="D514" s="7"/>
-      <c r="E514" s="7"/>
+      <c r="C514" s="5"/>
+      <c r="D514" s="6"/>
+      <c r="E514" s="6"/>
       <c r="I514" s="2"/>
     </row>
     <row r="515" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C515" s="6"/>
-      <c r="D515" s="7"/>
-      <c r="E515" s="7"/>
+      <c r="C515" s="5"/>
+      <c r="D515" s="6"/>
+      <c r="E515" s="6"/>
       <c r="I515" s="2"/>
     </row>
     <row r="516" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C516" s="6"/>
-      <c r="D516" s="7"/>
-      <c r="E516" s="7"/>
+      <c r="C516" s="5"/>
+      <c r="D516" s="6"/>
+      <c r="E516" s="6"/>
       <c r="I516" s="2"/>
     </row>
     <row r="517" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C517" s="6"/>
-      <c r="D517" s="7"/>
-      <c r="E517" s="7"/>
+      <c r="C517" s="5"/>
+      <c r="D517" s="6"/>
+      <c r="E517" s="6"/>
       <c r="I517" s="2"/>
     </row>
     <row r="518" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C518" s="6"/>
-      <c r="D518" s="7"/>
-      <c r="E518" s="7"/>
+      <c r="C518" s="5"/>
+      <c r="D518" s="6"/>
+      <c r="E518" s="6"/>
       <c r="I518" s="2"/>
     </row>
     <row r="519" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C519" s="6"/>
-      <c r="D519" s="7"/>
-      <c r="E519" s="7"/>
+      <c r="C519" s="5"/>
+      <c r="D519" s="6"/>
+      <c r="E519" s="6"/>
       <c r="I519" s="2"/>
     </row>
     <row r="520" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C520" s="6"/>
-      <c r="D520" s="7"/>
-      <c r="E520" s="7"/>
+      <c r="C520" s="5"/>
+      <c r="D520" s="6"/>
+      <c r="E520" s="6"/>
       <c r="I520" s="2"/>
     </row>
     <row r="521" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C521" s="6"/>
-      <c r="D521" s="7"/>
-      <c r="E521" s="7"/>
+      <c r="C521" s="5"/>
+      <c r="D521" s="6"/>
+      <c r="E521" s="6"/>
       <c r="I521" s="2"/>
     </row>
     <row r="522" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C522" s="6"/>
-      <c r="D522" s="7"/>
-      <c r="E522" s="7"/>
+      <c r="C522" s="5"/>
+      <c r="D522" s="6"/>
+      <c r="E522" s="6"/>
       <c r="I522" s="2"/>
     </row>
     <row r="523" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C523" s="6"/>
-      <c r="D523" s="7"/>
-      <c r="E523" s="7"/>
+      <c r="C523" s="5"/>
+      <c r="D523" s="6"/>
+      <c r="E523" s="6"/>
       <c r="I523" s="2"/>
     </row>
     <row r="524" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C524" s="6"/>
-      <c r="D524" s="7"/>
-      <c r="E524" s="7"/>
+      <c r="C524" s="5"/>
+      <c r="D524" s="6"/>
+      <c r="E524" s="6"/>
       <c r="I524" s="2"/>
     </row>
     <row r="525" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C525" s="6"/>
-      <c r="D525" s="7"/>
-      <c r="E525" s="7"/>
+      <c r="C525" s="5"/>
+      <c r="D525" s="6"/>
+      <c r="E525" s="6"/>
       <c r="I525" s="2"/>
     </row>
     <row r="526" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C526" s="6"/>
-      <c r="D526" s="7"/>
-      <c r="E526" s="7"/>
+      <c r="C526" s="5"/>
+      <c r="D526" s="6"/>
+      <c r="E526" s="6"/>
       <c r="I526" s="2"/>
     </row>
     <row r="527" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C527" s="6"/>
-      <c r="D527" s="7"/>
-      <c r="E527" s="7"/>
+      <c r="C527" s="5"/>
+      <c r="D527" s="6"/>
+      <c r="E527" s="6"/>
       <c r="I527" s="2"/>
     </row>
     <row r="528" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C528" s="6"/>
-      <c r="D528" s="7"/>
-      <c r="E528" s="7"/>
+      <c r="C528" s="5"/>
+      <c r="D528" s="6"/>
+      <c r="E528" s="6"/>
       <c r="I528" s="2"/>
     </row>
     <row r="529" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C529" s="6"/>
-      <c r="D529" s="7"/>
-      <c r="E529" s="7"/>
+      <c r="C529" s="5"/>
+      <c r="D529" s="6"/>
+      <c r="E529" s="6"/>
       <c r="I529" s="2"/>
     </row>
     <row r="530" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C530" s="6"/>
-      <c r="D530" s="7"/>
-      <c r="E530" s="7"/>
+      <c r="C530" s="5"/>
+      <c r="D530" s="6"/>
+      <c r="E530" s="6"/>
       <c r="I530" s="2"/>
     </row>
     <row r="531" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C531" s="6"/>
-      <c r="D531" s="7"/>
-      <c r="E531" s="7"/>
+      <c r="C531" s="5"/>
+      <c r="D531" s="6"/>
+      <c r="E531" s="6"/>
       <c r="I531" s="2"/>
     </row>
     <row r="532" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C532" s="6"/>
-      <c r="D532" s="7"/>
-      <c r="E532" s="7"/>
+      <c r="C532" s="5"/>
+      <c r="D532" s="6"/>
+      <c r="E532" s="6"/>
       <c r="I532" s="2"/>
     </row>
     <row r="533" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C533" s="6"/>
-      <c r="D533" s="7"/>
-      <c r="E533" s="7"/>
+      <c r="C533" s="5"/>
+      <c r="D533" s="6"/>
+      <c r="E533" s="6"/>
       <c r="I533" s="2"/>
     </row>
     <row r="534" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C534" s="6"/>
-      <c r="D534" s="7"/>
-      <c r="E534" s="7"/>
+      <c r="C534" s="5"/>
+      <c r="D534" s="6"/>
+      <c r="E534" s="6"/>
       <c r="I534" s="2"/>
     </row>
     <row r="535" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C535" s="6"/>
-      <c r="D535" s="7"/>
-      <c r="E535" s="7"/>
+      <c r="C535" s="5"/>
+      <c r="D535" s="6"/>
+      <c r="E535" s="6"/>
       <c r="I535" s="2"/>
     </row>
     <row r="536" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C536" s="6"/>
-      <c r="D536" s="7"/>
-      <c r="E536" s="7"/>
+      <c r="C536" s="5"/>
+      <c r="D536" s="6"/>
+      <c r="E536" s="6"/>
       <c r="I536" s="2"/>
     </row>
     <row r="537" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C537" s="6"/>
-      <c r="D537" s="7"/>
-      <c r="E537" s="7"/>
+      <c r="C537" s="5"/>
+      <c r="D537" s="6"/>
+      <c r="E537" s="6"/>
       <c r="I537" s="2"/>
     </row>
     <row r="538" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C538" s="6"/>
-      <c r="D538" s="7"/>
-      <c r="E538" s="7"/>
+      <c r="C538" s="5"/>
+      <c r="D538" s="6"/>
+      <c r="E538" s="6"/>
       <c r="I538" s="2"/>
     </row>
     <row r="539" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C539" s="6"/>
-      <c r="D539" s="7"/>
-      <c r="E539" s="7"/>
+      <c r="C539" s="5"/>
+      <c r="D539" s="6"/>
+      <c r="E539" s="6"/>
       <c r="I539" s="2"/>
     </row>
     <row r="540" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C540" s="6"/>
-      <c r="D540" s="7"/>
-      <c r="E540" s="7"/>
+      <c r="C540" s="5"/>
+      <c r="D540" s="6"/>
+      <c r="E540" s="6"/>
       <c r="I540" s="2"/>
     </row>
     <row r="541" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C541" s="6"/>
-      <c r="D541" s="7"/>
-      <c r="E541" s="7"/>
+      <c r="C541" s="5"/>
+      <c r="D541" s="6"/>
+      <c r="E541" s="6"/>
       <c r="I541" s="2"/>
     </row>
     <row r="542" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C542" s="6"/>
-      <c r="D542" s="7"/>
-      <c r="E542" s="7"/>
+      <c r="C542" s="5"/>
+      <c r="D542" s="6"/>
+      <c r="E542" s="6"/>
       <c r="I542" s="2"/>
     </row>
     <row r="543" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C543" s="6"/>
-      <c r="D543" s="7"/>
-      <c r="E543" s="7"/>
+      <c r="C543" s="5"/>
+      <c r="D543" s="6"/>
+      <c r="E543" s="6"/>
       <c r="I543" s="2"/>
     </row>
     <row r="544" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C544" s="6"/>
-      <c r="D544" s="7"/>
-      <c r="E544" s="7"/>
+      <c r="C544" s="5"/>
+      <c r="D544" s="6"/>
+      <c r="E544" s="6"/>
       <c r="I544" s="2"/>
     </row>
     <row r="545" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C545" s="6"/>
-      <c r="D545" s="7"/>
-      <c r="E545" s="7"/>
+      <c r="C545" s="5"/>
+      <c r="D545" s="6"/>
+      <c r="E545" s="6"/>
       <c r="I545" s="2"/>
     </row>
     <row r="546" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C546" s="6"/>
-      <c r="D546" s="7"/>
-      <c r="E546" s="7"/>
+      <c r="C546" s="5"/>
+      <c r="D546" s="6"/>
+      <c r="E546" s="6"/>
       <c r="I546" s="2"/>
     </row>
     <row r="547" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C547" s="6"/>
-      <c r="D547" s="7"/>
-      <c r="E547" s="7"/>
+      <c r="C547" s="5"/>
+      <c r="D547" s="6"/>
+      <c r="E547" s="6"/>
       <c r="I547" s="2"/>
     </row>
     <row r="548" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C548" s="6"/>
-      <c r="D548" s="7"/>
-      <c r="E548" s="7"/>
+      <c r="C548" s="5"/>
+      <c r="D548" s="6"/>
+      <c r="E548" s="6"/>
       <c r="I548" s="2"/>
     </row>
     <row r="549" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C549" s="6"/>
-      <c r="D549" s="7"/>
-      <c r="E549" s="7"/>
+      <c r="C549" s="5"/>
+      <c r="D549" s="6"/>
+      <c r="E549" s="6"/>
       <c r="I549" s="2"/>
     </row>
     <row r="550" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C550" s="6"/>
-      <c r="D550" s="7"/>
-      <c r="E550" s="7"/>
+      <c r="C550" s="5"/>
+      <c r="D550" s="6"/>
+      <c r="E550" s="6"/>
       <c r="I550" s="2"/>
     </row>
     <row r="551" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C551" s="6"/>
-      <c r="D551" s="7"/>
-      <c r="E551" s="7"/>
+      <c r="C551" s="5"/>
+      <c r="D551" s="6"/>
+      <c r="E551" s="6"/>
       <c r="I551" s="2"/>
     </row>
     <row r="552" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C552" s="6"/>
-      <c r="D552" s="7"/>
-      <c r="E552" s="7"/>
+      <c r="C552" s="5"/>
+      <c r="D552" s="6"/>
+      <c r="E552" s="6"/>
       <c r="I552" s="2"/>
     </row>
     <row r="553" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C553" s="6"/>
-      <c r="D553" s="7"/>
-      <c r="E553" s="7"/>
+      <c r="C553" s="5"/>
+      <c r="D553" s="6"/>
+      <c r="E553" s="6"/>
       <c r="I553" s="2"/>
     </row>
     <row r="554" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C554" s="6"/>
-      <c r="D554" s="7"/>
-      <c r="E554" s="7"/>
+      <c r="C554" s="5"/>
+      <c r="D554" s="6"/>
+      <c r="E554" s="6"/>
       <c r="I554" s="2"/>
     </row>
     <row r="555" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C555" s="6"/>
-      <c r="D555" s="7"/>
-      <c r="E555" s="7"/>
+      <c r="C555" s="5"/>
+      <c r="D555" s="6"/>
+      <c r="E555" s="6"/>
       <c r="I555" s="2"/>
     </row>
     <row r="556" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C556" s="6"/>
-      <c r="D556" s="7"/>
-      <c r="E556" s="7"/>
+      <c r="C556" s="5"/>
+      <c r="D556" s="6"/>
+      <c r="E556" s="6"/>
       <c r="I556" s="2"/>
     </row>
     <row r="557" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C557" s="6"/>
-      <c r="D557" s="7"/>
-      <c r="E557" s="7"/>
+      <c r="C557" s="5"/>
+      <c r="D557" s="6"/>
+      <c r="E557" s="6"/>
       <c r="I557" s="2"/>
     </row>
     <row r="558" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C558" s="6"/>
-      <c r="D558" s="7"/>
-      <c r="E558" s="7"/>
+      <c r="C558" s="5"/>
+      <c r="D558" s="6"/>
+      <c r="E558" s="6"/>
       <c r="I558" s="2"/>
     </row>
     <row r="559" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C559" s="6"/>
-      <c r="D559" s="7"/>
-      <c r="E559" s="7"/>
+      <c r="C559" s="5"/>
+      <c r="D559" s="6"/>
+      <c r="E559" s="6"/>
       <c r="I559" s="2"/>
     </row>
     <row r="560" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C560" s="6"/>
-      <c r="D560" s="7"/>
-      <c r="E560" s="7"/>
+      <c r="C560" s="5"/>
+      <c r="D560" s="6"/>
+      <c r="E560" s="6"/>
       <c r="I560" s="2"/>
     </row>
     <row r="561" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C561" s="6"/>
-      <c r="D561" s="7"/>
-      <c r="E561" s="7"/>
+      <c r="C561" s="5"/>
+      <c r="D561" s="6"/>
+      <c r="E561" s="6"/>
       <c r="I561" s="2"/>
     </row>
     <row r="562" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C562" s="6"/>
-      <c r="D562" s="7"/>
-      <c r="E562" s="7"/>
+      <c r="C562" s="5"/>
+      <c r="D562" s="6"/>
+      <c r="E562" s="6"/>
       <c r="I562" s="2"/>
     </row>
     <row r="563" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C563" s="6"/>
-      <c r="D563" s="7"/>
-      <c r="E563" s="7"/>
+      <c r="C563" s="5"/>
+      <c r="D563" s="6"/>
+      <c r="E563" s="6"/>
       <c r="I563" s="2"/>
     </row>
     <row r="564" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C564" s="6"/>
-      <c r="D564" s="7"/>
-      <c r="E564" s="7"/>
+      <c r="C564" s="5"/>
+      <c r="D564" s="6"/>
+      <c r="E564" s="6"/>
       <c r="I564" s="2"/>
     </row>
     <row r="565" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C565" s="6"/>
-      <c r="D565" s="7"/>
-      <c r="E565" s="7"/>
+      <c r="C565" s="5"/>
+      <c r="D565" s="6"/>
+      <c r="E565" s="6"/>
       <c r="I565" s="2"/>
     </row>
     <row r="566" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C566" s="6"/>
-      <c r="D566" s="7"/>
-      <c r="E566" s="7"/>
+      <c r="C566" s="5"/>
+      <c r="D566" s="6"/>
+      <c r="E566" s="6"/>
       <c r="I566" s="2"/>
     </row>
     <row r="567" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C567" s="6"/>
-      <c r="D567" s="7"/>
-      <c r="E567" s="7"/>
+      <c r="C567" s="5"/>
+      <c r="D567" s="6"/>
+      <c r="E567" s="6"/>
       <c r="I567" s="2"/>
     </row>
     <row r="568" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C568" s="6"/>
-      <c r="D568" s="7"/>
-      <c r="E568" s="7"/>
+      <c r="C568" s="5"/>
+      <c r="D568" s="6"/>
+      <c r="E568" s="6"/>
       <c r="I568" s="2"/>
     </row>
     <row r="569" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C569" s="6"/>
-      <c r="D569" s="7"/>
-      <c r="E569" s="7"/>
+      <c r="C569" s="5"/>
+      <c r="D569" s="6"/>
+      <c r="E569" s="6"/>
       <c r="I569" s="2"/>
     </row>
     <row r="570" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C570" s="6"/>
-      <c r="D570" s="7"/>
-      <c r="E570" s="7"/>
+      <c r="C570" s="5"/>
+      <c r="D570" s="6"/>
+      <c r="E570" s="6"/>
       <c r="I570" s="2"/>
     </row>
     <row r="571" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C571" s="6"/>
-      <c r="D571" s="7"/>
-      <c r="E571" s="7"/>
+      <c r="C571" s="5"/>
+      <c r="D571" s="6"/>
+      <c r="E571" s="6"/>
       <c r="I571" s="2"/>
     </row>
     <row r="572" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C572" s="6"/>
-      <c r="D572" s="7"/>
-      <c r="E572" s="7"/>
+      <c r="C572" s="5"/>
+      <c r="D572" s="6"/>
+      <c r="E572" s="6"/>
       <c r="I572" s="2"/>
     </row>
     <row r="573" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C573" s="6"/>
-      <c r="D573" s="7"/>
-      <c r="E573" s="7"/>
+      <c r="C573" s="5"/>
+      <c r="D573" s="6"/>
+      <c r="E573" s="6"/>
       <c r="I573" s="2"/>
     </row>
     <row r="574" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C574" s="6"/>
-      <c r="D574" s="7"/>
-      <c r="E574" s="7"/>
+      <c r="C574" s="5"/>
+      <c r="D574" s="6"/>
+      <c r="E574" s="6"/>
       <c r="I574" s="2"/>
     </row>
     <row r="575" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C575" s="6"/>
-      <c r="D575" s="7"/>
-      <c r="E575" s="7"/>
+      <c r="C575" s="5"/>
+      <c r="D575" s="6"/>
+      <c r="E575" s="6"/>
       <c r="I575" s="2"/>
     </row>
     <row r="576" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C576" s="6"/>
-      <c r="D576" s="7"/>
-      <c r="E576" s="7"/>
+      <c r="C576" s="5"/>
+      <c r="D576" s="6"/>
+      <c r="E576" s="6"/>
       <c r="I576" s="2"/>
     </row>
     <row r="577" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C577" s="6"/>
-      <c r="D577" s="7"/>
-      <c r="E577" s="7"/>
+      <c r="C577" s="5"/>
+      <c r="D577" s="6"/>
+      <c r="E577" s="6"/>
       <c r="I577" s="2"/>
     </row>
     <row r="578" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C578" s="6"/>
-      <c r="D578" s="7"/>
-      <c r="E578" s="7"/>
+      <c r="C578" s="5"/>
+      <c r="D578" s="6"/>
+      <c r="E578" s="6"/>
       <c r="I578" s="2"/>
     </row>
     <row r="579" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C579" s="6"/>
-      <c r="D579" s="7"/>
-      <c r="E579" s="7"/>
+      <c r="C579" s="5"/>
+      <c r="D579" s="6"/>
+      <c r="E579" s="6"/>
       <c r="I579" s="2"/>
     </row>
     <row r="580" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C580" s="6"/>
-      <c r="D580" s="7"/>
-      <c r="E580" s="7"/>
+      <c r="C580" s="5"/>
+      <c r="D580" s="6"/>
+      <c r="E580" s="6"/>
       <c r="I580" s="2"/>
     </row>
     <row r="581" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C581" s="6"/>
-      <c r="D581" s="7"/>
-      <c r="E581" s="7"/>
+      <c r="C581" s="5"/>
+      <c r="D581" s="6"/>
+      <c r="E581" s="6"/>
       <c r="I581" s="2"/>
     </row>
     <row r="582" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C582" s="6"/>
-      <c r="D582" s="7"/>
-      <c r="E582" s="7"/>
+      <c r="C582" s="5"/>
+      <c r="D582" s="6"/>
+      <c r="E582" s="6"/>
       <c r="I582" s="2"/>
     </row>
     <row r="583" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C583" s="6"/>
-      <c r="D583" s="7"/>
-      <c r="E583" s="7"/>
+      <c r="C583" s="5"/>
+      <c r="D583" s="6"/>
+      <c r="E583" s="6"/>
       <c r="I583" s="2"/>
     </row>
     <row r="584" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C584" s="6"/>
-      <c r="D584" s="7"/>
-      <c r="E584" s="7"/>
+      <c r="C584" s="5"/>
+      <c r="D584" s="6"/>
+      <c r="E584" s="6"/>
       <c r="I584" s="2"/>
     </row>
     <row r="585" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C585" s="6"/>
-      <c r="D585" s="7"/>
-      <c r="E585" s="7"/>
+      <c r="C585" s="5"/>
+      <c r="D585" s="6"/>
+      <c r="E585" s="6"/>
       <c r="I585" s="2"/>
     </row>
     <row r="586" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C586" s="6"/>
-      <c r="D586" s="7"/>
-      <c r="E586" s="7"/>
+      <c r="C586" s="5"/>
+      <c r="D586" s="6"/>
+      <c r="E586" s="6"/>
       <c r="I586" s="2"/>
     </row>
     <row r="587" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C587" s="6"/>
-      <c r="D587" s="7"/>
-      <c r="E587" s="7"/>
+      <c r="C587" s="5"/>
+      <c r="D587" s="6"/>
+      <c r="E587" s="6"/>
       <c r="I587" s="2"/>
     </row>
     <row r="588" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C588" s="6"/>
-      <c r="D588" s="7"/>
-      <c r="E588" s="7"/>
+      <c r="C588" s="5"/>
+      <c r="D588" s="6"/>
+      <c r="E588" s="6"/>
       <c r="I588" s="2"/>
     </row>
     <row r="589" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C589" s="6"/>
-      <c r="D589" s="7"/>
-      <c r="E589" s="7"/>
+      <c r="C589" s="5"/>
+      <c r="D589" s="6"/>
+      <c r="E589" s="6"/>
       <c r="I589" s="2"/>
     </row>
     <row r="590" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C590" s="6"/>
-      <c r="D590" s="7"/>
-      <c r="E590" s="7"/>
+      <c r="C590" s="5"/>
+      <c r="D590" s="6"/>
+      <c r="E590" s="6"/>
       <c r="I590" s="2"/>
     </row>
     <row r="591" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C591" s="6"/>
-      <c r="D591" s="7"/>
-      <c r="E591" s="7"/>
+      <c r="C591" s="5"/>
+      <c r="D591" s="6"/>
+      <c r="E591" s="6"/>
       <c r="I591" s="2"/>
     </row>
     <row r="592" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C592" s="6"/>
-      <c r="D592" s="7"/>
-      <c r="E592" s="7"/>
+      <c r="C592" s="5"/>
+      <c r="D592" s="6"/>
+      <c r="E592" s="6"/>
       <c r="I592" s="2"/>
     </row>
     <row r="593" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C593" s="6"/>
-      <c r="D593" s="7"/>
-      <c r="E593" s="7"/>
+      <c r="C593" s="5"/>
+      <c r="D593" s="6"/>
+      <c r="E593" s="6"/>
       <c r="I593" s="2"/>
     </row>
     <row r="594" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C594" s="6"/>
-      <c r="D594" s="7"/>
-      <c r="E594" s="7"/>
+      <c r="C594" s="5"/>
+      <c r="D594" s="6"/>
+      <c r="E594" s="6"/>
       <c r="I594" s="2"/>
     </row>
     <row r="595" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C595" s="6"/>
-      <c r="D595" s="7"/>
-      <c r="E595" s="7"/>
+      <c r="C595" s="5"/>
+      <c r="D595" s="6"/>
+      <c r="E595" s="6"/>
       <c r="I595" s="2"/>
     </row>
     <row r="596" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C596" s="6"/>
-      <c r="D596" s="7"/>
-      <c r="E596" s="7"/>
+      <c r="C596" s="5"/>
+      <c r="D596" s="6"/>
+      <c r="E596" s="6"/>
       <c r="I596" s="2"/>
     </row>
     <row r="597" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C597" s="6"/>
-      <c r="D597" s="7"/>
-      <c r="E597" s="7"/>
+      <c r="C597" s="5"/>
+      <c r="D597" s="6"/>
+      <c r="E597" s="6"/>
       <c r="I597" s="2"/>
     </row>
     <row r="598" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C598" s="6"/>
-      <c r="D598" s="7"/>
-      <c r="E598" s="7"/>
+      <c r="C598" s="5"/>
+      <c r="D598" s="6"/>
+      <c r="E598" s="6"/>
       <c r="I598" s="2"/>
     </row>
     <row r="599" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C599" s="6"/>
-      <c r="D599" s="7"/>
-      <c r="E599" s="7"/>
+      <c r="C599" s="5"/>
+      <c r="D599" s="6"/>
+      <c r="E599" s="6"/>
       <c r="I599" s="2"/>
     </row>
     <row r="600" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C600" s="6"/>
-      <c r="D600" s="7"/>
-      <c r="E600" s="7"/>
+      <c r="C600" s="5"/>
+      <c r="D600" s="6"/>
+      <c r="E600" s="6"/>
       <c r="I600" s="2"/>
     </row>
     <row r="601" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C601" s="6"/>
-      <c r="D601" s="7"/>
-      <c r="E601" s="7"/>
+      <c r="C601" s="5"/>
+      <c r="D601" s="6"/>
+      <c r="E601" s="6"/>
       <c r="I601" s="2"/>
     </row>
     <row r="602" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C602" s="6"/>
-      <c r="D602" s="7"/>
-      <c r="E602" s="7"/>
+      <c r="C602" s="5"/>
+      <c r="D602" s="6"/>
+      <c r="E602" s="6"/>
       <c r="I602" s="2"/>
     </row>
     <row r="603" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C603" s="6"/>
-      <c r="D603" s="7"/>
-      <c r="E603" s="7"/>
+      <c r="C603" s="5"/>
+      <c r="D603" s="6"/>
+      <c r="E603" s="6"/>
       <c r="I603" s="2"/>
     </row>
     <row r="604" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C604" s="6"/>
-      <c r="D604" s="7"/>
-      <c r="E604" s="7"/>
+      <c r="C604" s="5"/>
+      <c r="D604" s="6"/>
+      <c r="E604" s="6"/>
       <c r="I604" s="2"/>
     </row>
     <row r="605" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C605" s="6"/>
-      <c r="D605" s="7"/>
-      <c r="E605" s="7"/>
+      <c r="C605" s="5"/>
+      <c r="D605" s="6"/>
+      <c r="E605" s="6"/>
       <c r="I605" s="2"/>
     </row>
     <row r="606" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C606" s="6"/>
-      <c r="D606" s="7"/>
-      <c r="E606" s="7"/>
+      <c r="C606" s="5"/>
+      <c r="D606" s="6"/>
+      <c r="E606" s="6"/>
       <c r="I606" s="2"/>
     </row>
     <row r="607" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C607" s="6"/>
-      <c r="D607" s="7"/>
-      <c r="E607" s="7"/>
+      <c r="C607" s="5"/>
+      <c r="D607" s="6"/>
+      <c r="E607" s="6"/>
       <c r="I607" s="2"/>
     </row>
     <row r="608" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C608" s="6"/>
-      <c r="D608" s="7"/>
-      <c r="E608" s="7"/>
+      <c r="C608" s="5"/>
+      <c r="D608" s="6"/>
+      <c r="E608" s="6"/>
       <c r="I608" s="2"/>
     </row>
     <row r="609" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C609" s="6"/>
-      <c r="D609" s="7"/>
-      <c r="E609" s="7"/>
+      <c r="C609" s="5"/>
+      <c r="D609" s="6"/>
+      <c r="E609" s="6"/>
       <c r="I609" s="2"/>
     </row>
     <row r="610" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C610" s="6"/>
-      <c r="D610" s="7"/>
-      <c r="E610" s="7"/>
+      <c r="C610" s="5"/>
+      <c r="D610" s="6"/>
+      <c r="E610" s="6"/>
       <c r="I610" s="2"/>
     </row>
     <row r="611" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C611" s="6"/>
-      <c r="D611" s="7"/>
-      <c r="E611" s="7"/>
+      <c r="C611" s="5"/>
+      <c r="D611" s="6"/>
+      <c r="E611" s="6"/>
       <c r="I611" s="2"/>
     </row>
     <row r="612" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C612" s="6"/>
-      <c r="D612" s="7"/>
-      <c r="E612" s="7"/>
+      <c r="C612" s="5"/>
+      <c r="D612" s="6"/>
+      <c r="E612" s="6"/>
       <c r="I612" s="2"/>
     </row>
     <row r="613" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C613" s="6"/>
-      <c r="D613" s="7"/>
-      <c r="E613" s="7"/>
+      <c r="C613" s="5"/>
+      <c r="D613" s="6"/>
+      <c r="E613" s="6"/>
       <c r="I613" s="2"/>
     </row>
     <row r="614" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C614" s="6"/>
-      <c r="D614" s="7"/>
-      <c r="E614" s="7"/>
+      <c r="C614" s="5"/>
+      <c r="D614" s="6"/>
+      <c r="E614" s="6"/>
       <c r="I614" s="2"/>
     </row>
     <row r="615" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C615" s="6"/>
-      <c r="D615" s="7"/>
-      <c r="E615" s="7"/>
+      <c r="C615" s="5"/>
+      <c r="D615" s="6"/>
+      <c r="E615" s="6"/>
       <c r="I615" s="2"/>
     </row>
     <row r="616" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C616" s="6"/>
-      <c r="D616" s="7"/>
-      <c r="E616" s="7"/>
+      <c r="C616" s="5"/>
+      <c r="D616" s="6"/>
+      <c r="E616" s="6"/>
       <c r="I616" s="2"/>
     </row>
     <row r="617" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C617" s="6"/>
-      <c r="D617" s="7"/>
-      <c r="E617" s="7"/>
+      <c r="C617" s="5"/>
+      <c r="D617" s="6"/>
+      <c r="E617" s="6"/>
       <c r="I617" s="2"/>
     </row>
     <row r="618" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C618" s="6"/>
-      <c r="D618" s="7"/>
-      <c r="E618" s="7"/>
+      <c r="C618" s="5"/>
+      <c r="D618" s="6"/>
+      <c r="E618" s="6"/>
       <c r="I618" s="2"/>
     </row>
     <row r="619" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C619" s="6"/>
-      <c r="D619" s="7"/>
-      <c r="E619" s="7"/>
+      <c r="C619" s="5"/>
+      <c r="D619" s="6"/>
+      <c r="E619" s="6"/>
       <c r="I619" s="2"/>
     </row>
     <row r="620" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C620" s="6"/>
-      <c r="D620" s="7"/>
-      <c r="E620" s="7"/>
+      <c r="C620" s="5"/>
+      <c r="D620" s="6"/>
+      <c r="E620" s="6"/>
       <c r="I620" s="2"/>
     </row>
     <row r="621" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C621" s="6"/>
-      <c r="D621" s="7"/>
-      <c r="E621" s="7"/>
+      <c r="C621" s="5"/>
+      <c r="D621" s="6"/>
+      <c r="E621" s="6"/>
       <c r="I621" s="2"/>
     </row>
     <row r="622" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C622" s="6"/>
-      <c r="D622" s="7"/>
-      <c r="E622" s="7"/>
+      <c r="C622" s="5"/>
+      <c r="D622" s="6"/>
+      <c r="E622" s="6"/>
       <c r="I622" s="2"/>
     </row>
     <row r="623" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C623" s="6"/>
-      <c r="D623" s="7"/>
-      <c r="E623" s="7"/>
+      <c r="C623" s="5"/>
+      <c r="D623" s="6"/>
+      <c r="E623" s="6"/>
       <c r="I623" s="2"/>
     </row>
     <row r="624" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C624" s="6"/>
-      <c r="D624" s="7"/>
-      <c r="E624" s="7"/>
+      <c r="C624" s="5"/>
+      <c r="D624" s="6"/>
+      <c r="E624" s="6"/>
       <c r="I624" s="2"/>
     </row>
     <row r="625" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C625" s="6"/>
-      <c r="D625" s="7"/>
-      <c r="E625" s="7"/>
+      <c r="C625" s="5"/>
+      <c r="D625" s="6"/>
+      <c r="E625" s="6"/>
       <c r="I625" s="2"/>
     </row>
     <row r="626" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C626" s="6"/>
-      <c r="D626" s="7"/>
-      <c r="E626" s="7"/>
+      <c r="C626" s="5"/>
+      <c r="D626" s="6"/>
+      <c r="E626" s="6"/>
       <c r="I626" s="2"/>
     </row>
     <row r="627" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C627" s="6"/>
-      <c r="D627" s="7"/>
-      <c r="E627" s="7"/>
+      <c r="C627" s="5"/>
+      <c r="D627" s="6"/>
+      <c r="E627" s="6"/>
       <c r="I627" s="2"/>
     </row>
     <row r="628" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C628" s="6"/>
-      <c r="D628" s="7"/>
-      <c r="E628" s="7"/>
+      <c r="C628" s="5"/>
+      <c r="D628" s="6"/>
+      <c r="E628" s="6"/>
       <c r="I628" s="2"/>
     </row>
     <row r="629" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C629" s="6"/>
-      <c r="D629" s="7"/>
-      <c r="E629" s="7"/>
+      <c r="C629" s="5"/>
+      <c r="D629" s="6"/>
+      <c r="E629" s="6"/>
       <c r="I629" s="2"/>
     </row>
     <row r="630" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C630" s="6"/>
-      <c r="D630" s="7"/>
-      <c r="E630" s="7"/>
+      <c r="C630" s="5"/>
+      <c r="D630" s="6"/>
+      <c r="E630" s="6"/>
       <c r="I630" s="2"/>
     </row>
     <row r="631" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C631" s="6"/>
-      <c r="D631" s="7"/>
-      <c r="E631" s="7"/>
+      <c r="C631" s="5"/>
+      <c r="D631" s="6"/>
+      <c r="E631" s="6"/>
       <c r="I631" s="2"/>
     </row>
     <row r="632" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C632" s="6"/>
-      <c r="D632" s="7"/>
-      <c r="E632" s="7"/>
+      <c r="C632" s="5"/>
+      <c r="D632" s="6"/>
+      <c r="E632" s="6"/>
       <c r="I632" s="2"/>
     </row>
     <row r="633" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C633" s="6"/>
-      <c r="D633" s="7"/>
-      <c r="E633" s="7"/>
+      <c r="C633" s="5"/>
+      <c r="D633" s="6"/>
+      <c r="E633" s="6"/>
       <c r="I633" s="2"/>
     </row>
     <row r="634" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C634" s="6"/>
-      <c r="D634" s="7"/>
-      <c r="E634" s="7"/>
+      <c r="C634" s="5"/>
+      <c r="D634" s="6"/>
+      <c r="E634" s="6"/>
       <c r="I634" s="2"/>
     </row>
     <row r="635" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C635" s="6"/>
-      <c r="D635" s="7"/>
-      <c r="E635" s="7"/>
+      <c r="C635" s="5"/>
+      <c r="D635" s="6"/>
+      <c r="E635" s="6"/>
       <c r="I635" s="2"/>
     </row>
     <row r="636" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C636" s="6"/>
-      <c r="D636" s="7"/>
-      <c r="E636" s="7"/>
+      <c r="C636" s="5"/>
+      <c r="D636" s="6"/>
+      <c r="E636" s="6"/>
       <c r="I636" s="2"/>
     </row>
     <row r="637" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C637" s="6"/>
-      <c r="D637" s="7"/>
-      <c r="E637" s="7"/>
+      <c r="C637" s="5"/>
+      <c r="D637" s="6"/>
+      <c r="E637" s="6"/>
       <c r="I637" s="2"/>
     </row>
     <row r="638" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C638" s="6"/>
-      <c r="D638" s="7"/>
-      <c r="E638" s="7"/>
+      <c r="C638" s="5"/>
+      <c r="D638" s="6"/>
+      <c r="E638" s="6"/>
       <c r="I638" s="2"/>
     </row>
     <row r="639" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C639" s="6"/>
-      <c r="D639" s="7"/>
-      <c r="E639" s="7"/>
+      <c r="C639" s="5"/>
+      <c r="D639" s="6"/>
+      <c r="E639" s="6"/>
       <c r="I639" s="2"/>
     </row>
     <row r="640" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C640" s="6"/>
-      <c r="D640" s="7"/>
-      <c r="E640" s="7"/>
+      <c r="C640" s="5"/>
+      <c r="D640" s="6"/>
+      <c r="E640" s="6"/>
       <c r="I640" s="2"/>
     </row>
     <row r="641" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C641" s="6"/>
-      <c r="D641" s="7"/>
-      <c r="E641" s="7"/>
+      <c r="C641" s="5"/>
+      <c r="D641" s="6"/>
+      <c r="E641" s="6"/>
       <c r="I641" s="2"/>
     </row>
     <row r="642" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C642" s="6"/>
-      <c r="D642" s="7"/>
-      <c r="E642" s="7"/>
+      <c r="C642" s="5"/>
+      <c r="D642" s="6"/>
+      <c r="E642" s="6"/>
       <c r="I642" s="2"/>
     </row>
     <row r="643" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C643" s="6"/>
-      <c r="D643" s="7"/>
-      <c r="E643" s="7"/>
+      <c r="C643" s="5"/>
+      <c r="D643" s="6"/>
+      <c r="E643" s="6"/>
       <c r="I643" s="2"/>
     </row>
     <row r="644" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C644" s="6"/>
-      <c r="D644" s="7"/>
-      <c r="E644" s="7"/>
+      <c r="C644" s="5"/>
+      <c r="D644" s="6"/>
+      <c r="E644" s="6"/>
       <c r="I644" s="2"/>
     </row>
     <row r="645" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C645" s="6"/>
-      <c r="D645" s="7"/>
-      <c r="E645" s="7"/>
+      <c r="C645" s="5"/>
+      <c r="D645" s="6"/>
+      <c r="E645" s="6"/>
       <c r="I645" s="2"/>
     </row>
     <row r="646" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C646" s="6"/>
-      <c r="D646" s="7"/>
-      <c r="E646" s="7"/>
+      <c r="C646" s="5"/>
+      <c r="D646" s="6"/>
+      <c r="E646" s="6"/>
       <c r="I646" s="2"/>
     </row>
     <row r="647" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C647" s="6"/>
-      <c r="D647" s="7"/>
-      <c r="E647" s="7"/>
+      <c r="C647" s="5"/>
+      <c r="D647" s="6"/>
+      <c r="E647" s="6"/>
       <c r="I647" s="2"/>
     </row>
     <row r="648" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C648" s="6"/>
-      <c r="D648" s="7"/>
-      <c r="E648" s="7"/>
+      <c r="C648" s="5"/>
+      <c r="D648" s="6"/>
+      <c r="E648" s="6"/>
       <c r="I648" s="2"/>
     </row>
     <row r="649" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C649" s="6"/>
-      <c r="D649" s="7"/>
-      <c r="E649" s="7"/>
+      <c r="C649" s="5"/>
+      <c r="D649" s="6"/>
+      <c r="E649" s="6"/>
       <c r="I649" s="2"/>
     </row>
     <row r="650" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C650" s="6"/>
-      <c r="D650" s="7"/>
-      <c r="E650" s="7"/>
+      <c r="C650" s="5"/>
+      <c r="D650" s="6"/>
+      <c r="E650" s="6"/>
       <c r="I650" s="2"/>
     </row>
     <row r="651" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C651" s="6"/>
-      <c r="D651" s="7"/>
-      <c r="E651" s="7"/>
+      <c r="C651" s="5"/>
+      <c r="D651" s="6"/>
+      <c r="E651" s="6"/>
       <c r="I651" s="2"/>
     </row>
     <row r="652" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C652" s="6"/>
-      <c r="D652" s="7"/>
-      <c r="E652" s="7"/>
+      <c r="C652" s="5"/>
+      <c r="D652" s="6"/>
+      <c r="E652" s="6"/>
       <c r="I652" s="2"/>
     </row>
     <row r="653" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C653" s="6"/>
-      <c r="D653" s="7"/>
-      <c r="E653" s="7"/>
+      <c r="C653" s="5"/>
+      <c r="D653" s="6"/>
+      <c r="E653" s="6"/>
       <c r="I653" s="2"/>
     </row>
     <row r="654" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C654" s="6"/>
-      <c r="D654" s="7"/>
-      <c r="E654" s="7"/>
+      <c r="C654" s="5"/>
+      <c r="D654" s="6"/>
+      <c r="E654" s="6"/>
       <c r="I654" s="2"/>
     </row>
     <row r="655" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C655" s="6"/>
-      <c r="D655" s="7"/>
-      <c r="E655" s="7"/>
+      <c r="C655" s="5"/>
+      <c r="D655" s="6"/>
+      <c r="E655" s="6"/>
       <c r="I655" s="2"/>
     </row>
     <row r="656" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C656" s="6"/>
-      <c r="D656" s="7"/>
-      <c r="E656" s="7"/>
+      <c r="C656" s="5"/>
+      <c r="D656" s="6"/>
+      <c r="E656" s="6"/>
       <c r="I656" s="2"/>
     </row>
     <row r="657" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C657" s="6"/>
-      <c r="D657" s="7"/>
-      <c r="E657" s="7"/>
+      <c r="C657" s="5"/>
+      <c r="D657" s="6"/>
+      <c r="E657" s="6"/>
       <c r="I657" s="2"/>
     </row>
     <row r="658" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C658" s="6"/>
-      <c r="D658" s="7"/>
-      <c r="E658" s="7"/>
+      <c r="C658" s="5"/>
+      <c r="D658" s="6"/>
+      <c r="E658" s="6"/>
       <c r="I658" s="2"/>
     </row>
     <row r="659" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C659" s="6"/>
-      <c r="D659" s="7"/>
-      <c r="E659" s="7"/>
+      <c r="C659" s="5"/>
+      <c r="D659" s="6"/>
+      <c r="E659" s="6"/>
       <c r="I659" s="2"/>
     </row>
     <row r="660" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C660" s="6"/>
-      <c r="D660" s="7"/>
-      <c r="E660" s="7"/>
+      <c r="C660" s="5"/>
+      <c r="D660" s="6"/>
+      <c r="E660" s="6"/>
       <c r="I660" s="2"/>
     </row>
     <row r="661" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C661" s="6"/>
-      <c r="D661" s="7"/>
-      <c r="E661" s="7"/>
+      <c r="C661" s="5"/>
+      <c r="D661" s="6"/>
+      <c r="E661" s="6"/>
       <c r="I661" s="2"/>
     </row>
     <row r="662" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C662" s="6"/>
-      <c r="D662" s="7"/>
-      <c r="E662" s="7"/>
+      <c r="C662" s="5"/>
+      <c r="D662" s="6"/>
+      <c r="E662" s="6"/>
       <c r="I662" s="2"/>
     </row>
     <row r="663" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C663" s="6"/>
-      <c r="D663" s="7"/>
-      <c r="E663" s="7"/>
+      <c r="C663" s="5"/>
+      <c r="D663" s="6"/>
+      <c r="E663" s="6"/>
       <c r="I663" s="2"/>
     </row>
     <row r="664" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C664" s="6"/>
-      <c r="D664" s="7"/>
-      <c r="E664" s="7"/>
+      <c r="C664" s="5"/>
+      <c r="D664" s="6"/>
+      <c r="E664" s="6"/>
       <c r="I664" s="2"/>
     </row>
     <row r="665" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C665" s="6"/>
-      <c r="D665" s="7"/>
-      <c r="E665" s="7"/>
+      <c r="C665" s="5"/>
+      <c r="D665" s="6"/>
+      <c r="E665" s="6"/>
       <c r="I665" s="2"/>
     </row>
     <row r="666" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C666" s="6"/>
-      <c r="D666" s="7"/>
-      <c r="E666" s="7"/>
+      <c r="C666" s="5"/>
+      <c r="D666" s="6"/>
+      <c r="E666" s="6"/>
       <c r="I666" s="2"/>
     </row>
     <row r="667" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C667" s="6"/>
-      <c r="D667" s="7"/>
-      <c r="E667" s="7"/>
+      <c r="C667" s="5"/>
+      <c r="D667" s="6"/>
+      <c r="E667" s="6"/>
       <c r="I667" s="2"/>
     </row>
     <row r="668" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C668" s="6"/>
-      <c r="D668" s="7"/>
-      <c r="E668" s="7"/>
+      <c r="C668" s="5"/>
+      <c r="D668" s="6"/>
+      <c r="E668" s="6"/>
       <c r="I668" s="2"/>
     </row>
     <row r="669" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C669" s="6"/>
-      <c r="D669" s="7"/>
-      <c r="E669" s="7"/>
+      <c r="C669" s="5"/>
+      <c r="D669" s="6"/>
+      <c r="E669" s="6"/>
       <c r="I669" s="2"/>
     </row>
     <row r="670" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C670" s="6"/>
-      <c r="D670" s="7"/>
-      <c r="E670" s="7"/>
+      <c r="C670" s="5"/>
+      <c r="D670" s="6"/>
+      <c r="E670" s="6"/>
       <c r="I670" s="2"/>
     </row>
     <row r="671" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C671" s="6"/>
-      <c r="D671" s="7"/>
-      <c r="E671" s="7"/>
+      <c r="C671" s="5"/>
+      <c r="D671" s="6"/>
+      <c r="E671" s="6"/>
       <c r="I671" s="2"/>
     </row>
     <row r="672" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C672" s="6"/>
-      <c r="D672" s="7"/>
-      <c r="E672" s="7"/>
+      <c r="C672" s="5"/>
+      <c r="D672" s="6"/>
+      <c r="E672" s="6"/>
       <c r="I672" s="2"/>
     </row>
     <row r="673" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C673" s="6"/>
-      <c r="D673" s="7"/>
-      <c r="E673" s="7"/>
+      <c r="C673" s="5"/>
+      <c r="D673" s="6"/>
+      <c r="E673" s="6"/>
       <c r="I673" s="2"/>
     </row>
     <row r="674" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C674" s="6"/>
-      <c r="D674" s="7"/>
-      <c r="E674" s="7"/>
+      <c r="C674" s="5"/>
+      <c r="D674" s="6"/>
+      <c r="E674" s="6"/>
       <c r="I674" s="2"/>
     </row>
     <row r="675" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C675" s="6"/>
-      <c r="D675" s="7"/>
-      <c r="E675" s="7"/>
+      <c r="C675" s="5"/>
+      <c r="D675" s="6"/>
+      <c r="E675" s="6"/>
       <c r="I675" s="2"/>
     </row>
     <row r="676" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C676" s="6"/>
-      <c r="D676" s="7"/>
-      <c r="E676" s="7"/>
+      <c r="C676" s="5"/>
+      <c r="D676" s="6"/>
+      <c r="E676" s="6"/>
       <c r="I676" s="2"/>
     </row>
     <row r="677" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C677" s="6"/>
-      <c r="D677" s="7"/>
-      <c r="E677" s="7"/>
+      <c r="C677" s="5"/>
+      <c r="D677" s="6"/>
+      <c r="E677" s="6"/>
       <c r="I677" s="2"/>
     </row>
     <row r="678" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C678" s="6"/>
-      <c r="D678" s="7"/>
-      <c r="E678" s="7"/>
+      <c r="C678" s="5"/>
+      <c r="D678" s="6"/>
+      <c r="E678" s="6"/>
       <c r="I678" s="2"/>
     </row>
     <row r="679" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C679" s="6"/>
-      <c r="D679" s="7"/>
-      <c r="E679" s="7"/>
+      <c r="C679" s="5"/>
+      <c r="D679" s="6"/>
+      <c r="E679" s="6"/>
       <c r="I679" s="2"/>
     </row>
     <row r="680" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C680" s="6"/>
-      <c r="D680" s="7"/>
-      <c r="E680" s="7"/>
+      <c r="C680" s="5"/>
+      <c r="D680" s="6"/>
+      <c r="E680" s="6"/>
       <c r="I680" s="2"/>
     </row>
     <row r="681" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C681" s="6"/>
-      <c r="D681" s="7"/>
-      <c r="E681" s="7"/>
+      <c r="C681" s="5"/>
+      <c r="D681" s="6"/>
+      <c r="E681" s="6"/>
       <c r="I681" s="2"/>
     </row>
     <row r="682" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C682" s="6"/>
-      <c r="D682" s="7"/>
-      <c r="E682" s="7"/>
+      <c r="C682" s="5"/>
+      <c r="D682" s="6"/>
+      <c r="E682" s="6"/>
       <c r="I682" s="2"/>
     </row>
     <row r="683" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C683" s="6"/>
-      <c r="D683" s="7"/>
-      <c r="E683" s="7"/>
+      <c r="C683" s="5"/>
+      <c r="D683" s="6"/>
+      <c r="E683" s="6"/>
       <c r="I683" s="2"/>
     </row>
     <row r="684" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C684" s="6"/>
-      <c r="D684" s="7"/>
-      <c r="E684" s="7"/>
+      <c r="C684" s="5"/>
+      <c r="D684" s="6"/>
+      <c r="E684" s="6"/>
       <c r="I684" s="2"/>
     </row>
     <row r="685" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C685" s="6"/>
-      <c r="D685" s="7"/>
-      <c r="E685" s="7"/>
+      <c r="C685" s="5"/>
+      <c r="D685" s="6"/>
+      <c r="E685" s="6"/>
       <c r="I685" s="2"/>
     </row>
     <row r="686" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C686" s="6"/>
-      <c r="D686" s="7"/>
-      <c r="E686" s="7"/>
+      <c r="C686" s="5"/>
+      <c r="D686" s="6"/>
+      <c r="E686" s="6"/>
       <c r="I686" s="2"/>
     </row>
     <row r="687" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C687" s="6"/>
-      <c r="D687" s="7"/>
-      <c r="E687" s="7"/>
+      <c r="C687" s="5"/>
+      <c r="D687" s="6"/>
+      <c r="E687" s="6"/>
       <c r="I687" s="2"/>
     </row>
     <row r="688" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C688" s="6"/>
-      <c r="D688" s="7"/>
-      <c r="E688" s="7"/>
+      <c r="C688" s="5"/>
+      <c r="D688" s="6"/>
+      <c r="E688" s="6"/>
       <c r="I688" s="2"/>
     </row>
     <row r="689" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C689" s="6"/>
-      <c r="D689" s="7"/>
-      <c r="E689" s="7"/>
+      <c r="C689" s="5"/>
+      <c r="D689" s="6"/>
+      <c r="E689" s="6"/>
       <c r="I689" s="2"/>
     </row>
     <row r="690" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C690" s="6"/>
-      <c r="D690" s="7"/>
-      <c r="E690" s="7"/>
+      <c r="C690" s="5"/>
+      <c r="D690" s="6"/>
+      <c r="E690" s="6"/>
       <c r="I690" s="2"/>
     </row>
     <row r="691" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C691" s="6"/>
-      <c r="D691" s="7"/>
-      <c r="E691" s="7"/>
+      <c r="C691" s="5"/>
+      <c r="D691" s="6"/>
+      <c r="E691" s="6"/>
       <c r="I691" s="2"/>
     </row>
     <row r="692" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C692" s="6"/>
-      <c r="D692" s="7"/>
-      <c r="E692" s="7"/>
+      <c r="C692" s="5"/>
+      <c r="D692" s="6"/>
+      <c r="E692" s="6"/>
       <c r="I692" s="2"/>
     </row>
     <row r="693" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C693" s="6"/>
-      <c r="D693" s="7"/>
-      <c r="E693" s="7"/>
+      <c r="C693" s="5"/>
+      <c r="D693" s="6"/>
+      <c r="E693" s="6"/>
       <c r="I693" s="2"/>
     </row>
     <row r="694" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C694" s="6"/>
-      <c r="D694" s="7"/>
-      <c r="E694" s="7"/>
+      <c r="C694" s="5"/>
+      <c r="D694" s="6"/>
+      <c r="E694" s="6"/>
       <c r="I694" s="2"/>
     </row>
     <row r="695" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C695" s="6"/>
-      <c r="D695" s="7"/>
-      <c r="E695" s="7"/>
+      <c r="C695" s="5"/>
+      <c r="D695" s="6"/>
+      <c r="E695" s="6"/>
       <c r="I695" s="2"/>
     </row>
     <row r="696" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C696" s="6"/>
-      <c r="D696" s="7"/>
-      <c r="E696" s="7"/>
+      <c r="C696" s="5"/>
+      <c r="D696" s="6"/>
+      <c r="E696" s="6"/>
       <c r="I696" s="2"/>
     </row>
     <row r="697" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C697" s="6"/>
-      <c r="D697" s="7"/>
-      <c r="E697" s="7"/>
+      <c r="C697" s="5"/>
+      <c r="D697" s="6"/>
+      <c r="E697" s="6"/>
       <c r="I697" s="2"/>
     </row>
     <row r="698" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C698" s="6"/>
-      <c r="D698" s="7"/>
-      <c r="E698" s="7"/>
+      <c r="C698" s="5"/>
+      <c r="D698" s="6"/>
+      <c r="E698" s="6"/>
       <c r="I698" s="2"/>
     </row>
     <row r="699" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C699" s="6"/>
-      <c r="D699" s="7"/>
-      <c r="E699" s="7"/>
+      <c r="C699" s="5"/>
+      <c r="D699" s="6"/>
+      <c r="E699" s="6"/>
       <c r="I699" s="2"/>
     </row>
     <row r="700" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C700" s="6"/>
-      <c r="D700" s="7"/>
-      <c r="E700" s="7"/>
+      <c r="C700" s="5"/>
+      <c r="D700" s="6"/>
+      <c r="E700" s="6"/>
       <c r="I700" s="2"/>
     </row>
     <row r="701" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C701" s="6"/>
-      <c r="D701" s="7"/>
-      <c r="E701" s="7"/>
+      <c r="C701" s="5"/>
+      <c r="D701" s="6"/>
+      <c r="E701" s="6"/>
       <c r="I701" s="2"/>
     </row>
     <row r="702" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C702" s="6"/>
-      <c r="D702" s="7"/>
-      <c r="E702" s="7"/>
+      <c r="C702" s="5"/>
+      <c r="D702" s="6"/>
+      <c r="E702" s="6"/>
       <c r="I702" s="2"/>
     </row>
     <row r="703" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C703" s="6"/>
-      <c r="D703" s="7"/>
-      <c r="E703" s="7"/>
+      <c r="C703" s="5"/>
+      <c r="D703" s="6"/>
+      <c r="E703" s="6"/>
       <c r="I703" s="2"/>
     </row>
     <row r="704" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C704" s="6"/>
-      <c r="D704" s="7"/>
-      <c r="E704" s="7"/>
+      <c r="C704" s="5"/>
+      <c r="D704" s="6"/>
+      <c r="E704" s="6"/>
       <c r="I704" s="2"/>
     </row>
     <row r="705" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C705" s="6"/>
-      <c r="D705" s="7"/>
-      <c r="E705" s="7"/>
+      <c r="C705" s="5"/>
+      <c r="D705" s="6"/>
+      <c r="E705" s="6"/>
       <c r="I705" s="2"/>
     </row>
     <row r="706" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C706" s="6"/>
-      <c r="D706" s="7"/>
-      <c r="E706" s="7"/>
+      <c r="C706" s="5"/>
+      <c r="D706" s="6"/>
+      <c r="E706" s="6"/>
       <c r="I706" s="2"/>
     </row>
     <row r="707" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C707" s="6"/>
-      <c r="D707" s="7"/>
-      <c r="E707" s="7"/>
+      <c r="C707" s="5"/>
+      <c r="D707" s="6"/>
+      <c r="E707" s="6"/>
       <c r="I707" s="2"/>
     </row>
     <row r="708" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C708" s="6"/>
-      <c r="D708" s="7"/>
-      <c r="E708" s="7"/>
+      <c r="C708" s="5"/>
+      <c r="D708" s="6"/>
+      <c r="E708" s="6"/>
       <c r="I708" s="2"/>
     </row>
     <row r="709" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C709" s="6"/>
-      <c r="D709" s="7"/>
-      <c r="E709" s="7"/>
+      <c r="C709" s="5"/>
+      <c r="D709" s="6"/>
+      <c r="E709" s="6"/>
       <c r="I709" s="2"/>
     </row>
     <row r="710" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C710" s="6"/>
-      <c r="D710" s="7"/>
-      <c r="E710" s="7"/>
+      <c r="C710" s="5"/>
+      <c r="D710" s="6"/>
+      <c r="E710" s="6"/>
       <c r="I710" s="2"/>
     </row>
     <row r="711" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C711" s="6"/>
-      <c r="D711" s="7"/>
-      <c r="E711" s="7"/>
+      <c r="C711" s="5"/>
+      <c r="D711" s="6"/>
+      <c r="E711" s="6"/>
       <c r="I711" s="2"/>
     </row>
     <row r="712" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C712" s="6"/>
-      <c r="D712" s="7"/>
-      <c r="E712" s="7"/>
+      <c r="C712" s="5"/>
+      <c r="D712" s="6"/>
+      <c r="E712" s="6"/>
       <c r="I712" s="2"/>
     </row>
     <row r="713" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C713" s="6"/>
-      <c r="D713" s="7"/>
-      <c r="E713" s="7"/>
+      <c r="C713" s="5"/>
+      <c r="D713" s="6"/>
+      <c r="E713" s="6"/>
       <c r="I713" s="2"/>
     </row>
     <row r="714" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C714" s="6"/>
-      <c r="D714" s="7"/>
-      <c r="E714" s="7"/>
+      <c r="C714" s="5"/>
+      <c r="D714" s="6"/>
+      <c r="E714" s="6"/>
       <c r="I714" s="2"/>
     </row>
     <row r="715" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C715" s="6"/>
-      <c r="D715" s="7"/>
-      <c r="E715" s="7"/>
+      <c r="C715" s="5"/>
+      <c r="D715" s="6"/>
+      <c r="E715" s="6"/>
       <c r="I715" s="2"/>
     </row>
     <row r="716" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C716" s="6"/>
-      <c r="D716" s="7"/>
-      <c r="E716" s="7"/>
+      <c r="C716" s="5"/>
+      <c r="D716" s="6"/>
+      <c r="E716" s="6"/>
       <c r="I716" s="2"/>
     </row>
     <row r="717" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C717" s="6"/>
-      <c r="D717" s="7"/>
-      <c r="E717" s="7"/>
+      <c r="C717" s="5"/>
+      <c r="D717" s="6"/>
+      <c r="E717" s="6"/>
       <c r="I717" s="2"/>
     </row>
     <row r="718" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C718" s="6"/>
-      <c r="D718" s="7"/>
-      <c r="E718" s="7"/>
+      <c r="C718" s="5"/>
+      <c r="D718" s="6"/>
+      <c r="E718" s="6"/>
       <c r="I718" s="2"/>
     </row>
     <row r="719" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C719" s="6"/>
-      <c r="D719" s="7"/>
-      <c r="E719" s="7"/>
+      <c r="C719" s="5"/>
+      <c r="D719" s="6"/>
+      <c r="E719" s="6"/>
       <c r="I719" s="2"/>
     </row>
     <row r="720" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C720" s="6"/>
-      <c r="D720" s="7"/>
-      <c r="E720" s="7"/>
+      <c r="C720" s="5"/>
+      <c r="D720" s="6"/>
+      <c r="E720" s="6"/>
       <c r="I720" s="2"/>
     </row>
     <row r="721" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C721" s="6"/>
-      <c r="D721" s="7"/>
-      <c r="E721" s="7"/>
+      <c r="C721" s="5"/>
+      <c r="D721" s="6"/>
+      <c r="E721" s="6"/>
       <c r="I721" s="2"/>
     </row>
     <row r="722" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C722" s="6"/>
-      <c r="D722" s="7"/>
-      <c r="E722" s="7"/>
+      <c r="C722" s="5"/>
+      <c r="D722" s="6"/>
+      <c r="E722" s="6"/>
       <c r="I722" s="2"/>
     </row>
     <row r="723" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C723" s="6"/>
-      <c r="D723" s="7"/>
-      <c r="E723" s="7"/>
+      <c r="C723" s="5"/>
+      <c r="D723" s="6"/>
+      <c r="E723" s="6"/>
       <c r="I723" s="2"/>
     </row>
     <row r="724" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C724" s="6"/>
-      <c r="D724" s="7"/>
-      <c r="E724" s="7"/>
+      <c r="C724" s="5"/>
+      <c r="D724" s="6"/>
+      <c r="E724" s="6"/>
       <c r="I724" s="2"/>
     </row>
     <row r="725" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C725" s="6"/>
-      <c r="D725" s="7"/>
-      <c r="E725" s="7"/>
+      <c r="C725" s="5"/>
+      <c r="D725" s="6"/>
+      <c r="E725" s="6"/>
       <c r="I725" s="2"/>
     </row>
     <row r="726" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C726" s="6"/>
-      <c r="D726" s="7"/>
-      <c r="E726" s="7"/>
+      <c r="C726" s="5"/>
+      <c r="D726" s="6"/>
+      <c r="E726" s="6"/>
       <c r="I726" s="2"/>
     </row>
     <row r="727" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C727" s="6"/>
-      <c r="D727" s="7"/>
-      <c r="E727" s="7"/>
+      <c r="C727" s="5"/>
+      <c r="D727" s="6"/>
+      <c r="E727" s="6"/>
       <c r="I727" s="2"/>
     </row>
     <row r="728" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C728" s="6"/>
-      <c r="D728" s="7"/>
-      <c r="E728" s="7"/>
+      <c r="C728" s="5"/>
+      <c r="D728" s="6"/>
+      <c r="E728" s="6"/>
       <c r="I728" s="2"/>
     </row>
     <row r="729" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C729" s="6"/>
-      <c r="D729" s="7"/>
-      <c r="E729" s="7"/>
+      <c r="C729" s="5"/>
+      <c r="D729" s="6"/>
+      <c r="E729" s="6"/>
       <c r="I729" s="2"/>
     </row>
     <row r="730" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C730" s="6"/>
-      <c r="D730" s="7"/>
-      <c r="E730" s="7"/>
+      <c r="C730" s="5"/>
+      <c r="D730" s="6"/>
+      <c r="E730" s="6"/>
       <c r="I730" s="2"/>
     </row>
     <row r="731" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C731" s="6"/>
-      <c r="D731" s="7"/>
-      <c r="E731" s="7"/>
+      <c r="C731" s="5"/>
+      <c r="D731" s="6"/>
+      <c r="E731" s="6"/>
       <c r="I731" s="2"/>
     </row>
     <row r="732" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C732" s="6"/>
-      <c r="D732" s="7"/>
-      <c r="E732" s="7"/>
+      <c r="C732" s="5"/>
+      <c r="D732" s="6"/>
+      <c r="E732" s="6"/>
       <c r="I732" s="2"/>
     </row>
     <row r="733" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C733" s="6"/>
-      <c r="D733" s="7"/>
-      <c r="E733" s="7"/>
+      <c r="C733" s="5"/>
+      <c r="D733" s="6"/>
+      <c r="E733" s="6"/>
       <c r="I733" s="2"/>
     </row>
     <row r="734" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C734" s="6"/>
-      <c r="D734" s="7"/>
-      <c r="E734" s="7"/>
+      <c r="C734" s="5"/>
+      <c r="D734" s="6"/>
+      <c r="E734" s="6"/>
       <c r="I734" s="2"/>
     </row>
     <row r="735" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C735" s="6"/>
-      <c r="D735" s="7"/>
-      <c r="E735" s="7"/>
+      <c r="C735" s="5"/>
+      <c r="D735" s="6"/>
+      <c r="E735" s="6"/>
       <c r="I735" s="2"/>
     </row>
     <row r="736" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C736" s="6"/>
-      <c r="D736" s="7"/>
-      <c r="E736" s="7"/>
+      <c r="C736" s="5"/>
+      <c r="D736" s="6"/>
+      <c r="E736" s="6"/>
       <c r="I736" s="2"/>
     </row>
     <row r="737" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C737" s="6"/>
-      <c r="D737" s="7"/>
-      <c r="E737" s="7"/>
+      <c r="C737" s="5"/>
+      <c r="D737" s="6"/>
+      <c r="E737" s="6"/>
       <c r="I737" s="2"/>
     </row>
     <row r="738" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C738" s="6"/>
-      <c r="D738" s="7"/>
-      <c r="E738" s="7"/>
+      <c r="C738" s="5"/>
+      <c r="D738" s="6"/>
+      <c r="E738" s="6"/>
       <c r="I738" s="2"/>
     </row>
     <row r="739" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C739" s="6"/>
-      <c r="D739" s="7"/>
-      <c r="E739" s="7"/>
+      <c r="C739" s="5"/>
+      <c r="D739" s="6"/>
+      <c r="E739" s="6"/>
       <c r="I739" s="2"/>
     </row>
     <row r="740" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C740" s="6"/>
-      <c r="D740" s="7"/>
-      <c r="E740" s="7"/>
+      <c r="C740" s="5"/>
+      <c r="D740" s="6"/>
+      <c r="E740" s="6"/>
       <c r="I740" s="2"/>
     </row>
     <row r="741" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C741" s="6"/>
-      <c r="D741" s="7"/>
-      <c r="E741" s="7"/>
+      <c r="C741" s="5"/>
+      <c r="D741" s="6"/>
+      <c r="E741" s="6"/>
       <c r="I741" s="2"/>
     </row>
     <row r="742" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C742" s="6"/>
-      <c r="D742" s="7"/>
-      <c r="E742" s="7"/>
+      <c r="C742" s="5"/>
+      <c r="D742" s="6"/>
+      <c r="E742" s="6"/>
       <c r="I742" s="2"/>
     </row>
     <row r="743" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C743" s="6"/>
-      <c r="D743" s="7"/>
-      <c r="E743" s="7"/>
+      <c r="C743" s="5"/>
+      <c r="D743" s="6"/>
+      <c r="E743" s="6"/>
       <c r="I743" s="2"/>
     </row>
     <row r="744" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C744" s="6"/>
-      <c r="D744" s="7"/>
-      <c r="E744" s="7"/>
+      <c r="C744" s="5"/>
+      <c r="D744" s="6"/>
+      <c r="E744" s="6"/>
       <c r="I744" s="2"/>
     </row>
     <row r="745" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C745" s="6"/>
-      <c r="D745" s="7"/>
-      <c r="E745" s="7"/>
+      <c r="C745" s="5"/>
+      <c r="D745" s="6"/>
+      <c r="E745" s="6"/>
       <c r="I745" s="2"/>
     </row>
     <row r="746" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C746" s="6"/>
-      <c r="D746" s="7"/>
-      <c r="E746" s="7"/>
+      <c r="C746" s="5"/>
+      <c r="D746" s="6"/>
+      <c r="E746" s="6"/>
       <c r="I746" s="2"/>
     </row>
     <row r="747" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C747" s="6"/>
-      <c r="D747" s="7"/>
-      <c r="E747" s="7"/>
+      <c r="C747" s="5"/>
+      <c r="D747" s="6"/>
+      <c r="E747" s="6"/>
       <c r="I747" s="2"/>
     </row>
     <row r="748" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C748" s="6"/>
-      <c r="D748" s="7"/>
-      <c r="E748" s="7"/>
+      <c r="C748" s="5"/>
+      <c r="D748" s="6"/>
+      <c r="E748" s="6"/>
       <c r="I748" s="2"/>
     </row>
     <row r="749" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C749" s="6"/>
-      <c r="D749" s="7"/>
-      <c r="E749" s="7"/>
+      <c r="C749" s="5"/>
+      <c r="D749" s="6"/>
+      <c r="E749" s="6"/>
       <c r="I749" s="2"/>
     </row>
     <row r="750" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C750" s="6"/>
-      <c r="D750" s="7"/>
-      <c r="E750" s="7"/>
+      <c r="C750" s="5"/>
+      <c r="D750" s="6"/>
+      <c r="E750" s="6"/>
       <c r="I750" s="2"/>
     </row>
     <row r="751" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C751" s="6"/>
-      <c r="D751" s="7"/>
-      <c r="E751" s="7"/>
+      <c r="C751" s="5"/>
+      <c r="D751" s="6"/>
+      <c r="E751" s="6"/>
       <c r="I751" s="2"/>
     </row>
     <row r="752" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C752" s="6"/>
-      <c r="D752" s="7"/>
-      <c r="E752" s="7"/>
+      <c r="C752" s="5"/>
+      <c r="D752" s="6"/>
+      <c r="E752" s="6"/>
       <c r="I752" s="2"/>
     </row>
     <row r="753" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C753" s="6"/>
-      <c r="D753" s="7"/>
-      <c r="E753" s="7"/>
+      <c r="C753" s="5"/>
+      <c r="D753" s="6"/>
+      <c r="E753" s="6"/>
       <c r="I753" s="2"/>
     </row>
     <row r="754" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C754" s="6"/>
-      <c r="D754" s="7"/>
-      <c r="E754" s="7"/>
+      <c r="C754" s="5"/>
+      <c r="D754" s="6"/>
+      <c r="E754" s="6"/>
       <c r="I754" s="2"/>
     </row>
     <row r="755" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C755" s="6"/>
-      <c r="D755" s="7"/>
-      <c r="E755" s="7"/>
+      <c r="C755" s="5"/>
+      <c r="D755" s="6"/>
+      <c r="E755" s="6"/>
       <c r="I755" s="2"/>
     </row>
     <row r="756" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C756" s="6"/>
-      <c r="D756" s="7"/>
-      <c r="E756" s="7"/>
+      <c r="C756" s="5"/>
+      <c r="D756" s="6"/>
+      <c r="E756" s="6"/>
       <c r="I756" s="2"/>
     </row>
     <row r="757" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C757" s="6"/>
-      <c r="D757" s="7"/>
-      <c r="E757" s="7"/>
+      <c r="C757" s="5"/>
+      <c r="D757" s="6"/>
+      <c r="E757" s="6"/>
       <c r="I757" s="2"/>
     </row>
     <row r="758" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C758" s="6"/>
-      <c r="D758" s="7"/>
-      <c r="E758" s="7"/>
+      <c r="C758" s="5"/>
+      <c r="D758" s="6"/>
+      <c r="E758" s="6"/>
       <c r="I758" s="2"/>
     </row>
     <row r="759" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C759" s="6"/>
-      <c r="D759" s="7"/>
-      <c r="E759" s="7"/>
+      <c r="C759" s="5"/>
+      <c r="D759" s="6"/>
+      <c r="E759" s="6"/>
       <c r="I759" s="2"/>
     </row>
     <row r="760" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C760" s="6"/>
-      <c r="D760" s="7"/>
-      <c r="E760" s="7"/>
+      <c r="C760" s="5"/>
+      <c r="D760" s="6"/>
+      <c r="E760" s="6"/>
       <c r="I760" s="2"/>
     </row>
     <row r="761" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C761" s="6"/>
-      <c r="D761" s="7"/>
-      <c r="E761" s="7"/>
+      <c r="C761" s="5"/>
+      <c r="D761" s="6"/>
+      <c r="E761" s="6"/>
       <c r="I761" s="2"/>
     </row>
     <row r="762" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C762" s="6"/>
-      <c r="D762" s="7"/>
-      <c r="E762" s="7"/>
+      <c r="C762" s="5"/>
+      <c r="D762" s="6"/>
+      <c r="E762" s="6"/>
       <c r="I762" s="2"/>
     </row>
     <row r="763" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C763" s="6"/>
-      <c r="D763" s="7"/>
-      <c r="E763" s="7"/>
+      <c r="C763" s="5"/>
+      <c r="D763" s="6"/>
+      <c r="E763" s="6"/>
       <c r="I763" s="2"/>
     </row>
     <row r="764" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C764" s="6"/>
-      <c r="D764" s="7"/>
-      <c r="E764" s="7"/>
+      <c r="C764" s="5"/>
+      <c r="D764" s="6"/>
+      <c r="E764" s="6"/>
       <c r="I764" s="2"/>
     </row>
     <row r="765" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C765" s="6"/>
-      <c r="D765" s="7"/>
-      <c r="E765" s="7"/>
+      <c r="C765" s="5"/>
+      <c r="D765" s="6"/>
+      <c r="E765" s="6"/>
       <c r="I765" s="2"/>
     </row>
     <row r="766" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C766" s="6"/>
-      <c r="D766" s="7"/>
-      <c r="E766" s="7"/>
+      <c r="C766" s="5"/>
+      <c r="D766" s="6"/>
+      <c r="E766" s="6"/>
       <c r="I766" s="2"/>
     </row>
     <row r="767" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C767" s="6"/>
-      <c r="D767" s="7"/>
-      <c r="E767" s="7"/>
+      <c r="C767" s="5"/>
+      <c r="D767" s="6"/>
+      <c r="E767" s="6"/>
       <c r="I767" s="2"/>
     </row>
     <row r="768" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C768" s="6"/>
-      <c r="D768" s="7"/>
-      <c r="E768" s="7"/>
+      <c r="C768" s="5"/>
+      <c r="D768" s="6"/>
+      <c r="E768" s="6"/>
       <c r="I768" s="2"/>
     </row>
     <row r="769" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C769" s="6"/>
-      <c r="D769" s="7"/>
-      <c r="E769" s="7"/>
+      <c r="C769" s="5"/>
+      <c r="D769" s="6"/>
+      <c r="E769" s="6"/>
       <c r="I769" s="2"/>
     </row>
     <row r="770" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C770" s="6"/>
-      <c r="D770" s="7"/>
-      <c r="E770" s="7"/>
+      <c r="C770" s="5"/>
+      <c r="D770" s="6"/>
+      <c r="E770" s="6"/>
       <c r="I770" s="2"/>
     </row>
     <row r="771" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C771" s="6"/>
-      <c r="D771" s="7"/>
-      <c r="E771" s="7"/>
+      <c r="C771" s="5"/>
+      <c r="D771" s="6"/>
+      <c r="E771" s="6"/>
       <c r="I771" s="2"/>
     </row>
     <row r="772" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C772" s="6"/>
-      <c r="D772" s="7"/>
-      <c r="E772" s="7"/>
+      <c r="C772" s="5"/>
+      <c r="D772" s="6"/>
+      <c r="E772" s="6"/>
       <c r="I772" s="2"/>
     </row>
     <row r="773" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C773" s="6"/>
-      <c r="D773" s="7"/>
-      <c r="E773" s="7"/>
+      <c r="C773" s="5"/>
+      <c r="D773" s="6"/>
+      <c r="E773" s="6"/>
       <c r="I773" s="2"/>
     </row>
     <row r="774" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C774" s="6"/>
-      <c r="D774" s="7"/>
-      <c r="E774" s="7"/>
+      <c r="C774" s="5"/>
+      <c r="D774" s="6"/>
+      <c r="E774" s="6"/>
       <c r="I774" s="2"/>
     </row>
     <row r="775" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C775" s="6"/>
-      <c r="D775" s="7"/>
-      <c r="E775" s="7"/>
+      <c r="C775" s="5"/>
+      <c r="D775" s="6"/>
+      <c r="E775" s="6"/>
       <c r="I775" s="2"/>
     </row>
     <row r="776" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C776" s="6"/>
-      <c r="D776" s="7"/>
-      <c r="E776" s="7"/>
+      <c r="C776" s="5"/>
+      <c r="D776" s="6"/>
+      <c r="E776" s="6"/>
       <c r="I776" s="2"/>
     </row>
     <row r="777" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C777" s="6"/>
-      <c r="D777" s="7"/>
-      <c r="E777" s="7"/>
+      <c r="C777" s="5"/>
+      <c r="D777" s="6"/>
+      <c r="E777" s="6"/>
       <c r="I777" s="2"/>
     </row>
     <row r="778" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C778" s="6"/>
-      <c r="D778" s="7"/>
-      <c r="E778" s="7"/>
+      <c r="C778" s="5"/>
+      <c r="D778" s="6"/>
+      <c r="E778" s="6"/>
       <c r="I778" s="2"/>
     </row>
     <row r="779" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C779" s="6"/>
-      <c r="D779" s="7"/>
-      <c r="E779" s="7"/>
+      <c r="C779" s="5"/>
+      <c r="D779" s="6"/>
+      <c r="E779" s="6"/>
       <c r="I779" s="2"/>
     </row>
     <row r="780" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C780" s="6"/>
-      <c r="D780" s="7"/>
-      <c r="E780" s="7"/>
+      <c r="C780" s="5"/>
+      <c r="D780" s="6"/>
+      <c r="E780" s="6"/>
       <c r="I780" s="2"/>
     </row>
     <row r="781" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C781" s="6"/>
-      <c r="D781" s="7"/>
-      <c r="E781" s="7"/>
+      <c r="C781" s="5"/>
+      <c r="D781" s="6"/>
+      <c r="E781" s="6"/>
       <c r="I781" s="2"/>
     </row>
     <row r="782" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C782" s="6"/>
-      <c r="D782" s="7"/>
-      <c r="E782" s="7"/>
+      <c r="C782" s="5"/>
+      <c r="D782" s="6"/>
+      <c r="E782" s="6"/>
       <c r="I782" s="2"/>
     </row>
     <row r="783" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C783" s="6"/>
-      <c r="D783" s="7"/>
-      <c r="E783" s="7"/>
+      <c r="C783" s="5"/>
+      <c r="D783" s="6"/>
+      <c r="E783" s="6"/>
       <c r="I783" s="2"/>
     </row>
     <row r="784" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C784" s="6"/>
-      <c r="D784" s="7"/>
-      <c r="E784" s="7"/>
+      <c r="C784" s="5"/>
+      <c r="D784" s="6"/>
+      <c r="E784" s="6"/>
       <c r="I784" s="2"/>
     </row>
     <row r="785" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C785" s="6"/>
-      <c r="D785" s="7"/>
-      <c r="E785" s="7"/>
+      <c r="C785" s="5"/>
+      <c r="D785" s="6"/>
+      <c r="E785" s="6"/>
       <c r="I785" s="2"/>
     </row>
     <row r="786" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C786" s="6"/>
-      <c r="D786" s="7"/>
-      <c r="E786" s="7"/>
+      <c r="C786" s="5"/>
+      <c r="D786" s="6"/>
+      <c r="E786" s="6"/>
       <c r="I786" s="2"/>
     </row>
     <row r="787" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C787" s="6"/>
-      <c r="D787" s="7"/>
-      <c r="E787" s="7"/>
+      <c r="C787" s="5"/>
+      <c r="D787" s="6"/>
+      <c r="E787" s="6"/>
       <c r="I787" s="2"/>
     </row>
     <row r="788" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C788" s="6"/>
-      <c r="D788" s="7"/>
-      <c r="E788" s="7"/>
+      <c r="C788" s="5"/>
+      <c r="D788" s="6"/>
+      <c r="E788" s="6"/>
       <c r="I788" s="2"/>
     </row>
     <row r="789" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C789" s="6"/>
-      <c r="D789" s="7"/>
-      <c r="E789" s="7"/>
+      <c r="C789" s="5"/>
+      <c r="D789" s="6"/>
+      <c r="E789" s="6"/>
       <c r="I789" s="2"/>
     </row>
     <row r="790" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C790" s="6"/>
-      <c r="D790" s="7"/>
-      <c r="E790" s="7"/>
+      <c r="C790" s="5"/>
+      <c r="D790" s="6"/>
+      <c r="E790" s="6"/>
       <c r="I790" s="2"/>
     </row>
     <row r="791" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C791" s="6"/>
-      <c r="D791" s="7"/>
-      <c r="E791" s="7"/>
+      <c r="C791" s="5"/>
+      <c r="D791" s="6"/>
+      <c r="E791" s="6"/>
       <c r="I791" s="2"/>
     </row>
     <row r="792" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C792" s="6"/>
-      <c r="D792" s="7"/>
-      <c r="E792" s="7"/>
+      <c r="C792" s="5"/>
+      <c r="D792" s="6"/>
+      <c r="E792" s="6"/>
       <c r="I792" s="2"/>
     </row>
     <row r="793" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C793" s="6"/>
-      <c r="D793" s="7"/>
-      <c r="E793" s="7"/>
+      <c r="C793" s="5"/>
+      <c r="D793" s="6"/>
+      <c r="E793" s="6"/>
       <c r="I793" s="2"/>
     </row>
     <row r="794" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C794" s="6"/>
-      <c r="D794" s="7"/>
-      <c r="E794" s="7"/>
+      <c r="C794" s="5"/>
+      <c r="D794" s="6"/>
+      <c r="E794" s="6"/>
       <c r="I794" s="2"/>
     </row>
     <row r="795" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C795" s="6"/>
-      <c r="D795" s="7"/>
-      <c r="E795" s="7"/>
+      <c r="C795" s="5"/>
+      <c r="D795" s="6"/>
+      <c r="E795" s="6"/>
       <c r="I795" s="2"/>
     </row>
     <row r="796" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C796" s="6"/>
-      <c r="D796" s="7"/>
-      <c r="E796" s="7"/>
+      <c r="C796" s="5"/>
+      <c r="D796" s="6"/>
+      <c r="E796" s="6"/>
       <c r="I796" s="2"/>
     </row>
     <row r="797" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C797" s="6"/>
-      <c r="D797" s="7"/>
-      <c r="E797" s="7"/>
+      <c r="C797" s="5"/>
+      <c r="D797" s="6"/>
+      <c r="E797" s="6"/>
       <c r="I797" s="2"/>
     </row>
     <row r="798" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C798" s="6"/>
-      <c r="D798" s="7"/>
-      <c r="E798" s="7"/>
+      <c r="C798" s="5"/>
+      <c r="D798" s="6"/>
+      <c r="E798" s="6"/>
       <c r="I798" s="2"/>
     </row>
     <row r="799" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C799" s="6"/>
-      <c r="D799" s="7"/>
-      <c r="E799" s="7"/>
+      <c r="C799" s="5"/>
+      <c r="D799" s="6"/>
+      <c r="E799" s="6"/>
       <c r="I799" s="2"/>
     </row>
     <row r="800" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C800" s="6"/>
-      <c r="D800" s="7"/>
-      <c r="E800" s="7"/>
+      <c r="C800" s="5"/>
+      <c r="D800" s="6"/>
+      <c r="E800" s="6"/>
       <c r="I800" s="2"/>
     </row>
     <row r="801" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C801" s="6"/>
-      <c r="D801" s="7"/>
-      <c r="E801" s="7"/>
+      <c r="C801" s="5"/>
+      <c r="D801" s="6"/>
+      <c r="E801" s="6"/>
       <c r="I801" s="2"/>
     </row>
     <row r="802" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C802" s="6"/>
-      <c r="D802" s="7"/>
-      <c r="E802" s="7"/>
+      <c r="C802" s="5"/>
+      <c r="D802" s="6"/>
+      <c r="E802" s="6"/>
       <c r="I802" s="2"/>
     </row>
     <row r="803" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C803" s="6"/>
-      <c r="D803" s="7"/>
-      <c r="E803" s="7"/>
+      <c r="C803" s="5"/>
+      <c r="D803" s="6"/>
+      <c r="E803" s="6"/>
       <c r="I803" s="2"/>
     </row>
     <row r="804" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C804" s="6"/>
-      <c r="D804" s="7"/>
-      <c r="E804" s="7"/>
+      <c r="C804" s="5"/>
+      <c r="D804" s="6"/>
+      <c r="E804" s="6"/>
       <c r="I804" s="2"/>
     </row>
     <row r="805" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C805" s="6"/>
-      <c r="D805" s="7"/>
-      <c r="E805" s="7"/>
+      <c r="C805" s="5"/>
+      <c r="D805" s="6"/>
+      <c r="E805" s="6"/>
       <c r="I805" s="2"/>
     </row>
     <row r="806" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C806" s="6"/>
-      <c r="D806" s="7"/>
-      <c r="E806" s="7"/>
+      <c r="C806" s="5"/>
+      <c r="D806" s="6"/>
+      <c r="E806" s="6"/>
       <c r="I806" s="2"/>
     </row>
     <row r="807" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C807" s="6"/>
-      <c r="D807" s="7"/>
-      <c r="E807" s="7"/>
+      <c r="C807" s="5"/>
+      <c r="D807" s="6"/>
+      <c r="E807" s="6"/>
       <c r="I807" s="2"/>
     </row>
     <row r="808" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C808" s="6"/>
-      <c r="D808" s="7"/>
-      <c r="E808" s="7"/>
+      <c r="C808" s="5"/>
+      <c r="D808" s="6"/>
+      <c r="E808" s="6"/>
       <c r="I808" s="2"/>
     </row>
     <row r="809" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C809" s="6"/>
-      <c r="D809" s="7"/>
-      <c r="E809" s="7"/>
+      <c r="C809" s="5"/>
+      <c r="D809" s="6"/>
+      <c r="E809" s="6"/>
       <c r="I809" s="2"/>
     </row>
     <row r="810" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C810" s="6"/>
-      <c r="D810" s="7"/>
-      <c r="E810" s="7"/>
+      <c r="C810" s="5"/>
+      <c r="D810" s="6"/>
+      <c r="E810" s="6"/>
       <c r="I810" s="2"/>
     </row>
     <row r="811" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C811" s="6"/>
-      <c r="D811" s="7"/>
-      <c r="E811" s="7"/>
+      <c r="C811" s="5"/>
+      <c r="D811" s="6"/>
+      <c r="E811" s="6"/>
       <c r="I811" s="2"/>
     </row>
     <row r="812" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C812" s="6"/>
-      <c r="D812" s="7"/>
-      <c r="E812" s="7"/>
+      <c r="C812" s="5"/>
+      <c r="D812" s="6"/>
+      <c r="E812" s="6"/>
       <c r="I812" s="2"/>
     </row>
     <row r="813" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C813" s="6"/>
-      <c r="D813" s="7"/>
-      <c r="E813" s="7"/>
+      <c r="C813" s="5"/>
+      <c r="D813" s="6"/>
+      <c r="E813" s="6"/>
       <c r="I813" s="2"/>
     </row>
     <row r="814" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C814" s="6"/>
-      <c r="D814" s="7"/>
-      <c r="E814" s="7"/>
+      <c r="C814" s="5"/>
+      <c r="D814" s="6"/>
+      <c r="E814" s="6"/>
       <c r="I814" s="2"/>
     </row>
     <row r="815" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C815" s="6"/>
-      <c r="D815" s="7"/>
-      <c r="E815" s="7"/>
+      <c r="C815" s="5"/>
+      <c r="D815" s="6"/>
+      <c r="E815" s="6"/>
       <c r="I815" s="2"/>
     </row>
     <row r="816" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C816" s="6"/>
-      <c r="D816" s="7"/>
-      <c r="E816" s="7"/>
+      <c r="C816" s="5"/>
+      <c r="D816" s="6"/>
+      <c r="E816" s="6"/>
       <c r="I816" s="2"/>
     </row>
     <row r="817" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C817" s="6"/>
-      <c r="D817" s="7"/>
-      <c r="E817" s="7"/>
+      <c r="C817" s="5"/>
+      <c r="D817" s="6"/>
+      <c r="E817" s="6"/>
       <c r="I817" s="2"/>
     </row>
     <row r="818" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C818" s="6"/>
-      <c r="D818" s="7"/>
-      <c r="E818" s="7"/>
+      <c r="C818" s="5"/>
+      <c r="D818" s="6"/>
+      <c r="E818" s="6"/>
       <c r="I818" s="2"/>
     </row>
     <row r="819" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C819" s="6"/>
-      <c r="D819" s="7"/>
-      <c r="E819" s="7"/>
+      <c r="C819" s="5"/>
+      <c r="D819" s="6"/>
+      <c r="E819" s="6"/>
       <c r="I819" s="2"/>
     </row>
     <row r="820" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C820" s="6"/>
-      <c r="D820" s="7"/>
-      <c r="E820" s="7"/>
+      <c r="C820" s="5"/>
+      <c r="D820" s="6"/>
+      <c r="E820" s="6"/>
       <c r="I820" s="2"/>
     </row>
     <row r="821" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C821" s="6"/>
-      <c r="D821" s="7"/>
-      <c r="E821" s="7"/>
+      <c r="C821" s="5"/>
+      <c r="D821" s="6"/>
+      <c r="E821" s="6"/>
       <c r="I821" s="2"/>
     </row>
     <row r="822" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C822" s="6"/>
-      <c r="D822" s="7"/>
-      <c r="E822" s="7"/>
+      <c r="C822" s="5"/>
+      <c r="D822" s="6"/>
+      <c r="E822" s="6"/>
       <c r="I822" s="2"/>
     </row>
     <row r="823" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C823" s="6"/>
-      <c r="D823" s="7"/>
-      <c r="E823" s="7"/>
+      <c r="C823" s="5"/>
+      <c r="D823" s="6"/>
+      <c r="E823" s="6"/>
       <c r="I823" s="2"/>
     </row>
     <row r="824" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C824" s="6"/>
-      <c r="D824" s="7"/>
-      <c r="E824" s="7"/>
+      <c r="C824" s="5"/>
+      <c r="D824" s="6"/>
+      <c r="E824" s="6"/>
       <c r="I824" s="2"/>
     </row>
     <row r="825" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C825" s="6"/>
-      <c r="D825" s="7"/>
-      <c r="E825" s="7"/>
+      <c r="C825" s="5"/>
+      <c r="D825" s="6"/>
+      <c r="E825" s="6"/>
       <c r="I825" s="2"/>
     </row>
     <row r="826" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C826" s="6"/>
-      <c r="D826" s="7"/>
-      <c r="E826" s="7"/>
+      <c r="C826" s="5"/>
+      <c r="D826" s="6"/>
+      <c r="E826" s="6"/>
       <c r="I826" s="2"/>
     </row>
     <row r="827" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C827" s="6"/>
-      <c r="D827" s="7"/>
-      <c r="E827" s="7"/>
+      <c r="C827" s="5"/>
+      <c r="D827" s="6"/>
+      <c r="E827" s="6"/>
       <c r="I827" s="2"/>
     </row>
     <row r="828" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C828" s="6"/>
-      <c r="D828" s="7"/>
-      <c r="E828" s="7"/>
+      <c r="C828" s="5"/>
+      <c r="D828" s="6"/>
+      <c r="E828" s="6"/>
       <c r="I828" s="2"/>
     </row>
     <row r="829" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C829" s="6"/>
-      <c r="D829" s="7"/>
-      <c r="E829" s="7"/>
+      <c r="C829" s="5"/>
+      <c r="D829" s="6"/>
+      <c r="E829" s="6"/>
       <c r="I829" s="2"/>
     </row>
     <row r="830" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C830" s="6"/>
-      <c r="D830" s="7"/>
-      <c r="E830" s="7"/>
+      <c r="C830" s="5"/>
+      <c r="D830" s="6"/>
+      <c r="E830" s="6"/>
       <c r="I830" s="2"/>
     </row>
     <row r="831" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C831" s="6"/>
-      <c r="D831" s="7"/>
-      <c r="E831" s="7"/>
+      <c r="C831" s="5"/>
+      <c r="D831" s="6"/>
+      <c r="E831" s="6"/>
       <c r="I831" s="2"/>
     </row>
     <row r="832" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C832" s="6"/>
-      <c r="D832" s="7"/>
-      <c r="E832" s="7"/>
+      <c r="C832" s="5"/>
+      <c r="D832" s="6"/>
+      <c r="E832" s="6"/>
       <c r="I832" s="2"/>
     </row>
     <row r="833" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C833" s="6"/>
-      <c r="D833" s="7"/>
-      <c r="E833" s="7"/>
+      <c r="C833" s="5"/>
+      <c r="D833" s="6"/>
+      <c r="E833" s="6"/>
       <c r="I833" s="2"/>
     </row>
     <row r="834" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C834" s="6"/>
-      <c r="D834" s="7"/>
-      <c r="E834" s="7"/>
+      <c r="C834" s="5"/>
+      <c r="D834" s="6"/>
+      <c r="E834" s="6"/>
       <c r="I834" s="2"/>
     </row>
     <row r="835" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C835" s="6"/>
-      <c r="D835" s="7"/>
-      <c r="E835" s="7"/>
+      <c r="C835" s="5"/>
+      <c r="D835" s="6"/>
+      <c r="E835" s="6"/>
       <c r="I835" s="2"/>
     </row>
     <row r="836" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C836" s="6"/>
-      <c r="D836" s="7"/>
-      <c r="E836" s="7"/>
+      <c r="C836" s="5"/>
+      <c r="D836" s="6"/>
+      <c r="E836" s="6"/>
       <c r="I836" s="2"/>
     </row>
     <row r="837" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C837" s="6"/>
-      <c r="D837" s="7"/>
-      <c r="E837" s="7"/>
+      <c r="C837" s="5"/>
+      <c r="D837" s="6"/>
+      <c r="E837" s="6"/>
       <c r="I837" s="2"/>
     </row>
     <row r="838" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C838" s="6"/>
-      <c r="D838" s="7"/>
-      <c r="E838" s="7"/>
+      <c r="C838" s="5"/>
+      <c r="D838" s="6"/>
+      <c r="E838" s="6"/>
       <c r="I838" s="2"/>
     </row>
     <row r="839" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C839" s="6"/>
-      <c r="D839" s="7"/>
-      <c r="E839" s="7"/>
+      <c r="C839" s="5"/>
+      <c r="D839" s="6"/>
+      <c r="E839" s="6"/>
       <c r="I839" s="2"/>
     </row>
     <row r="840" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C840" s="6"/>
-      <c r="D840" s="7"/>
-      <c r="E840" s="7"/>
+      <c r="C840" s="5"/>
+      <c r="D840" s="6"/>
+      <c r="E840" s="6"/>
       <c r="I840" s="2"/>
     </row>
     <row r="841" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C841" s="6"/>
-      <c r="D841" s="7"/>
-      <c r="E841" s="7"/>
+      <c r="C841" s="5"/>
+      <c r="D841" s="6"/>
+      <c r="E841" s="6"/>
       <c r="I841" s="2"/>
     </row>
     <row r="842" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C842" s="6"/>
-      <c r="D842" s="7"/>
-      <c r="E842" s="7"/>
+      <c r="C842" s="5"/>
+      <c r="D842" s="6"/>
+      <c r="E842" s="6"/>
       <c r="I842" s="2"/>
     </row>
     <row r="843" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C843" s="6"/>
-      <c r="D843" s="7"/>
-      <c r="E843" s="7"/>
+      <c r="C843" s="5"/>
+      <c r="D843" s="6"/>
+      <c r="E843" s="6"/>
       <c r="I843" s="2"/>
     </row>
     <row r="844" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C844" s="6"/>
-      <c r="D844" s="7"/>
-      <c r="E844" s="7"/>
+      <c r="C844" s="5"/>
+      <c r="D844" s="6"/>
+      <c r="E844" s="6"/>
       <c r="I844" s="2"/>
     </row>
     <row r="845" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C845" s="6"/>
-      <c r="D845" s="7"/>
-      <c r="E845" s="7"/>
+      <c r="C845" s="5"/>
+      <c r="D845" s="6"/>
+      <c r="E845" s="6"/>
       <c r="I845" s="2"/>
     </row>
     <row r="846" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C846" s="6"/>
-      <c r="D846" s="7"/>
-      <c r="E846" s="7"/>
+      <c r="C846" s="5"/>
+      <c r="D846" s="6"/>
+      <c r="E846" s="6"/>
       <c r="I846" s="2"/>
     </row>
     <row r="847" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C847" s="6"/>
-      <c r="D847" s="7"/>
-      <c r="E847" s="7"/>
+      <c r="C847" s="5"/>
+      <c r="D847" s="6"/>
+      <c r="E847" s="6"/>
       <c r="I847" s="2"/>
     </row>
     <row r="848" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C848" s="6"/>
-      <c r="D848" s="7"/>
-      <c r="E848" s="7"/>
+      <c r="C848" s="5"/>
+      <c r="D848" s="6"/>
+      <c r="E848" s="6"/>
       <c r="I848" s="2"/>
     </row>
     <row r="849" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C849" s="6"/>
-      <c r="D849" s="7"/>
-      <c r="E849" s="7"/>
+      <c r="C849" s="5"/>
+      <c r="D849" s="6"/>
+      <c r="E849" s="6"/>
       <c r="I849" s="2"/>
     </row>
     <row r="850" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C850" s="6"/>
-      <c r="D850" s="7"/>
-      <c r="E850" s="7"/>
+      <c r="C850" s="5"/>
+      <c r="D850" s="6"/>
+      <c r="E850" s="6"/>
       <c r="I850" s="2"/>
     </row>
     <row r="851" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C851" s="6"/>
-      <c r="D851" s="7"/>
-      <c r="E851" s="7"/>
+      <c r="C851" s="5"/>
+      <c r="D851" s="6"/>
+      <c r="E851" s="6"/>
       <c r="I851" s="2"/>
     </row>
     <row r="852" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C852" s="6"/>
-      <c r="D852" s="7"/>
-      <c r="E852" s="7"/>
+      <c r="C852" s="5"/>
+      <c r="D852" s="6"/>
+      <c r="E852" s="6"/>
       <c r="I852" s="2"/>
     </row>
     <row r="853" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C853" s="6"/>
-      <c r="D853" s="7"/>
-      <c r="E853" s="7"/>
+      <c r="C853" s="5"/>
+      <c r="D853" s="6"/>
+      <c r="E853" s="6"/>
       <c r="I853" s="2"/>
     </row>
     <row r="854" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C854" s="6"/>
-      <c r="D854" s="7"/>
-      <c r="E854" s="7"/>
+      <c r="C854" s="5"/>
+      <c r="D854" s="6"/>
+      <c r="E854" s="6"/>
       <c r="I854" s="2"/>
     </row>
     <row r="855" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C855" s="6"/>
-      <c r="D855" s="7"/>
-      <c r="E855" s="7"/>
+      <c r="C855" s="5"/>
+      <c r="D855" s="6"/>
+      <c r="E855" s="6"/>
       <c r="I855" s="2"/>
     </row>
     <row r="856" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C856" s="6"/>
-      <c r="D856" s="7"/>
-      <c r="E856" s="7"/>
+      <c r="C856" s="5"/>
+      <c r="D856" s="6"/>
+      <c r="E856" s="6"/>
       <c r="I856" s="2"/>
     </row>
     <row r="857" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C857" s="6"/>
-      <c r="D857" s="7"/>
-      <c r="E857" s="7"/>
+      <c r="C857" s="5"/>
+      <c r="D857" s="6"/>
+      <c r="E857" s="6"/>
       <c r="I857" s="2"/>
     </row>
     <row r="858" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C858" s="6"/>
-      <c r="D858" s="7"/>
-      <c r="E858" s="7"/>
+      <c r="C858" s="5"/>
+      <c r="D858" s="6"/>
+      <c r="E858" s="6"/>
       <c r="I858" s="2"/>
     </row>
     <row r="859" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C859" s="6"/>
-      <c r="D859" s="7"/>
-      <c r="E859" s="7"/>
+      <c r="C859" s="5"/>
+      <c r="D859" s="6"/>
+      <c r="E859" s="6"/>
       <c r="I859" s="2"/>
     </row>
     <row r="860" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C860" s="6"/>
-      <c r="D860" s="7"/>
-      <c r="E860" s="7"/>
+      <c r="C860" s="5"/>
+      <c r="D860" s="6"/>
+      <c r="E860" s="6"/>
       <c r="I860" s="2"/>
     </row>
     <row r="861" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C861" s="6"/>
-      <c r="D861" s="7"/>
-      <c r="E861" s="7"/>
+      <c r="C861" s="5"/>
+      <c r="D861" s="6"/>
+      <c r="E861" s="6"/>
       <c r="I861" s="2"/>
     </row>
     <row r="862" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C862" s="6"/>
-      <c r="D862" s="7"/>
-      <c r="E862" s="7"/>
+      <c r="C862" s="5"/>
+      <c r="D862" s="6"/>
+      <c r="E862" s="6"/>
       <c r="I862" s="2"/>
     </row>
     <row r="863" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C863" s="6"/>
-      <c r="D863" s="7"/>
-      <c r="E863" s="7"/>
+      <c r="C863" s="5"/>
+      <c r="D863" s="6"/>
+      <c r="E863" s="6"/>
       <c r="I863" s="2"/>
     </row>
     <row r="864" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C864" s="6"/>
-      <c r="D864" s="7"/>
-      <c r="E864" s="7"/>
+      <c r="C864" s="5"/>
+      <c r="D864" s="6"/>
+      <c r="E864" s="6"/>
       <c r="I864" s="2"/>
     </row>
     <row r="865" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C865" s="6"/>
-      <c r="D865" s="7"/>
-      <c r="E865" s="7"/>
+      <c r="C865" s="5"/>
+      <c r="D865" s="6"/>
+      <c r="E865" s="6"/>
       <c r="I865" s="2"/>
     </row>
     <row r="866" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C866" s="6"/>
-      <c r="D866" s="7"/>
-      <c r="E866" s="7"/>
+      <c r="C866" s="5"/>
+      <c r="D866" s="6"/>
+      <c r="E866" s="6"/>
       <c r="I866" s="2"/>
     </row>
     <row r="867" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C867" s="6"/>
-      <c r="D867" s="7"/>
-      <c r="E867" s="7"/>
+      <c r="C867" s="5"/>
+      <c r="D867" s="6"/>
+      <c r="E867" s="6"/>
       <c r="I867" s="2"/>
     </row>
     <row r="868" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C868" s="6"/>
-      <c r="D868" s="7"/>
-      <c r="E868" s="7"/>
+      <c r="C868" s="5"/>
+      <c r="D868" s="6"/>
+      <c r="E868" s="6"/>
       <c r="I868" s="2"/>
     </row>
     <row r="869" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C869" s="6"/>
-      <c r="D869" s="7"/>
-      <c r="E869" s="7"/>
+      <c r="C869" s="5"/>
+      <c r="D869" s="6"/>
+      <c r="E869" s="6"/>
       <c r="I869" s="2"/>
     </row>
     <row r="870" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C870" s="6"/>
-      <c r="D870" s="7"/>
-      <c r="E870" s="7"/>
+      <c r="C870" s="5"/>
+      <c r="D870" s="6"/>
+      <c r="E870" s="6"/>
       <c r="I870" s="2"/>
     </row>
     <row r="871" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C871" s="6"/>
-      <c r="D871" s="7"/>
-      <c r="E871" s="7"/>
+      <c r="C871" s="5"/>
+      <c r="D871" s="6"/>
+      <c r="E871" s="6"/>
       <c r="I871" s="2"/>
     </row>
     <row r="872" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C872" s="6"/>
-      <c r="D872" s="7"/>
-      <c r="E872" s="7"/>
+      <c r="C872" s="5"/>
+      <c r="D872" s="6"/>
+      <c r="E872" s="6"/>
       <c r="I872" s="2"/>
     </row>
     <row r="873" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C873" s="6"/>
-      <c r="D873" s="7"/>
-      <c r="E873" s="7"/>
+      <c r="C873" s="5"/>
+      <c r="D873" s="6"/>
+      <c r="E873" s="6"/>
       <c r="I873" s="2"/>
     </row>
     <row r="874" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C874" s="6"/>
-      <c r="D874" s="7"/>
-      <c r="E874" s="7"/>
+      <c r="C874" s="5"/>
+      <c r="D874" s="6"/>
+      <c r="E874" s="6"/>
       <c r="I874" s="2"/>
     </row>
     <row r="875" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C875" s="6"/>
-      <c r="D875" s="7"/>
-      <c r="E875" s="7"/>
+      <c r="C875" s="5"/>
+      <c r="D875" s="6"/>
+      <c r="E875" s="6"/>
       <c r="I875" s="2"/>
     </row>
     <row r="876" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C876" s="6"/>
-      <c r="D876" s="7"/>
-      <c r="E876" s="7"/>
+      <c r="C876" s="5"/>
+      <c r="D876" s="6"/>
+      <c r="E876" s="6"/>
       <c r="I876" s="2"/>
     </row>
     <row r="877" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C877" s="6"/>
-      <c r="D877" s="7"/>
-      <c r="E877" s="7"/>
+      <c r="C877" s="5"/>
+      <c r="D877" s="6"/>
+      <c r="E877" s="6"/>
       <c r="I877" s="2"/>
     </row>
     <row r="878" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C878" s="6"/>
-      <c r="D878" s="7"/>
-      <c r="E878" s="7"/>
+      <c r="C878" s="5"/>
+      <c r="D878" s="6"/>
+      <c r="E878" s="6"/>
       <c r="I878" s="2"/>
     </row>
     <row r="879" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C879" s="6"/>
-      <c r="D879" s="7"/>
-      <c r="E879" s="7"/>
+      <c r="C879" s="5"/>
+      <c r="D879" s="6"/>
+      <c r="E879" s="6"/>
       <c r="I879" s="2"/>
     </row>
     <row r="880" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C880" s="6"/>
-      <c r="D880" s="7"/>
-      <c r="E880" s="7"/>
+      <c r="C880" s="5"/>
+      <c r="D880" s="6"/>
+      <c r="E880" s="6"/>
       <c r="I880" s="2"/>
     </row>
     <row r="881" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C881" s="6"/>
-      <c r="D881" s="7"/>
-      <c r="E881" s="7"/>
+      <c r="C881" s="5"/>
+      <c r="D881" s="6"/>
+      <c r="E881" s="6"/>
       <c r="I881" s="2"/>
     </row>
     <row r="882" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C882" s="6"/>
-      <c r="D882" s="7"/>
-      <c r="E882" s="7"/>
+      <c r="C882" s="5"/>
+      <c r="D882" s="6"/>
+      <c r="E882" s="6"/>
       <c r="I882" s="2"/>
     </row>
     <row r="883" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C883" s="6"/>
-      <c r="D883" s="7"/>
-      <c r="E883" s="7"/>
+      <c r="C883" s="5"/>
+      <c r="D883" s="6"/>
+      <c r="E883" s="6"/>
       <c r="I883" s="2"/>
     </row>
     <row r="884" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C884" s="6"/>
-      <c r="D884" s="7"/>
-      <c r="E884" s="7"/>
+      <c r="C884" s="5"/>
+      <c r="D884" s="6"/>
+      <c r="E884" s="6"/>
       <c r="I884" s="2"/>
     </row>
     <row r="885" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C885" s="6"/>
-      <c r="D885" s="7"/>
-      <c r="E885" s="7"/>
+      <c r="C885" s="5"/>
+      <c r="D885" s="6"/>
+      <c r="E885" s="6"/>
       <c r="I885" s="2"/>
     </row>
     <row r="886" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C886" s="6"/>
-      <c r="D886" s="7"/>
-      <c r="E886" s="7"/>
+      <c r="C886" s="5"/>
+      <c r="D886" s="6"/>
+      <c r="E886" s="6"/>
       <c r="I886" s="2"/>
     </row>
     <row r="887" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C887" s="6"/>
-      <c r="D887" s="7"/>
-      <c r="E887" s="7"/>
+      <c r="C887" s="5"/>
+      <c r="D887" s="6"/>
+      <c r="E887" s="6"/>
       <c r="I887" s="2"/>
     </row>
     <row r="888" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C888" s="6"/>
-      <c r="D888" s="7"/>
-      <c r="E888" s="7"/>
+      <c r="C888" s="5"/>
+      <c r="D888" s="6"/>
+      <c r="E888" s="6"/>
       <c r="I888" s="2"/>
     </row>
     <row r="889" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C889" s="6"/>
-      <c r="D889" s="7"/>
-      <c r="E889" s="7"/>
+      <c r="C889" s="5"/>
+      <c r="D889" s="6"/>
+      <c r="E889" s="6"/>
       <c r="I889" s="2"/>
     </row>
     <row r="890" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C890" s="6"/>
-      <c r="D890" s="7"/>
-      <c r="E890" s="7"/>
+      <c r="C890" s="5"/>
+      <c r="D890" s="6"/>
+      <c r="E890" s="6"/>
       <c r="I890" s="2"/>
     </row>
     <row r="891" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C891" s="6"/>
-      <c r="D891" s="7"/>
-      <c r="E891" s="7"/>
+      <c r="C891" s="5"/>
+      <c r="D891" s="6"/>
+      <c r="E891" s="6"/>
       <c r="I891" s="2"/>
     </row>
     <row r="892" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C892" s="6"/>
-      <c r="D892" s="7"/>
-      <c r="E892" s="7"/>
+      <c r="C892" s="5"/>
+      <c r="D892" s="6"/>
+      <c r="E892" s="6"/>
       <c r="I892" s="2"/>
     </row>
     <row r="893" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C893" s="6"/>
-      <c r="D893" s="7"/>
-      <c r="E893" s="7"/>
+      <c r="C893" s="5"/>
+      <c r="D893" s="6"/>
+      <c r="E893" s="6"/>
       <c r="I893" s="2"/>
     </row>
     <row r="894" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C894" s="6"/>
-      <c r="D894" s="7"/>
-      <c r="E894" s="7"/>
+      <c r="C894" s="5"/>
+      <c r="D894" s="6"/>
+      <c r="E894" s="6"/>
       <c r="I894" s="2"/>
     </row>
     <row r="895" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C895" s="6"/>
-      <c r="D895" s="7"/>
-      <c r="E895" s="7"/>
+      <c r="C895" s="5"/>
+      <c r="D895" s="6"/>
+      <c r="E895" s="6"/>
       <c r="I895" s="2"/>
     </row>
     <row r="896" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C896" s="6"/>
-      <c r="D896" s="7"/>
-      <c r="E896" s="7"/>
+      <c r="C896" s="5"/>
+      <c r="D896" s="6"/>
+      <c r="E896" s="6"/>
       <c r="I896" s="2"/>
     </row>
     <row r="897" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C897" s="6"/>
-      <c r="D897" s="7"/>
-      <c r="E897" s="7"/>
+      <c r="C897" s="5"/>
+      <c r="D897" s="6"/>
+      <c r="E897" s="6"/>
       <c r="I897" s="2"/>
     </row>
     <row r="898" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C898" s="6"/>
-      <c r="D898" s="7"/>
-      <c r="E898" s="7"/>
+      <c r="C898" s="5"/>
+      <c r="D898" s="6"/>
+      <c r="E898" s="6"/>
       <c r="I898" s="2"/>
     </row>
     <row r="899" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C899" s="6"/>
-      <c r="D899" s="7"/>
-      <c r="E899" s="7"/>
+      <c r="C899" s="5"/>
+      <c r="D899" s="6"/>
+      <c r="E899" s="6"/>
       <c r="I899" s="2"/>
     </row>
     <row r="900" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C900" s="6"/>
-      <c r="D900" s="7"/>
-      <c r="E900" s="7"/>
+      <c r="C900" s="5"/>
+      <c r="D900" s="6"/>
+      <c r="E900" s="6"/>
       <c r="I900" s="2"/>
     </row>
     <row r="901" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C901" s="6"/>
-      <c r="D901" s="7"/>
-      <c r="E901" s="7"/>
+      <c r="C901" s="5"/>
+      <c r="D901" s="6"/>
+      <c r="E901" s="6"/>
       <c r="I901" s="2"/>
     </row>
     <row r="902" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C902" s="6"/>
-      <c r="D902" s="7"/>
-      <c r="E902" s="7"/>
+      <c r="C902" s="5"/>
+      <c r="D902" s="6"/>
+      <c r="E902" s="6"/>
       <c r="I902" s="2"/>
     </row>
     <row r="903" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C903" s="6"/>
-      <c r="D903" s="7"/>
-      <c r="E903" s="7"/>
+      <c r="C903" s="5"/>
+      <c r="D903" s="6"/>
+      <c r="E903" s="6"/>
       <c r="I903" s="2"/>
     </row>
     <row r="904" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C904" s="6"/>
-      <c r="D904" s="7"/>
-      <c r="E904" s="7"/>
+      <c r="C904" s="5"/>
+      <c r="D904" s="6"/>
+      <c r="E904" s="6"/>
       <c r="I904" s="2"/>
     </row>
     <row r="905" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C905" s="6"/>
-      <c r="D905" s="7"/>
-      <c r="E905" s="7"/>
+      <c r="C905" s="5"/>
+      <c r="D905" s="6"/>
+      <c r="E905" s="6"/>
       <c r="I905" s="2"/>
     </row>
     <row r="906" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C906" s="6"/>
-      <c r="D906" s="7"/>
-      <c r="E906" s="7"/>
+      <c r="C906" s="5"/>
+      <c r="D906" s="6"/>
+      <c r="E906" s="6"/>
       <c r="I906" s="2"/>
     </row>
     <row r="907" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C907" s="6"/>
-      <c r="D907" s="7"/>
-      <c r="E907" s="7"/>
+      <c r="C907" s="5"/>
+      <c r="D907" s="6"/>
+      <c r="E907" s="6"/>
       <c r="I907" s="2"/>
     </row>
     <row r="908" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C908" s="6"/>
-      <c r="D908" s="7"/>
-      <c r="E908" s="7"/>
+      <c r="C908" s="5"/>
+      <c r="D908" s="6"/>
+      <c r="E908" s="6"/>
       <c r="I908" s="2"/>
     </row>
     <row r="909" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C909" s="6"/>
-      <c r="D909" s="7"/>
-      <c r="E909" s="7"/>
+      <c r="C909" s="5"/>
+      <c r="D909" s="6"/>
+      <c r="E909" s="6"/>
       <c r="I909" s="2"/>
     </row>
     <row r="910" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C910" s="6"/>
-      <c r="D910" s="7"/>
-      <c r="E910" s="7"/>
+      <c r="C910" s="5"/>
+      <c r="D910" s="6"/>
+      <c r="E910" s="6"/>
       <c r="I910" s="2"/>
     </row>
     <row r="911" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C911" s="6"/>
-      <c r="D911" s="7"/>
-      <c r="E911" s="7"/>
+      <c r="C911" s="5"/>
+      <c r="D911" s="6"/>
+      <c r="E911" s="6"/>
       <c r="I911" s="2"/>
     </row>
     <row r="912" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C912" s="6"/>
-      <c r="D912" s="7"/>
-      <c r="E912" s="7"/>
+      <c r="C912" s="5"/>
+      <c r="D912" s="6"/>
+      <c r="E912" s="6"/>
       <c r="I912" s="2"/>
     </row>
     <row r="913" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C913" s="6"/>
-      <c r="D913" s="7"/>
-      <c r="E913" s="7"/>
+      <c r="C913" s="5"/>
+      <c r="D913" s="6"/>
+      <c r="E913" s="6"/>
       <c r="I913" s="2"/>
     </row>
     <row r="914" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C914" s="6"/>
-      <c r="D914" s="7"/>
-      <c r="E914" s="7"/>
+      <c r="C914" s="5"/>
+      <c r="D914" s="6"/>
+      <c r="E914" s="6"/>
       <c r="I914" s="2"/>
     </row>
     <row r="915" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C915" s="6"/>
-      <c r="D915" s="7"/>
-      <c r="E915" s="7"/>
+      <c r="C915" s="5"/>
+      <c r="D915" s="6"/>
+      <c r="E915" s="6"/>
       <c r="I915" s="2"/>
     </row>
     <row r="916" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C916" s="6"/>
-      <c r="D916" s="7"/>
-      <c r="E916" s="7"/>
+      <c r="C916" s="5"/>
+      <c r="D916" s="6"/>
+      <c r="E916" s="6"/>
       <c r="I916" s="2"/>
     </row>
     <row r="917" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C917" s="6"/>
-      <c r="D917" s="7"/>
-      <c r="E917" s="7"/>
+      <c r="C917" s="5"/>
+      <c r="D917" s="6"/>
+      <c r="E917" s="6"/>
       <c r="I917" s="2"/>
     </row>
     <row r="918" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C918" s="6"/>
-      <c r="D918" s="7"/>
-      <c r="E918" s="7"/>
+      <c r="C918" s="5"/>
+      <c r="D918" s="6"/>
+      <c r="E918" s="6"/>
       <c r="I918" s="2"/>
     </row>
     <row r="919" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C919" s="6"/>
-      <c r="D919" s="7"/>
-      <c r="E919" s="7"/>
+      <c r="C919" s="5"/>
+      <c r="D919" s="6"/>
+      <c r="E919" s="6"/>
       <c r="I919" s="2"/>
     </row>
     <row r="920" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C920" s="6"/>
-      <c r="D920" s="7"/>
-      <c r="E920" s="7"/>
+      <c r="C920" s="5"/>
+      <c r="D920" s="6"/>
+      <c r="E920" s="6"/>
       <c r="I920" s="2"/>
     </row>
     <row r="921" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C921" s="6"/>
-      <c r="D921" s="7"/>
-      <c r="E921" s="7"/>
+      <c r="C921" s="5"/>
+      <c r="D921" s="6"/>
+      <c r="E921" s="6"/>
       <c r="I921" s="2"/>
     </row>
     <row r="922" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C922" s="6"/>
-      <c r="D922" s="7"/>
-      <c r="E922" s="7"/>
+      <c r="C922" s="5"/>
+      <c r="D922" s="6"/>
+      <c r="E922" s="6"/>
       <c r="I922" s="2"/>
     </row>
     <row r="923" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C923" s="6"/>
-      <c r="D923" s="7"/>
-      <c r="E923" s="7"/>
+      <c r="C923" s="5"/>
+      <c r="D923" s="6"/>
+      <c r="E923" s="6"/>
       <c r="I923" s="2"/>
     </row>
     <row r="924" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C924" s="6"/>
-      <c r="D924" s="7"/>
-      <c r="E924" s="7"/>
+      <c r="C924" s="5"/>
+      <c r="D924" s="6"/>
+      <c r="E924" s="6"/>
       <c r="I924" s="2"/>
     </row>
     <row r="925" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C925" s="6"/>
-      <c r="D925" s="7"/>
-      <c r="E925" s="7"/>
+      <c r="C925" s="5"/>
+      <c r="D925" s="6"/>
+      <c r="E925" s="6"/>
       <c r="I925" s="2"/>
     </row>
     <row r="926" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C926" s="6"/>
-      <c r="D926" s="7"/>
-      <c r="E926" s="7"/>
+      <c r="C926" s="5"/>
+      <c r="D926" s="6"/>
+      <c r="E926" s="6"/>
       <c r="I926" s="2"/>
     </row>
     <row r="927" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C927" s="6"/>
-      <c r="D927" s="7"/>
-      <c r="E927" s="7"/>
+      <c r="C927" s="5"/>
+      <c r="D927" s="6"/>
+      <c r="E927" s="6"/>
       <c r="I927" s="2"/>
     </row>
     <row r="928" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C928" s="6"/>
-      <c r="D928" s="7"/>
-      <c r="E928" s="7"/>
+      <c r="C928" s="5"/>
+      <c r="D928" s="6"/>
+      <c r="E928" s="6"/>
       <c r="I928" s="2"/>
     </row>
     <row r="929" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C929" s="6"/>
-      <c r="D929" s="7"/>
-      <c r="E929" s="7"/>
+      <c r="C929" s="5"/>
+      <c r="D929" s="6"/>
+      <c r="E929" s="6"/>
       <c r="I929" s="2"/>
     </row>
     <row r="930" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C930" s="6"/>
-      <c r="D930" s="7"/>
-      <c r="E930" s="7"/>
+      <c r="C930" s="5"/>
+      <c r="D930" s="6"/>
+      <c r="E930" s="6"/>
       <c r="I930" s="2"/>
     </row>
     <row r="931" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C931" s="6"/>
-      <c r="D931" s="7"/>
-      <c r="E931" s="7"/>
+      <c r="C931" s="5"/>
+      <c r="D931" s="6"/>
+      <c r="E931" s="6"/>
       <c r="I931" s="2"/>
     </row>
     <row r="932" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C932" s="6"/>
-      <c r="D932" s="7"/>
-      <c r="E932" s="7"/>
+      <c r="C932" s="5"/>
+      <c r="D932" s="6"/>
+      <c r="E932" s="6"/>
       <c r="I932" s="2"/>
     </row>
     <row r="933" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C933" s="6"/>
-      <c r="D933" s="7"/>
-      <c r="E933" s="7"/>
+      <c r="C933" s="5"/>
+      <c r="D933" s="6"/>
+      <c r="E933" s="6"/>
       <c r="I933" s="2"/>
     </row>
     <row r="934" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C934" s="6"/>
-      <c r="D934" s="7"/>
-      <c r="E934" s="7"/>
+      <c r="C934" s="5"/>
+      <c r="D934" s="6"/>
+      <c r="E934" s="6"/>
       <c r="I934" s="2"/>
     </row>
     <row r="935" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C935" s="6"/>
-      <c r="D935" s="7"/>
-      <c r="E935" s="7"/>
+      <c r="C935" s="5"/>
+      <c r="D935" s="6"/>
+      <c r="E935" s="6"/>
       <c r="I935" s="2"/>
     </row>
     <row r="936" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C936" s="6"/>
-      <c r="D936" s="7"/>
-      <c r="E936" s="7"/>
+      <c r="C936" s="5"/>
+      <c r="D936" s="6"/>
+      <c r="E936" s="6"/>
       <c r="I936" s="2"/>
     </row>
     <row r="937" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C937" s="6"/>
-      <c r="D937" s="7"/>
-      <c r="E937" s="7"/>
+      <c r="C937" s="5"/>
+      <c r="D937" s="6"/>
+      <c r="E937" s="6"/>
       <c r="I937" s="2"/>
     </row>
     <row r="938" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C938" s="6"/>
-      <c r="D938" s="7"/>
-      <c r="E938" s="7"/>
+      <c r="C938" s="5"/>
+      <c r="D938" s="6"/>
+      <c r="E938" s="6"/>
       <c r="I938" s="2"/>
     </row>
     <row r="939" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C939" s="6"/>
-      <c r="D939" s="7"/>
-      <c r="E939" s="7"/>
+      <c r="C939" s="5"/>
+      <c r="D939" s="6"/>
+      <c r="E939" s="6"/>
       <c r="I939" s="2"/>
     </row>
     <row r="940" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C940" s="6"/>
-      <c r="D940" s="7"/>
-      <c r="E940" s="7"/>
+      <c r="C940" s="5"/>
+      <c r="D940" s="6"/>
+      <c r="E940" s="6"/>
       <c r="I940" s="2"/>
     </row>
     <row r="941" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C941" s="6"/>
-      <c r="D941" s="7"/>
-      <c r="E941" s="7"/>
+      <c r="C941" s="5"/>
+      <c r="D941" s="6"/>
+      <c r="E941" s="6"/>
       <c r="I941" s="2"/>
     </row>
     <row r="942" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C942" s="6"/>
-      <c r="D942" s="7"/>
-      <c r="E942" s="7"/>
+      <c r="C942" s="5"/>
+      <c r="D942" s="6"/>
+      <c r="E942" s="6"/>
       <c r="I942" s="2"/>
     </row>
     <row r="943" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C943" s="6"/>
-      <c r="D943" s="7"/>
-      <c r="E943" s="7"/>
+      <c r="C943" s="5"/>
+      <c r="D943" s="6"/>
+      <c r="E943" s="6"/>
       <c r="I943" s="2"/>
     </row>
     <row r="944" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C944" s="6"/>
-      <c r="D944" s="7"/>
-      <c r="E944" s="7"/>
+      <c r="C944" s="5"/>
+      <c r="D944" s="6"/>
+      <c r="E944" s="6"/>
       <c r="I944" s="2"/>
     </row>
     <row r="945" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C945" s="6"/>
-      <c r="D945" s="7"/>
-      <c r="E945" s="7"/>
+      <c r="C945" s="5"/>
+      <c r="D945" s="6"/>
+      <c r="E945" s="6"/>
       <c r="I945" s="2"/>
     </row>
     <row r="946" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C946" s="6"/>
-      <c r="D946" s="7"/>
-      <c r="E946" s="7"/>
+      <c r="C946" s="5"/>
+      <c r="D946" s="6"/>
+      <c r="E946" s="6"/>
       <c r="I946" s="2"/>
     </row>
     <row r="947" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C947" s="6"/>
-      <c r="D947" s="7"/>
-      <c r="E947" s="7"/>
+      <c r="C947" s="5"/>
+      <c r="D947" s="6"/>
+      <c r="E947" s="6"/>
       <c r="I947" s="2"/>
     </row>
     <row r="948" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C948" s="6"/>
-      <c r="D948" s="7"/>
-      <c r="E948" s="7"/>
+      <c r="C948" s="5"/>
+      <c r="D948" s="6"/>
+      <c r="E948" s="6"/>
       <c r="I948" s="2"/>
     </row>
     <row r="949" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C949" s="6"/>
-      <c r="D949" s="7"/>
-      <c r="E949" s="7"/>
+      <c r="C949" s="5"/>
+      <c r="D949" s="6"/>
+      <c r="E949" s="6"/>
       <c r="I949" s="2"/>
     </row>
     <row r="950" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C950" s="6"/>
-      <c r="D950" s="7"/>
-      <c r="E950" s="7"/>
+      <c r="C950" s="5"/>
+      <c r="D950" s="6"/>
+      <c r="E950" s="6"/>
       <c r="I950" s="2"/>
     </row>
     <row r="951" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C951" s="6"/>
-      <c r="D951" s="7"/>
-      <c r="E951" s="7"/>
+      <c r="C951" s="5"/>
+      <c r="D951" s="6"/>
+      <c r="E951" s="6"/>
       <c r="I951" s="2"/>
     </row>
     <row r="952" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C952" s="6"/>
-      <c r="D952" s="7"/>
-      <c r="E952" s="7"/>
+      <c r="C952" s="5"/>
+      <c r="D952" s="6"/>
+      <c r="E952" s="6"/>
       <c r="I952" s="2"/>
     </row>
     <row r="953" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C953" s="6"/>
-      <c r="D953" s="7"/>
-      <c r="E953" s="7"/>
+      <c r="C953" s="5"/>
+      <c r="D953" s="6"/>
+      <c r="E953" s="6"/>
       <c r="I953" s="2"/>
     </row>
     <row r="954" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C954" s="6"/>
-      <c r="D954" s="7"/>
-      <c r="E954" s="7"/>
+      <c r="C954" s="5"/>
+      <c r="D954" s="6"/>
+      <c r="E954" s="6"/>
       <c r="I954" s="2"/>
     </row>
     <row r="955" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C955" s="6"/>
-      <c r="D955" s="7"/>
-      <c r="E955" s="7"/>
+      <c r="C955" s="5"/>
+      <c r="D955" s="6"/>
+      <c r="E955" s="6"/>
       <c r="I955" s="2"/>
     </row>
     <row r="956" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C956" s="6"/>
-      <c r="D956" s="7"/>
-      <c r="E956" s="7"/>
+      <c r="C956" s="5"/>
+      <c r="D956" s="6"/>
+      <c r="E956" s="6"/>
       <c r="I956" s="2"/>
     </row>
     <row r="957" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C957" s="6"/>
-      <c r="D957" s="7"/>
-      <c r="E957" s="7"/>
+      <c r="C957" s="5"/>
+      <c r="D957" s="6"/>
+      <c r="E957" s="6"/>
       <c r="I957" s="2"/>
     </row>
     <row r="958" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C958" s="6"/>
-      <c r="D958" s="7"/>
-      <c r="E958" s="7"/>
+      <c r="C958" s="5"/>
+      <c r="D958" s="6"/>
+      <c r="E958" s="6"/>
       <c r="I958" s="2"/>
     </row>
     <row r="959" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C959" s="6"/>
-      <c r="D959" s="7"/>
-      <c r="E959" s="7"/>
+      <c r="C959" s="5"/>
+      <c r="D959" s="6"/>
+      <c r="E959" s="6"/>
       <c r="I959" s="2"/>
     </row>
     <row r="960" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C960" s="6"/>
-      <c r="D960" s="7"/>
-      <c r="E960" s="7"/>
+      <c r="C960" s="5"/>
+      <c r="D960" s="6"/>
+      <c r="E960" s="6"/>
       <c r="I960" s="2"/>
     </row>
     <row r="961" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C961" s="6"/>
-      <c r="D961" s="7"/>
-      <c r="E961" s="7"/>
+      <c r="C961" s="5"/>
+      <c r="D961" s="6"/>
+      <c r="E961" s="6"/>
       <c r="I961" s="2"/>
     </row>
     <row r="962" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C962" s="6"/>
-      <c r="D962" s="7"/>
-      <c r="E962" s="7"/>
+      <c r="C962" s="5"/>
+      <c r="D962" s="6"/>
+      <c r="E962" s="6"/>
       <c r="I962" s="2"/>
     </row>
     <row r="963" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C963" s="6"/>
-      <c r="D963" s="7"/>
-      <c r="E963" s="7"/>
+      <c r="C963" s="5"/>
+      <c r="D963" s="6"/>
+      <c r="E963" s="6"/>
       <c r="I963" s="2"/>
     </row>
     <row r="964" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C964" s="6"/>
-      <c r="D964" s="7"/>
-      <c r="E964" s="7"/>
+      <c r="C964" s="5"/>
+      <c r="D964" s="6"/>
+      <c r="E964" s="6"/>
       <c r="I964" s="2"/>
     </row>
     <row r="965" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C965" s="6"/>
-      <c r="D965" s="7"/>
-      <c r="E965" s="7"/>
+      <c r="C965" s="5"/>
+      <c r="D965" s="6"/>
+      <c r="E965" s="6"/>
       <c r="I965" s="2"/>
     </row>
     <row r="966" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C966" s="6"/>
-      <c r="D966" s="7"/>
-      <c r="E966" s="7"/>
+      <c r="C966" s="5"/>
+      <c r="D966" s="6"/>
+      <c r="E966" s="6"/>
       <c r="I966" s="2"/>
     </row>
     <row r="967" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C967" s="6"/>
-      <c r="D967" s="7"/>
-      <c r="E967" s="7"/>
+      <c r="C967" s="5"/>
+      <c r="D967" s="6"/>
+      <c r="E967" s="6"/>
       <c r="I967" s="2"/>
     </row>
     <row r="968" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C968" s="6"/>
-      <c r="D968" s="7"/>
-      <c r="E968" s="7"/>
+      <c r="C968" s="5"/>
+      <c r="D968" s="6"/>
+      <c r="E968" s="6"/>
       <c r="I968" s="2"/>
     </row>
     <row r="969" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C969" s="6"/>
-      <c r="D969" s="7"/>
-      <c r="E969" s="7"/>
+      <c r="C969" s="5"/>
+      <c r="D969" s="6"/>
+      <c r="E969" s="6"/>
       <c r="I969" s="2"/>
     </row>
     <row r="970" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C970" s="6"/>
-      <c r="D970" s="7"/>
-      <c r="E970" s="7"/>
+      <c r="C970" s="5"/>
+      <c r="D970" s="6"/>
+      <c r="E970" s="6"/>
       <c r="I970" s="2"/>
     </row>
     <row r="971" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C971" s="6"/>
-      <c r="D971" s="7"/>
-      <c r="E971" s="7"/>
+      <c r="C971" s="5"/>
+      <c r="D971" s="6"/>
+      <c r="E971" s="6"/>
       <c r="I971" s="2"/>
     </row>
     <row r="972" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C972" s="6"/>
-      <c r="D972" s="7"/>
-      <c r="E972" s="7"/>
+      <c r="C972" s="5"/>
+      <c r="D972" s="6"/>
+      <c r="E972" s="6"/>
       <c r="I972" s="2"/>
     </row>
     <row r="973" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C973" s="6"/>
-      <c r="D973" s="7"/>
-      <c r="E973" s="7"/>
+      <c r="C973" s="5"/>
+      <c r="D973" s="6"/>
+      <c r="E973" s="6"/>
       <c r="I973" s="2"/>
     </row>
     <row r="974" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C974" s="6"/>
-      <c r="D974" s="7"/>
-      <c r="E974" s="7"/>
+      <c r="C974" s="5"/>
+      <c r="D974" s="6"/>
+      <c r="E974" s="6"/>
       <c r="I974" s="2"/>
     </row>
     <row r="975" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C975" s="6"/>
-      <c r="D975" s="7"/>
-      <c r="E975" s="7"/>
+      <c r="C975" s="5"/>
+      <c r="D975" s="6"/>
+      <c r="E975" s="6"/>
       <c r="I975" s="2"/>
     </row>
     <row r="976" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C976" s="6"/>
-      <c r="D976" s="7"/>
-      <c r="E976" s="7"/>
+      <c r="C976" s="5"/>
+      <c r="D976" s="6"/>
+      <c r="E976" s="6"/>
       <c r="I976" s="2"/>
     </row>
     <row r="977" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C977" s="6"/>
-      <c r="D977" s="7"/>
-      <c r="E977" s="7"/>
+      <c r="C977" s="5"/>
+      <c r="D977" s="6"/>
+      <c r="E977" s="6"/>
       <c r="I977" s="2"/>
     </row>
     <row r="978" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C978" s="6"/>
-      <c r="D978" s="7"/>
-      <c r="E978" s="7"/>
+      <c r="C978" s="5"/>
+      <c r="D978" s="6"/>
+      <c r="E978" s="6"/>
       <c r="I978" s="2"/>
     </row>
     <row r="979" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C979" s="6"/>
-      <c r="D979" s="7"/>
-      <c r="E979" s="7"/>
+      <c r="C979" s="5"/>
+      <c r="D979" s="6"/>
+      <c r="E979" s="6"/>
       <c r="I979" s="2"/>
     </row>
     <row r="980" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C980" s="6"/>
-      <c r="D980" s="7"/>
-      <c r="E980" s="7"/>
+      <c r="C980" s="5"/>
+      <c r="D980" s="6"/>
+      <c r="E980" s="6"/>
       <c r="I980" s="2"/>
     </row>
     <row r="981" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C981" s="6"/>
-      <c r="D981" s="7"/>
-      <c r="E981" s="7"/>
+      <c r="C981" s="5"/>
+      <c r="D981" s="6"/>
+      <c r="E981" s="6"/>
       <c r="I981" s="2"/>
     </row>
     <row r="982" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C982" s="6"/>
-      <c r="D982" s="7"/>
-      <c r="E982" s="7"/>
+      <c r="C982" s="5"/>
+      <c r="D982" s="6"/>
+      <c r="E982" s="6"/>
       <c r="I982" s="2"/>
     </row>
     <row r="983" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C983" s="6"/>
-      <c r="D983" s="7"/>
-      <c r="E983" s="7"/>
+      <c r="C983" s="5"/>
+      <c r="D983" s="6"/>
+      <c r="E983" s="6"/>
       <c r="I983" s="2"/>
     </row>
     <row r="984" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C984" s="6"/>
-      <c r="D984" s="7"/>
-      <c r="E984" s="7"/>
+      <c r="C984" s="5"/>
+      <c r="D984" s="6"/>
+      <c r="E984" s="6"/>
       <c r="I984" s="2"/>
     </row>
     <row r="985" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C985" s="6"/>
-      <c r="D985" s="7"/>
-      <c r="E985" s="7"/>
+      <c r="C985" s="5"/>
+      <c r="D985" s="6"/>
+      <c r="E985" s="6"/>
       <c r="I985" s="2"/>
     </row>
     <row r="986" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C986" s="6"/>
-      <c r="D986" s="7"/>
-      <c r="E986" s="7"/>
+      <c r="C986" s="5"/>
+      <c r="D986" s="6"/>
+      <c r="E986" s="6"/>
       <c r="I986" s="2"/>
     </row>
     <row r="987" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C987" s="6"/>
-      <c r="D987" s="7"/>
-      <c r="E987" s="7"/>
+      <c r="C987" s="5"/>
+      <c r="D987" s="6"/>
+      <c r="E987" s="6"/>
       <c r="I987" s="2"/>
     </row>
     <row r="988" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C988" s="6"/>
-      <c r="D988" s="7"/>
-      <c r="E988" s="7"/>
+      <c r="C988" s="5"/>
+      <c r="D988" s="6"/>
+      <c r="E988" s="6"/>
       <c r="I988" s="2"/>
     </row>
     <row r="989" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C989" s="6"/>
-      <c r="D989" s="7"/>
-      <c r="E989" s="7"/>
+      <c r="C989" s="5"/>
+      <c r="D989" s="6"/>
+      <c r="E989" s="6"/>
       <c r="I989" s="2"/>
     </row>
     <row r="990" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C990" s="6"/>
-      <c r="D990" s="7"/>
-      <c r="E990" s="7"/>
+      <c r="C990" s="5"/>
+      <c r="D990" s="6"/>
+      <c r="E990" s="6"/>
       <c r="I990" s="2"/>
     </row>
     <row r="991" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C991" s="6"/>
-      <c r="D991" s="7"/>
-      <c r="E991" s="7"/>
+      <c r="C991" s="5"/>
+      <c r="D991" s="6"/>
+      <c r="E991" s="6"/>
       <c r="I991" s="2"/>
     </row>
     <row r="992" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C992" s="6"/>
-      <c r="D992" s="7"/>
-      <c r="E992" s="7"/>
+      <c r="C992" s="5"/>
+      <c r="D992" s="6"/>
+      <c r="E992" s="6"/>
       <c r="I992" s="2"/>
     </row>
     <row r="993" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C993" s="6"/>
-      <c r="D993" s="7"/>
-      <c r="E993" s="7"/>
+      <c r="C993" s="5"/>
+      <c r="D993" s="6"/>
+      <c r="E993" s="6"/>
       <c r="I993" s="2"/>
     </row>
     <row r="994" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C994" s="6"/>
-      <c r="D994" s="7"/>
-      <c r="E994" s="7"/>
+      <c r="C994" s="5"/>
+      <c r="D994" s="6"/>
+      <c r="E994" s="6"/>
       <c r="I994" s="2"/>
     </row>
     <row r="995" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C995" s="6"/>
-      <c r="D995" s="7"/>
-      <c r="E995" s="7"/>
+      <c r="C995" s="5"/>
+      <c r="D995" s="6"/>
+      <c r="E995" s="6"/>
       <c r="I995" s="2"/>
     </row>
     <row r="996" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C996" s="6"/>
-      <c r="D996" s="7"/>
-      <c r="E996" s="7"/>
+      <c r="C996" s="5"/>
+      <c r="D996" s="6"/>
+      <c r="E996" s="6"/>
       <c r="I996" s="2"/>
     </row>
     <row r="997" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C997" s="6"/>
-      <c r="D997" s="7"/>
-      <c r="E997" s="7"/>
+      <c r="C997" s="5"/>
+      <c r="D997" s="6"/>
+      <c r="E997" s="6"/>
       <c r="I997" s="2"/>
     </row>
     <row r="998" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C998" s="6"/>
-      <c r="D998" s="7"/>
-      <c r="E998" s="7"/>
+      <c r="C998" s="5"/>
+      <c r="D998" s="6"/>
+      <c r="E998" s="6"/>
       <c r="I998" s="2"/>
     </row>
     <row r="999" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C999" s="6"/>
-      <c r="D999" s="7"/>
-      <c r="E999" s="7"/>
+      <c r="C999" s="5"/>
+      <c r="D999" s="6"/>
+      <c r="E999" s="6"/>
       <c r="I999" s="2"/>
     </row>
     <row r="1000" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C1000" s="6"/>
-      <c r="D1000" s="7"/>
-      <c r="E1000" s="7"/>
+      <c r="C1000" s="5"/>
+      <c r="D1000" s="6"/>
+      <c r="E1000" s="6"/>
       <c r="I1000" s="2"/>
     </row>
     <row r="1001" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C1001" s="6"/>
-      <c r="D1001" s="7"/>
-      <c r="E1001" s="7"/>
+      <c r="C1001" s="5"/>
+      <c r="D1001" s="6"/>
+      <c r="E1001" s="6"/>
     </row>
     <row r="1002" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C1002" s="6"/>
-      <c r="D1002" s="7"/>
-      <c r="E1002" s="7"/>
+      <c r="C1002" s="5"/>
+      <c r="D1002" s="6"/>
+      <c r="E1002" s="6"/>
     </row>
     <row r="1003" spans="3:9" x14ac:dyDescent="0.3">
-      <c r="C1003" s="6"/>
-      <c r="D1003" s="7"/>
-      <c r="E1003" s="7"/>
+      <c r="C1003" s="5"/>
+      <c r="D1003" s="6"/>
+      <c r="E1003" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:I1000" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -6801,47 +6815,47 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-    </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -6886,9 +6900,6 @@
       <c r="D13" t="s">
         <v>13</v>
       </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
       <c r="F13">
         <v>0</v>
       </c>
@@ -6896,10 +6907,10 @@
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -6909,69 +6920,67 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
